--- a/Analyses Excel/Préparation_Stage_Academique_2026_(exercices_pratique).xlsx
+++ b/Analyses Excel/Préparation_Stage_Academique_2026_(exercices_pratique).xlsx
@@ -2,15 +2,15 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27932"/>
-  <workbookPr hidePivotFieldList="1" defaultThemeVersion="202300"/>
+  <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\JevainBkg\Projets\Datascience-roadmap\Analyses Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{E567BEA4-DD89-402B-9A4C-2579A89A3DB3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8E2A80A8-4FBA-40E7-80A4-40CE42A1091B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13740" firstSheet="1" activeTab="1" xr2:uid="{7D3A7277-DCDC-4547-AB5A-331124B03413}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13740" xr2:uid="{7D3A7277-DCDC-4547-AB5A-331124B03413}"/>
   </bookViews>
   <sheets>
     <sheet name="Dataset_day1" sheetId="1" r:id="rId1"/>
@@ -74,7 +74,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="692" uniqueCount="178">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="684" uniqueCount="190">
   <si>
     <t>transaction_id</t>
   </si>
@@ -220,9 +220,6 @@
     <t>Best canal</t>
   </si>
   <si>
-    <t>Nombre de transaction</t>
-  </si>
-  <si>
     <t>T011</t>
   </si>
   <si>
@@ -608,16 +605,84 @@
   </si>
   <si>
     <t>Periodes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Debut de l'analyse </t>
+  </si>
+  <si>
+    <t>Question 1 : Quel est le chiffre d’affaires total ?</t>
+  </si>
+  <si>
+    <t>Question 2 : Quelle commune vend le plus ?</t>
+  </si>
+  <si>
+    <t>Question 3  : Quel produit rapporte le plus ?</t>
+  </si>
+  <si>
+    <t>Question 4  : Quel canal semble le plus utilisé ?</t>
+  </si>
+  <si>
+    <t>N°</t>
+  </si>
+  <si>
+    <t>Je recommande :</t>
+  </si>
+  <si>
+    <t>1. Le lancement d’actions promotionnelles ciblées dans ces zones</t>
+  </si>
+  <si>
+    <t>2. Une analyse terrain sur la disponibilité des agents et points de vente</t>
+  </si>
+  <si>
+    <t>3. Une enquête client pour identifier d’éventuels freins (prix, couverture réseau, concurrence)</t>
+  </si>
+  <si>
+    <t>4. Un renforcement de la visibilité locale via SMS promotionnels ou activations terrain</t>
+  </si>
+  <si>
+    <t>Remarques et avis personnels :</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Après analyse, j’observe que les communes de </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos Display"/>
+        <family val="2"/>
+      </rPr>
+      <t>Limete (9 000 FC), Masina (10 000 FC) et Matete (11 000 FC)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos Display"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> présentent une performance inférieure à celle de la Gombe.</t>
+    </r>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="0"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -630,13 +695,54 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Aptos Display"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Aptos Display"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="10">
+  <fills count="13">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor theme="4"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.79998168889431442"/>
+        <bgColor theme="4" tint="0.79998168889431442"/>
+      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -686,13 +792,32 @@
         <bgColor theme="4" tint="0.79998168889431442"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4DD36D"/>
+        <bgColor theme="9" tint="0.39997558519241921"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </top>
+      <bottom style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -708,15 +833,18 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="34">
+  <cellXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -737,13 +865,22 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -756,19 +893,19 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" pivotButton="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
@@ -777,206 +914,42 @@
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="11" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="0" xfId="0" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="223">
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="9" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="9" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <alignment wrapText="1"/>
-    </dxf>
-    <dxf>
-      <alignment wrapText="1"/>
-    </dxf>
-    <dxf>
-      <alignment wrapText="1"/>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="9" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="9" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="9" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="9" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <alignment wrapText="1"/>
-    </dxf>
-    <dxf>
-      <alignment wrapText="1"/>
-    </dxf>
-    <dxf>
-      <alignment wrapText="1"/>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="9" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <alignment wrapText="1"/>
-    </dxf>
-    <dxf>
-      <alignment wrapText="1"/>
-    </dxf>
-    <dxf>
-      <alignment wrapText="1"/>
-    </dxf>
-    <dxf>
-      <alignment wrapText="1"/>
-    </dxf>
-    <dxf>
-      <alignment wrapText="1"/>
-    </dxf>
-    <dxf>
-      <alignment wrapText="1"/>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <alignment wrapText="1"/>
-    </dxf>
-    <dxf>
-      <alignment wrapText="1"/>
-    </dxf>
-    <dxf>
-      <alignment wrapText="1"/>
-    </dxf>
-    <dxf>
-      <alignment wrapText="1"/>
-    </dxf>
-    <dxf>
-      <alignment wrapText="1"/>
-    </dxf>
-    <dxf>
-      <alignment wrapText="1"/>
-    </dxf>
-    <dxf>
-      <alignment wrapText="1"/>
-    </dxf>
-    <dxf>
-      <alignment wrapText="1"/>
-    </dxf>
-    <dxf>
-      <alignment wrapText="1"/>
-    </dxf>
-    <dxf>
-      <alignment wrapText="1"/>
-    </dxf>
-    <dxf>
-      <alignment wrapText="1"/>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="9" tint="0.59999389629810485"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="9" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="9" tint="0.59999389629810485"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <alignment wrapText="1"/>
-    </dxf>
-    <dxf>
-      <alignment wrapText="1"/>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <alignment wrapText="1"/>
-    </dxf>
-    <dxf>
-      <alignment wrapText="1"/>
-    </dxf>
-    <dxf>
-      <alignment wrapText="1"/>
-    </dxf>
-    <dxf>
-      <alignment wrapText="1"/>
-    </dxf>
+  <dxfs count="162">
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -1080,7 +1053,14 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
-          <bgColor theme="9" tint="0.79998168889431442"/>
+          <bgColor theme="9" tint="0.39997558519241921"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="9" tint="0.39997558519241921"/>
         </patternFill>
       </fill>
     </dxf>
@@ -1094,7 +1074,36 @@
     <dxf>
       <fill>
         <patternFill>
-          <bgColor theme="9" tint="0.79998168889431442"/>
+          <fgColor theme="9" tint="0.39997558519241921"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF4DD36D"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="9" tint="0.39997558519241921"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="9" tint="0.39997558519241921"/>
         </patternFill>
       </fill>
     </dxf>
@@ -1106,16 +1115,230 @@
       </fill>
     </dxf>
     <dxf>
-      <alignment wrapText="1"/>
-    </dxf>
-    <dxf>
-      <alignment wrapText="1"/>
-    </dxf>
-    <dxf>
-      <alignment wrapText="1"/>
-    </dxf>
-    <dxf>
-      <alignment wrapText="1"/>
+      <fill>
+        <patternFill>
+          <fgColor theme="9" tint="0.39997558519241921"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF4DD36D"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="9" tint="0.39997558519241921"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="9" tint="0.39997558519241921"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="9" tint="0.39997558519241921"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="9" tint="0.39997558519241921"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="9" tint="0.39997558519241921"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="9" tint="0.39997558519241921"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF4DD36D"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="6" tint="-0.249977111117893"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <fgColor theme="9" tint="0.39997558519241921"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="9" tint="0.39997558519241921"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="9" tint="0.39997558519241921"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="9" tint="0.39997558519241921"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="9" tint="0.39997558519241921"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="9" tint="0.39997558519241921"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="9" tint="0.39997558519241921"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="9" tint="0.39997558519241921"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="9" tint="0.39997558519241921"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="9" tint="0.39997558519241921"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="9" tint="0.39997558519241921"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="9" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
     </dxf>
     <dxf>
       <alignment wrapText="1"/>
@@ -1155,9 +1378,6 @@
       <alignment wrapText="1"/>
     </dxf>
     <dxf>
-      <alignment wrapText="0"/>
-    </dxf>
-    <dxf>
       <alignment wrapText="1"/>
     </dxf>
     <dxf>
@@ -1167,100 +1387,16 @@
       <alignment wrapText="1"/>
     </dxf>
     <dxf>
-      <alignment wrapText="0"/>
-    </dxf>
-    <dxf>
-      <alignment wrapText="0"/>
-    </dxf>
-    <dxf>
       <alignment wrapText="1"/>
     </dxf>
     <dxf>
-      <alignment wrapText="0"/>
-    </dxf>
-    <dxf>
       <alignment wrapText="1"/>
     </dxf>
     <dxf>
-      <alignment wrapText="0"/>
-    </dxf>
-    <dxf>
       <alignment wrapText="1"/>
     </dxf>
     <dxf>
-      <alignment wrapText="0"/>
-    </dxf>
-    <dxf>
       <alignment wrapText="1"/>
-    </dxf>
-    <dxf>
-      <alignment wrapText="0"/>
-    </dxf>
-    <dxf>
-      <alignment wrapText="1"/>
-    </dxf>
-    <dxf>
-      <alignment wrapText="0"/>
-    </dxf>
-    <dxf>
-      <alignment wrapText="1"/>
-    </dxf>
-    <dxf>
-      <alignment wrapText="0"/>
-    </dxf>
-    <dxf>
-      <alignment wrapText="1"/>
-    </dxf>
-    <dxf>
-      <alignment wrapText="0"/>
-    </dxf>
-    <dxf>
-      <alignment wrapText="1"/>
-    </dxf>
-    <dxf>
-      <alignment wrapText="0"/>
-    </dxf>
-    <dxf>
-      <alignment wrapText="1"/>
-    </dxf>
-    <dxf>
-      <alignment wrapText="0"/>
-    </dxf>
-    <dxf>
-      <alignment wrapText="1"/>
-    </dxf>
-    <dxf>
-      <alignment wrapText="1"/>
-    </dxf>
-    <dxf>
-      <alignment wrapText="1"/>
-    </dxf>
-    <dxf>
-      <alignment wrapText="0"/>
-    </dxf>
-    <dxf>
-      <alignment wrapText="0"/>
-    </dxf>
-    <dxf>
-      <alignment wrapText="0"/>
-    </dxf>
-    <dxf>
-      <alignment wrapText="1"/>
-    </dxf>
-    <dxf>
-      <alignment wrapText="0"/>
-    </dxf>
-    <dxf>
-      <alignment wrapText="1"/>
-    </dxf>
-    <dxf>
-      <alignment wrapText="1"/>
-    </dxf>
-    <dxf>
-      <alignment wrapText="0"/>
-    </dxf>
-    <dxf>
-      <alignment wrapText="0"/>
     </dxf>
     <dxf>
       <alignment wrapText="1"/>
@@ -1303,79 +1439,10 @@
       <alignment wrapText="1"/>
     </dxf>
     <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
       <alignment wrapText="1"/>
     </dxf>
     <dxf>
-      <alignment wrapText="1"/>
-    </dxf>
-    <dxf>
-      <alignment wrapText="1"/>
-    </dxf>
-    <dxf>
-      <alignment wrapText="1"/>
-    </dxf>
-    <dxf>
-      <alignment wrapText="1"/>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <alignment wrapText="1"/>
-    </dxf>
-    <dxf>
-      <alignment wrapText="1"/>
-    </dxf>
-    <dxf>
-      <alignment wrapText="1"/>
-    </dxf>
-    <dxf>
-      <alignment wrapText="1"/>
-    </dxf>
-    <dxf>
-      <alignment wrapText="1"/>
-    </dxf>
-    <dxf>
-      <alignment wrapText="1"/>
-    </dxf>
-    <dxf>
-      <alignment wrapText="1"/>
-    </dxf>
-    <dxf>
-      <alignment wrapText="1"/>
-    </dxf>
-    <dxf>
-      <alignment wrapText="1"/>
-    </dxf>
-    <dxf>
-      <alignment wrapText="1"/>
-    </dxf>
-    <dxf>
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment wrapText="1"/>
-    </dxf>
-    <dxf>
-      <alignment wrapText="1"/>
     </dxf>
     <dxf>
       <alignment wrapText="1"/>
@@ -1760,6 +1827,7 @@
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <mruColors>
+      <color rgb="FF4DD36D"/>
       <color rgb="FFF2C4CB"/>
       <color rgb="FFF7ADE7"/>
     </mruColors>
@@ -2754,26 +2822,40 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{E7C3AA10-AB61-4891-90BA-EFDE96126BD0}" name="Tableau croisé dynamique15" cacheId="36" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valeurs" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
-  <location ref="B31:C35" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{0A94A5AA-7939-49B7-A6DD-E9354366584E}" name="Tableau croisé dynamique11" cacheId="36" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valeurs" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+  <location ref="B53:C57" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="7">
-    <pivotField showAll="0"/>
-    <pivotField axis="axisRow" numFmtId="14" showAll="0">
-      <items count="4">
+    <pivotField dataField="1" showAll="0">
+      <items count="11">
         <item x="0"/>
         <item x="1"/>
         <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item x="6"/>
+        <item x="7"/>
+        <item x="8"/>
+        <item x="9"/>
         <item t="default"/>
       </items>
     </pivotField>
+    <pivotField numFmtId="14" showAll="0"/>
     <pivotField showAll="0"/>
     <pivotField showAll="0"/>
     <pivotField showAll="0"/>
-    <pivotField dataField="1" showAll="0"/>
     <pivotField showAll="0"/>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="4">
+        <item x="2"/>
+        <item x="0"/>
+        <item x="1"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
   </pivotFields>
   <rowFields count="1">
-    <field x="1"/>
+    <field x="6"/>
   </rowFields>
   <rowItems count="4">
     <i>
@@ -2793,8 +2875,28 @@
     <i/>
   </colItems>
   <dataFields count="1">
-    <dataField name="Somme de montant_fc" fld="5" baseField="0" baseItem="0"/>
+    <dataField name="Nombre de transaction_id" fld="0" subtotal="count" baseField="0" baseItem="0"/>
   </dataFields>
+  <formats count="2">
+    <format dxfId="148">
+      <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
+        <references count="1">
+          <reference field="6" count="1">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="147">
+      <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
+        <references count="1">
+          <reference field="6" count="1">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+  </formats>
   <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
@@ -2808,219 +2910,6 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable10.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{B6B3D1A4-0B77-482E-9D3E-CEB1DCD7B445}" name="Tableau croisé dynamique28" cacheId="63" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valeurs" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
-  <location ref="J11:P17" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
-  <pivotFields count="7">
-    <pivotField showAll="0"/>
-    <pivotField numFmtId="14" showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField axis="axisCol" showAll="0">
-      <items count="6">
-        <item x="0"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item x="4"/>
-        <item x="3"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField axis="axisRow" showAll="0">
-      <items count="5">
-        <item x="0"/>
-        <item x="2"/>
-        <item x="3"/>
-        <item x="1"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField dataField="1" showAll="0"/>
-  </pivotFields>
-  <rowFields count="1">
-    <field x="5"/>
-  </rowFields>
-  <rowItems count="5">
-    <i>
-      <x/>
-    </i>
-    <i>
-      <x v="1"/>
-    </i>
-    <i>
-      <x v="2"/>
-    </i>
-    <i>
-      <x v="3"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </rowItems>
-  <colFields count="1">
-    <field x="4"/>
-  </colFields>
-  <colItems count="6">
-    <i>
-      <x/>
-    </i>
-    <i>
-      <x v="1"/>
-    </i>
-    <i>
-      <x v="2"/>
-    </i>
-    <i>
-      <x v="3"/>
-    </i>
-    <i>
-      <x v="4"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </colItems>
-  <dataFields count="1">
-    <dataField name="Somme de montant_fc" fld="6" baseField="0" baseItem="0"/>
-  </dataFields>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable11.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{ED04ABC1-CC07-43AE-8AC6-404199804ABF}" name="Tableau croisé dynamique27" cacheId="63" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valeurs" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
-  <location ref="N3:P9" firstHeaderRow="0" firstDataRow="1" firstDataCol="1"/>
-  <pivotFields count="7">
-    <pivotField dataField="1" showAll="0"/>
-    <pivotField numFmtId="14" showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField axis="axisRow" showAll="0" sortType="descending">
-      <items count="6">
-        <item x="0"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item x="4"/>
-        <item x="3"/>
-        <item t="default"/>
-      </items>
-      <autoSortScope>
-        <pivotArea dataOnly="0" outline="0" fieldPosition="0">
-          <references count="1">
-            <reference field="4294967294" count="1" selected="0">
-              <x v="1"/>
-            </reference>
-          </references>
-        </pivotArea>
-      </autoSortScope>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField dataField="1" showAll="0"/>
-  </pivotFields>
-  <rowFields count="1">
-    <field x="4"/>
-  </rowFields>
-  <rowItems count="6">
-    <i>
-      <x/>
-    </i>
-    <i>
-      <x v="4"/>
-    </i>
-    <i>
-      <x v="3"/>
-    </i>
-    <i>
-      <x v="1"/>
-    </i>
-    <i>
-      <x v="2"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </rowItems>
-  <colFields count="1">
-    <field x="-2"/>
-  </colFields>
-  <colItems count="2">
-    <i>
-      <x/>
-    </i>
-    <i i="1">
-      <x v="1"/>
-    </i>
-  </colItems>
-  <dataFields count="2">
-    <dataField name="Nombre de transaction_id" fld="0" subtotal="count" baseField="0" baseItem="0"/>
-    <dataField name="Somme de montant_fc" fld="6" baseField="0" baseItem="0"/>
-  </dataFields>
-  <formats count="2">
-    <format dxfId="175">
-      <pivotArea field="4" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
-    </format>
-    <format dxfId="174">
-      <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="2">
-            <x v="0"/>
-            <x v="1"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </format>
-  </formats>
-  <conditionalFormats count="2">
-    <conditionalFormat priority="4">
-      <pivotAreas count="1">
-        <pivotArea type="data" collapsedLevelsAreSubtotals="1" fieldPosition="0">
-          <references count="2">
-            <reference field="4294967294" count="1" selected="0">
-              <x v="1"/>
-            </reference>
-            <reference field="4" count="5">
-              <x v="0"/>
-              <x v="1"/>
-              <x v="2"/>
-              <x v="3"/>
-              <x v="4"/>
-            </reference>
-          </references>
-        </pivotArea>
-      </pivotAreas>
-    </conditionalFormat>
-    <conditionalFormat priority="3">
-      <pivotAreas count="1">
-        <pivotArea type="data" outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0">
-          <references count="1">
-            <reference field="4294967294" count="1" selected="0">
-              <x v="1"/>
-            </reference>
-          </references>
-        </pivotArea>
-      </pivotAreas>
-    </conditionalFormat>
-  </conditionalFormats>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable12.xml><?xml version="1.0" encoding="utf-8"?>
 <pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{977B8F9E-FB0D-490A-8AEA-204AC7739D25}" name="Tableau croisé dynamique26" cacheId="63" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valeurs" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="J3:L9" firstHeaderRow="0" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="7">
@@ -3089,10 +2978,10 @@
     <dataField name="Somme de montant_fc" fld="6" baseField="0" baseItem="0"/>
   </dataFields>
   <formats count="5">
-    <format dxfId="173">
+    <format dxfId="112">
       <pivotArea field="2" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
     </format>
-    <format dxfId="172">
+    <format dxfId="111">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="1">
           <reference field="4294967294" count="2">
@@ -3102,7 +2991,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="170">
+    <format dxfId="109">
       <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
         <references count="1">
           <reference field="2" count="2">
@@ -3112,7 +3001,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="169">
+    <format dxfId="108">
       <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
         <references count="1">
           <reference field="2" count="2">
@@ -3122,7 +3011,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="168">
+    <format dxfId="107">
       <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
         <references count="1">
           <reference field="2" count="2">
@@ -3165,7 +3054,7 @@
 </pivotTableDefinition>
 </file>
 
-<file path=xl/pivotTables/pivotTable13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/pivotTables/pivotTable11.xml><?xml version="1.0" encoding="utf-8"?>
 <pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{6EBF1115-1B87-4153-A189-EC270D369D56}" name="Tableau croisé dynamique35" cacheId="77" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valeurs" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="I2:Y12" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
   <pivotFields count="6">
@@ -3304,10 +3193,10 @@
     <dataField name="Somme de montant_fc" fld="5" baseField="0" baseItem="0"/>
   </dataFields>
   <formats count="2">
-    <format dxfId="155">
+    <format dxfId="94">
       <pivotArea field="2" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
     </format>
-    <format dxfId="154">
+    <format dxfId="93">
       <pivotArea dataOnly="0" labelOnly="1" grandCol="1" outline="0" fieldPosition="0"/>
     </format>
   </formats>
@@ -3323,7 +3212,7 @@
 </pivotTableDefinition>
 </file>
 
-<file path=xl/pivotTables/pivotTable14.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/pivotTables/pivotTable12.xml><?xml version="1.0" encoding="utf-8"?>
 <pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{6CF2CD07-335D-47F6-B7D4-64AD9F8422C1}" name="Tableau croisé dynamique34" cacheId="77" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valeurs" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="H20:I25" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="6">
@@ -3388,13 +3277,13 @@
     <dataField name="Nombre de transaction_id" fld="0" subtotal="count" baseField="0" baseItem="0"/>
   </dataFields>
   <formats count="3">
-    <format dxfId="160">
+    <format dxfId="99">
       <pivotArea field="4" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
     </format>
-    <format dxfId="159">
+    <format dxfId="98">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
     </format>
-    <format dxfId="158">
+    <format dxfId="97">
       <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
         <references count="1">
           <reference field="4" count="1">
@@ -3416,7 +3305,7 @@
 </pivotTableDefinition>
 </file>
 
-<file path=xl/pivotTables/pivotTable15.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/pivotTables/pivotTable13.xml><?xml version="1.0" encoding="utf-8"?>
 <pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{12A32755-1450-4078-8441-200639987E8B}" name="Tableau croisé dynamique33" cacheId="77" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valeurs" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="E20:F26" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="6">
@@ -3485,10 +3374,10 @@
     <dataField name="Nombre de transaction_id" fld="0" subtotal="count" baseField="0" baseItem="0"/>
   </dataFields>
   <formats count="2">
-    <format dxfId="167">
+    <format dxfId="106">
       <pivotArea field="3" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
     </format>
-    <format dxfId="166">
+    <format dxfId="105">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
     </format>
   </formats>
@@ -3542,7 +3431,7 @@
 </pivotTableDefinition>
 </file>
 
-<file path=xl/pivotTables/pivotTable16.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/pivotTables/pivotTable14.xml><?xml version="1.0" encoding="utf-8"?>
 <pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{FFBC07AA-ACC0-49E5-BC9B-2B10D6352CD6}" name="Tableau croisé dynamique32" cacheId="77" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valeurs" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="B20:C29" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="6">
@@ -3631,10 +3520,10 @@
     <dataField name="Nombre de transaction_id" fld="0" subtotal="count" baseField="0" baseItem="0"/>
   </dataFields>
   <formats count="2">
-    <format dxfId="156">
+    <format dxfId="95">
       <pivotArea field="2" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
     </format>
-    <format dxfId="157">
+    <format dxfId="96">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
     </format>
   </formats>
@@ -3650,7 +3539,7 @@
 </pivotTableDefinition>
 </file>
 
-<file path=xl/pivotTables/pivotTable17.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/pivotTables/pivotTable15.xml><?xml version="1.0" encoding="utf-8"?>
 <pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{1508B158-EB77-4324-A140-92124BCC4586}" name="Tableau croisé dynamique39" cacheId="84" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valeurs" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" rowHeaderCaption="Periodes">
   <location ref="M19:AG25" firstHeaderRow="1" firstDataRow="3" firstDataCol="1"/>
   <pivotFields count="7">
@@ -3811,29 +3700,29 @@
     <dataField name="Nombre de transaction_id" fld="0" subtotal="count" baseField="0" baseItem="0"/>
   </dataFields>
   <formats count="24">
-    <format dxfId="139">
+    <format dxfId="78">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
     </format>
-    <format dxfId="128">
+    <format dxfId="73">
       <pivotArea type="origin" dataOnly="0" labelOnly="1" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="127">
+    <format dxfId="72">
       <pivotArea field="2" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisCol" fieldPosition="0"/>
     </format>
-    <format dxfId="126">
+    <format dxfId="71">
       <pivotArea type="topRight" dataOnly="0" labelOnly="1" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="125">
+    <format dxfId="70">
       <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
         <references count="1">
           <reference field="6" count="0"/>
         </references>
       </pivotArea>
     </format>
-    <format dxfId="100">
+    <format dxfId="69">
       <pivotArea field="6" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
     </format>
-    <format dxfId="94">
+    <format dxfId="68">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="2">
           <reference field="4294967294" count="2">
@@ -3846,7 +3735,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="92">
+    <format dxfId="67">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="2">
           <reference field="4294967294" count="2">
@@ -3859,7 +3748,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="90">
+    <format dxfId="66">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="2">
           <reference field="4294967294" count="2">
@@ -3872,7 +3761,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="88">
+    <format dxfId="65">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="2">
           <reference field="4294967294" count="2">
@@ -3885,7 +3774,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="86">
+    <format dxfId="64">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="2">
           <reference field="4294967294" count="2">
@@ -3898,7 +3787,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="84">
+    <format dxfId="63">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="2">
           <reference field="4294967294" count="2">
@@ -3911,7 +3800,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="82">
+    <format dxfId="62">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="2">
           <reference field="4294967294" count="2">
@@ -3924,7 +3813,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="80">
+    <format dxfId="61">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="2">
           <reference field="4294967294" count="2">
@@ -3937,7 +3826,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="78">
+    <format dxfId="60">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="2">
           <reference field="4294967294" count="2">
@@ -3950,7 +3839,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="71">
+    <format dxfId="57">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="2">
           <reference field="4294967294" count="1">
@@ -3962,7 +3851,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="66">
+    <format dxfId="53">
       <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
         <references count="1">
           <reference field="2" count="1">
@@ -3971,7 +3860,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="65">
+    <format dxfId="52">
       <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
         <references count="1">
           <reference field="2" count="1">
@@ -3980,7 +3869,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="64">
+    <format dxfId="51">
       <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
         <references count="1">
           <reference field="2" count="7">
@@ -3995,7 +3884,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="61">
+    <format dxfId="50">
       <pivotArea field="2" dataOnly="0" labelOnly="1" grandCol="1" outline="0" axis="axisCol" fieldPosition="0">
         <references count="1">
           <reference field="4294967294" count="1" selected="0">
@@ -4004,7 +3893,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="59">
+    <format dxfId="49">
       <pivotArea field="2" dataOnly="0" labelOnly="1" grandCol="1" outline="0" axis="axisCol" fieldPosition="0">
         <references count="1">
           <reference field="4294967294" count="1" selected="0">
@@ -4013,7 +3902,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="57">
+    <format dxfId="48">
       <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
         <references count="3">
           <reference field="4294967294" count="1" selected="0">
@@ -4026,7 +3915,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="56">
+    <format dxfId="47">
       <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
         <references count="3">
           <reference field="4294967294" count="1" selected="0">
@@ -4039,7 +3928,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="55">
+    <format dxfId="46">
       <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
         <references count="3">
           <reference field="4294967294" count="1" selected="0">
@@ -4065,7 +3954,7 @@
 </pivotTableDefinition>
 </file>
 
-<file path=xl/pivotTables/pivotTable18.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/pivotTables/pivotTable16.xml><?xml version="1.0" encoding="utf-8"?>
 <pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{19B725E5-E44B-4C51-9E5D-DFB5B7840FB2}" name="Tableau croisé dynamique38" cacheId="84" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valeurs" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" rowHeaderCaption="Periodes">
   <location ref="J21:K25" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="7">
@@ -4134,10 +4023,10 @@
     <dataField name="CA" fld="5" baseField="6" baseItem="0"/>
   </dataFields>
   <formats count="2">
-    <format dxfId="76">
+    <format dxfId="59">
       <pivotArea field="6" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
     </format>
-    <format dxfId="73">
+    <format dxfId="58">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
     </format>
   </formats>
@@ -4171,7 +4060,7 @@
 </pivotTableDefinition>
 </file>
 
-<file path=xl/pivotTables/pivotTable19.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/pivotTables/pivotTable17.xml><?xml version="1.0" encoding="utf-8"?>
 <pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{5F47745C-4696-420B-92A1-AB6748DDECE4}" name="Tableau croisé dynamique37" cacheId="84" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valeurs" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" rowHeaderCaption="Periodes">
   <location ref="J12:T17" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
   <pivotFields count="7">
@@ -4272,7 +4161,7 @@
     <dataField name="Nombre de transaction_id" fld="0" subtotal="count" baseField="0" baseItem="0"/>
   </dataFields>
   <formats count="8">
-    <format dxfId="143">
+    <format dxfId="82">
       <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
         <references count="2">
           <reference field="3" count="1" selected="0">
@@ -4284,7 +4173,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="142">
+    <format dxfId="81">
       <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
         <references count="2">
           <reference field="3" count="1" selected="0">
@@ -4296,7 +4185,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="141">
+    <format dxfId="80">
       <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
         <references count="2">
           <reference field="3" count="1" selected="0">
@@ -4308,7 +4197,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="140">
+    <format dxfId="79">
       <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
         <references count="2">
           <reference field="3" count="1" selected="0">
@@ -4320,20 +4209,20 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="69">
+    <format dxfId="56">
       <pivotArea field="6" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
     </format>
-    <format dxfId="68">
+    <format dxfId="55">
       <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
         <references count="1">
           <reference field="3" count="0"/>
         </references>
       </pivotArea>
     </format>
-    <format dxfId="67">
+    <format dxfId="54">
       <pivotArea dataOnly="0" labelOnly="1" grandCol="1" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="54">
+    <format dxfId="45">
       <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
         <references count="2">
           <reference field="3" count="1" selected="0">
@@ -4358,88 +4247,7 @@
 </pivotTableDefinition>
 </file>
 
-<file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{014E5D72-7D74-4C6E-BF93-D6DFAD3D0B97}" name="Tableau croisé dynamique14" cacheId="36" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valeurs" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
-  <location ref="H25:J30" firstHeaderRow="0" firstDataRow="1" firstDataCol="1"/>
-  <pivotFields count="7">
-    <pivotField dataField="1" showAll="0">
-      <items count="11">
-        <item x="0"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item x="3"/>
-        <item x="4"/>
-        <item x="5"/>
-        <item x="6"/>
-        <item x="7"/>
-        <item x="8"/>
-        <item x="9"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField numFmtId="14" showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField axis="axisRow" showAll="0">
-      <items count="5">
-        <item x="3"/>
-        <item x="0"/>
-        <item x="2"/>
-        <item x="1"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField dataField="1" showAll="0"/>
-    <pivotField showAll="0"/>
-  </pivotFields>
-  <rowFields count="1">
-    <field x="4"/>
-  </rowFields>
-  <rowItems count="5">
-    <i>
-      <x/>
-    </i>
-    <i>
-      <x v="1"/>
-    </i>
-    <i>
-      <x v="2"/>
-    </i>
-    <i>
-      <x v="3"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </rowItems>
-  <colFields count="1">
-    <field x="-2"/>
-  </colFields>
-  <colItems count="2">
-    <i>
-      <x/>
-    </i>
-    <i i="1">
-      <x v="1"/>
-    </i>
-  </colItems>
-  <dataFields count="2">
-    <dataField name="Somme de montant_fc" fld="5" baseField="0" baseItem="0"/>
-    <dataField name="Nombre de transaction" fld="0" subtotal="count" baseField="4" baseItem="0"/>
-  </dataFields>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable20.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/pivotTables/pivotTable18.xml><?xml version="1.0" encoding="utf-8"?>
 <pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{1E2F9B57-B688-4923-9689-D300C6FD2A2D}" name="Tableau croisé dynamique36" cacheId="84" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valeurs" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" rowHeaderCaption="Periodes">
   <location ref="J2:T7" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
   <pivotFields count="7">
@@ -4527,7 +4335,7 @@
     <dataField name="Nombre de transaction_id" fld="0" subtotal="count" baseField="0" baseItem="0"/>
   </dataFields>
   <formats count="6">
-    <format dxfId="146">
+    <format dxfId="85">
       <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
         <references count="2">
           <reference field="2" count="4" selected="0">
@@ -4542,7 +4350,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="145">
+    <format dxfId="84">
       <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
         <references count="2">
           <reference field="2" count="1" selected="0">
@@ -4554,7 +4362,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="144">
+    <format dxfId="83">
       <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
         <references count="2">
           <reference field="2" count="1" selected="0">
@@ -4566,13 +4374,13 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="135">
+    <format dxfId="76">
       <pivotArea type="origin" dataOnly="0" labelOnly="1" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="134">
+    <format dxfId="75">
       <pivotArea field="2" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisCol" fieldPosition="0"/>
     </format>
-    <format dxfId="133">
+    <format dxfId="74">
       <pivotArea type="topRight" dataOnly="0" labelOnly="1" outline="0" fieldPosition="0"/>
     </format>
   </formats>
@@ -4588,83 +4396,9 @@
 </pivotTableDefinition>
 </file>
 
-<file path=xl/pivotTables/pivotTable3.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{0A94A5AA-7939-49B7-A6DD-E9354366584E}" name="Tableau croisé dynamique11" cacheId="36" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valeurs" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
-  <location ref="K17:L21" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
-  <pivotFields count="7">
-    <pivotField showAll="0"/>
-    <pivotField numFmtId="14" showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField dataField="1" showAll="0"/>
-    <pivotField axis="axisRow" showAll="0">
-      <items count="4">
-        <item x="2"/>
-        <item x="0"/>
-        <item x="1"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-  </pivotFields>
-  <rowFields count="1">
-    <field x="6"/>
-  </rowFields>
-  <rowItems count="4">
-    <i>
-      <x/>
-    </i>
-    <i>
-      <x v="1"/>
-    </i>
-    <i>
-      <x v="2"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </rowItems>
-  <colItems count="1">
-    <i/>
-  </colItems>
-  <dataFields count="1">
-    <dataField name="Somme de montant_fc" fld="5" baseField="0" baseItem="0"/>
-  </dataFields>
-  <formats count="2">
-    <format dxfId="209">
-      <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
-        <references count="1">
-          <reference field="6" count="1">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </format>
-    <format dxfId="208">
-      <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
-        <references count="1">
-          <reference field="6" count="1">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </format>
-  </formats>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
 <pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{0E420E65-FA27-4856-B341-2B171A7E7366}" name="Tableau croisé dynamique10" cacheId="36" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valeurs" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
-  <location ref="H17:I22" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+  <location ref="B43:C48" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="7">
     <pivotField showAll="0"/>
     <pivotField numFmtId="14" showAll="0"/>
@@ -4718,7 +4452,7 @@
     <dataField name="Somme de montant_fc" fld="5" baseField="0" baseItem="0"/>
   </dataFields>
   <formats count="2">
-    <format dxfId="211">
+    <format dxfId="150">
       <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
         <references count="1">
           <reference field="4" count="1">
@@ -4727,7 +4461,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="210">
+    <format dxfId="149">
       <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
         <references count="1">
           <reference field="4" count="1">
@@ -4737,6 +4471,25 @@
       </pivotArea>
     </format>
   </formats>
+  <conditionalFormats count="1">
+    <conditionalFormat priority="1">
+      <pivotAreas count="1">
+        <pivotArea type="data" collapsedLevelsAreSubtotals="1" fieldPosition="0">
+          <references count="2">
+            <reference field="4294967294" count="1" selected="0">
+              <x v="0"/>
+            </reference>
+            <reference field="4" count="4">
+              <x v="0"/>
+              <x v="1"/>
+              <x v="2"/>
+              <x v="3"/>
+            </reference>
+          </references>
+        </pivotArea>
+      </pivotAreas>
+    </conditionalFormat>
+  </conditionalFormats>
   <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
@@ -4749,9 +4502,9 @@
 </pivotTableDefinition>
 </file>
 
-<file path=xl/pivotTables/pivotTable5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/pivotTables/pivotTable3.xml><?xml version="1.0" encoding="utf-8"?>
 <pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{0489F5AA-4386-45E5-9C54-88F4AB4B8C8B}" name="Tableau croisé dynamique8" cacheId="36" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valeurs" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
-  <location ref="E17:F23" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+  <location ref="B31:C37" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="7">
     <pivotField showAll="0">
       <items count="11">
@@ -4770,7 +4523,7 @@
     </pivotField>
     <pivotField numFmtId="14" showAll="0"/>
     <pivotField showAll="0"/>
-    <pivotField axis="axisRow" showAll="0" sortType="descending">
+    <pivotField axis="axisRow" showAll="0">
       <items count="6">
         <item x="0"/>
         <item x="1"/>
@@ -4779,15 +4532,6 @@
         <item x="3"/>
         <item t="default"/>
       </items>
-      <autoSortScope>
-        <pivotArea dataOnly="0" outline="0" fieldPosition="0">
-          <references count="1">
-            <reference field="4294967294" count="1" selected="0">
-              <x v="0"/>
-            </reference>
-          </references>
-        </pivotArea>
-      </autoSortScope>
     </pivotField>
     <pivotField showAll="0"/>
     <pivotField dataField="1" showAll="0" sumSubtotal="1">
@@ -4809,16 +4553,16 @@
       <x/>
     </i>
     <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i>
       <x v="4"/>
-    </i>
-    <i>
-      <x v="3"/>
-    </i>
-    <i>
-      <x v="2"/>
-    </i>
-    <i>
-      <x v="1"/>
     </i>
     <i t="grand">
       <x/>
@@ -4830,8 +4574,8 @@
   <dataFields count="1">
     <dataField name="Somme de montant_fc" fld="5" baseField="0" baseItem="0"/>
   </dataFields>
-  <formats count="2">
-    <format dxfId="213">
+  <formats count="6">
+    <format dxfId="152">
       <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
         <references count="1">
           <reference field="3" count="1">
@@ -4840,7 +4584,43 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="212">
+    <format dxfId="151">
+      <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
+        <references count="1">
+          <reference field="3" count="1">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="34">
+      <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
+        <references count="1">
+          <reference field="3" count="1">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="33">
+      <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
+        <references count="1">
+          <reference field="3" count="1">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="32">
+      <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
+        <references count="1">
+          <reference field="3" count="1">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="29">
       <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
         <references count="1">
           <reference field="3" count="1">
@@ -4850,6 +4630,26 @@
       </pivotArea>
     </format>
   </formats>
+  <conditionalFormats count="1">
+    <conditionalFormat priority="3">
+      <pivotAreas count="1">
+        <pivotArea type="data" collapsedLevelsAreSubtotals="1" fieldPosition="0">
+          <references count="2">
+            <reference field="4294967294" count="1" selected="0">
+              <x v="0"/>
+            </reference>
+            <reference field="3" count="5">
+              <x v="0"/>
+              <x v="1"/>
+              <x v="2"/>
+              <x v="3"/>
+              <x v="4"/>
+            </reference>
+          </references>
+        </pivotArea>
+      </pivotAreas>
+    </conditionalFormat>
+  </conditionalFormats>
   <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
@@ -4862,11 +4662,11 @@
 </pivotTableDefinition>
 </file>
 
-<file path=xl/pivotTables/pivotTable6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/pivotTables/pivotTable4.xml><?xml version="1.0" encoding="utf-8"?>
 <pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{7B72621D-595A-4AC1-AE02-1074C41FD4EA}" name="Tableau croisé dynamique7" cacheId="36" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valeurs" grandTotalCaption="CA" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
-  <location ref="B17:C28" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+  <location ref="B20:C24" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="7">
-    <pivotField axis="axisRow" showAll="0">
+    <pivotField showAll="0">
       <items count="11">
         <item x="0"/>
         <item x="1"/>
@@ -4881,17 +4681,33 @@
         <item t="default"/>
       </items>
     </pivotField>
-    <pivotField numFmtId="14" showAll="0"/>
+    <pivotField axis="axisRow" numFmtId="14" showAll="0">
+      <items count="4">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
     <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
+    <pivotField showAll="0">
+      <items count="6">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="4"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
     <pivotField showAll="0"/>
     <pivotField dataField="1" showAll="0"/>
     <pivotField showAll="0"/>
   </pivotFields>
   <rowFields count="1">
-    <field x="0"/>
+    <field x="1"/>
   </rowFields>
-  <rowItems count="11">
+  <rowItems count="4">
     <i>
       <x/>
     </i>
@@ -4900,27 +4716,6 @@
     </i>
     <i>
       <x v="2"/>
-    </i>
-    <i>
-      <x v="3"/>
-    </i>
-    <i>
-      <x v="4"/>
-    </i>
-    <i>
-      <x v="5"/>
-    </i>
-    <i>
-      <x v="6"/>
-    </i>
-    <i>
-      <x v="7"/>
-    </i>
-    <i>
-      <x v="8"/>
-    </i>
-    <i>
-      <x v="9"/>
     </i>
     <i t="grand">
       <x/>
@@ -4944,7 +4739,7 @@
 </pivotTableDefinition>
 </file>
 
-<file path=xl/pivotTables/pivotTable7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/pivotTables/pivotTable5.xml><?xml version="1.0" encoding="utf-8"?>
 <pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{307774D1-06E3-4866-B6C8-A311F7479B8C}" name="Tableau croisé dynamique25" cacheId="53" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valeurs" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="B20:T26" firstHeaderRow="1" firstDataRow="3" firstDataCol="1"/>
   <pivotFields count="7">
@@ -5065,7 +4860,7 @@
     <dataField name="Somme de montant_fc" fld="5" baseField="0" baseItem="0"/>
   </dataFields>
   <formats count="17">
-    <format dxfId="182">
+    <format dxfId="121">
       <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
         <references count="2">
           <reference field="1" count="2">
@@ -5078,10 +4873,10 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="183">
+    <format dxfId="122">
       <pivotArea field="1" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
     </format>
-    <format dxfId="184">
+    <format dxfId="123">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="2">
           <reference field="4294967294" count="2">
@@ -5094,7 +4889,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="185">
+    <format dxfId="124">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="2">
           <reference field="4294967294" count="2">
@@ -5107,7 +4902,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="186">
+    <format dxfId="125">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="2">
           <reference field="4294967294" count="2">
@@ -5120,7 +4915,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="187">
+    <format dxfId="126">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="2">
           <reference field="4294967294" count="2">
@@ -5133,7 +4928,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="188">
+    <format dxfId="127">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="2">
           <reference field="4294967294" count="2">
@@ -5146,7 +4941,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="189">
+    <format dxfId="128">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="2">
           <reference field="4294967294" count="2">
@@ -5159,7 +4954,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="190">
+    <format dxfId="129">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="2">
           <reference field="4294967294" count="2">
@@ -5172,7 +4967,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="191">
+    <format dxfId="130">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="2">
           <reference field="4294967294" count="2">
@@ -5185,7 +4980,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="192">
+    <format dxfId="131">
       <pivotArea field="2" dataOnly="0" labelOnly="1" grandCol="1" outline="0" axis="axisCol" fieldPosition="0">
         <references count="1">
           <reference field="4294967294" count="1" selected="0">
@@ -5194,7 +4989,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="193">
+    <format dxfId="132">
       <pivotArea field="2" dataOnly="0" labelOnly="1" grandCol="1" outline="0" axis="axisCol" fieldPosition="0">
         <references count="1">
           <reference field="4294967294" count="1" selected="0">
@@ -5203,10 +4998,10 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="194">
+    <format dxfId="133">
       <pivotArea field="2" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisCol" fieldPosition="0"/>
     </format>
-    <format dxfId="195">
+    <format dxfId="134">
       <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
         <references count="3">
           <reference field="4294967294" count="2" selected="0">
@@ -5223,7 +5018,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="196">
+    <format dxfId="135">
       <pivotArea dataOnly="0" labelOnly="1" offset="A256" fieldPosition="0">
         <references count="1">
           <reference field="2" count="1">
@@ -5232,7 +5027,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="197">
+    <format dxfId="136">
       <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
         <references count="3">
           <reference field="4294967294" count="1" selected="0">
@@ -5247,7 +5042,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="198">
+    <format dxfId="137">
       <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
         <references count="3">
           <reference field="4294967294" count="1" selected="0">
@@ -5275,7 +5070,7 @@
 </pivotTableDefinition>
 </file>
 
-<file path=xl/pivotTables/pivotTable8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/pivotTables/pivotTable6.xml><?xml version="1.0" encoding="utf-8"?>
 <pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{E03AB932-5DD7-4CAF-BF0A-30F67C3B60D8}" name="Tableau croisé dynamique17" cacheId="53" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valeurs" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" rowHeaderCaption="Clients/canal">
   <location ref="J7:N17" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
   <pivotFields count="7">
@@ -5378,17 +5173,17 @@
     <dataField name="Canal preferé par client" fld="0" subtotal="count" baseField="0" baseItem="0"/>
   </dataFields>
   <formats count="3">
-    <format dxfId="201">
+    <format dxfId="140">
       <pivotArea field="2" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
     </format>
-    <format dxfId="200">
+    <format dxfId="139">
       <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
         <references count="1">
           <reference field="6" count="0"/>
         </references>
       </pivotArea>
     </format>
-    <format dxfId="199">
+    <format dxfId="138">
       <pivotArea dataOnly="0" labelOnly="1" grandCol="1" outline="0" fieldPosition="0"/>
     </format>
   </formats>
@@ -5404,7 +5199,7 @@
 </pivotTableDefinition>
 </file>
 
-<file path=xl/pivotTables/pivotTable9.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/pivotTables/pivotTable7.xml><?xml version="1.0" encoding="utf-8"?>
 <pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{A22EDBCB-2740-4BFE-81A8-879F344A3DF7}" name="Tableau croisé dynamique16" cacheId="53" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valeurs" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" rowHeaderCaption="Clients">
   <location ref="P8:R17" firstHeaderRow="0" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="7">
@@ -5482,6 +5277,219 @@
     <dataField name="Frequence par client" fld="0" subtotal="count" baseField="2" baseItem="0"/>
     <dataField name="Depense par client" fld="5" baseField="2" baseItem="0"/>
   </dataFields>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable8.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{B6B3D1A4-0B77-482E-9D3E-CEB1DCD7B445}" name="Tableau croisé dynamique28" cacheId="63" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valeurs" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+  <location ref="J11:P17" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
+  <pivotFields count="7">
+    <pivotField showAll="0"/>
+    <pivotField numFmtId="14" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField axis="axisCol" showAll="0">
+      <items count="6">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="4"/>
+        <item x="3"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="5">
+        <item x="0"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="1"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField dataField="1" showAll="0"/>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="5"/>
+  </rowFields>
+  <rowItems count="5">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colFields count="1">
+    <field x="4"/>
+  </colFields>
+  <colItems count="6">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i>
+      <x v="4"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Somme de montant_fc" fld="6" baseField="0" baseItem="0"/>
+  </dataFields>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable9.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{ED04ABC1-CC07-43AE-8AC6-404199804ABF}" name="Tableau croisé dynamique27" cacheId="63" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valeurs" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+  <location ref="N3:P9" firstHeaderRow="0" firstDataRow="1" firstDataCol="1"/>
+  <pivotFields count="7">
+    <pivotField dataField="1" showAll="0"/>
+    <pivotField numFmtId="14" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField axis="axisRow" showAll="0" sortType="descending">
+      <items count="6">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="4"/>
+        <item x="3"/>
+        <item t="default"/>
+      </items>
+      <autoSortScope>
+        <pivotArea dataOnly="0" outline="0" fieldPosition="0">
+          <references count="1">
+            <reference field="4294967294" count="1" selected="0">
+              <x v="1"/>
+            </reference>
+          </references>
+        </pivotArea>
+      </autoSortScope>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField dataField="1" showAll="0"/>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="4"/>
+  </rowFields>
+  <rowItems count="6">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="4"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colFields count="1">
+    <field x="-2"/>
+  </colFields>
+  <colItems count="2">
+    <i>
+      <x/>
+    </i>
+    <i i="1">
+      <x v="1"/>
+    </i>
+  </colItems>
+  <dataFields count="2">
+    <dataField name="Nombre de transaction_id" fld="0" subtotal="count" baseField="0" baseItem="0"/>
+    <dataField name="Somme de montant_fc" fld="6" baseField="0" baseItem="0"/>
+  </dataFields>
+  <formats count="2">
+    <format dxfId="114">
+      <pivotArea field="4" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
+    </format>
+    <format dxfId="113">
+      <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="2">
+            <x v="0"/>
+            <x v="1"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+  </formats>
+  <conditionalFormats count="2">
+    <conditionalFormat priority="4">
+      <pivotAreas count="1">
+        <pivotArea type="data" collapsedLevelsAreSubtotals="1" fieldPosition="0">
+          <references count="2">
+            <reference field="4294967294" count="1" selected="0">
+              <x v="1"/>
+            </reference>
+            <reference field="4" count="5">
+              <x v="0"/>
+              <x v="1"/>
+              <x v="2"/>
+              <x v="3"/>
+              <x v="4"/>
+            </reference>
+          </references>
+        </pivotArea>
+      </pivotAreas>
+    </conditionalFormat>
+    <conditionalFormat priority="3">
+      <pivotAreas count="1">
+        <pivotArea type="data" outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0">
+          <references count="1">
+            <reference field="4294967294" count="1" selected="0">
+              <x v="1"/>
+            </reference>
+          </references>
+        </pivotArea>
+      </pivotAreas>
+    </conditionalFormat>
+  </conditionalFormats>
   <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
@@ -5543,16 +5551,16 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{6EC83A65-D9A6-475F-8D16-1CE811FFF2E9}" name="Tableau1" displayName="Tableau1" ref="B4:H14" totalsRowShown="0" headerRowDxfId="214" dataDxfId="215">
-  <autoFilter ref="B4:H14" xr:uid="{6EC83A65-D9A6-475F-8D16-1CE811FFF2E9}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{6EC83A65-D9A6-475F-8D16-1CE811FFF2E9}" name="Tableau1" displayName="Tableau1" ref="B3:H13" totalsRowShown="0" headerRowDxfId="153" dataDxfId="154">
+  <autoFilter ref="B3:H13" xr:uid="{6EC83A65-D9A6-475F-8D16-1CE811FFF2E9}"/>
   <tableColumns count="7">
-    <tableColumn id="1" xr3:uid="{54537CD7-847D-4C04-9BD6-B993FB8C0924}" name="transaction_id" dataDxfId="222"/>
-    <tableColumn id="2" xr3:uid="{7DFAA592-DC98-463C-A6AF-A94A0F915646}" name="date" dataDxfId="221"/>
-    <tableColumn id="3" xr3:uid="{122DF7BD-714F-4B55-830F-7573F364E80A}" name="client_id" dataDxfId="220"/>
-    <tableColumn id="4" xr3:uid="{1B94713D-DD23-416E-B23B-98EF629AFCBE}" name="commune" dataDxfId="219"/>
-    <tableColumn id="5" xr3:uid="{084E48D7-3EDD-4FC4-B38B-BD3872EDFF23}" name="produit" dataDxfId="218"/>
-    <tableColumn id="6" xr3:uid="{D1BF92F6-B520-4D49-B97E-C1395DDE5A98}" name="montant_fc" dataDxfId="217"/>
-    <tableColumn id="7" xr3:uid="{21C18558-D71D-47B7-B0D0-001594508953}" name="canal" dataDxfId="216"/>
+    <tableColumn id="1" xr3:uid="{54537CD7-847D-4C04-9BD6-B993FB8C0924}" name="transaction_id" dataDxfId="161"/>
+    <tableColumn id="2" xr3:uid="{7DFAA592-DC98-463C-A6AF-A94A0F915646}" name="date" dataDxfId="160"/>
+    <tableColumn id="3" xr3:uid="{122DF7BD-714F-4B55-830F-7573F364E80A}" name="client_id" dataDxfId="159"/>
+    <tableColumn id="4" xr3:uid="{1B94713D-DD23-416E-B23B-98EF629AFCBE}" name="commune" dataDxfId="158"/>
+    <tableColumn id="5" xr3:uid="{084E48D7-3EDD-4FC4-B38B-BD3872EDFF23}" name="produit" dataDxfId="157"/>
+    <tableColumn id="6" xr3:uid="{D1BF92F6-B520-4D49-B97E-C1395DDE5A98}" name="montant_fc" dataDxfId="156"/>
+    <tableColumn id="7" xr3:uid="{21C18558-D71D-47B7-B0D0-001594508953}" name="canal" dataDxfId="155"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -5562,13 +5570,13 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{5B43BC6D-66A6-432F-982F-C406FA282078}" name="Dataset_day2__2" displayName="Dataset_day2__2" ref="B2:H17" tableType="queryTable" totalsRowShown="0">
   <autoFilter ref="B2:H17" xr:uid="{5B43BC6D-66A6-432F-982F-C406FA282078}"/>
   <tableColumns count="7">
-    <tableColumn id="1" xr3:uid="{F0363F15-00D8-44D9-B9E8-73E1201A36E6}" uniqueName="1" name="transaction_id" queryTableFieldId="1" dataDxfId="207"/>
-    <tableColumn id="2" xr3:uid="{85F76B94-3323-41EB-B99E-F9DE7DD9EF5D}" uniqueName="2" name="date" queryTableFieldId="2" dataDxfId="206"/>
-    <tableColumn id="3" xr3:uid="{90258075-E8BA-4181-AEBF-14DCE9CF1AC4}" uniqueName="3" name="client_id" queryTableFieldId="3" dataDxfId="205"/>
-    <tableColumn id="4" xr3:uid="{3B088930-C813-470C-9790-11DA318C42A1}" uniqueName="4" name="commune" queryTableFieldId="4" dataDxfId="204"/>
-    <tableColumn id="5" xr3:uid="{E074DF00-E0E7-41D6-B91A-ABE22CB1881A}" uniqueName="5" name="produit" queryTableFieldId="5" dataDxfId="203"/>
+    <tableColumn id="1" xr3:uid="{F0363F15-00D8-44D9-B9E8-73E1201A36E6}" uniqueName="1" name="transaction_id" queryTableFieldId="1" dataDxfId="146"/>
+    <tableColumn id="2" xr3:uid="{85F76B94-3323-41EB-B99E-F9DE7DD9EF5D}" uniqueName="2" name="date" queryTableFieldId="2" dataDxfId="145"/>
+    <tableColumn id="3" xr3:uid="{90258075-E8BA-4181-AEBF-14DCE9CF1AC4}" uniqueName="3" name="client_id" queryTableFieldId="3" dataDxfId="144"/>
+    <tableColumn id="4" xr3:uid="{3B088930-C813-470C-9790-11DA318C42A1}" uniqueName="4" name="commune" queryTableFieldId="4" dataDxfId="143"/>
+    <tableColumn id="5" xr3:uid="{E074DF00-E0E7-41D6-B91A-ABE22CB1881A}" uniqueName="5" name="produit" queryTableFieldId="5" dataDxfId="142"/>
     <tableColumn id="6" xr3:uid="{7C01ABE9-F9C0-40F6-9F95-D610FB820086}" uniqueName="6" name="montant_fc" queryTableFieldId="6"/>
-    <tableColumn id="7" xr3:uid="{30F6D1BA-4065-4D54-BF94-1BE05C99AC63}" uniqueName="7" name="canal" queryTableFieldId="7" dataDxfId="202"/>
+    <tableColumn id="7" xr3:uid="{30F6D1BA-4065-4D54-BF94-1BE05C99AC63}" uniqueName="7" name="canal" queryTableFieldId="7" dataDxfId="141"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -5578,12 +5586,12 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{A4A0DCA2-C1C4-44D4-AD45-BDA248A44995}" name="Dataset_day3" displayName="Dataset_day3" ref="B2:H17" tableType="queryTable" totalsRowShown="0">
   <autoFilter ref="B2:H17" xr:uid="{A4A0DCA2-C1C4-44D4-AD45-BDA248A44995}"/>
   <tableColumns count="7">
-    <tableColumn id="1" xr3:uid="{A0067E32-0369-4D8A-BDF1-C8B907B86BD0}" uniqueName="1" name="transaction_id" queryTableFieldId="1" dataDxfId="181"/>
-    <tableColumn id="2" xr3:uid="{C68FAFFA-BEA0-4F94-BA99-6450F477971E}" uniqueName="2" name="date" queryTableFieldId="2" dataDxfId="180"/>
-    <tableColumn id="3" xr3:uid="{CDF65428-BE02-471D-A8F7-90F1D8454251}" uniqueName="3" name="agent_id" queryTableFieldId="3" dataDxfId="179"/>
-    <tableColumn id="4" xr3:uid="{22F84FAA-57F1-425F-B37C-F8428C49E033}" uniqueName="4" name="client_id" queryTableFieldId="4" dataDxfId="178"/>
-    <tableColumn id="5" xr3:uid="{93A8CFD1-D585-478D-9AFB-02301838500E}" uniqueName="5" name="commune" queryTableFieldId="5" dataDxfId="177"/>
-    <tableColumn id="6" xr3:uid="{956E7CEA-E833-4F96-9E51-2D67194B8C61}" uniqueName="6" name="produit" queryTableFieldId="6" dataDxfId="176"/>
+    <tableColumn id="1" xr3:uid="{A0067E32-0369-4D8A-BDF1-C8B907B86BD0}" uniqueName="1" name="transaction_id" queryTableFieldId="1" dataDxfId="120"/>
+    <tableColumn id="2" xr3:uid="{C68FAFFA-BEA0-4F94-BA99-6450F477971E}" uniqueName="2" name="date" queryTableFieldId="2" dataDxfId="119"/>
+    <tableColumn id="3" xr3:uid="{CDF65428-BE02-471D-A8F7-90F1D8454251}" uniqueName="3" name="agent_id" queryTableFieldId="3" dataDxfId="118"/>
+    <tableColumn id="4" xr3:uid="{22F84FAA-57F1-425F-B37C-F8428C49E033}" uniqueName="4" name="client_id" queryTableFieldId="4" dataDxfId="117"/>
+    <tableColumn id="5" xr3:uid="{93A8CFD1-D585-478D-9AFB-02301838500E}" uniqueName="5" name="commune" queryTableFieldId="5" dataDxfId="116"/>
+    <tableColumn id="6" xr3:uid="{956E7CEA-E833-4F96-9E51-2D67194B8C61}" uniqueName="6" name="produit" queryTableFieldId="6" dataDxfId="115"/>
     <tableColumn id="7" xr3:uid="{E636C8A0-3C3C-48BE-AFE5-1B3DB129CA7E}" uniqueName="7" name="montant_fc" queryTableFieldId="7"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
@@ -5594,11 +5602,11 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{AB24B926-8F3E-4EE6-9138-D47BB2378B02}" name="Dataset_day4" displayName="Dataset_day4" ref="B2:G17" totalsRowShown="0">
   <autoFilter ref="B2:G17" xr:uid="{AB24B926-8F3E-4EE6-9138-D47BB2378B02}"/>
   <tableColumns count="6">
-    <tableColumn id="1" xr3:uid="{2FA77349-5B7D-430C-A299-CA8EF8B94F8F}" name="transaction_id" dataDxfId="165"/>
-    <tableColumn id="2" xr3:uid="{EA88A0A8-EDC4-468E-80F4-EF0578FE9A03}" name="date" dataDxfId="164"/>
-    <tableColumn id="3" xr3:uid="{811F8411-B146-492E-A697-2D905854F94D}" name="client_id" dataDxfId="163"/>
-    <tableColumn id="4" xr3:uid="{7B37CE19-01A8-4470-8A2B-849B751FB37D}" name="commune" dataDxfId="162"/>
-    <tableColumn id="5" xr3:uid="{863A1A63-AC11-4715-82E2-F6EC444E5B51}" name="produit" dataDxfId="161"/>
+    <tableColumn id="1" xr3:uid="{2FA77349-5B7D-430C-A299-CA8EF8B94F8F}" name="transaction_id" dataDxfId="104"/>
+    <tableColumn id="2" xr3:uid="{EA88A0A8-EDC4-468E-80F4-EF0578FE9A03}" name="date" dataDxfId="103"/>
+    <tableColumn id="3" xr3:uid="{811F8411-B146-492E-A697-2D905854F94D}" name="client_id" dataDxfId="102"/>
+    <tableColumn id="4" xr3:uid="{7B37CE19-01A8-4470-8A2B-849B751FB37D}" name="commune" dataDxfId="101"/>
+    <tableColumn id="5" xr3:uid="{863A1A63-AC11-4715-82E2-F6EC444E5B51}" name="produit" dataDxfId="100"/>
     <tableColumn id="6" xr3:uid="{DDFB738A-4C05-4F97-882D-16FE65EF8A7E}" name="montant_fc"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
@@ -5606,7 +5614,7 @@
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="9" xr:uid="{B1C5B688-9C67-4CAD-9DAE-7207D5E5E850}" name="Tableau9" displayName="Tableau9" ref="AA3:AA11" totalsRowShown="0" headerRowDxfId="153">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="9" xr:uid="{B1C5B688-9C67-4CAD-9DAE-7207D5E5E850}" name="Tableau9" displayName="Tableau9" ref="AA3:AA11" totalsRowShown="0" headerRowDxfId="92">
   <autoFilter ref="AA3:AA11" xr:uid="{B1C5B688-9C67-4CAD-9DAE-7207D5E5E850}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="AA4:AA11">
     <sortCondition ref="AA3:AA11"/>
@@ -5621,16 +5629,16 @@
 </file>
 
 <file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="10" xr:uid="{C4A92EC0-501A-4751-9A16-2163E0BD39EA}" name="Dataset_day5" displayName="Dataset_day5" ref="B2:H17" tableType="queryTable" totalsRowShown="0" headerRowDxfId="136">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="10" xr:uid="{C4A92EC0-501A-4751-9A16-2163E0BD39EA}" name="Dataset_day5" displayName="Dataset_day5" ref="B2:H17" tableType="queryTable" totalsRowShown="0" headerRowDxfId="77">
   <autoFilter ref="B2:H17" xr:uid="{C4A92EC0-501A-4751-9A16-2163E0BD39EA}"/>
   <tableColumns count="7">
-    <tableColumn id="1" xr3:uid="{FBC21564-1B48-423F-AFDB-04B5AE20CF75}" uniqueName="1" name="transaction_id" queryTableFieldId="1" dataDxfId="152"/>
-    <tableColumn id="2" xr3:uid="{CA4A50D7-5720-4F71-ACD1-3781681C0231}" uniqueName="2" name="date" queryTableFieldId="2" dataDxfId="151"/>
-    <tableColumn id="3" xr3:uid="{A265E5F8-50A6-4DD3-8C5E-10BB05E3F126}" uniqueName="3" name="client_id" queryTableFieldId="3" dataDxfId="150"/>
-    <tableColumn id="4" xr3:uid="{0E595B89-2727-474B-B4A6-66BC0AC0864A}" uniqueName="4" name="commune" queryTableFieldId="4" dataDxfId="149"/>
-    <tableColumn id="5" xr3:uid="{4D992877-9744-466D-982E-E1F06CDEF762}" uniqueName="5" name="produit" queryTableFieldId="5" dataDxfId="148"/>
+    <tableColumn id="1" xr3:uid="{FBC21564-1B48-423F-AFDB-04B5AE20CF75}" uniqueName="1" name="transaction_id" queryTableFieldId="1" dataDxfId="91"/>
+    <tableColumn id="2" xr3:uid="{CA4A50D7-5720-4F71-ACD1-3781681C0231}" uniqueName="2" name="date" queryTableFieldId="2" dataDxfId="90"/>
+    <tableColumn id="3" xr3:uid="{A265E5F8-50A6-4DD3-8C5E-10BB05E3F126}" uniqueName="3" name="client_id" queryTableFieldId="3" dataDxfId="89"/>
+    <tableColumn id="4" xr3:uid="{0E595B89-2727-474B-B4A6-66BC0AC0864A}" uniqueName="4" name="commune" queryTableFieldId="4" dataDxfId="88"/>
+    <tableColumn id="5" xr3:uid="{4D992877-9744-466D-982E-E1F06CDEF762}" uniqueName="5" name="produit" queryTableFieldId="5" dataDxfId="87"/>
     <tableColumn id="6" xr3:uid="{D10FAE6E-7969-4551-94AB-82C2D27DFD50}" uniqueName="6" name="montant_fc" queryTableFieldId="6"/>
-    <tableColumn id="7" xr3:uid="{7306D68B-3C9A-40F7-A0D9-E00CC8C73541}" uniqueName="7" name="periode" queryTableFieldId="7" dataDxfId="147"/>
+    <tableColumn id="7" xr3:uid="{7306D68B-3C9A-40F7-A0D9-E00CC8C73541}" uniqueName="7" name="periode" queryTableFieldId="7" dataDxfId="86"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -5641,7 +5649,7 @@
   <autoFilter ref="A1:G6" xr:uid="{68E59C74-D329-4B48-A967-CC868365949C}"/>
   <tableColumns count="7">
     <tableColumn id="1" xr3:uid="{C102BD58-3DF8-48B7-9114-2067608D3DB4}" name="transaction_id"/>
-    <tableColumn id="2" xr3:uid="{998F6E83-476D-414D-8353-8E6146354739}" name="date" dataDxfId="171"/>
+    <tableColumn id="2" xr3:uid="{998F6E83-476D-414D-8353-8E6146354739}" name="date" dataDxfId="110"/>
     <tableColumn id="3" xr3:uid="{1ACC5CD9-2A0F-4DB2-B7B7-A25781DA1795}" name="agent_id"/>
     <tableColumn id="4" xr3:uid="{D4B111D2-01DE-4AFC-91B0-641E23172B8C}" name="client_id"/>
     <tableColumn id="5" xr3:uid="{C0E2906A-2633-4FB3-89D8-883ADDF86D4F}" name="commune"/>
@@ -5969,616 +5977,695 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{04B3012F-C756-4CF6-A456-1922518EC017}">
-  <dimension ref="B2:L35"/>
+  <dimension ref="A2:I70"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="3" width="21.42578125" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="21.42578125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="11.140625" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="21.42578125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="24.42578125" bestFit="1" customWidth="1"/>
+    <col min="5" max="9" width="21.42578125" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="21.85546875" bestFit="1" customWidth="1"/>
     <col min="11" max="12" width="21.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B2" s="11" t="s">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="B2" s="16" t="s">
         <v>43</v>
       </c>
-      <c r="C2" s="11"/>
-      <c r="D2" s="11"/>
-      <c r="E2" s="11"/>
-      <c r="F2" s="11"/>
-      <c r="G2" s="11"/>
-      <c r="H2" s="11"/>
-    </row>
-    <row r="4" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B4" s="1" t="s">
+      <c r="C2" s="16"/>
+      <c r="D2" s="16"/>
+      <c r="E2" s="16"/>
+      <c r="F2" s="16"/>
+      <c r="G2" s="16"/>
+      <c r="H2" s="16"/>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A3" s="13" t="s">
+        <v>182</v>
+      </c>
+      <c r="B3" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="C4" s="1" t="s">
+      <c r="C3" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="D4" s="1" t="s">
+      <c r="D3" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="E4" s="1" t="s">
+      <c r="E3" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="F4" s="1" t="s">
+      <c r="F3" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="G4" s="3" t="s">
+      <c r="G3" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="H4" s="1" t="s">
+      <c r="H3" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="I4" s="1"/>
-    </row>
-    <row r="5" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B5" s="4" t="s">
+      <c r="I3" s="2"/>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A4" s="14">
+        <v>1</v>
+      </c>
+      <c r="B4" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="C5" s="6">
+      <c r="C4" s="7">
         <v>46143</v>
       </c>
-      <c r="D5" s="4" t="s">
+      <c r="D4" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="E5" s="4" t="s">
+      <c r="E4" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="F5" s="4" t="s">
+      <c r="F4" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="G5" s="2">
+      <c r="G4" s="3">
         <v>10000</v>
       </c>
-      <c r="H5" s="4" t="s">
+      <c r="H4" s="5" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="6" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B6" s="4" t="s">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A5" s="15">
+        <v>2</v>
+      </c>
+      <c r="B5" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="C6" s="6">
+      <c r="C5" s="7">
         <v>46143</v>
       </c>
-      <c r="D6" s="4" t="s">
+      <c r="D5" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="E6" s="4" t="s">
+      <c r="E5" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="F6" s="4" t="s">
+      <c r="F5" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="G6" s="2">
+      <c r="G5" s="3">
         <v>3000</v>
       </c>
-      <c r="H6" s="4" t="s">
+      <c r="H5" s="5" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="7" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B7" s="4" t="s">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A6" s="14">
+        <v>3</v>
+      </c>
+      <c r="B6" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="C7" s="6">
+      <c r="C6" s="7">
         <v>46143</v>
       </c>
-      <c r="D7" s="4" t="s">
+      <c r="D6" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="E7" s="4" t="s">
+      <c r="E6" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="F7" s="4" t="s">
+      <c r="F6" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="G7" s="2">
+      <c r="G6" s="3">
         <v>10000</v>
       </c>
-      <c r="H7" s="4" t="s">
+      <c r="H6" s="5" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="8" spans="2:12" ht="30" x14ac:dyDescent="0.25">
-      <c r="B8" s="4" t="s">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A7" s="15">
+        <v>4</v>
+      </c>
+      <c r="B7" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="C8" s="6">
+      <c r="C7" s="7">
         <v>46144</v>
       </c>
-      <c r="D8" s="4" t="s">
+      <c r="D7" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="E8" s="4" t="s">
+      <c r="E7" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="F8" s="4" t="s">
+      <c r="F7" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="G8" s="2">
+      <c r="G7" s="3">
         <v>1000</v>
       </c>
-      <c r="H8" s="4" t="s">
+      <c r="H7" s="5" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="9" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B9" s="4" t="s">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A8" s="14">
+        <v>5</v>
+      </c>
+      <c r="B8" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="C9" s="6">
+      <c r="C8" s="7">
         <v>46144</v>
       </c>
-      <c r="D9" s="4" t="s">
+      <c r="D8" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="E9" s="4" t="s">
+      <c r="E8" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="F9" s="4" t="s">
+      <c r="F8" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="G9" s="2">
+      <c r="G8" s="3">
         <v>18000</v>
       </c>
-      <c r="H9" s="4" t="s">
+      <c r="H8" s="5" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="10" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B10" s="4" t="s">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A9" s="15">
+        <v>6</v>
+      </c>
+      <c r="B9" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="C10" s="6">
+      <c r="C9" s="7">
         <v>46144</v>
       </c>
-      <c r="D10" s="4" t="s">
+      <c r="D9" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="E10" s="4" t="s">
+      <c r="E9" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="F10" s="4" t="s">
+      <c r="F9" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="G10" s="2">
+      <c r="G9" s="3">
         <v>3000</v>
       </c>
-      <c r="H10" s="4" t="s">
+      <c r="H9" s="5" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="11" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B11" s="4" t="s">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A10" s="14">
+        <v>7</v>
+      </c>
+      <c r="B10" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="C11" s="6">
+      <c r="C10" s="7">
         <v>46145</v>
       </c>
-      <c r="D11" s="4" t="s">
+      <c r="D10" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="E11" s="4" t="s">
+      <c r="E10" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="F11" s="4" t="s">
+      <c r="F10" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="G11" s="2">
+      <c r="G10" s="3">
         <v>10000</v>
       </c>
-      <c r="H11" s="4" t="s">
+      <c r="H10" s="5" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="12" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B12" s="4" t="s">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A11" s="15">
+        <v>8</v>
+      </c>
+      <c r="B11" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="C12" s="6">
+      <c r="C11" s="7">
         <v>46145</v>
       </c>
-      <c r="D12" s="4" t="s">
+      <c r="D11" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="E12" s="4" t="s">
+      <c r="E11" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="F12" s="4" t="s">
+      <c r="F11" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="G12" s="2">
+      <c r="G11" s="3">
         <v>3000</v>
       </c>
-      <c r="H12" s="4" t="s">
+      <c r="H11" s="5" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="13" spans="2:12" ht="30" x14ac:dyDescent="0.25">
-      <c r="B13" s="4" t="s">
+    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A12" s="14">
+        <v>9</v>
+      </c>
+      <c r="B12" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="C13" s="6">
+      <c r="C12" s="7">
         <v>46145</v>
       </c>
-      <c r="D13" s="4" t="s">
+      <c r="D12" s="5" t="s">
         <v>34</v>
       </c>
-      <c r="E13" s="4" t="s">
+      <c r="E12" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="F13" s="4" t="s">
+      <c r="F12" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="G13" s="2">
+      <c r="G12" s="3">
         <v>18000</v>
       </c>
-      <c r="H13" s="4" t="s">
+      <c r="H12" s="5" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="14" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B14" s="4" t="s">
+    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A13" s="15">
+        <v>10</v>
+      </c>
+      <c r="B13" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="C14" s="6">
+      <c r="C13" s="7">
         <v>46145</v>
       </c>
-      <c r="D14" s="4" t="s">
+      <c r="D13" s="5" t="s">
         <v>36</v>
       </c>
-      <c r="E14" s="4" t="s">
+      <c r="E13" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="F14" s="4" t="s">
+      <c r="F13" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="G14" s="2">
+      <c r="G13" s="3">
         <v>1000</v>
       </c>
-      <c r="H14" s="4" t="s">
+      <c r="H13" s="5" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="16" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B16" s="12" t="s">
+    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="B14" s="5"/>
+      <c r="C14" s="7"/>
+      <c r="D14" s="5"/>
+      <c r="E14" s="5"/>
+      <c r="F14" s="5"/>
+      <c r="G14" s="3"/>
+      <c r="H14" s="5"/>
+    </row>
+    <row r="15" spans="1:9" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B15" s="39" t="s">
+        <v>177</v>
+      </c>
+      <c r="C15" s="38"/>
+      <c r="D15" s="38"/>
+      <c r="E15" s="38"/>
+      <c r="F15" s="38"/>
+      <c r="G15" s="38"/>
+      <c r="H15" s="38"/>
+    </row>
+    <row r="16" spans="1:9" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B16" s="40"/>
+      <c r="C16" s="1"/>
+      <c r="D16" s="1"/>
+      <c r="E16" s="1"/>
+      <c r="F16" s="1"/>
+      <c r="G16" s="1"/>
+      <c r="H16" s="1"/>
+    </row>
+    <row r="17" spans="2:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B17" s="39" t="s">
+        <v>178</v>
+      </c>
+      <c r="C17" s="39"/>
+      <c r="D17" s="39"/>
+      <c r="E17" s="41"/>
+    </row>
+    <row r="19" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B19" s="16" t="s">
         <v>44</v>
       </c>
-      <c r="C16" s="12"/>
-      <c r="E16" s="12" t="s">
+      <c r="C19" s="16"/>
+    </row>
+    <row r="20" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B20" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="C20" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="21" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B21" s="19">
+        <v>46143</v>
+      </c>
+      <c r="C21" s="10">
+        <v>23000</v>
+      </c>
+    </row>
+    <row r="22" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B22" s="19">
+        <v>46144</v>
+      </c>
+      <c r="C22" s="10">
+        <v>22000</v>
+      </c>
+    </row>
+    <row r="23" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B23" s="19">
+        <v>46145</v>
+      </c>
+      <c r="C23" s="10">
+        <v>32000</v>
+      </c>
+    </row>
+    <row r="24" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B24" s="19" t="s">
+        <v>37</v>
+      </c>
+      <c r="C24" s="10">
+        <v>77000</v>
+      </c>
+    </row>
+    <row r="26" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B26" s="9"/>
+      <c r="C26" s="10"/>
+    </row>
+    <row r="27" spans="2:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B27" s="39" t="s">
+        <v>179</v>
+      </c>
+      <c r="C27" s="39"/>
+      <c r="D27" s="39"/>
+      <c r="E27" s="41"/>
+      <c r="F27" s="1"/>
+      <c r="G27" s="1"/>
+    </row>
+    <row r="30" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B30" s="16" t="s">
         <v>45</v>
       </c>
-      <c r="F16" s="12"/>
-      <c r="H16" s="12" t="s">
-        <v>46</v>
-      </c>
-      <c r="I16" s="12"/>
-      <c r="K16" s="12" t="s">
-        <v>47</v>
-      </c>
-      <c r="L16" s="11"/>
-    </row>
-    <row r="17" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B17" s="7" t="s">
-        <v>38</v>
-      </c>
-      <c r="C17" t="s">
-        <v>41</v>
-      </c>
-      <c r="E17" s="7" t="s">
-        <v>38</v>
-      </c>
-      <c r="F17" t="s">
-        <v>41</v>
-      </c>
-      <c r="H17" s="7" t="s">
-        <v>38</v>
-      </c>
-      <c r="I17" t="s">
-        <v>41</v>
-      </c>
-      <c r="K17" s="7" t="s">
-        <v>38</v>
-      </c>
-      <c r="L17" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="18" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B18" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="C18" s="9">
-        <v>10000</v>
-      </c>
-      <c r="E18" s="13" t="s">
-        <v>9</v>
-      </c>
-      <c r="F18" s="14">
-        <v>29000</v>
-      </c>
-      <c r="H18" s="13" t="s">
-        <v>26</v>
-      </c>
-      <c r="I18" s="14">
-        <v>36000</v>
-      </c>
-      <c r="K18" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="L18" s="14">
-        <v>39000</v>
-      </c>
-    </row>
-    <row r="19" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B19" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="C19" s="9">
-        <v>3000</v>
-      </c>
-      <c r="E19" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="F19" s="9">
-        <v>18000</v>
-      </c>
-      <c r="H19" s="8" t="s">
-        <v>10</v>
-      </c>
-      <c r="I19" s="9">
-        <v>30000</v>
-      </c>
-      <c r="K19" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="L19" s="9">
-        <v>29000</v>
-      </c>
-    </row>
-    <row r="20" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B20" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="C20" s="9">
-        <v>10000</v>
-      </c>
-      <c r="E20" s="8" t="s">
-        <v>19</v>
-      </c>
-      <c r="F20" s="9">
-        <v>11000</v>
-      </c>
-      <c r="H20" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="I20" s="9">
-        <v>9000</v>
-      </c>
-      <c r="K20" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="L20" s="9">
-        <v>9000</v>
-      </c>
-    </row>
-    <row r="21" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B21" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="C21" s="9">
-        <v>1000</v>
-      </c>
-      <c r="E21" s="8" t="s">
-        <v>31</v>
-      </c>
-      <c r="F21" s="9">
-        <v>10000</v>
-      </c>
-      <c r="H21" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="I21" s="9">
-        <v>2000</v>
-      </c>
-      <c r="K21" s="8" t="s">
-        <v>40</v>
-      </c>
-      <c r="L21" s="9">
-        <v>77000</v>
-      </c>
-    </row>
-    <row r="22" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B22" s="8" t="s">
-        <v>23</v>
-      </c>
-      <c r="C22" s="9">
-        <v>18000</v>
-      </c>
-      <c r="E22" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="F22" s="9">
-        <v>9000</v>
-      </c>
-      <c r="H22" s="8" t="s">
-        <v>40</v>
-      </c>
-      <c r="I22" s="9">
-        <v>77000</v>
-      </c>
-    </row>
-    <row r="23" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B23" s="8" t="s">
-        <v>27</v>
-      </c>
-      <c r="C23" s="9">
-        <v>3000</v>
-      </c>
-      <c r="E23" s="8" t="s">
-        <v>40</v>
-      </c>
-      <c r="F23" s="9">
-        <v>77000</v>
-      </c>
-    </row>
-    <row r="24" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B24" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="C24" s="9">
-        <v>10000</v>
-      </c>
-    </row>
-    <row r="25" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B25" s="8" t="s">
-        <v>32</v>
-      </c>
-      <c r="C25" s="9">
-        <v>3000</v>
-      </c>
-      <c r="H25" s="7" t="s">
-        <v>38</v>
-      </c>
-      <c r="I25" t="s">
-        <v>41</v>
-      </c>
-      <c r="J25" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="26" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B26" s="8" t="s">
-        <v>33</v>
-      </c>
-      <c r="C26" s="9">
-        <v>18000</v>
-      </c>
-      <c r="H26" s="8" t="s">
-        <v>26</v>
-      </c>
-      <c r="I26" s="9">
-        <v>36000</v>
-      </c>
-      <c r="J26" s="9">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="27" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B27" s="8" t="s">
-        <v>35</v>
-      </c>
-      <c r="C27" s="9">
-        <v>1000</v>
-      </c>
-      <c r="H27" s="8" t="s">
-        <v>10</v>
-      </c>
-      <c r="I27" s="9">
-        <v>30000</v>
-      </c>
-      <c r="J27" s="9">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="28" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B28" s="8" t="s">
-        <v>37</v>
-      </c>
-      <c r="C28" s="9">
-        <v>77000</v>
-      </c>
-      <c r="H28" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="I28" s="9">
-        <v>2000</v>
-      </c>
-      <c r="J28" s="9">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="29" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="H29" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="I29" s="9">
-        <v>9000</v>
-      </c>
-      <c r="J29" s="9">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="30" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="H30" s="8" t="s">
-        <v>40</v>
-      </c>
-      <c r="I30" s="9">
-        <v>77000</v>
-      </c>
-      <c r="J30" s="9">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="31" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B31" s="7" t="s">
+      <c r="C30" s="16"/>
+    </row>
+    <row r="31" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B31" s="8" t="s">
         <v>38</v>
       </c>
       <c r="C31" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="32" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B32" s="15">
-        <v>46143</v>
-      </c>
-      <c r="C32" s="9">
-        <v>23000</v>
-      </c>
-    </row>
-    <row r="33" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B33" s="15">
-        <v>46144</v>
-      </c>
-      <c r="C33" s="9">
-        <v>22000</v>
-      </c>
-    </row>
-    <row r="34" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B34" s="15">
-        <v>46145</v>
-      </c>
-      <c r="C34" s="9">
-        <v>32000</v>
-      </c>
-    </row>
-    <row r="35" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B35" s="15" t="s">
+    <row r="32" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B32" s="42" t="s">
+        <v>9</v>
+      </c>
+      <c r="C32" s="23">
+        <v>29000</v>
+      </c>
+    </row>
+    <row r="33" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B33" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="C33" s="10">
+        <v>9000</v>
+      </c>
+    </row>
+    <row r="34" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B34" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="C34" s="10">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="35" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B35" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="C35" s="10">
+        <v>11000</v>
+      </c>
+    </row>
+    <row r="36" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B36" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="C36" s="10">
+        <v>18000</v>
+      </c>
+    </row>
+    <row r="37" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B37" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="C35" s="9">
+      <c r="C37" s="10">
         <v>77000</v>
       </c>
     </row>
+    <row r="40" spans="2:4" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B40" s="39" t="s">
+        <v>180</v>
+      </c>
+      <c r="C40" s="39"/>
+      <c r="D40" s="39"/>
+    </row>
+    <row r="42" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B42" s="16" t="s">
+        <v>46</v>
+      </c>
+      <c r="C42" s="16"/>
+    </row>
+    <row r="43" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B43" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="C43" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="44" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B44" s="17" t="s">
+        <v>26</v>
+      </c>
+      <c r="C44" s="18">
+        <v>36000</v>
+      </c>
+    </row>
+    <row r="45" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B45" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="C45" s="10">
+        <v>30000</v>
+      </c>
+    </row>
+    <row r="46" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B46" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="C46" s="10">
+        <v>9000</v>
+      </c>
+    </row>
+    <row r="47" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B47" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="C47" s="10">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="48" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B48" s="9" t="s">
+        <v>40</v>
+      </c>
+      <c r="C48" s="10">
+        <v>77000</v>
+      </c>
+    </row>
+    <row r="50" spans="2:5" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B50" s="39" t="s">
+        <v>181</v>
+      </c>
+      <c r="C50" s="39"/>
+      <c r="D50" s="39"/>
+    </row>
+    <row r="52" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B52" s="16" t="s">
+        <v>47</v>
+      </c>
+      <c r="C52" s="12"/>
+    </row>
+    <row r="53" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B53" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="C53" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="54" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B54" s="17" t="s">
+        <v>20</v>
+      </c>
+      <c r="C54" s="18">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="55" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B55" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="C55" s="10">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="56" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B56" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="C56" s="10">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="57" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B57" s="9" t="s">
+        <v>40</v>
+      </c>
+      <c r="C57" s="10">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="60" spans="2:5" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="B60" s="46" t="s">
+        <v>188</v>
+      </c>
+      <c r="C60" s="46"/>
+    </row>
+    <row r="62" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B62" s="44" t="s">
+        <v>189</v>
+      </c>
+      <c r="C62" s="44"/>
+      <c r="D62" s="44"/>
+      <c r="E62" s="44"/>
+    </row>
+    <row r="63" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B63" s="44"/>
+      <c r="C63" s="44"/>
+      <c r="D63" s="44"/>
+      <c r="E63" s="44"/>
+    </row>
+    <row r="64" spans="2:5" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B64" s="45"/>
+      <c r="C64" s="45"/>
+      <c r="D64" s="45"/>
+      <c r="E64" s="45"/>
+    </row>
+    <row r="65" spans="2:2" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="B65" s="47" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="66" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B66" s="43"/>
+    </row>
+    <row r="67" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B67" s="48" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="68" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B68" s="48" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="69" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B69" s="48" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="70" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B70" s="48" t="s">
+        <v>187</v>
+      </c>
+    </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" columnSort="1" ref="H25:J30">
-    <sortCondition descending="1" ref="J25"/>
-  </sortState>
-  <mergeCells count="5">
+  <mergeCells count="12">
+    <mergeCell ref="B27:D27"/>
+    <mergeCell ref="B40:D40"/>
+    <mergeCell ref="B50:D50"/>
+    <mergeCell ref="B60:C60"/>
+    <mergeCell ref="B62:E63"/>
     <mergeCell ref="B2:H2"/>
-    <mergeCell ref="B16:C16"/>
-    <mergeCell ref="E16:F16"/>
-    <mergeCell ref="H16:I16"/>
-    <mergeCell ref="K16:L16"/>
+    <mergeCell ref="B19:C19"/>
+    <mergeCell ref="B30:C30"/>
+    <mergeCell ref="B42:C42"/>
+    <mergeCell ref="B52:C52"/>
+    <mergeCell ref="B15:H15"/>
+    <mergeCell ref="B17:D17"/>
   </mergeCells>
+  <conditionalFormatting pivot="1" sqref="C32:C36">
+    <cfRule type="colorScale" priority="3">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B32">
+    <cfRule type="colorScale" priority="2">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting pivot="1" sqref="C44:C47">
+    <cfRule type="colorScale" priority="1">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
-    <tablePart r:id="rId7"/>
+    <tablePart r:id="rId5"/>
   </tableParts>
 </worksheet>
 </file>
@@ -6634,842 +6721,842 @@
       </c>
     </row>
     <row r="3" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B3" s="9" t="s">
-        <v>49</v>
-      </c>
-      <c r="C3" s="5">
+      <c r="B3" s="10" t="s">
+        <v>48</v>
+      </c>
+      <c r="C3" s="6">
         <v>46146</v>
       </c>
-      <c r="D3" s="9" t="s">
+      <c r="D3" s="10" t="s">
         <v>8</v>
       </c>
-      <c r="E3" s="9" t="s">
+      <c r="E3" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="F3" s="9" t="s">
+      <c r="F3" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G3">
         <v>18000</v>
       </c>
-      <c r="H3" s="9" t="s">
+      <c r="H3" s="10" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="4" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B4" s="9" t="s">
-        <v>50</v>
-      </c>
-      <c r="C4" s="5">
+      <c r="B4" s="10" t="s">
+        <v>49</v>
+      </c>
+      <c r="C4" s="6">
         <v>46146</v>
       </c>
-      <c r="D4" s="9" t="s">
+      <c r="D4" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="E4" s="9" t="s">
+      <c r="E4" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="F4" s="9" t="s">
+      <c r="F4" s="10" t="s">
         <v>15</v>
       </c>
       <c r="G4">
         <v>3000</v>
       </c>
-      <c r="H4" s="9" t="s">
+      <c r="H4" s="10" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="5" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B5" s="9" t="s">
-        <v>51</v>
-      </c>
-      <c r="C5" s="5">
+      <c r="B5" s="10" t="s">
+        <v>50</v>
+      </c>
+      <c r="C5" s="6">
         <v>46146</v>
       </c>
-      <c r="D5" s="9" t="s">
+      <c r="D5" s="10" t="s">
         <v>8</v>
       </c>
-      <c r="E5" s="9" t="s">
+      <c r="E5" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="F5" s="9" t="s">
+      <c r="F5" s="10" t="s">
         <v>10</v>
       </c>
       <c r="G5">
         <v>10000</v>
       </c>
-      <c r="H5" s="9" t="s">
+      <c r="H5" s="10" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="6" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B6" s="9" t="s">
+      <c r="B6" s="10" t="s">
+        <v>51</v>
+      </c>
+      <c r="C6" s="6">
+        <v>46146</v>
+      </c>
+      <c r="D6" s="10" t="s">
         <v>52</v>
       </c>
-      <c r="C6" s="5">
-        <v>46146</v>
-      </c>
-      <c r="D6" s="9" t="s">
-        <v>53</v>
-      </c>
-      <c r="E6" s="9" t="s">
+      <c r="E6" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="F6" s="9" t="s">
+      <c r="F6" s="10" t="s">
         <v>22</v>
       </c>
       <c r="G6">
         <v>1000</v>
       </c>
-      <c r="H6" s="9" t="s">
+      <c r="H6" s="10" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="7" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B7" s="9" t="s">
+      <c r="B7" s="10" t="s">
+        <v>53</v>
+      </c>
+      <c r="C7" s="6">
+        <v>46146</v>
+      </c>
+      <c r="D7" s="10" t="s">
         <v>54</v>
       </c>
-      <c r="C7" s="5">
-        <v>46146</v>
-      </c>
-      <c r="D7" s="9" t="s">
-        <v>55</v>
-      </c>
-      <c r="E7" s="9" t="s">
+      <c r="E7" s="10" t="s">
         <v>31</v>
       </c>
-      <c r="F7" s="9" t="s">
+      <c r="F7" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G7">
         <v>18000</v>
       </c>
-      <c r="H7" s="9" t="s">
+      <c r="H7" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="J7" s="7" t="s">
-        <v>74</v>
-      </c>
-      <c r="K7" s="7" t="s">
+      <c r="J7" s="8" t="s">
+        <v>73</v>
+      </c>
+      <c r="K7" s="8" t="s">
         <v>42</v>
       </c>
     </row>
     <row r="8" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B8" s="9" t="s">
-        <v>56</v>
-      </c>
-      <c r="C8" s="5">
+      <c r="B8" s="10" t="s">
+        <v>55</v>
+      </c>
+      <c r="C8" s="6">
         <v>46147</v>
       </c>
-      <c r="D8" s="9" t="s">
+      <c r="D8" s="10" t="s">
         <v>8</v>
       </c>
-      <c r="E8" s="9" t="s">
+      <c r="E8" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="F8" s="9" t="s">
+      <c r="F8" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G8">
         <v>18000</v>
       </c>
-      <c r="H8" s="9" t="s">
+      <c r="H8" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="J8" s="16" t="s">
-        <v>76</v>
-      </c>
-      <c r="K8" s="10" t="s">
+      <c r="J8" s="20" t="s">
+        <v>75</v>
+      </c>
+      <c r="K8" s="11" t="s">
         <v>20</v>
       </c>
-      <c r="L8" s="10" t="s">
+      <c r="L8" s="11" t="s">
         <v>11</v>
       </c>
-      <c r="M8" s="10" t="s">
+      <c r="M8" s="11" t="s">
         <v>16</v>
       </c>
-      <c r="N8" s="10" t="s">
+      <c r="N8" s="11" t="s">
         <v>40</v>
       </c>
-      <c r="P8" s="7" t="s">
-        <v>75</v>
+      <c r="P8" s="8" t="s">
+        <v>74</v>
       </c>
       <c r="Q8" t="s">
+        <v>71</v>
+      </c>
+      <c r="R8" t="s">
         <v>72</v>
       </c>
-      <c r="R8" t="s">
-        <v>73</v>
-      </c>
     </row>
     <row r="9" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B9" s="9" t="s">
-        <v>57</v>
-      </c>
-      <c r="C9" s="5">
+      <c r="B9" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="C9" s="6">
         <v>46147</v>
       </c>
-      <c r="D9" s="9" t="s">
+      <c r="D9" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="E9" s="9" t="s">
+      <c r="E9" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="F9" s="9" t="s">
+      <c r="F9" s="10" t="s">
         <v>15</v>
       </c>
       <c r="G9">
         <v>3000</v>
       </c>
-      <c r="H9" s="9" t="s">
+      <c r="H9" s="10" t="s">
         <v>16</v>
       </c>
-      <c r="J9" s="8" t="s">
+      <c r="J9" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="K9" s="9"/>
-      <c r="L9" s="9">
+      <c r="K9" s="10"/>
+      <c r="L9" s="10">
         <v>7</v>
       </c>
-      <c r="M9" s="9"/>
-      <c r="N9" s="9">
+      <c r="M9" s="10"/>
+      <c r="N9" s="10">
         <v>7</v>
       </c>
-      <c r="P9" s="8" t="s">
+      <c r="P9" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="Q9" s="9">
+      <c r="Q9" s="10">
         <v>7</v>
       </c>
-      <c r="R9" s="9">
+      <c r="R9" s="10">
         <v>110000</v>
       </c>
     </row>
     <row r="10" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B10" s="9" t="s">
+      <c r="B10" s="10" t="s">
+        <v>57</v>
+      </c>
+      <c r="C10" s="6">
+        <v>46147</v>
+      </c>
+      <c r="D10" s="10" t="s">
         <v>58</v>
       </c>
-      <c r="C10" s="5">
-        <v>46147</v>
-      </c>
-      <c r="D10" s="9" t="s">
-        <v>59</v>
-      </c>
-      <c r="E10" s="9" t="s">
+      <c r="E10" s="10" t="s">
         <v>25</v>
       </c>
-      <c r="F10" s="9" t="s">
+      <c r="F10" s="10" t="s">
         <v>10</v>
       </c>
       <c r="G10">
         <v>10000</v>
       </c>
-      <c r="H10" s="9" t="s">
+      <c r="H10" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="J10" s="8" t="s">
+      <c r="J10" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="K10" s="9"/>
-      <c r="L10" s="9"/>
-      <c r="M10" s="9">
+      <c r="K10" s="10"/>
+      <c r="L10" s="10"/>
+      <c r="M10" s="10">
         <v>2</v>
       </c>
-      <c r="N10" s="9">
+      <c r="N10" s="10">
         <v>2</v>
       </c>
-      <c r="P10" s="8" t="s">
+      <c r="P10" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="Q10" s="9">
+      <c r="Q10" s="10">
         <v>2</v>
       </c>
-      <c r="R10" s="9">
+      <c r="R10" s="10">
         <v>6000</v>
       </c>
     </row>
     <row r="11" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B11" s="9" t="s">
-        <v>60</v>
-      </c>
-      <c r="C11" s="5">
+      <c r="B11" s="10" t="s">
+        <v>59</v>
+      </c>
+      <c r="C11" s="6">
         <v>46147</v>
       </c>
-      <c r="D11" s="9" t="s">
+      <c r="D11" s="10" t="s">
         <v>8</v>
       </c>
-      <c r="E11" s="9" t="s">
+      <c r="E11" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="F11" s="9" t="s">
+      <c r="F11" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G11">
         <v>18000</v>
       </c>
-      <c r="H11" s="9" t="s">
+      <c r="H11" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="J11" s="8" t="s">
-        <v>53</v>
-      </c>
-      <c r="K11" s="9">
+      <c r="J11" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="K11" s="10">
         <v>1</v>
       </c>
-      <c r="L11" s="9"/>
-      <c r="M11" s="9"/>
-      <c r="N11" s="9">
+      <c r="L11" s="10"/>
+      <c r="M11" s="10"/>
+      <c r="N11" s="10">
         <v>1</v>
       </c>
-      <c r="P11" s="8" t="s">
-        <v>53</v>
-      </c>
-      <c r="Q11" s="9">
+      <c r="P11" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="Q11" s="10">
         <v>1</v>
       </c>
-      <c r="R11" s="9">
+      <c r="R11" s="10">
         <v>1000</v>
       </c>
     </row>
     <row r="12" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B12" s="9" t="s">
+      <c r="B12" s="10" t="s">
+        <v>60</v>
+      </c>
+      <c r="C12" s="6">
+        <v>46147</v>
+      </c>
+      <c r="D12" s="10" t="s">
         <v>61</v>
       </c>
-      <c r="C12" s="5">
-        <v>46147</v>
-      </c>
-      <c r="D12" s="9" t="s">
-        <v>62</v>
-      </c>
-      <c r="E12" s="9" t="s">
+      <c r="E12" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="F12" s="9" t="s">
+      <c r="F12" s="10" t="s">
         <v>22</v>
       </c>
       <c r="G12">
         <v>1000</v>
       </c>
-      <c r="H12" s="9" t="s">
+      <c r="H12" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="J12" s="8" t="s">
-        <v>55</v>
-      </c>
-      <c r="K12" s="9">
+      <c r="J12" s="9" t="s">
+        <v>54</v>
+      </c>
+      <c r="K12" s="10">
         <v>1</v>
       </c>
-      <c r="L12" s="9"/>
-      <c r="M12" s="9"/>
-      <c r="N12" s="9">
+      <c r="L12" s="10"/>
+      <c r="M12" s="10"/>
+      <c r="N12" s="10">
         <v>1</v>
       </c>
-      <c r="P12" s="8" t="s">
-        <v>55</v>
-      </c>
-      <c r="Q12" s="9">
+      <c r="P12" s="9" t="s">
+        <v>54</v>
+      </c>
+      <c r="Q12" s="10">
         <v>1</v>
       </c>
-      <c r="R12" s="9">
+      <c r="R12" s="10">
         <v>18000</v>
       </c>
     </row>
     <row r="13" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B13" s="9" t="s">
-        <v>63</v>
-      </c>
-      <c r="C13" s="5">
+      <c r="B13" s="10" t="s">
+        <v>62</v>
+      </c>
+      <c r="C13" s="6">
         <v>46147</v>
       </c>
-      <c r="D13" s="9" t="s">
+      <c r="D13" s="10" t="s">
         <v>8</v>
       </c>
-      <c r="E13" s="9" t="s">
+      <c r="E13" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="F13" s="9" t="s">
+      <c r="F13" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G13">
         <v>18000</v>
       </c>
-      <c r="H13" s="9" t="s">
+      <c r="H13" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="J13" s="8" t="s">
-        <v>59</v>
-      </c>
-      <c r="K13" s="9">
+      <c r="J13" s="9" t="s">
+        <v>58</v>
+      </c>
+      <c r="K13" s="10">
         <v>1</v>
       </c>
-      <c r="L13" s="9"/>
-      <c r="M13" s="9"/>
-      <c r="N13" s="9">
+      <c r="L13" s="10"/>
+      <c r="M13" s="10"/>
+      <c r="N13" s="10">
         <v>1</v>
       </c>
-      <c r="P13" s="8" t="s">
-        <v>59</v>
-      </c>
-      <c r="Q13" s="9">
+      <c r="P13" s="9" t="s">
+        <v>58</v>
+      </c>
+      <c r="Q13" s="10">
         <v>1</v>
       </c>
-      <c r="R13" s="9">
+      <c r="R13" s="10">
         <v>10000</v>
       </c>
     </row>
     <row r="14" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B14" s="9" t="s">
+      <c r="B14" s="10" t="s">
+        <v>63</v>
+      </c>
+      <c r="C14" s="6">
+        <v>46147</v>
+      </c>
+      <c r="D14" s="10" t="s">
         <v>64</v>
       </c>
-      <c r="C14" s="5">
-        <v>46147</v>
-      </c>
-      <c r="D14" s="9" t="s">
-        <v>65</v>
-      </c>
-      <c r="E14" s="9" t="s">
+      <c r="E14" s="10" t="s">
         <v>31</v>
       </c>
-      <c r="F14" s="9" t="s">
+      <c r="F14" s="10" t="s">
         <v>15</v>
       </c>
       <c r="G14">
         <v>3000</v>
       </c>
-      <c r="H14" s="9" t="s">
+      <c r="H14" s="10" t="s">
         <v>16</v>
       </c>
-      <c r="J14" s="8" t="s">
-        <v>62</v>
-      </c>
-      <c r="K14" s="9"/>
-      <c r="L14" s="9">
+      <c r="J14" s="9" t="s">
+        <v>61</v>
+      </c>
+      <c r="K14" s="10"/>
+      <c r="L14" s="10">
         <v>1</v>
       </c>
-      <c r="M14" s="9"/>
-      <c r="N14" s="9">
+      <c r="M14" s="10"/>
+      <c r="N14" s="10">
         <v>1</v>
       </c>
-      <c r="P14" s="8" t="s">
-        <v>62</v>
-      </c>
-      <c r="Q14" s="9">
+      <c r="P14" s="9" t="s">
+        <v>61</v>
+      </c>
+      <c r="Q14" s="10">
         <v>1</v>
       </c>
-      <c r="R14" s="9">
+      <c r="R14" s="10">
         <v>1000</v>
       </c>
     </row>
     <row r="15" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B15" s="9" t="s">
-        <v>66</v>
-      </c>
-      <c r="C15" s="5">
+      <c r="B15" s="10" t="s">
+        <v>65</v>
+      </c>
+      <c r="C15" s="6">
         <v>46147</v>
       </c>
-      <c r="D15" s="9" t="s">
+      <c r="D15" s="10" t="s">
         <v>8</v>
       </c>
-      <c r="E15" s="9" t="s">
+      <c r="E15" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="F15" s="9" t="s">
+      <c r="F15" s="10" t="s">
         <v>10</v>
       </c>
       <c r="G15">
         <v>10000</v>
       </c>
-      <c r="H15" s="9" t="s">
+      <c r="H15" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="J15" s="8" t="s">
-        <v>65</v>
-      </c>
-      <c r="K15" s="9"/>
-      <c r="L15" s="9"/>
-      <c r="M15" s="9">
+      <c r="J15" s="9" t="s">
+        <v>64</v>
+      </c>
+      <c r="K15" s="10"/>
+      <c r="L15" s="10"/>
+      <c r="M15" s="10">
         <v>1</v>
       </c>
-      <c r="N15" s="9">
+      <c r="N15" s="10">
         <v>1</v>
       </c>
-      <c r="P15" s="8" t="s">
-        <v>65</v>
-      </c>
-      <c r="Q15" s="9">
+      <c r="P15" s="9" t="s">
+        <v>64</v>
+      </c>
+      <c r="Q15" s="10">
         <v>1</v>
       </c>
-      <c r="R15" s="9">
+      <c r="R15" s="10">
         <v>3000</v>
       </c>
     </row>
     <row r="16" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B16" s="9" t="s">
+      <c r="B16" s="10" t="s">
+        <v>66</v>
+      </c>
+      <c r="C16" s="6">
+        <v>46148</v>
+      </c>
+      <c r="D16" s="10" t="s">
         <v>67</v>
       </c>
-      <c r="C16" s="5">
-        <v>46148</v>
-      </c>
-      <c r="D16" s="9" t="s">
-        <v>68</v>
-      </c>
-      <c r="E16" s="9" t="s">
+      <c r="E16" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="F16" s="9" t="s">
+      <c r="F16" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G16">
         <v>18000</v>
       </c>
-      <c r="H16" s="9" t="s">
+      <c r="H16" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="J16" s="8" t="s">
+      <c r="J16" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="K16" s="10">
+        <v>1</v>
+      </c>
+      <c r="L16" s="10"/>
+      <c r="M16" s="10"/>
+      <c r="N16" s="10">
+        <v>1</v>
+      </c>
+      <c r="P16" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="Q16" s="10">
+        <v>1</v>
+      </c>
+      <c r="R16" s="10">
+        <v>18000</v>
+      </c>
+    </row>
+    <row r="17" spans="2:20" x14ac:dyDescent="0.25">
+      <c r="B17" s="10" t="s">
         <v>68</v>
       </c>
-      <c r="K16" s="9">
-        <v>1</v>
-      </c>
-      <c r="L16" s="9"/>
-      <c r="M16" s="9"/>
-      <c r="N16" s="9">
-        <v>1</v>
-      </c>
-      <c r="P16" s="8" t="s">
-        <v>68</v>
-      </c>
-      <c r="Q16" s="9">
-        <v>1</v>
-      </c>
-      <c r="R16" s="9">
-        <v>18000</v>
-      </c>
-    </row>
-    <row r="17" spans="2:20" x14ac:dyDescent="0.25">
-      <c r="B17" s="9" t="s">
-        <v>69</v>
-      </c>
-      <c r="C17" s="5">
+      <c r="C17" s="6">
         <v>46148</v>
       </c>
-      <c r="D17" s="9" t="s">
+      <c r="D17" s="10" t="s">
         <v>8</v>
       </c>
-      <c r="E17" s="9" t="s">
+      <c r="E17" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="F17" s="9" t="s">
+      <c r="F17" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G17">
         <v>18000</v>
       </c>
-      <c r="H17" s="9" t="s">
+      <c r="H17" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="J17" s="8" t="s">
+      <c r="J17" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="K17" s="9">
+      <c r="K17" s="10">
         <v>4</v>
       </c>
-      <c r="L17" s="9">
+      <c r="L17" s="10">
         <v>8</v>
       </c>
-      <c r="M17" s="9">
+      <c r="M17" s="10">
         <v>3</v>
       </c>
-      <c r="N17" s="9">
+      <c r="N17" s="10">
         <v>15</v>
       </c>
-      <c r="P17" s="8" t="s">
+      <c r="P17" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="Q17" s="9">
+      <c r="Q17" s="10">
         <v>15</v>
       </c>
-      <c r="R17" s="9">
+      <c r="R17" s="10">
         <v>167000</v>
       </c>
     </row>
     <row r="19" spans="2:20" x14ac:dyDescent="0.25">
-      <c r="F19" s="8"/>
-      <c r="G19" s="9"/>
-      <c r="H19" s="9"/>
-      <c r="I19" s="9"/>
-      <c r="J19" s="9"/>
+      <c r="F19" s="9"/>
+      <c r="G19" s="10"/>
+      <c r="H19" s="10"/>
+      <c r="I19" s="10"/>
+      <c r="J19" s="10"/>
     </row>
     <row r="20" spans="2:20" ht="30" x14ac:dyDescent="0.25">
-      <c r="C20" s="18" t="s">
+      <c r="C20" s="22" t="s">
         <v>42</v>
       </c>
     </row>
     <row r="21" spans="2:20" ht="70.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C21" s="20" t="s">
+      <c r="C21" s="24" t="s">
         <v>8</v>
       </c>
       <c r="E21" t="s">
         <v>13</v>
       </c>
       <c r="G21" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="I21" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="K21" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="M21" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="O21" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="Q21" t="s">
-        <v>68</v>
-      </c>
-      <c r="S21" s="17" t="s">
+        <v>67</v>
+      </c>
+      <c r="S21" s="21" t="s">
+        <v>69</v>
+      </c>
+      <c r="T21" s="21" t="s">
         <v>70</v>
       </c>
-      <c r="T21" s="17" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="22" spans="2:20" s="17" customFormat="1" ht="39" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B22" s="18" t="s">
+    </row>
+    <row r="22" spans="2:20" s="21" customFormat="1" ht="39" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B22" s="22" t="s">
         <v>38</v>
       </c>
-      <c r="C22" s="17" t="s">
+      <c r="C22" s="21" t="s">
         <v>39</v>
       </c>
-      <c r="D22" s="17" t="s">
+      <c r="D22" s="21" t="s">
         <v>41</v>
       </c>
-      <c r="E22" s="17" t="s">
+      <c r="E22" s="21" t="s">
         <v>39</v>
       </c>
-      <c r="F22" s="17" t="s">
+      <c r="F22" s="21" t="s">
         <v>41</v>
       </c>
-      <c r="G22" s="17" t="s">
+      <c r="G22" s="21" t="s">
         <v>39</v>
       </c>
-      <c r="H22" s="17" t="s">
+      <c r="H22" s="21" t="s">
         <v>41</v>
       </c>
-      <c r="I22" s="17" t="s">
+      <c r="I22" s="21" t="s">
         <v>39</v>
       </c>
-      <c r="J22" s="17" t="s">
+      <c r="J22" s="21" t="s">
         <v>41</v>
       </c>
-      <c r="K22" s="17" t="s">
+      <c r="K22" s="21" t="s">
         <v>39</v>
       </c>
-      <c r="L22" s="17" t="s">
+      <c r="L22" s="21" t="s">
         <v>41</v>
       </c>
-      <c r="M22" s="17" t="s">
+      <c r="M22" s="21" t="s">
         <v>39</v>
       </c>
-      <c r="N22" s="17" t="s">
+      <c r="N22" s="21" t="s">
         <v>41</v>
       </c>
-      <c r="O22" s="17" t="s">
+      <c r="O22" s="21" t="s">
         <v>39</v>
       </c>
-      <c r="P22" s="17" t="s">
+      <c r="P22" s="21" t="s">
         <v>41</v>
       </c>
-      <c r="Q22" s="17" t="s">
+      <c r="Q22" s="21" t="s">
         <v>39</v>
       </c>
-      <c r="R22" s="17" t="s">
+      <c r="R22" s="21" t="s">
         <v>41</v>
       </c>
     </row>
     <row r="23" spans="2:20" x14ac:dyDescent="0.25">
-      <c r="B23" s="15">
+      <c r="B23" s="19">
         <v>46146</v>
       </c>
-      <c r="C23" s="19">
+      <c r="C23" s="23">
         <v>2</v>
       </c>
-      <c r="D23" s="19">
+      <c r="D23" s="23">
         <v>28000</v>
       </c>
-      <c r="E23" s="9">
+      <c r="E23" s="10">
         <v>1</v>
       </c>
-      <c r="F23" s="9">
+      <c r="F23" s="10">
         <v>3000</v>
       </c>
-      <c r="G23" s="9">
+      <c r="G23" s="10">
         <v>1</v>
       </c>
-      <c r="H23" s="9">
+      <c r="H23" s="10">
         <v>1000</v>
       </c>
-      <c r="I23" s="9">
+      <c r="I23" s="10">
         <v>1</v>
       </c>
-      <c r="J23" s="9">
+      <c r="J23" s="10">
         <v>18000</v>
       </c>
-      <c r="K23" s="9"/>
-      <c r="L23" s="9"/>
-      <c r="M23" s="9"/>
-      <c r="N23" s="9"/>
-      <c r="O23" s="9"/>
-      <c r="P23" s="9"/>
-      <c r="Q23" s="9"/>
-      <c r="R23" s="9"/>
-      <c r="S23" s="9">
+      <c r="K23" s="10"/>
+      <c r="L23" s="10"/>
+      <c r="M23" s="10"/>
+      <c r="N23" s="10"/>
+      <c r="O23" s="10"/>
+      <c r="P23" s="10"/>
+      <c r="Q23" s="10"/>
+      <c r="R23" s="10"/>
+      <c r="S23" s="10">
         <v>5</v>
       </c>
-      <c r="T23" s="9">
+      <c r="T23" s="10">
         <v>50000</v>
       </c>
     </row>
     <row r="24" spans="2:20" x14ac:dyDescent="0.25">
-      <c r="B24" s="15">
+      <c r="B24" s="19">
         <v>46147</v>
       </c>
-      <c r="C24" s="21">
+      <c r="C24" s="25">
         <v>4</v>
       </c>
-      <c r="D24" s="21">
+      <c r="D24" s="25">
         <v>64000</v>
       </c>
-      <c r="E24" s="9">
+      <c r="E24" s="10">
         <v>1</v>
       </c>
-      <c r="F24" s="9">
+      <c r="F24" s="10">
         <v>3000</v>
       </c>
-      <c r="G24" s="9"/>
-      <c r="H24" s="9"/>
-      <c r="I24" s="9"/>
-      <c r="J24" s="9"/>
-      <c r="K24" s="9">
+      <c r="G24" s="10"/>
+      <c r="H24" s="10"/>
+      <c r="I24" s="10"/>
+      <c r="J24" s="10"/>
+      <c r="K24" s="10">
         <v>1</v>
       </c>
-      <c r="L24" s="9">
+      <c r="L24" s="10">
         <v>10000</v>
       </c>
-      <c r="M24" s="9">
+      <c r="M24" s="10">
         <v>1</v>
       </c>
-      <c r="N24" s="9">
+      <c r="N24" s="10">
         <v>1000</v>
       </c>
-      <c r="O24" s="9">
+      <c r="O24" s="10">
         <v>1</v>
       </c>
-      <c r="P24" s="9">
+      <c r="P24" s="10">
         <v>3000</v>
       </c>
-      <c r="Q24" s="9"/>
-      <c r="R24" s="9"/>
-      <c r="S24" s="9">
+      <c r="Q24" s="10"/>
+      <c r="R24" s="10"/>
+      <c r="S24" s="10">
         <v>8</v>
       </c>
-      <c r="T24" s="9">
+      <c r="T24" s="10">
         <v>81000</v>
       </c>
     </row>
     <row r="25" spans="2:20" x14ac:dyDescent="0.25">
-      <c r="B25" s="15">
+      <c r="B25" s="19">
         <v>46148</v>
       </c>
-      <c r="C25" s="9">
+      <c r="C25" s="10">
         <v>1</v>
       </c>
-      <c r="D25" s="9">
+      <c r="D25" s="10">
         <v>18000</v>
       </c>
-      <c r="E25" s="9"/>
-      <c r="F25" s="9"/>
-      <c r="G25" s="9"/>
-      <c r="H25" s="9"/>
-      <c r="I25" s="9"/>
-      <c r="J25" s="9"/>
-      <c r="K25" s="9"/>
-      <c r="L25" s="9"/>
-      <c r="M25" s="9"/>
-      <c r="N25" s="9"/>
-      <c r="O25" s="9"/>
-      <c r="P25" s="9"/>
-      <c r="Q25" s="9">
+      <c r="E25" s="10"/>
+      <c r="F25" s="10"/>
+      <c r="G25" s="10"/>
+      <c r="H25" s="10"/>
+      <c r="I25" s="10"/>
+      <c r="J25" s="10"/>
+      <c r="K25" s="10"/>
+      <c r="L25" s="10"/>
+      <c r="M25" s="10"/>
+      <c r="N25" s="10"/>
+      <c r="O25" s="10"/>
+      <c r="P25" s="10"/>
+      <c r="Q25" s="10">
         <v>1</v>
       </c>
-      <c r="R25" s="9">
+      <c r="R25" s="10">
         <v>18000</v>
       </c>
-      <c r="S25" s="9">
+      <c r="S25" s="10">
         <v>2</v>
       </c>
-      <c r="T25" s="9">
+      <c r="T25" s="10">
         <v>36000</v>
       </c>
     </row>
     <row r="26" spans="2:20" x14ac:dyDescent="0.25">
-      <c r="B26" s="15" t="s">
+      <c r="B26" s="19" t="s">
         <v>40</v>
       </c>
-      <c r="C26" s="9">
+      <c r="C26" s="10">
         <v>7</v>
       </c>
-      <c r="D26" s="9">
+      <c r="D26" s="10">
         <v>110000</v>
       </c>
-      <c r="E26" s="9">
+      <c r="E26" s="10">
         <v>2</v>
       </c>
-      <c r="F26" s="9">
+      <c r="F26" s="10">
         <v>6000</v>
       </c>
-      <c r="G26" s="9">
+      <c r="G26" s="10">
         <v>1</v>
       </c>
-      <c r="H26" s="9">
+      <c r="H26" s="10">
         <v>1000</v>
       </c>
-      <c r="I26" s="9">
+      <c r="I26" s="10">
         <v>1</v>
       </c>
-      <c r="J26" s="9">
+      <c r="J26" s="10">
         <v>18000</v>
       </c>
-      <c r="K26" s="9">
+      <c r="K26" s="10">
         <v>1</v>
       </c>
-      <c r="L26" s="9">
+      <c r="L26" s="10">
         <v>10000</v>
       </c>
-      <c r="M26" s="9">
+      <c r="M26" s="10">
         <v>1</v>
       </c>
-      <c r="N26" s="9">
+      <c r="N26" s="10">
         <v>1000</v>
       </c>
-      <c r="O26" s="9">
+      <c r="O26" s="10">
         <v>1</v>
       </c>
-      <c r="P26" s="9">
+      <c r="P26" s="10">
         <v>3000</v>
       </c>
-      <c r="Q26" s="9">
+      <c r="Q26" s="10">
         <v>1</v>
       </c>
-      <c r="R26" s="9">
+      <c r="R26" s="10">
         <v>18000</v>
       </c>
-      <c r="S26" s="9">
+      <c r="S26" s="10">
         <v>15</v>
       </c>
-      <c r="T26" s="9">
+      <c r="T26" s="10">
         <v>167000</v>
       </c>
     </row>
@@ -7507,7 +7594,7 @@
         <v>1</v>
       </c>
       <c r="D2" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E2" t="s">
         <v>2</v>
@@ -7521,322 +7608,322 @@
       <c r="H2" t="s">
         <v>5</v>
       </c>
-      <c r="J2" s="12" t="s">
+      <c r="J2" s="16" t="s">
+        <v>117</v>
+      </c>
+      <c r="K2" s="16"/>
+      <c r="L2" s="16"/>
+      <c r="N2" s="16" t="s">
         <v>118</v>
       </c>
-      <c r="K2" s="12"/>
-      <c r="L2" s="12"/>
-      <c r="N2" s="12" t="s">
-        <v>119</v>
-      </c>
-      <c r="O2" s="12"/>
-      <c r="P2" s="12"/>
+      <c r="O2" s="16"/>
+      <c r="P2" s="16"/>
     </row>
     <row r="3" spans="2:16" ht="45" x14ac:dyDescent="0.25">
-      <c r="B3" s="9" t="s">
+      <c r="B3" s="10" t="s">
+        <v>82</v>
+      </c>
+      <c r="C3" s="6">
+        <v>46149</v>
+      </c>
+      <c r="D3" s="10" t="s">
         <v>83</v>
       </c>
-      <c r="C3" s="5">
-        <v>46149</v>
-      </c>
-      <c r="D3" s="9" t="s">
+      <c r="E3" s="10" t="s">
         <v>84</v>
       </c>
-      <c r="E3" s="9" t="s">
-        <v>85</v>
-      </c>
-      <c r="F3" s="9" t="s">
+      <c r="F3" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="G3" s="9" t="s">
+      <c r="G3" s="10" t="s">
         <v>26</v>
       </c>
       <c r="H3">
         <v>18000</v>
       </c>
-      <c r="J3" s="18" t="s">
+      <c r="J3" s="22" t="s">
         <v>38</v>
       </c>
-      <c r="K3" s="17" t="s">
+      <c r="K3" s="21" t="s">
         <v>39</v>
       </c>
-      <c r="L3" s="17" t="s">
+      <c r="L3" s="21" t="s">
         <v>41</v>
       </c>
-      <c r="M3" s="17"/>
-      <c r="N3" s="18" t="s">
+      <c r="M3" s="21"/>
+      <c r="N3" s="22" t="s">
         <v>38</v>
       </c>
-      <c r="O3" s="17" t="s">
+      <c r="O3" s="21" t="s">
         <v>39</v>
       </c>
-      <c r="P3" s="17" t="s">
+      <c r="P3" s="21" t="s">
         <v>41</v>
       </c>
     </row>
     <row r="4" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="B4" s="9" t="s">
+      <c r="B4" s="10" t="s">
+        <v>85</v>
+      </c>
+      <c r="C4" s="6">
+        <v>46149</v>
+      </c>
+      <c r="D4" s="10" t="s">
         <v>86</v>
       </c>
-      <c r="C4" s="5">
-        <v>46149</v>
-      </c>
-      <c r="D4" s="9" t="s">
+      <c r="E4" s="10" t="s">
         <v>87</v>
       </c>
-      <c r="E4" s="9" t="s">
-        <v>88</v>
-      </c>
-      <c r="F4" s="9" t="s">
+      <c r="F4" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="G4" s="9" t="s">
+      <c r="G4" s="10" t="s">
         <v>15</v>
       </c>
       <c r="H4">
         <v>3000</v>
       </c>
-      <c r="J4" s="8" t="s">
-        <v>84</v>
-      </c>
-      <c r="K4" s="9">
+      <c r="J4" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="K4" s="10">
         <v>5</v>
       </c>
-      <c r="L4" s="9">
+      <c r="L4" s="10">
         <v>82000</v>
       </c>
-      <c r="N4" s="8" t="s">
+      <c r="N4" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="O4" s="9">
+      <c r="O4" s="10">
         <v>5</v>
       </c>
-      <c r="P4" s="9">
+      <c r="P4" s="10">
         <v>82000</v>
       </c>
     </row>
     <row r="5" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="B5" s="9" t="s">
+      <c r="B5" s="10" t="s">
+        <v>88</v>
+      </c>
+      <c r="C5" s="6">
+        <v>46149</v>
+      </c>
+      <c r="D5" s="10" t="s">
+        <v>83</v>
+      </c>
+      <c r="E5" s="10" t="s">
         <v>89</v>
       </c>
-      <c r="C5" s="5">
-        <v>46149</v>
-      </c>
-      <c r="D5" s="9" t="s">
-        <v>84</v>
-      </c>
-      <c r="E5" s="9" t="s">
-        <v>90</v>
-      </c>
-      <c r="F5" s="9" t="s">
+      <c r="F5" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="G5" s="9" t="s">
+      <c r="G5" s="10" t="s">
         <v>10</v>
       </c>
       <c r="H5">
         <v>10000</v>
       </c>
-      <c r="J5" s="8" t="s">
-        <v>95</v>
-      </c>
-      <c r="K5" s="9">
+      <c r="J5" s="9" t="s">
+        <v>94</v>
+      </c>
+      <c r="K5" s="10">
         <v>2</v>
       </c>
-      <c r="L5" s="9">
+      <c r="L5" s="10">
         <v>36000</v>
       </c>
-      <c r="N5" s="8" t="s">
+      <c r="N5" s="9" t="s">
         <v>25</v>
       </c>
-      <c r="O5" s="9">
+      <c r="O5" s="10">
         <v>2</v>
       </c>
-      <c r="P5" s="9">
+      <c r="P5" s="10">
         <v>36000</v>
       </c>
     </row>
     <row r="6" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="B6" s="9" t="s">
+      <c r="B6" s="10" t="s">
+        <v>90</v>
+      </c>
+      <c r="C6" s="6">
+        <v>46149</v>
+      </c>
+      <c r="D6" s="10" t="s">
         <v>91</v>
       </c>
-      <c r="C6" s="5">
-        <v>46149</v>
-      </c>
-      <c r="D6" s="9" t="s">
+      <c r="E6" s="10" t="s">
         <v>92</v>
       </c>
-      <c r="E6" s="9" t="s">
-        <v>93</v>
-      </c>
-      <c r="F6" s="9" t="s">
+      <c r="F6" s="10" t="s">
         <v>31</v>
       </c>
-      <c r="G6" s="9" t="s">
+      <c r="G6" s="10" t="s">
         <v>22</v>
       </c>
       <c r="H6">
         <v>1000</v>
       </c>
-      <c r="J6" s="8" t="s">
-        <v>106</v>
-      </c>
-      <c r="K6" s="9">
+      <c r="J6" s="9" t="s">
+        <v>105</v>
+      </c>
+      <c r="K6" s="10">
         <v>2</v>
       </c>
-      <c r="L6" s="9">
+      <c r="L6" s="10">
         <v>20000</v>
       </c>
-      <c r="N6" s="8" t="s">
+      <c r="N6" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="O6" s="9">
+      <c r="O6" s="10">
         <v>2</v>
       </c>
-      <c r="P6" s="9">
+      <c r="P6" s="10">
         <v>20000</v>
       </c>
     </row>
     <row r="7" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="B7" s="9" t="s">
+      <c r="B7" s="10" t="s">
+        <v>93</v>
+      </c>
+      <c r="C7" s="6">
+        <v>46149</v>
+      </c>
+      <c r="D7" s="10" t="s">
         <v>94</v>
       </c>
-      <c r="C7" s="5">
-        <v>46149</v>
-      </c>
-      <c r="D7" s="9" t="s">
+      <c r="E7" s="10" t="s">
         <v>95</v>
       </c>
-      <c r="E7" s="9" t="s">
-        <v>96</v>
-      </c>
-      <c r="F7" s="9" t="s">
+      <c r="F7" s="10" t="s">
         <v>25</v>
       </c>
-      <c r="G7" s="9" t="s">
+      <c r="G7" s="10" t="s">
         <v>26</v>
       </c>
       <c r="H7">
         <v>18000</v>
       </c>
-      <c r="J7" s="22" t="s">
-        <v>87</v>
-      </c>
-      <c r="K7" s="9">
+      <c r="J7" s="26" t="s">
+        <v>86</v>
+      </c>
+      <c r="K7" s="10">
         <v>3</v>
       </c>
-      <c r="L7" s="9">
+      <c r="L7" s="10">
         <v>9000</v>
       </c>
-      <c r="N7" s="8" t="s">
+      <c r="N7" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="O7" s="9">
+      <c r="O7" s="10">
         <v>3</v>
       </c>
-      <c r="P7" s="9">
+      <c r="P7" s="10">
         <v>9000</v>
       </c>
     </row>
     <row r="8" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="B8" s="9" t="s">
+      <c r="B8" s="10" t="s">
+        <v>96</v>
+      </c>
+      <c r="C8" s="6">
+        <v>46150</v>
+      </c>
+      <c r="D8" s="10" t="s">
+        <v>83</v>
+      </c>
+      <c r="E8" s="10" t="s">
         <v>97</v>
       </c>
-      <c r="C8" s="5">
-        <v>46150</v>
-      </c>
-      <c r="D8" s="9" t="s">
-        <v>84</v>
-      </c>
-      <c r="E8" s="9" t="s">
-        <v>98</v>
-      </c>
-      <c r="F8" s="9" t="s">
+      <c r="F8" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="G8" s="9" t="s">
+      <c r="G8" s="10" t="s">
         <v>26</v>
       </c>
       <c r="H8">
         <v>18000</v>
       </c>
-      <c r="J8" s="22" t="s">
-        <v>92</v>
-      </c>
-      <c r="K8" s="9">
+      <c r="J8" s="26" t="s">
+        <v>91</v>
+      </c>
+      <c r="K8" s="10">
         <v>3</v>
       </c>
-      <c r="L8" s="9">
+      <c r="L8" s="10">
         <v>3000</v>
       </c>
-      <c r="N8" s="8" t="s">
+      <c r="N8" s="9" t="s">
         <v>31</v>
       </c>
-      <c r="O8" s="9">
+      <c r="O8" s="10">
         <v>3</v>
       </c>
-      <c r="P8" s="9">
+      <c r="P8" s="10">
         <v>3000</v>
       </c>
     </row>
     <row r="9" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="B9" s="9" t="s">
+      <c r="B9" s="10" t="s">
+        <v>98</v>
+      </c>
+      <c r="C9" s="6">
+        <v>46150</v>
+      </c>
+      <c r="D9" s="10" t="s">
+        <v>86</v>
+      </c>
+      <c r="E9" s="10" t="s">
         <v>99</v>
       </c>
-      <c r="C9" s="5">
-        <v>46150</v>
-      </c>
-      <c r="D9" s="9" t="s">
-        <v>87</v>
-      </c>
-      <c r="E9" s="9" t="s">
-        <v>100</v>
-      </c>
-      <c r="F9" s="9" t="s">
+      <c r="F9" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="G9" s="9" t="s">
+      <c r="G9" s="10" t="s">
         <v>15</v>
       </c>
       <c r="H9">
         <v>3000</v>
       </c>
-      <c r="J9" s="8" t="s">
+      <c r="J9" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="K9" s="9">
+      <c r="K9" s="10">
         <v>15</v>
       </c>
-      <c r="L9" s="9">
+      <c r="L9" s="10">
         <v>150000</v>
       </c>
-      <c r="N9" s="8" t="s">
+      <c r="N9" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="O9" s="9">
+      <c r="O9" s="10">
         <v>15</v>
       </c>
-      <c r="P9" s="9">
+      <c r="P9" s="10">
         <v>150000</v>
       </c>
     </row>
     <row r="10" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="B10" s="9" t="s">
+      <c r="B10" s="10" t="s">
+        <v>100</v>
+      </c>
+      <c r="C10" s="6">
+        <v>46150</v>
+      </c>
+      <c r="D10" s="10" t="s">
+        <v>91</v>
+      </c>
+      <c r="E10" s="10" t="s">
         <v>101</v>
       </c>
-      <c r="C10" s="5">
-        <v>46150</v>
-      </c>
-      <c r="D10" s="9" t="s">
-        <v>92</v>
-      </c>
-      <c r="E10" s="9" t="s">
-        <v>102</v>
-      </c>
-      <c r="F10" s="9" t="s">
+      <c r="F10" s="10" t="s">
         <v>31</v>
       </c>
-      <c r="G10" s="9" t="s">
+      <c r="G10" s="10" t="s">
         <v>22</v>
       </c>
       <c r="H10">
@@ -7844,57 +7931,57 @@
       </c>
     </row>
     <row r="11" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="B11" s="9" t="s">
+      <c r="B11" s="10" t="s">
+        <v>102</v>
+      </c>
+      <c r="C11" s="6">
+        <v>46150</v>
+      </c>
+      <c r="D11" s="10" t="s">
+        <v>83</v>
+      </c>
+      <c r="E11" s="10" t="s">
         <v>103</v>
       </c>
-      <c r="C11" s="5">
-        <v>46150</v>
-      </c>
-      <c r="D11" s="9" t="s">
-        <v>84</v>
-      </c>
-      <c r="E11" s="9" t="s">
-        <v>104</v>
-      </c>
-      <c r="F11" s="9" t="s">
+      <c r="F11" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="G11" s="9" t="s">
+      <c r="G11" s="10" t="s">
         <v>26</v>
       </c>
       <c r="H11">
         <v>18000</v>
       </c>
-      <c r="J11" s="7" t="s">
+      <c r="J11" s="8" t="s">
         <v>41</v>
       </c>
-      <c r="K11" s="7" t="s">
+      <c r="K11" s="8" t="s">
         <v>42</v>
       </c>
     </row>
     <row r="12" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="B12" s="9" t="s">
+      <c r="B12" s="10" t="s">
+        <v>104</v>
+      </c>
+      <c r="C12" s="6">
+        <v>46150</v>
+      </c>
+      <c r="D12" s="10" t="s">
         <v>105</v>
       </c>
-      <c r="C12" s="5">
-        <v>46150</v>
-      </c>
-      <c r="D12" s="9" t="s">
+      <c r="E12" s="10" t="s">
         <v>106</v>
       </c>
-      <c r="E12" s="9" t="s">
-        <v>107</v>
-      </c>
-      <c r="F12" s="9" t="s">
+      <c r="F12" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="G12" s="9" t="s">
+      <c r="G12" s="10" t="s">
         <v>10</v>
       </c>
       <c r="H12">
         <v>10000</v>
       </c>
-      <c r="J12" s="7" t="s">
+      <c r="J12" s="8" t="s">
         <v>38</v>
       </c>
       <c r="K12" t="s">
@@ -7917,198 +8004,198 @@
       </c>
     </row>
     <row r="13" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="B13" s="9" t="s">
+      <c r="B13" s="10" t="s">
+        <v>107</v>
+      </c>
+      <c r="C13" s="6">
+        <v>46151</v>
+      </c>
+      <c r="D13" s="10" t="s">
+        <v>83</v>
+      </c>
+      <c r="E13" s="10" t="s">
         <v>108</v>
       </c>
-      <c r="C13" s="5">
-        <v>46151</v>
-      </c>
-      <c r="D13" s="9" t="s">
-        <v>84</v>
-      </c>
-      <c r="E13" s="9" t="s">
-        <v>109</v>
-      </c>
-      <c r="F13" s="9" t="s">
+      <c r="F13" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="G13" s="9" t="s">
+      <c r="G13" s="10" t="s">
         <v>26</v>
       </c>
       <c r="H13">
         <v>18000</v>
       </c>
-      <c r="J13" s="8" t="s">
+      <c r="J13" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="K13" s="9">
+      <c r="K13" s="10">
         <v>72000</v>
       </c>
-      <c r="L13" s="9"/>
-      <c r="M13" s="9"/>
-      <c r="N13" s="9"/>
-      <c r="O13" s="9">
+      <c r="L13" s="10"/>
+      <c r="M13" s="10"/>
+      <c r="N13" s="10"/>
+      <c r="O13" s="10">
         <v>36000</v>
       </c>
-      <c r="P13" s="9">
+      <c r="P13" s="10">
         <v>108000</v>
       </c>
     </row>
     <row r="14" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="B14" s="9" t="s">
+      <c r="B14" s="10" t="s">
+        <v>109</v>
+      </c>
+      <c r="C14" s="6">
+        <v>46151</v>
+      </c>
+      <c r="D14" s="10" t="s">
+        <v>86</v>
+      </c>
+      <c r="E14" s="10" t="s">
         <v>110</v>
       </c>
-      <c r="C14" s="5">
-        <v>46151</v>
-      </c>
-      <c r="D14" s="9" t="s">
-        <v>87</v>
-      </c>
-      <c r="E14" s="9" t="s">
-        <v>111</v>
-      </c>
-      <c r="F14" s="9" t="s">
+      <c r="F14" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="G14" s="9" t="s">
+      <c r="G14" s="10" t="s">
         <v>15</v>
       </c>
       <c r="H14">
         <v>3000</v>
       </c>
-      <c r="J14" s="8" t="s">
+      <c r="J14" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="K14" s="9">
+      <c r="K14" s="10">
         <v>10000</v>
       </c>
-      <c r="L14" s="9"/>
-      <c r="M14" s="9"/>
-      <c r="N14" s="9">
+      <c r="L14" s="10"/>
+      <c r="M14" s="10"/>
+      <c r="N14" s="10">
         <v>20000</v>
       </c>
-      <c r="O14" s="9"/>
-      <c r="P14" s="9">
+      <c r="O14" s="10"/>
+      <c r="P14" s="10">
         <v>30000</v>
       </c>
     </row>
     <row r="15" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="B15" s="9" t="s">
+      <c r="B15" s="10" t="s">
+        <v>111</v>
+      </c>
+      <c r="C15" s="6">
+        <v>46151</v>
+      </c>
+      <c r="D15" s="10" t="s">
+        <v>91</v>
+      </c>
+      <c r="E15" s="10" t="s">
         <v>112</v>
       </c>
-      <c r="C15" s="5">
-        <v>46151</v>
-      </c>
-      <c r="D15" s="9" t="s">
-        <v>92</v>
-      </c>
-      <c r="E15" s="9" t="s">
-        <v>113</v>
-      </c>
-      <c r="F15" s="9" t="s">
+      <c r="F15" s="10" t="s">
         <v>31</v>
       </c>
-      <c r="G15" s="9" t="s">
+      <c r="G15" s="10" t="s">
         <v>22</v>
       </c>
       <c r="H15">
         <v>1000</v>
       </c>
-      <c r="J15" s="8" t="s">
+      <c r="J15" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="K15" s="9"/>
-      <c r="L15" s="9"/>
-      <c r="M15" s="9">
+      <c r="K15" s="10"/>
+      <c r="L15" s="10"/>
+      <c r="M15" s="10">
         <v>3000</v>
       </c>
-      <c r="N15" s="9"/>
-      <c r="O15" s="9"/>
-      <c r="P15" s="9">
+      <c r="N15" s="10"/>
+      <c r="O15" s="10"/>
+      <c r="P15" s="10">
         <v>3000</v>
       </c>
     </row>
     <row r="16" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="B16" s="9" t="s">
+      <c r="B16" s="10" t="s">
+        <v>113</v>
+      </c>
+      <c r="C16" s="6">
+        <v>46151</v>
+      </c>
+      <c r="D16" s="10" t="s">
+        <v>94</v>
+      </c>
+      <c r="E16" s="10" t="s">
         <v>114</v>
       </c>
-      <c r="C16" s="5">
-        <v>46151</v>
-      </c>
-      <c r="D16" s="9" t="s">
-        <v>95</v>
-      </c>
-      <c r="E16" s="9" t="s">
-        <v>115</v>
-      </c>
-      <c r="F16" s="9" t="s">
+      <c r="F16" s="10" t="s">
         <v>25</v>
       </c>
-      <c r="G16" s="9" t="s">
+      <c r="G16" s="10" t="s">
         <v>26</v>
       </c>
       <c r="H16">
         <v>18000</v>
       </c>
-      <c r="J16" s="8" t="s">
+      <c r="J16" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="K16" s="9"/>
-      <c r="L16" s="9">
+      <c r="K16" s="10"/>
+      <c r="L16" s="10">
         <v>9000</v>
       </c>
-      <c r="M16" s="9"/>
-      <c r="N16" s="9"/>
-      <c r="O16" s="9"/>
-      <c r="P16" s="9">
+      <c r="M16" s="10"/>
+      <c r="N16" s="10"/>
+      <c r="O16" s="10"/>
+      <c r="P16" s="10">
         <v>9000</v>
       </c>
     </row>
     <row r="17" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="B17" s="9" t="s">
+      <c r="B17" s="10" t="s">
+        <v>115</v>
+      </c>
+      <c r="C17" s="6">
+        <v>46151</v>
+      </c>
+      <c r="D17" s="10" t="s">
+        <v>105</v>
+      </c>
+      <c r="E17" s="10" t="s">
         <v>116</v>
       </c>
-      <c r="C17" s="5">
-        <v>46151</v>
-      </c>
-      <c r="D17" s="9" t="s">
-        <v>106</v>
-      </c>
-      <c r="E17" s="9" t="s">
-        <v>117</v>
-      </c>
-      <c r="F17" s="9" t="s">
+      <c r="F17" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="G17" s="9" t="s">
+      <c r="G17" s="10" t="s">
         <v>10</v>
       </c>
       <c r="H17">
         <v>10000</v>
       </c>
-      <c r="J17" s="8" t="s">
+      <c r="J17" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="K17" s="9">
+      <c r="K17" s="10">
         <v>82000</v>
       </c>
-      <c r="L17" s="9">
+      <c r="L17" s="10">
         <v>9000</v>
       </c>
-      <c r="M17" s="9">
+      <c r="M17" s="10">
         <v>3000</v>
       </c>
-      <c r="N17" s="9">
+      <c r="N17" s="10">
         <v>20000</v>
       </c>
-      <c r="O17" s="9">
+      <c r="O17" s="10">
         <v>36000</v>
       </c>
-      <c r="P17" s="9">
+      <c r="P17" s="10">
         <v>150000</v>
       </c>
     </row>
-    <row r="20" spans="2:16" s="17" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="2:16" s="21" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B20"/>
       <c r="C20"/>
       <c r="D20"/>
@@ -8119,22 +8206,22 @@
     <mergeCell ref="N2:P2"/>
   </mergeCells>
   <conditionalFormatting pivot="1" sqref="L4:L8">
-    <cfRule type="cellIs" dxfId="53" priority="5" operator="lessThan">
+    <cfRule type="cellIs" dxfId="9" priority="5" operator="lessThan">
       <formula>10000</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting pivot="1" sqref="P4:P8">
-    <cfRule type="cellIs" dxfId="52" priority="4" operator="lessThan">
+    <cfRule type="cellIs" dxfId="8" priority="4" operator="lessThan">
       <formula>$Q$4</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting pivot="1" sqref="P4:P9">
-    <cfRule type="cellIs" dxfId="51" priority="3" operator="lessThan">
+    <cfRule type="cellIs" dxfId="7" priority="3" operator="lessThan">
       <formula>30000</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J7:J8">
-    <cfRule type="cellIs" dxfId="49" priority="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="5" priority="1" operator="lessThan">
       <formula>10000</formula>
     </cfRule>
   </conditionalFormatting>
@@ -8195,135 +8282,135 @@
       <c r="G2" t="s">
         <v>5</v>
       </c>
-      <c r="I2" s="7" t="s">
+      <c r="I2" s="8" t="s">
         <v>41</v>
       </c>
-      <c r="J2" s="7" t="s">
+      <c r="J2" s="8" t="s">
         <v>42</v>
       </c>
     </row>
     <row r="3" spans="2:27" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B3" s="9" t="s">
+      <c r="B3" s="10" t="s">
+        <v>119</v>
+      </c>
+      <c r="C3" s="6">
+        <v>46152</v>
+      </c>
+      <c r="D3" s="10" t="s">
         <v>120</v>
       </c>
-      <c r="C3" s="5">
-        <v>46152</v>
-      </c>
-      <c r="D3" s="9" t="s">
-        <v>121</v>
-      </c>
-      <c r="E3" s="9" t="s">
+      <c r="E3" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="F3" s="9" t="s">
+      <c r="F3" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G3">
         <v>18000</v>
       </c>
-      <c r="I3" s="18" t="s">
+      <c r="I3" s="22" t="s">
         <v>38</v>
       </c>
       <c r="J3" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="K3" t="s">
+        <v>121</v>
+      </c>
+      <c r="L3" t="s">
+        <v>123</v>
+      </c>
+      <c r="M3" t="s">
+        <v>125</v>
+      </c>
+      <c r="N3" t="s">
+        <v>126</v>
+      </c>
+      <c r="O3" t="s">
+        <v>128</v>
+      </c>
+      <c r="P3" t="s">
+        <v>130</v>
+      </c>
+      <c r="Q3" t="s">
+        <v>131</v>
+      </c>
+      <c r="R3" t="s">
+        <v>132</v>
+      </c>
+      <c r="S3" t="s">
+        <v>134</v>
+      </c>
+      <c r="T3" t="s">
+        <v>135</v>
+      </c>
+      <c r="U3" t="s">
+        <v>136</v>
+      </c>
+      <c r="V3" t="s">
+        <v>138</v>
+      </c>
+      <c r="W3" t="s">
+        <v>139</v>
+      </c>
+      <c r="X3" t="s">
+        <v>141</v>
+      </c>
+      <c r="Y3" s="21" t="s">
+        <v>40</v>
+      </c>
+      <c r="AA3" s="29" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="4" spans="2:27" x14ac:dyDescent="0.25">
+      <c r="B4" s="10" t="s">
+        <v>121</v>
+      </c>
+      <c r="C4" s="6">
+        <v>46152</v>
+      </c>
+      <c r="D4" s="10" t="s">
         <v>122</v>
       </c>
-      <c r="L3" t="s">
-        <v>124</v>
-      </c>
-      <c r="M3" t="s">
-        <v>126</v>
-      </c>
-      <c r="N3" t="s">
-        <v>127</v>
-      </c>
-      <c r="O3" t="s">
-        <v>129</v>
-      </c>
-      <c r="P3" t="s">
-        <v>131</v>
-      </c>
-      <c r="Q3" t="s">
-        <v>132</v>
-      </c>
-      <c r="R3" t="s">
-        <v>133</v>
-      </c>
-      <c r="S3" t="s">
-        <v>135</v>
-      </c>
-      <c r="T3" t="s">
-        <v>136</v>
-      </c>
-      <c r="U3" t="s">
-        <v>137</v>
-      </c>
-      <c r="V3" t="s">
-        <v>139</v>
-      </c>
-      <c r="W3" t="s">
-        <v>140</v>
-      </c>
-      <c r="X3" t="s">
-        <v>142</v>
-      </c>
-      <c r="Y3" s="17" t="s">
-        <v>40</v>
-      </c>
-      <c r="AA3" s="25" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="4" spans="2:27" x14ac:dyDescent="0.25">
-      <c r="B4" s="9" t="s">
-        <v>122</v>
-      </c>
-      <c r="C4" s="5">
-        <v>46152</v>
-      </c>
-      <c r="D4" s="9" t="s">
-        <v>123</v>
-      </c>
-      <c r="E4" s="9" t="s">
+      <c r="E4" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="F4" s="9" t="s">
+      <c r="F4" s="10" t="s">
         <v>15</v>
       </c>
       <c r="G4">
         <v>3000</v>
       </c>
-      <c r="I4" s="8" t="s">
-        <v>121</v>
-      </c>
-      <c r="J4" s="9">
+      <c r="I4" s="9" t="s">
+        <v>120</v>
+      </c>
+      <c r="J4" s="10">
         <v>18000</v>
       </c>
-      <c r="K4" s="9"/>
-      <c r="L4" s="9"/>
-      <c r="M4" s="9">
+      <c r="K4" s="10"/>
+      <c r="L4" s="10"/>
+      <c r="M4" s="10">
         <v>18000</v>
       </c>
-      <c r="N4" s="9"/>
-      <c r="O4" s="9"/>
-      <c r="P4" s="9">
+      <c r="N4" s="10"/>
+      <c r="O4" s="10"/>
+      <c r="P4" s="10">
         <v>10000</v>
       </c>
-      <c r="Q4" s="9"/>
-      <c r="R4" s="9"/>
-      <c r="S4" s="9">
+      <c r="Q4" s="10"/>
+      <c r="R4" s="10"/>
+      <c r="S4" s="10">
         <v>18000</v>
       </c>
-      <c r="T4" s="9"/>
-      <c r="U4" s="9"/>
-      <c r="V4" s="9">
+      <c r="T4" s="10"/>
+      <c r="U4" s="10"/>
+      <c r="V4" s="10">
         <v>18000</v>
       </c>
-      <c r="W4" s="9"/>
-      <c r="X4" s="9"/>
-      <c r="Y4" s="9">
+      <c r="W4" s="10"/>
+      <c r="X4" s="10"/>
+      <c r="Y4" s="10">
         <v>82000</v>
       </c>
       <c r="AA4">
@@ -8332,49 +8419,49 @@
       </c>
     </row>
     <row r="5" spans="2:27" x14ac:dyDescent="0.25">
-      <c r="B5" s="9" t="s">
+      <c r="B5" s="10" t="s">
+        <v>123</v>
+      </c>
+      <c r="C5" s="6">
+        <v>46152</v>
+      </c>
+      <c r="D5" s="10" t="s">
         <v>124</v>
       </c>
-      <c r="C5" s="5">
-        <v>46152</v>
-      </c>
-      <c r="D5" s="9" t="s">
-        <v>125</v>
-      </c>
-      <c r="E5" s="9" t="s">
+      <c r="E5" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="F5" s="9" t="s">
+      <c r="F5" s="10" t="s">
         <v>10</v>
       </c>
       <c r="G5">
         <v>10000</v>
       </c>
-      <c r="I5" s="8" t="s">
-        <v>123</v>
-      </c>
-      <c r="J5" s="9"/>
-      <c r="K5" s="9">
+      <c r="I5" s="9" t="s">
+        <v>122</v>
+      </c>
+      <c r="J5" s="10"/>
+      <c r="K5" s="10">
         <v>3000</v>
       </c>
-      <c r="L5" s="9"/>
-      <c r="M5" s="9"/>
-      <c r="N5" s="9"/>
-      <c r="O5" s="9"/>
-      <c r="P5" s="9"/>
-      <c r="Q5" s="9">
+      <c r="L5" s="10"/>
+      <c r="M5" s="10"/>
+      <c r="N5" s="10"/>
+      <c r="O5" s="10"/>
+      <c r="P5" s="10"/>
+      <c r="Q5" s="10">
         <v>3000</v>
       </c>
-      <c r="R5" s="9"/>
-      <c r="S5" s="9"/>
-      <c r="T5" s="9"/>
-      <c r="U5" s="9"/>
-      <c r="V5" s="9"/>
-      <c r="W5" s="9"/>
-      <c r="X5" s="9">
+      <c r="R5" s="10"/>
+      <c r="S5" s="10"/>
+      <c r="T5" s="10"/>
+      <c r="U5" s="10"/>
+      <c r="V5" s="10"/>
+      <c r="W5" s="10"/>
+      <c r="X5" s="10">
         <v>3000</v>
       </c>
-      <c r="Y5" s="9">
+      <c r="Y5" s="10">
         <v>9000</v>
       </c>
       <c r="AA5">
@@ -8383,47 +8470,47 @@
       </c>
     </row>
     <row r="6" spans="2:27" x14ac:dyDescent="0.25">
-      <c r="B6" s="9" t="s">
-        <v>126</v>
-      </c>
-      <c r="C6" s="5">
+      <c r="B6" s="10" t="s">
+        <v>125</v>
+      </c>
+      <c r="C6" s="6">
         <v>46153</v>
       </c>
-      <c r="D6" s="9" t="s">
-        <v>121</v>
-      </c>
-      <c r="E6" s="9" t="s">
+      <c r="D6" s="10" t="s">
+        <v>120</v>
+      </c>
+      <c r="E6" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="F6" s="9" t="s">
+      <c r="F6" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G6">
         <v>18000</v>
       </c>
-      <c r="I6" s="8" t="s">
-        <v>125</v>
-      </c>
-      <c r="J6" s="9"/>
-      <c r="K6" s="9"/>
-      <c r="L6" s="9">
+      <c r="I6" s="9" t="s">
+        <v>124</v>
+      </c>
+      <c r="J6" s="10"/>
+      <c r="K6" s="10"/>
+      <c r="L6" s="10">
         <v>10000</v>
       </c>
-      <c r="M6" s="9"/>
-      <c r="N6" s="9"/>
-      <c r="O6" s="9"/>
-      <c r="P6" s="9"/>
-      <c r="Q6" s="9"/>
-      <c r="R6" s="9"/>
-      <c r="S6" s="9"/>
-      <c r="T6" s="9">
+      <c r="M6" s="10"/>
+      <c r="N6" s="10"/>
+      <c r="O6" s="10"/>
+      <c r="P6" s="10"/>
+      <c r="Q6" s="10"/>
+      <c r="R6" s="10"/>
+      <c r="S6" s="10"/>
+      <c r="T6" s="10">
         <v>10000</v>
       </c>
-      <c r="U6" s="9"/>
-      <c r="V6" s="9"/>
-      <c r="W6" s="9"/>
-      <c r="X6" s="9"/>
-      <c r="Y6" s="9">
+      <c r="U6" s="10"/>
+      <c r="V6" s="10"/>
+      <c r="W6" s="10"/>
+      <c r="X6" s="10"/>
+      <c r="Y6" s="10">
         <v>20000</v>
       </c>
       <c r="AA6">
@@ -8432,45 +8519,45 @@
       </c>
     </row>
     <row r="7" spans="2:27" x14ac:dyDescent="0.25">
-      <c r="B7" s="9" t="s">
+      <c r="B7" s="10" t="s">
+        <v>126</v>
+      </c>
+      <c r="C7" s="6">
+        <v>46153</v>
+      </c>
+      <c r="D7" s="10" t="s">
         <v>127</v>
       </c>
-      <c r="C7" s="5">
-        <v>46153</v>
-      </c>
-      <c r="D7" s="9" t="s">
-        <v>128</v>
-      </c>
-      <c r="E7" s="9" t="s">
+      <c r="E7" s="10" t="s">
         <v>31</v>
       </c>
-      <c r="F7" s="9" t="s">
+      <c r="F7" s="10" t="s">
         <v>22</v>
       </c>
       <c r="G7">
         <v>1000</v>
       </c>
-      <c r="I7" s="8" t="s">
-        <v>128</v>
-      </c>
-      <c r="J7" s="9"/>
-      <c r="K7" s="9"/>
-      <c r="L7" s="9"/>
-      <c r="M7" s="9"/>
-      <c r="N7" s="9">
+      <c r="I7" s="9" t="s">
+        <v>127</v>
+      </c>
+      <c r="J7" s="10"/>
+      <c r="K7" s="10"/>
+      <c r="L7" s="10"/>
+      <c r="M7" s="10"/>
+      <c r="N7" s="10">
         <v>1000</v>
       </c>
-      <c r="O7" s="9"/>
-      <c r="P7" s="9"/>
-      <c r="Q7" s="9"/>
-      <c r="R7" s="9"/>
-      <c r="S7" s="9"/>
-      <c r="T7" s="9"/>
-      <c r="U7" s="9"/>
-      <c r="V7" s="9"/>
-      <c r="W7" s="9"/>
-      <c r="X7" s="9"/>
-      <c r="Y7" s="9">
+      <c r="O7" s="10"/>
+      <c r="P7" s="10"/>
+      <c r="Q7" s="10"/>
+      <c r="R7" s="10"/>
+      <c r="S7" s="10"/>
+      <c r="T7" s="10"/>
+      <c r="U7" s="10"/>
+      <c r="V7" s="10"/>
+      <c r="W7" s="10"/>
+      <c r="X7" s="10"/>
+      <c r="Y7" s="10">
         <v>1000</v>
       </c>
       <c r="AA7">
@@ -8479,45 +8566,45 @@
       </c>
     </row>
     <row r="8" spans="2:27" x14ac:dyDescent="0.25">
-      <c r="B8" s="9" t="s">
+      <c r="B8" s="10" t="s">
+        <v>128</v>
+      </c>
+      <c r="C8" s="6">
+        <v>46153</v>
+      </c>
+      <c r="D8" s="10" t="s">
         <v>129</v>
       </c>
-      <c r="C8" s="5">
-        <v>46153</v>
-      </c>
-      <c r="D8" s="9" t="s">
-        <v>130</v>
-      </c>
-      <c r="E8" s="9" t="s">
+      <c r="E8" s="10" t="s">
         <v>25</v>
       </c>
-      <c r="F8" s="9" t="s">
+      <c r="F8" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G8">
         <v>18000</v>
       </c>
-      <c r="I8" s="8" t="s">
-        <v>130</v>
-      </c>
-      <c r="J8" s="9"/>
-      <c r="K8" s="9"/>
-      <c r="L8" s="9"/>
-      <c r="M8" s="9"/>
-      <c r="N8" s="9"/>
-      <c r="O8" s="9">
+      <c r="I8" s="9" t="s">
+        <v>129</v>
+      </c>
+      <c r="J8" s="10"/>
+      <c r="K8" s="10"/>
+      <c r="L8" s="10"/>
+      <c r="M8" s="10"/>
+      <c r="N8" s="10"/>
+      <c r="O8" s="10">
         <v>18000</v>
       </c>
-      <c r="P8" s="9"/>
-      <c r="Q8" s="9"/>
-      <c r="R8" s="9"/>
-      <c r="S8" s="9"/>
-      <c r="T8" s="9"/>
-      <c r="U8" s="9"/>
-      <c r="V8" s="9"/>
-      <c r="W8" s="9"/>
-      <c r="X8" s="9"/>
-      <c r="Y8" s="9">
+      <c r="P8" s="10"/>
+      <c r="Q8" s="10"/>
+      <c r="R8" s="10"/>
+      <c r="S8" s="10"/>
+      <c r="T8" s="10"/>
+      <c r="U8" s="10"/>
+      <c r="V8" s="10"/>
+      <c r="W8" s="10"/>
+      <c r="X8" s="10"/>
+      <c r="Y8" s="10">
         <v>18000</v>
       </c>
       <c r="AA8">
@@ -8526,45 +8613,45 @@
       </c>
     </row>
     <row r="9" spans="2:27" x14ac:dyDescent="0.25">
-      <c r="B9" s="9" t="s">
-        <v>131</v>
-      </c>
-      <c r="C9" s="5">
+      <c r="B9" s="10" t="s">
+        <v>130</v>
+      </c>
+      <c r="C9" s="6">
         <v>46154</v>
       </c>
-      <c r="D9" s="9" t="s">
-        <v>121</v>
-      </c>
-      <c r="E9" s="9" t="s">
+      <c r="D9" s="10" t="s">
+        <v>120</v>
+      </c>
+      <c r="E9" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="F9" s="9" t="s">
+      <c r="F9" s="10" t="s">
         <v>10</v>
       </c>
       <c r="G9">
         <v>10000</v>
       </c>
-      <c r="I9" s="8" t="s">
-        <v>134</v>
-      </c>
-      <c r="J9" s="9"/>
-      <c r="K9" s="9"/>
-      <c r="L9" s="9"/>
-      <c r="M9" s="9"/>
-      <c r="N9" s="9"/>
-      <c r="O9" s="9"/>
-      <c r="P9" s="9"/>
-      <c r="Q9" s="9"/>
-      <c r="R9" s="9">
+      <c r="I9" s="9" t="s">
+        <v>133</v>
+      </c>
+      <c r="J9" s="10"/>
+      <c r="K9" s="10"/>
+      <c r="L9" s="10"/>
+      <c r="M9" s="10"/>
+      <c r="N9" s="10"/>
+      <c r="O9" s="10"/>
+      <c r="P9" s="10"/>
+      <c r="Q9" s="10"/>
+      <c r="R9" s="10">
         <v>1000</v>
       </c>
-      <c r="S9" s="9"/>
-      <c r="T9" s="9"/>
-      <c r="U9" s="9"/>
-      <c r="V9" s="9"/>
-      <c r="W9" s="9"/>
-      <c r="X9" s="9"/>
-      <c r="Y9" s="9">
+      <c r="S9" s="10"/>
+      <c r="T9" s="10"/>
+      <c r="U9" s="10"/>
+      <c r="V9" s="10"/>
+      <c r="W9" s="10"/>
+      <c r="X9" s="10"/>
+      <c r="Y9" s="10">
         <v>1000</v>
       </c>
       <c r="AA9">
@@ -8573,45 +8660,45 @@
       </c>
     </row>
     <row r="10" spans="2:27" x14ac:dyDescent="0.25">
-      <c r="B10" s="9" t="s">
-        <v>132</v>
-      </c>
-      <c r="C10" s="5">
+      <c r="B10" s="10" t="s">
+        <v>131</v>
+      </c>
+      <c r="C10" s="6">
         <v>46154</v>
       </c>
-      <c r="D10" s="9" t="s">
-        <v>123</v>
-      </c>
-      <c r="E10" s="9" t="s">
+      <c r="D10" s="10" t="s">
+        <v>122</v>
+      </c>
+      <c r="E10" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="F10" s="9" t="s">
+      <c r="F10" s="10" t="s">
         <v>15</v>
       </c>
       <c r="G10">
         <v>3000</v>
       </c>
-      <c r="I10" s="8" t="s">
-        <v>138</v>
-      </c>
-      <c r="J10" s="9"/>
-      <c r="K10" s="9"/>
-      <c r="L10" s="9"/>
-      <c r="M10" s="9"/>
-      <c r="N10" s="9"/>
-      <c r="O10" s="9"/>
-      <c r="P10" s="9"/>
-      <c r="Q10" s="9"/>
-      <c r="R10" s="9"/>
-      <c r="S10" s="9"/>
-      <c r="T10" s="9"/>
-      <c r="U10" s="9">
+      <c r="I10" s="9" t="s">
+        <v>137</v>
+      </c>
+      <c r="J10" s="10"/>
+      <c r="K10" s="10"/>
+      <c r="L10" s="10"/>
+      <c r="M10" s="10"/>
+      <c r="N10" s="10"/>
+      <c r="O10" s="10"/>
+      <c r="P10" s="10"/>
+      <c r="Q10" s="10"/>
+      <c r="R10" s="10"/>
+      <c r="S10" s="10"/>
+      <c r="T10" s="10"/>
+      <c r="U10" s="10">
         <v>3000</v>
       </c>
-      <c r="V10" s="9"/>
-      <c r="W10" s="9"/>
-      <c r="X10" s="9"/>
-      <c r="Y10" s="9">
+      <c r="V10" s="10"/>
+      <c r="W10" s="10"/>
+      <c r="X10" s="10"/>
+      <c r="Y10" s="10">
         <v>3000</v>
       </c>
       <c r="AA10">
@@ -8620,45 +8707,45 @@
       </c>
     </row>
     <row r="11" spans="2:27" x14ac:dyDescent="0.25">
-      <c r="B11" s="9" t="s">
+      <c r="B11" s="10" t="s">
+        <v>132</v>
+      </c>
+      <c r="C11" s="6">
+        <v>46154</v>
+      </c>
+      <c r="D11" s="10" t="s">
         <v>133</v>
       </c>
-      <c r="C11" s="5">
-        <v>46154</v>
-      </c>
-      <c r="D11" s="9" t="s">
-        <v>134</v>
-      </c>
-      <c r="E11" s="9" t="s">
+      <c r="E11" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="F11" s="9" t="s">
+      <c r="F11" s="10" t="s">
         <v>22</v>
       </c>
       <c r="G11">
         <v>1000</v>
       </c>
-      <c r="I11" s="8" t="s">
-        <v>141</v>
-      </c>
-      <c r="J11" s="9"/>
-      <c r="K11" s="9"/>
-      <c r="L11" s="9"/>
-      <c r="M11" s="9"/>
-      <c r="N11" s="9"/>
-      <c r="O11" s="9"/>
-      <c r="P11" s="9"/>
-      <c r="Q11" s="9"/>
-      <c r="R11" s="9"/>
-      <c r="S11" s="9"/>
-      <c r="T11" s="9"/>
-      <c r="U11" s="9"/>
-      <c r="V11" s="9"/>
-      <c r="W11" s="9">
+      <c r="I11" s="9" t="s">
+        <v>140</v>
+      </c>
+      <c r="J11" s="10"/>
+      <c r="K11" s="10"/>
+      <c r="L11" s="10"/>
+      <c r="M11" s="10"/>
+      <c r="N11" s="10"/>
+      <c r="O11" s="10"/>
+      <c r="P11" s="10"/>
+      <c r="Q11" s="10"/>
+      <c r="R11" s="10"/>
+      <c r="S11" s="10"/>
+      <c r="T11" s="10"/>
+      <c r="U11" s="10"/>
+      <c r="V11" s="10"/>
+      <c r="W11" s="10">
         <v>18000</v>
       </c>
-      <c r="X11" s="9"/>
-      <c r="Y11" s="9">
+      <c r="X11" s="10"/>
+      <c r="Y11" s="10">
         <v>18000</v>
       </c>
       <c r="AA11">
@@ -8667,90 +8754,90 @@
       </c>
     </row>
     <row r="12" spans="2:27" x14ac:dyDescent="0.25">
-      <c r="B12" s="9" t="s">
-        <v>135</v>
-      </c>
-      <c r="C12" s="5">
+      <c r="B12" s="10" t="s">
+        <v>134</v>
+      </c>
+      <c r="C12" s="6">
         <v>46155</v>
       </c>
-      <c r="D12" s="9" t="s">
-        <v>121</v>
-      </c>
-      <c r="E12" s="9" t="s">
+      <c r="D12" s="10" t="s">
+        <v>120</v>
+      </c>
+      <c r="E12" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="F12" s="9" t="s">
+      <c r="F12" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G12">
         <v>18000</v>
       </c>
-      <c r="I12" s="8" t="s">
+      <c r="I12" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="J12" s="9">
+      <c r="J12" s="10">
         <v>18000</v>
       </c>
-      <c r="K12" s="9">
+      <c r="K12" s="10">
         <v>3000</v>
       </c>
-      <c r="L12" s="9">
+      <c r="L12" s="10">
         <v>10000</v>
       </c>
-      <c r="M12" s="9">
+      <c r="M12" s="10">
         <v>18000</v>
       </c>
-      <c r="N12" s="9">
+      <c r="N12" s="10">
         <v>1000</v>
       </c>
-      <c r="O12" s="9">
+      <c r="O12" s="10">
         <v>18000</v>
       </c>
-      <c r="P12" s="9">
+      <c r="P12" s="10">
         <v>10000</v>
       </c>
-      <c r="Q12" s="9">
+      <c r="Q12" s="10">
         <v>3000</v>
       </c>
-      <c r="R12" s="9">
+      <c r="R12" s="10">
         <v>1000</v>
       </c>
-      <c r="S12" s="9">
+      <c r="S12" s="10">
         <v>18000</v>
       </c>
-      <c r="T12" s="9">
+      <c r="T12" s="10">
         <v>10000</v>
       </c>
-      <c r="U12" s="9">
+      <c r="U12" s="10">
         <v>3000</v>
       </c>
-      <c r="V12" s="9">
+      <c r="V12" s="10">
         <v>18000</v>
       </c>
-      <c r="W12" s="9">
+      <c r="W12" s="10">
         <v>18000</v>
       </c>
-      <c r="X12" s="9">
+      <c r="X12" s="10">
         <v>3000</v>
       </c>
-      <c r="Y12" s="9">
+      <c r="Y12" s="10">
         <v>152000</v>
       </c>
     </row>
     <row r="13" spans="2:27" x14ac:dyDescent="0.25">
-      <c r="B13" s="9" t="s">
-        <v>136</v>
-      </c>
-      <c r="C13" s="5">
+      <c r="B13" s="10" t="s">
+        <v>135</v>
+      </c>
+      <c r="C13" s="6">
         <v>46155</v>
       </c>
-      <c r="D13" s="9" t="s">
-        <v>125</v>
-      </c>
-      <c r="E13" s="9" t="s">
+      <c r="D13" s="10" t="s">
+        <v>124</v>
+      </c>
+      <c r="E13" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="F13" s="9" t="s">
+      <c r="F13" s="10" t="s">
         <v>10</v>
       </c>
       <c r="G13">
@@ -8758,19 +8845,19 @@
       </c>
     </row>
     <row r="14" spans="2:27" x14ac:dyDescent="0.25">
-      <c r="B14" s="9" t="s">
+      <c r="B14" s="10" t="s">
+        <v>136</v>
+      </c>
+      <c r="C14" s="6">
+        <v>46155</v>
+      </c>
+      <c r="D14" s="10" t="s">
         <v>137</v>
       </c>
-      <c r="C14" s="5">
-        <v>46155</v>
-      </c>
-      <c r="D14" s="9" t="s">
-        <v>138</v>
-      </c>
-      <c r="E14" s="9" t="s">
+      <c r="E14" s="10" t="s">
         <v>31</v>
       </c>
-      <c r="F14" s="9" t="s">
+      <c r="F14" s="10" t="s">
         <v>15</v>
       </c>
       <c r="G14">
@@ -8778,19 +8865,19 @@
       </c>
     </row>
     <row r="15" spans="2:27" x14ac:dyDescent="0.25">
-      <c r="B15" s="9" t="s">
-        <v>139</v>
-      </c>
-      <c r="C15" s="5">
+      <c r="B15" s="10" t="s">
+        <v>138</v>
+      </c>
+      <c r="C15" s="6">
         <v>46156</v>
       </c>
-      <c r="D15" s="9" t="s">
-        <v>121</v>
-      </c>
-      <c r="E15" s="9" t="s">
+      <c r="D15" s="10" t="s">
+        <v>120</v>
+      </c>
+      <c r="E15" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="F15" s="9" t="s">
+      <c r="F15" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G15">
@@ -8798,19 +8885,19 @@
       </c>
     </row>
     <row r="16" spans="2:27" x14ac:dyDescent="0.25">
-      <c r="B16" s="9" t="s">
+      <c r="B16" s="10" t="s">
+        <v>139</v>
+      </c>
+      <c r="C16" s="6">
+        <v>46156</v>
+      </c>
+      <c r="D16" s="10" t="s">
         <v>140</v>
       </c>
-      <c r="C16" s="5">
-        <v>46156</v>
-      </c>
-      <c r="D16" s="9" t="s">
-        <v>141</v>
-      </c>
-      <c r="E16" s="9" t="s">
+      <c r="E16" s="10" t="s">
         <v>25</v>
       </c>
-      <c r="F16" s="9" t="s">
+      <c r="F16" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G16">
@@ -8818,203 +8905,203 @@
       </c>
     </row>
     <row r="17" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B17" s="9" t="s">
-        <v>142</v>
-      </c>
-      <c r="C17" s="5">
+      <c r="B17" s="10" t="s">
+        <v>141</v>
+      </c>
+      <c r="C17" s="6">
         <v>46156</v>
       </c>
-      <c r="D17" s="9" t="s">
-        <v>123</v>
-      </c>
-      <c r="E17" s="9" t="s">
+      <c r="D17" s="10" t="s">
+        <v>122</v>
+      </c>
+      <c r="E17" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="F17" s="9" t="s">
+      <c r="F17" s="10" t="s">
         <v>15</v>
       </c>
       <c r="G17">
         <v>3000</v>
       </c>
     </row>
-    <row r="20" spans="2:10" s="17" customFormat="1" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B20" s="18" t="s">
+    <row r="20" spans="2:10" s="21" customFormat="1" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B20" s="22" t="s">
         <v>38</v>
       </c>
-      <c r="C20" s="17" t="s">
+      <c r="C20" s="21" t="s">
         <v>39</v>
       </c>
-      <c r="E20" s="18" t="s">
+      <c r="E20" s="22" t="s">
         <v>38</v>
       </c>
-      <c r="F20" s="17" t="s">
+      <c r="F20" s="21" t="s">
         <v>39</v>
       </c>
-      <c r="H20" s="18" t="s">
+      <c r="H20" s="22" t="s">
         <v>38</v>
       </c>
-      <c r="I20" s="17" t="s">
+      <c r="I20" s="21" t="s">
         <v>39</v>
       </c>
       <c r="J20"/>
     </row>
     <row r="21" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B21" s="8" t="s">
-        <v>121</v>
-      </c>
-      <c r="C21" s="9">
+      <c r="B21" s="9" t="s">
+        <v>120</v>
+      </c>
+      <c r="C21" s="10">
         <v>5</v>
       </c>
-      <c r="E21" s="8" t="s">
+      <c r="E21" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="F21" s="9">
+      <c r="F21" s="10">
         <v>6</v>
       </c>
-      <c r="H21" s="8" t="s">
+      <c r="H21" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="I21" s="23">
+      <c r="I21" s="27">
         <v>6</v>
       </c>
     </row>
     <row r="22" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B22" s="8" t="s">
-        <v>123</v>
-      </c>
-      <c r="C22" s="9">
+      <c r="B22" s="9" t="s">
+        <v>122</v>
+      </c>
+      <c r="C22" s="10">
         <v>3</v>
       </c>
-      <c r="E22" s="8" t="s">
+      <c r="E22" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="F22" s="9">
+      <c r="F22" s="10">
         <v>3</v>
       </c>
-      <c r="H22" s="8" t="s">
+      <c r="H22" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="I22" s="9">
+      <c r="I22" s="10">
         <v>3</v>
       </c>
     </row>
     <row r="23" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B23" s="8" t="s">
-        <v>125</v>
-      </c>
-      <c r="C23" s="9">
+      <c r="B23" s="9" t="s">
+        <v>124</v>
+      </c>
+      <c r="C23" s="10">
         <v>2</v>
       </c>
-      <c r="E23" s="8" t="s">
+      <c r="E23" s="9" t="s">
         <v>31</v>
       </c>
-      <c r="F23" s="9">
+      <c r="F23" s="10">
         <v>2</v>
       </c>
-      <c r="H23" s="8" t="s">
+      <c r="H23" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="I23" s="9">
+      <c r="I23" s="10">
         <v>2</v>
       </c>
     </row>
     <row r="24" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B24" s="8" t="s">
-        <v>128</v>
-      </c>
-      <c r="C24" s="9">
+      <c r="B24" s="9" t="s">
+        <v>127</v>
+      </c>
+      <c r="C24" s="10">
         <v>1</v>
       </c>
-      <c r="E24" s="8" t="s">
+      <c r="E24" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="F24" s="9">
+      <c r="F24" s="10">
         <v>2</v>
       </c>
-      <c r="H24" s="8" t="s">
+      <c r="H24" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="I24" s="9">
+      <c r="I24" s="10">
         <v>4</v>
       </c>
     </row>
     <row r="25" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B25" s="8" t="s">
-        <v>130</v>
-      </c>
-      <c r="C25" s="9">
+      <c r="B25" s="9" t="s">
+        <v>129</v>
+      </c>
+      <c r="C25" s="10">
         <v>1</v>
       </c>
-      <c r="E25" s="8" t="s">
+      <c r="E25" s="9" t="s">
         <v>25</v>
       </c>
-      <c r="F25" s="9">
+      <c r="F25" s="10">
         <v>2</v>
       </c>
-      <c r="H25" s="8" t="s">
+      <c r="H25" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="I25" s="9">
+      <c r="I25" s="10">
         <v>15</v>
       </c>
     </row>
     <row r="26" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B26" s="8" t="s">
-        <v>134</v>
-      </c>
-      <c r="C26" s="9">
+      <c r="B26" s="9" t="s">
+        <v>133</v>
+      </c>
+      <c r="C26" s="10">
         <v>1</v>
       </c>
-      <c r="E26" s="8" t="s">
+      <c r="E26" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="F26" s="9">
+      <c r="F26" s="10">
         <v>15</v>
       </c>
     </row>
     <row r="27" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B27" s="8" t="s">
-        <v>138</v>
-      </c>
-      <c r="C27" s="9">
+      <c r="B27" s="9" t="s">
+        <v>137</v>
+      </c>
+      <c r="C27" s="10">
         <v>1</v>
       </c>
     </row>
     <row r="28" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B28" s="8" t="s">
-        <v>141</v>
-      </c>
-      <c r="C28" s="9">
+      <c r="B28" s="9" t="s">
+        <v>140</v>
+      </c>
+      <c r="C28" s="10">
         <v>1</v>
       </c>
     </row>
     <row r="29" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B29" s="8" t="s">
+      <c r="B29" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="C29" s="9">
+      <c r="C29" s="10">
         <v>15</v>
       </c>
     </row>
   </sheetData>
   <conditionalFormatting sqref="B20:C29">
-    <cfRule type="cellIs" dxfId="48" priority="5" operator="lessThan">
+    <cfRule type="cellIs" dxfId="4" priority="5" operator="lessThan">
       <formula>2</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting pivot="1" sqref="F21:F25">
-    <cfRule type="cellIs" dxfId="47" priority="4" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="3" priority="4" operator="greaterThan">
       <formula>5</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting pivot="1" sqref="F21:F25">
-    <cfRule type="cellIs" dxfId="46" priority="3" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="2" priority="3" operator="greaterThan">
       <formula>5</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AA4:AA11">
-    <cfRule type="top10" dxfId="45" priority="1" rank="2"/>
-    <cfRule type="top10" dxfId="44" priority="2" rank="2"/>
+    <cfRule type="top10" dxfId="1" priority="1" rank="2"/>
+    <cfRule type="top10" dxfId="0" priority="2" rank="2"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="2">
@@ -9069,759 +9156,759 @@
     <col min="38" max="38" width="12.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:20" s="17" customFormat="1" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B2" s="17" t="s">
+    <row r="2" spans="2:20" s="21" customFormat="1" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B2" s="21" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="17" t="s">
+      <c r="C2" s="21" t="s">
         <v>1</v>
       </c>
-      <c r="D2" s="17" t="s">
+      <c r="D2" s="21" t="s">
         <v>2</v>
       </c>
-      <c r="E2" s="17" t="s">
+      <c r="E2" s="21" t="s">
         <v>3</v>
       </c>
-      <c r="F2" s="17" t="s">
+      <c r="F2" s="21" t="s">
         <v>4</v>
       </c>
-      <c r="G2" s="17" t="s">
+      <c r="G2" s="21" t="s">
         <v>5</v>
       </c>
-      <c r="H2" s="17" t="s">
+      <c r="H2" s="21" t="s">
+        <v>143</v>
+      </c>
+      <c r="J2" s="22" t="s">
+        <v>39</v>
+      </c>
+      <c r="K2" s="22" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="3" spans="2:20" x14ac:dyDescent="0.25">
+      <c r="B3" s="10" t="s">
         <v>144</v>
       </c>
-      <c r="J2" s="18" t="s">
-        <v>39</v>
-      </c>
-      <c r="K2" s="18" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="3" spans="2:20" x14ac:dyDescent="0.25">
-      <c r="B3" s="9" t="s">
-        <v>145</v>
-      </c>
-      <c r="C3" s="5">
+      <c r="C3" s="6">
         <v>46157</v>
       </c>
-      <c r="D3" s="9" t="s">
-        <v>121</v>
-      </c>
-      <c r="E3" s="9" t="s">
+      <c r="D3" s="10" t="s">
+        <v>120</v>
+      </c>
+      <c r="E3" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="F3" s="9" t="s">
+      <c r="F3" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G3">
         <v>18000</v>
       </c>
-      <c r="H3" s="9" t="s">
-        <v>146</v>
-      </c>
-      <c r="J3" s="7" t="s">
-        <v>177</v>
+      <c r="H3" s="10" t="s">
+        <v>145</v>
+      </c>
+      <c r="J3" s="8" t="s">
+        <v>176</v>
       </c>
       <c r="K3" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="L3" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="M3" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="N3" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="O3" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="P3" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="Q3" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="R3" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="S3" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="T3" t="s">
         <v>40</v>
       </c>
     </row>
     <row r="4" spans="2:20" x14ac:dyDescent="0.25">
-      <c r="B4" s="9" t="s">
-        <v>147</v>
-      </c>
-      <c r="C4" s="5">
+      <c r="B4" s="10" t="s">
+        <v>146</v>
+      </c>
+      <c r="C4" s="6">
         <v>46157</v>
       </c>
-      <c r="D4" s="9" t="s">
-        <v>123</v>
-      </c>
-      <c r="E4" s="9" t="s">
+      <c r="D4" s="10" t="s">
+        <v>122</v>
+      </c>
+      <c r="E4" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="F4" s="9" t="s">
+      <c r="F4" s="10" t="s">
         <v>15</v>
       </c>
       <c r="G4">
         <v>3000</v>
       </c>
-      <c r="H4" s="9" t="s">
-        <v>146</v>
-      </c>
-      <c r="J4" s="8" t="s">
-        <v>146</v>
-      </c>
-      <c r="K4" s="9">
+      <c r="H4" s="10" t="s">
+        <v>145</v>
+      </c>
+      <c r="J4" s="9" t="s">
+        <v>145</v>
+      </c>
+      <c r="K4" s="10">
         <v>1</v>
       </c>
-      <c r="L4" s="9">
+      <c r="L4" s="10">
         <v>1</v>
       </c>
-      <c r="M4" s="9">
+      <c r="M4" s="10">
         <v>1</v>
       </c>
-      <c r="N4" s="9">
+      <c r="N4" s="10">
         <v>1</v>
       </c>
-      <c r="O4" s="9"/>
-      <c r="P4" s="9"/>
-      <c r="Q4" s="9"/>
-      <c r="R4" s="9"/>
-      <c r="S4" s="9"/>
-      <c r="T4" s="9">
+      <c r="O4" s="10"/>
+      <c r="P4" s="10"/>
+      <c r="Q4" s="10"/>
+      <c r="R4" s="10"/>
+      <c r="S4" s="10"/>
+      <c r="T4" s="10">
         <v>4</v>
       </c>
     </row>
     <row r="5" spans="2:20" x14ac:dyDescent="0.25">
-      <c r="B5" s="9" t="s">
-        <v>148</v>
-      </c>
-      <c r="C5" s="5">
+      <c r="B5" s="10" t="s">
+        <v>147</v>
+      </c>
+      <c r="C5" s="6">
         <v>46157</v>
       </c>
-      <c r="D5" s="9" t="s">
-        <v>125</v>
-      </c>
-      <c r="E5" s="9" t="s">
+      <c r="D5" s="10" t="s">
+        <v>124</v>
+      </c>
+      <c r="E5" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="F5" s="9" t="s">
+      <c r="F5" s="10" t="s">
         <v>10</v>
       </c>
       <c r="G5">
         <v>10000</v>
       </c>
-      <c r="H5" s="9" t="s">
-        <v>146</v>
-      </c>
-      <c r="J5" s="8" t="s">
-        <v>151</v>
-      </c>
-      <c r="K5" s="28">
+      <c r="H5" s="10" t="s">
+        <v>145</v>
+      </c>
+      <c r="J5" s="9" t="s">
+        <v>150</v>
+      </c>
+      <c r="K5" s="32">
         <v>2</v>
       </c>
-      <c r="L5" s="9">
+      <c r="L5" s="10">
         <v>1</v>
       </c>
-      <c r="M5" s="9">
+      <c r="M5" s="10">
         <v>1</v>
       </c>
-      <c r="N5" s="9"/>
-      <c r="O5" s="23">
+      <c r="N5" s="10"/>
+      <c r="O5" s="27">
         <v>1</v>
       </c>
-      <c r="P5" s="23">
+      <c r="P5" s="27">
         <v>1</v>
       </c>
-      <c r="Q5" s="23">
+      <c r="Q5" s="27">
         <v>1</v>
       </c>
-      <c r="R5" s="23">
+      <c r="R5" s="27">
         <v>1</v>
       </c>
-      <c r="S5" s="9"/>
-      <c r="T5" s="9">
+      <c r="S5" s="10"/>
+      <c r="T5" s="10">
         <v>8</v>
       </c>
     </row>
     <row r="6" spans="2:20" x14ac:dyDescent="0.25">
-      <c r="B6" s="9" t="s">
-        <v>149</v>
-      </c>
-      <c r="C6" s="5">
+      <c r="B6" s="10" t="s">
+        <v>148</v>
+      </c>
+      <c r="C6" s="6">
         <v>46157</v>
       </c>
-      <c r="D6" s="9" t="s">
-        <v>130</v>
-      </c>
-      <c r="E6" s="9" t="s">
+      <c r="D6" s="10" t="s">
+        <v>129</v>
+      </c>
+      <c r="E6" s="10" t="s">
         <v>25</v>
       </c>
-      <c r="F6" s="9" t="s">
+      <c r="F6" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G6">
         <v>18000</v>
       </c>
-      <c r="H6" s="9" t="s">
-        <v>146</v>
-      </c>
-      <c r="J6" s="8" t="s">
-        <v>167</v>
-      </c>
-      <c r="K6" s="9">
+      <c r="H6" s="10" t="s">
+        <v>145</v>
+      </c>
+      <c r="J6" s="9" t="s">
+        <v>166</v>
+      </c>
+      <c r="K6" s="10">
         <v>1</v>
       </c>
-      <c r="L6" s="9">
+      <c r="L6" s="10">
         <v>1</v>
       </c>
-      <c r="M6" s="9"/>
-      <c r="N6" s="9"/>
-      <c r="O6" s="9"/>
-      <c r="P6" s="9"/>
-      <c r="Q6" s="9"/>
-      <c r="R6" s="9"/>
-      <c r="S6" s="23">
+      <c r="M6" s="10"/>
+      <c r="N6" s="10"/>
+      <c r="O6" s="10"/>
+      <c r="P6" s="10"/>
+      <c r="Q6" s="10"/>
+      <c r="R6" s="10"/>
+      <c r="S6" s="27">
         <v>1</v>
       </c>
-      <c r="T6" s="9">
+      <c r="T6" s="10">
         <v>3</v>
       </c>
     </row>
     <row r="7" spans="2:20" x14ac:dyDescent="0.25">
-      <c r="B7" s="9" t="s">
-        <v>150</v>
-      </c>
-      <c r="C7" s="5">
+      <c r="B7" s="10" t="s">
+        <v>149</v>
+      </c>
+      <c r="C7" s="6">
         <v>46158</v>
       </c>
-      <c r="D7" s="9" t="s">
-        <v>121</v>
-      </c>
-      <c r="E7" s="9" t="s">
+      <c r="D7" s="10" t="s">
+        <v>120</v>
+      </c>
+      <c r="E7" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="F7" s="9" t="s">
+      <c r="F7" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G7">
         <v>12600</v>
       </c>
-      <c r="H7" s="9" t="s">
+      <c r="H7" s="10" t="s">
+        <v>150</v>
+      </c>
+      <c r="J7" s="9" t="s">
+        <v>40</v>
+      </c>
+      <c r="K7" s="10">
+        <v>4</v>
+      </c>
+      <c r="L7" s="10">
+        <v>3</v>
+      </c>
+      <c r="M7" s="10">
+        <v>2</v>
+      </c>
+      <c r="N7" s="10">
+        <v>1</v>
+      </c>
+      <c r="O7" s="10">
+        <v>1</v>
+      </c>
+      <c r="P7" s="10">
+        <v>1</v>
+      </c>
+      <c r="Q7" s="10">
+        <v>1</v>
+      </c>
+      <c r="R7" s="10">
+        <v>1</v>
+      </c>
+      <c r="S7" s="10">
+        <v>1</v>
+      </c>
+      <c r="T7" s="10">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="8" spans="2:20" x14ac:dyDescent="0.25">
+      <c r="B8" s="10" t="s">
         <v>151</v>
       </c>
-      <c r="J7" s="8" t="s">
-        <v>40</v>
-      </c>
-      <c r="K7" s="9">
-        <v>4</v>
-      </c>
-      <c r="L7" s="9">
-        <v>3</v>
-      </c>
-      <c r="M7" s="9">
-        <v>2</v>
-      </c>
-      <c r="N7" s="9">
-        <v>1</v>
-      </c>
-      <c r="O7" s="9">
-        <v>1</v>
-      </c>
-      <c r="P7" s="9">
-        <v>1</v>
-      </c>
-      <c r="Q7" s="9">
-        <v>1</v>
-      </c>
-      <c r="R7" s="9">
-        <v>1</v>
-      </c>
-      <c r="S7" s="9">
-        <v>1</v>
-      </c>
-      <c r="T7" s="9">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="8" spans="2:20" x14ac:dyDescent="0.25">
-      <c r="B8" s="9" t="s">
-        <v>152</v>
-      </c>
-      <c r="C8" s="5">
+      <c r="C8" s="6">
         <v>46158</v>
       </c>
-      <c r="D8" s="9" t="s">
-        <v>123</v>
-      </c>
-      <c r="E8" s="9" t="s">
+      <c r="D8" s="10" t="s">
+        <v>122</v>
+      </c>
+      <c r="E8" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="F8" s="9" t="s">
+      <c r="F8" s="10" t="s">
         <v>15</v>
       </c>
       <c r="G8">
         <v>3000</v>
       </c>
-      <c r="H8" s="9" t="s">
-        <v>151</v>
-      </c>
-      <c r="J8" s="27" t="s">
-        <v>172</v>
-      </c>
-      <c r="K8" s="33" t="s">
-        <v>154</v>
-      </c>
-      <c r="L8" s="33" t="s">
-        <v>156</v>
-      </c>
-      <c r="M8" s="33" t="s">
-        <v>160</v>
-      </c>
-      <c r="N8" s="33" t="s">
-        <v>164</v>
-      </c>
-      <c r="O8" s="33" t="s">
-        <v>170</v>
+      <c r="H8" s="10" t="s">
+        <v>150</v>
+      </c>
+      <c r="J8" s="31" t="s">
+        <v>171</v>
+      </c>
+      <c r="K8" s="37" t="s">
+        <v>153</v>
+      </c>
+      <c r="L8" s="37" t="s">
+        <v>155</v>
+      </c>
+      <c r="M8" s="37" t="s">
+        <v>159</v>
+      </c>
+      <c r="N8" s="37" t="s">
+        <v>163</v>
+      </c>
+      <c r="O8" s="37" t="s">
+        <v>169</v>
       </c>
     </row>
     <row r="9" spans="2:20" x14ac:dyDescent="0.25">
-      <c r="B9" s="9" t="s">
+      <c r="B9" s="10" t="s">
+        <v>152</v>
+      </c>
+      <c r="C9" s="6">
+        <v>46158</v>
+      </c>
+      <c r="D9" s="10" t="s">
         <v>153</v>
       </c>
-      <c r="C9" s="5">
-        <v>46158</v>
-      </c>
-      <c r="D9" s="9" t="s">
-        <v>154</v>
-      </c>
-      <c r="E9" s="9" t="s">
+      <c r="E9" s="10" t="s">
         <v>31</v>
       </c>
-      <c r="F9" s="9" t="s">
+      <c r="F9" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G9">
         <v>12600</v>
       </c>
-      <c r="H9" s="9" t="s">
-        <v>151</v>
-      </c>
-      <c r="J9" s="29" t="s">
-        <v>173</v>
-      </c>
-      <c r="K9" s="29" t="s">
-        <v>121</v>
+      <c r="H9" s="10" t="s">
+        <v>150</v>
+      </c>
+      <c r="J9" s="33" t="s">
+        <v>172</v>
+      </c>
+      <c r="K9" s="33" t="s">
+        <v>120</v>
       </c>
     </row>
     <row r="10" spans="2:20" x14ac:dyDescent="0.25">
-      <c r="B10" s="9" t="s">
+      <c r="B10" s="10" t="s">
+        <v>154</v>
+      </c>
+      <c r="C10" s="6">
+        <v>46158</v>
+      </c>
+      <c r="D10" s="10" t="s">
         <v>155</v>
       </c>
-      <c r="C10" s="5">
-        <v>46158</v>
-      </c>
-      <c r="D10" s="9" t="s">
+      <c r="E10" s="10" t="s">
         <v>156</v>
       </c>
-      <c r="E10" s="9" t="s">
-        <v>157</v>
-      </c>
-      <c r="F10" s="9" t="s">
+      <c r="F10" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G10">
         <v>12600</v>
       </c>
-      <c r="H10" s="9" t="s">
-        <v>151</v>
+      <c r="H10" s="10" t="s">
+        <v>150</v>
       </c>
     </row>
     <row r="11" spans="2:20" x14ac:dyDescent="0.25">
-      <c r="B11" s="9" t="s">
-        <v>158</v>
-      </c>
-      <c r="C11" s="5">
+      <c r="B11" s="10" t="s">
+        <v>157</v>
+      </c>
+      <c r="C11" s="6">
         <v>46159</v>
       </c>
-      <c r="D11" s="9" t="s">
-        <v>121</v>
-      </c>
-      <c r="E11" s="9" t="s">
+      <c r="D11" s="10" t="s">
+        <v>120</v>
+      </c>
+      <c r="E11" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="F11" s="9" t="s">
+      <c r="F11" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G11">
         <v>12600</v>
       </c>
-      <c r="H11" s="9" t="s">
-        <v>151</v>
+      <c r="H11" s="10" t="s">
+        <v>150</v>
       </c>
     </row>
     <row r="12" spans="2:20" x14ac:dyDescent="0.25">
-      <c r="B12" s="9" t="s">
+      <c r="B12" s="10" t="s">
+        <v>158</v>
+      </c>
+      <c r="C12" s="6">
+        <v>46159</v>
+      </c>
+      <c r="D12" s="10" t="s">
         <v>159</v>
       </c>
-      <c r="C12" s="5">
-        <v>46159</v>
-      </c>
-      <c r="D12" s="9" t="s">
+      <c r="E12" s="10" t="s">
         <v>160</v>
       </c>
-      <c r="E12" s="9" t="s">
-        <v>161</v>
-      </c>
-      <c r="F12" s="9" t="s">
+      <c r="F12" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G12">
         <v>12600</v>
       </c>
-      <c r="H12" s="9" t="s">
-        <v>151</v>
-      </c>
-      <c r="J12" s="7" t="s">
+      <c r="H12" s="10" t="s">
+        <v>150</v>
+      </c>
+      <c r="J12" s="8" t="s">
         <v>39</v>
       </c>
-      <c r="K12" s="7" t="s">
+      <c r="K12" s="8" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="13" spans="2:20" s="17" customFormat="1" ht="27" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B13" s="30" t="s">
+    <row r="13" spans="2:20" s="21" customFormat="1" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B13" s="34" t="s">
+        <v>161</v>
+      </c>
+      <c r="C13" s="35">
+        <v>46159</v>
+      </c>
+      <c r="D13" s="34" t="s">
+        <v>124</v>
+      </c>
+      <c r="E13" s="34" t="s">
+        <v>19</v>
+      </c>
+      <c r="F13" s="34" t="s">
+        <v>10</v>
+      </c>
+      <c r="G13" s="21">
+        <v>10000</v>
+      </c>
+      <c r="H13" s="34" t="s">
+        <v>150</v>
+      </c>
+      <c r="J13" s="22" t="s">
+        <v>176</v>
+      </c>
+      <c r="K13" s="21" t="s">
+        <v>160</v>
+      </c>
+      <c r="L13" s="21" t="s">
+        <v>9</v>
+      </c>
+      <c r="M13" s="21" t="s">
+        <v>156</v>
+      </c>
+      <c r="N13" s="21" t="s">
+        <v>14</v>
+      </c>
+      <c r="O13" s="21" t="s">
+        <v>31</v>
+      </c>
+      <c r="P13" s="21" t="s">
+        <v>19</v>
+      </c>
+      <c r="Q13" s="21" t="s">
+        <v>25</v>
+      </c>
+      <c r="R13" s="21" t="s">
+        <v>164</v>
+      </c>
+      <c r="S13" s="21" t="s">
+        <v>170</v>
+      </c>
+      <c r="T13" s="21" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="14" spans="2:20" x14ac:dyDescent="0.25">
+      <c r="B14" s="10" t="s">
         <v>162</v>
       </c>
-      <c r="C13" s="31">
+      <c r="C14" s="6">
         <v>46159</v>
       </c>
-      <c r="D13" s="30" t="s">
-        <v>125</v>
-      </c>
-      <c r="E13" s="30" t="s">
-        <v>19</v>
-      </c>
-      <c r="F13" s="30" t="s">
-        <v>10</v>
-      </c>
-      <c r="G13" s="17">
-        <v>10000</v>
-      </c>
-      <c r="H13" s="30" t="s">
-        <v>151</v>
-      </c>
-      <c r="J13" s="18" t="s">
-        <v>177</v>
-      </c>
-      <c r="K13" s="17" t="s">
-        <v>161</v>
-      </c>
-      <c r="L13" s="17" t="s">
-        <v>9</v>
-      </c>
-      <c r="M13" s="17" t="s">
-        <v>157</v>
-      </c>
-      <c r="N13" s="17" t="s">
-        <v>14</v>
-      </c>
-      <c r="O13" s="17" t="s">
-        <v>31</v>
-      </c>
-      <c r="P13" s="17" t="s">
-        <v>19</v>
-      </c>
-      <c r="Q13" s="17" t="s">
-        <v>25</v>
-      </c>
-      <c r="R13" s="17" t="s">
-        <v>165</v>
-      </c>
-      <c r="S13" s="17" t="s">
-        <v>171</v>
-      </c>
-      <c r="T13" s="17" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="14" spans="2:20" x14ac:dyDescent="0.25">
-      <c r="B14" s="9" t="s">
+      <c r="D14" s="10" t="s">
         <v>163</v>
       </c>
-      <c r="C14" s="5">
-        <v>46159</v>
-      </c>
-      <c r="D14" s="9" t="s">
+      <c r="E14" s="10" t="s">
         <v>164</v>
       </c>
-      <c r="E14" s="9" t="s">
-        <v>165</v>
-      </c>
-      <c r="F14" s="9" t="s">
+      <c r="F14" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G14">
         <v>12600</v>
       </c>
-      <c r="H14" s="9" t="s">
-        <v>151</v>
-      </c>
-      <c r="J14" s="8" t="s">
-        <v>146</v>
-      </c>
-      <c r="K14" s="9"/>
-      <c r="L14" s="9">
+      <c r="H14" s="10" t="s">
+        <v>150</v>
+      </c>
+      <c r="J14" s="9" t="s">
+        <v>145</v>
+      </c>
+      <c r="K14" s="10"/>
+      <c r="L14" s="10">
         <v>1</v>
       </c>
-      <c r="M14" s="9"/>
-      <c r="N14" s="9">
+      <c r="M14" s="10"/>
+      <c r="N14" s="10">
         <v>1</v>
       </c>
-      <c r="O14" s="9"/>
-      <c r="P14" s="9">
+      <c r="O14" s="10"/>
+      <c r="P14" s="10">
         <v>1</v>
       </c>
-      <c r="Q14" s="9">
+      <c r="Q14" s="10">
         <v>1</v>
       </c>
-      <c r="R14" s="9"/>
-      <c r="S14" s="9"/>
-      <c r="T14" s="9">
+      <c r="R14" s="10"/>
+      <c r="S14" s="10"/>
+      <c r="T14" s="10">
         <v>4</v>
       </c>
     </row>
     <row r="15" spans="2:20" x14ac:dyDescent="0.25">
-      <c r="B15" s="9" t="s">
-        <v>166</v>
-      </c>
-      <c r="C15" s="5">
+      <c r="B15" s="10" t="s">
+        <v>165</v>
+      </c>
+      <c r="C15" s="6">
         <v>46160</v>
       </c>
-      <c r="D15" s="9" t="s">
-        <v>121</v>
-      </c>
-      <c r="E15" s="9" t="s">
+      <c r="D15" s="10" t="s">
+        <v>120</v>
+      </c>
+      <c r="E15" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="F15" s="9" t="s">
+      <c r="F15" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G15">
         <v>18000</v>
       </c>
-      <c r="H15" s="9" t="s">
+      <c r="H15" s="10" t="s">
+        <v>166</v>
+      </c>
+      <c r="J15" s="9" t="s">
+        <v>150</v>
+      </c>
+      <c r="K15" s="27">
+        <v>1</v>
+      </c>
+      <c r="L15" s="10">
+        <v>2</v>
+      </c>
+      <c r="M15" s="27">
+        <v>1</v>
+      </c>
+      <c r="N15" s="10">
+        <v>1</v>
+      </c>
+      <c r="O15" s="27">
+        <v>1</v>
+      </c>
+      <c r="P15" s="10">
+        <v>1</v>
+      </c>
+      <c r="Q15" s="10"/>
+      <c r="R15" s="27">
+        <v>1</v>
+      </c>
+      <c r="S15" s="10"/>
+      <c r="T15" s="10">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="16" spans="2:20" x14ac:dyDescent="0.25">
+      <c r="B16" s="10" t="s">
         <v>167</v>
       </c>
-      <c r="J15" s="8" t="s">
-        <v>151</v>
-      </c>
-      <c r="K15" s="23">
-        <v>1</v>
-      </c>
-      <c r="L15" s="9">
-        <v>2</v>
-      </c>
-      <c r="M15" s="23">
-        <v>1</v>
-      </c>
-      <c r="N15" s="9">
-        <v>1</v>
-      </c>
-      <c r="O15" s="23">
-        <v>1</v>
-      </c>
-      <c r="P15" s="9">
-        <v>1</v>
-      </c>
-      <c r="Q15" s="9"/>
-      <c r="R15" s="23">
-        <v>1</v>
-      </c>
-      <c r="S15" s="9"/>
-      <c r="T15" s="9">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="16" spans="2:20" x14ac:dyDescent="0.25">
-      <c r="B16" s="9" t="s">
-        <v>168</v>
-      </c>
-      <c r="C16" s="5">
+      <c r="C16" s="6">
         <v>46160</v>
       </c>
-      <c r="D16" s="9" t="s">
-        <v>123</v>
-      </c>
-      <c r="E16" s="9" t="s">
+      <c r="D16" s="10" t="s">
+        <v>122</v>
+      </c>
+      <c r="E16" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="F16" s="9" t="s">
+      <c r="F16" s="10" t="s">
         <v>15</v>
       </c>
       <c r="G16">
         <v>3000</v>
       </c>
-      <c r="H16" s="9" t="s">
-        <v>167</v>
-      </c>
-      <c r="J16" s="8" t="s">
-        <v>167</v>
-      </c>
-      <c r="K16" s="9"/>
-      <c r="L16" s="9">
+      <c r="H16" s="10" t="s">
+        <v>166</v>
+      </c>
+      <c r="J16" s="9" t="s">
+        <v>166</v>
+      </c>
+      <c r="K16" s="10"/>
+      <c r="L16" s="10">
         <v>1</v>
       </c>
-      <c r="M16" s="9"/>
-      <c r="N16" s="9">
+      <c r="M16" s="10"/>
+      <c r="N16" s="10">
         <v>1</v>
       </c>
-      <c r="O16" s="9"/>
-      <c r="P16" s="9"/>
-      <c r="Q16" s="9"/>
-      <c r="R16" s="9"/>
-      <c r="S16" s="23">
+      <c r="O16" s="10"/>
+      <c r="P16" s="10"/>
+      <c r="Q16" s="10"/>
+      <c r="R16" s="10"/>
+      <c r="S16" s="27">
         <v>1</v>
       </c>
-      <c r="T16" s="9">
+      <c r="T16" s="10">
         <v>3</v>
       </c>
     </row>
     <row r="17" spans="2:38" x14ac:dyDescent="0.25">
-      <c r="B17" s="9" t="s">
+      <c r="B17" s="10" t="s">
+        <v>168</v>
+      </c>
+      <c r="C17" s="6">
+        <v>46160</v>
+      </c>
+      <c r="D17" s="10" t="s">
         <v>169</v>
       </c>
-      <c r="C17" s="5">
-        <v>46160</v>
-      </c>
-      <c r="D17" s="9" t="s">
+      <c r="E17" s="10" t="s">
         <v>170</v>
       </c>
-      <c r="E17" s="9" t="s">
-        <v>171</v>
-      </c>
-      <c r="F17" s="9" t="s">
+      <c r="F17" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G17">
         <v>18000</v>
       </c>
-      <c r="H17" s="9" t="s">
-        <v>167</v>
-      </c>
-      <c r="J17" s="8" t="s">
+      <c r="H17" s="10" t="s">
+        <v>166</v>
+      </c>
+      <c r="J17" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="K17" s="9">
+      <c r="K17" s="10">
         <v>1</v>
       </c>
-      <c r="L17" s="9">
+      <c r="L17" s="10">
         <v>4</v>
       </c>
-      <c r="M17" s="9">
+      <c r="M17" s="10">
         <v>1</v>
       </c>
-      <c r="N17" s="9">
+      <c r="N17" s="10">
         <v>3</v>
       </c>
-      <c r="O17" s="9">
+      <c r="O17" s="10">
         <v>1</v>
       </c>
-      <c r="P17" s="9">
+      <c r="P17" s="10">
         <v>2</v>
       </c>
-      <c r="Q17" s="9">
+      <c r="Q17" s="10">
         <v>1</v>
       </c>
-      <c r="R17" s="9">
+      <c r="R17" s="10">
         <v>1</v>
       </c>
-      <c r="S17" s="9">
+      <c r="S17" s="10">
         <v>1</v>
       </c>
-      <c r="T17" s="9">
+      <c r="T17" s="10">
         <v>15</v>
       </c>
     </row>
     <row r="18" spans="2:38" x14ac:dyDescent="0.25">
-      <c r="J18" s="27" t="s">
-        <v>174</v>
+      <c r="J18" s="31" t="s">
+        <v>173</v>
       </c>
     </row>
     <row r="19" spans="2:38" ht="45" x14ac:dyDescent="0.25">
-      <c r="M19" s="17"/>
-      <c r="N19" s="18" t="s">
+      <c r="M19" s="21"/>
+      <c r="N19" s="22" t="s">
         <v>42</v>
       </c>
-      <c r="P19" s="17"/>
-      <c r="Q19" s="17"/>
-      <c r="R19" s="17"/>
-      <c r="S19" s="17"/>
-      <c r="T19" s="17"/>
-      <c r="U19" s="17"/>
-      <c r="V19" s="17"/>
-      <c r="W19" s="17"/>
-      <c r="X19" s="17"/>
-      <c r="Y19" s="17"/>
-      <c r="Z19" s="17"/>
-      <c r="AA19" s="17"/>
-      <c r="AB19" s="17"/>
-      <c r="AC19" s="17"/>
-      <c r="AD19" s="17"/>
-      <c r="AE19" s="17"/>
-      <c r="AF19" s="17"/>
-      <c r="AG19" s="17"/>
-    </row>
-    <row r="20" spans="2:38" s="17" customFormat="1" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="N20" s="32" t="s">
-        <v>121</v>
-      </c>
-      <c r="O20" s="32"/>
-      <c r="P20" s="26" t="s">
-        <v>123</v>
-      </c>
-      <c r="Q20" s="26"/>
-      <c r="R20" s="32" t="s">
-        <v>125</v>
-      </c>
-      <c r="S20" s="32"/>
-      <c r="T20" s="26" t="s">
-        <v>130</v>
-      </c>
-      <c r="U20" s="26"/>
-      <c r="V20" s="32" t="s">
-        <v>154</v>
-      </c>
-      <c r="W20" s="32"/>
-      <c r="X20" s="26" t="s">
-        <v>156</v>
-      </c>
-      <c r="Y20" s="26"/>
-      <c r="Z20" s="32" t="s">
-        <v>160</v>
-      </c>
-      <c r="AA20" s="32"/>
-      <c r="AB20" s="26" t="s">
-        <v>164</v>
-      </c>
-      <c r="AC20" s="26"/>
-      <c r="AD20" s="32" t="s">
-        <v>170</v>
-      </c>
-      <c r="AE20" s="32"/>
-      <c r="AF20" s="17" t="s">
-        <v>71</v>
-      </c>
-      <c r="AG20" s="17" t="s">
+      <c r="P19" s="21"/>
+      <c r="Q19" s="21"/>
+      <c r="R19" s="21"/>
+      <c r="S19" s="21"/>
+      <c r="T19" s="21"/>
+      <c r="U19" s="21"/>
+      <c r="V19" s="21"/>
+      <c r="W19" s="21"/>
+      <c r="X19" s="21"/>
+      <c r="Y19" s="21"/>
+      <c r="Z19" s="21"/>
+      <c r="AA19" s="21"/>
+      <c r="AB19" s="21"/>
+      <c r="AC19" s="21"/>
+      <c r="AD19" s="21"/>
+      <c r="AE19" s="21"/>
+      <c r="AF19" s="21"/>
+      <c r="AG19" s="21"/>
+    </row>
+    <row r="20" spans="2:38" s="21" customFormat="1" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="N20" s="36" t="s">
+        <v>120</v>
+      </c>
+      <c r="O20" s="36"/>
+      <c r="P20" s="30" t="s">
+        <v>122</v>
+      </c>
+      <c r="Q20" s="30"/>
+      <c r="R20" s="36" t="s">
+        <v>124</v>
+      </c>
+      <c r="S20" s="36"/>
+      <c r="T20" s="30" t="s">
+        <v>129</v>
+      </c>
+      <c r="U20" s="30"/>
+      <c r="V20" s="36" t="s">
+        <v>153</v>
+      </c>
+      <c r="W20" s="36"/>
+      <c r="X20" s="30" t="s">
+        <v>155</v>
+      </c>
+      <c r="Y20" s="30"/>
+      <c r="Z20" s="36" t="s">
+        <v>159</v>
+      </c>
+      <c r="AA20" s="36"/>
+      <c r="AB20" s="30" t="s">
+        <v>163</v>
+      </c>
+      <c r="AC20" s="30"/>
+      <c r="AD20" s="36" t="s">
+        <v>169</v>
+      </c>
+      <c r="AE20" s="36"/>
+      <c r="AF20" s="21" t="s">
         <v>70</v>
+      </c>
+      <c r="AG20" s="21" t="s">
+        <v>69</v>
       </c>
       <c r="AH20"/>
       <c r="AI20"/>
@@ -9829,309 +9916,309 @@
       <c r="AK20"/>
       <c r="AL20"/>
     </row>
-    <row r="21" spans="2:38" s="17" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J21" s="18" t="s">
-        <v>177</v>
-      </c>
-      <c r="K21" s="17" t="s">
+    <row r="21" spans="2:38" s="21" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="J21" s="22" t="s">
+        <v>176</v>
+      </c>
+      <c r="K21" s="21" t="s">
         <v>37</v>
       </c>
-      <c r="M21" s="18" t="s">
-        <v>177</v>
-      </c>
-      <c r="N21" s="17" t="s">
+      <c r="M21" s="22" t="s">
+        <v>176</v>
+      </c>
+      <c r="N21" s="21" t="s">
         <v>41</v>
       </c>
-      <c r="O21" s="17" t="s">
+      <c r="O21" s="21" t="s">
         <v>39</v>
       </c>
-      <c r="P21" s="17" t="s">
+      <c r="P21" s="21" t="s">
         <v>41</v>
       </c>
-      <c r="Q21" s="17" t="s">
+      <c r="Q21" s="21" t="s">
         <v>39</v>
       </c>
-      <c r="R21" s="17" t="s">
+      <c r="R21" s="21" t="s">
         <v>41</v>
       </c>
-      <c r="S21" s="17" t="s">
+      <c r="S21" s="21" t="s">
         <v>39</v>
       </c>
-      <c r="T21" s="17" t="s">
+      <c r="T21" s="21" t="s">
         <v>41</v>
       </c>
-      <c r="U21" s="17" t="s">
+      <c r="U21" s="21" t="s">
         <v>39</v>
       </c>
-      <c r="V21" s="17" t="s">
+      <c r="V21" s="21" t="s">
         <v>41</v>
       </c>
-      <c r="W21" s="17" t="s">
+      <c r="W21" s="21" t="s">
         <v>39</v>
       </c>
-      <c r="X21" s="17" t="s">
+      <c r="X21" s="21" t="s">
         <v>41</v>
       </c>
-      <c r="Y21" s="17" t="s">
+      <c r="Y21" s="21" t="s">
         <v>39</v>
       </c>
-      <c r="Z21" s="17" t="s">
+      <c r="Z21" s="21" t="s">
         <v>41</v>
       </c>
-      <c r="AA21" s="17" t="s">
+      <c r="AA21" s="21" t="s">
         <v>39</v>
       </c>
-      <c r="AB21" s="17" t="s">
+      <c r="AB21" s="21" t="s">
         <v>41</v>
       </c>
-      <c r="AC21" s="17" t="s">
+      <c r="AC21" s="21" t="s">
         <v>39</v>
       </c>
-      <c r="AD21" s="17" t="s">
+      <c r="AD21" s="21" t="s">
         <v>41</v>
       </c>
-      <c r="AE21" s="17" t="s">
+      <c r="AE21" s="21" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="22" spans="2:38" x14ac:dyDescent="0.25">
-      <c r="J22" s="8" t="s">
-        <v>146</v>
-      </c>
-      <c r="K22" s="9">
+      <c r="J22" s="9" t="s">
+        <v>145</v>
+      </c>
+      <c r="K22" s="10">
         <v>49000</v>
       </c>
-      <c r="M22" s="8" t="s">
-        <v>146</v>
-      </c>
-      <c r="N22" s="23">
+      <c r="M22" s="9" t="s">
+        <v>145</v>
+      </c>
+      <c r="N22" s="27">
         <v>18000</v>
       </c>
-      <c r="O22" s="23">
+      <c r="O22" s="27">
         <v>1</v>
       </c>
-      <c r="P22" s="23">
+      <c r="P22" s="27">
         <v>3000</v>
       </c>
-      <c r="Q22" s="19">
+      <c r="Q22" s="23">
         <v>1</v>
       </c>
-      <c r="R22" s="19">
+      <c r="R22" s="23">
         <v>10000</v>
       </c>
-      <c r="S22" s="19">
+      <c r="S22" s="23">
         <v>1</v>
       </c>
-      <c r="T22" s="19">
+      <c r="T22" s="23">
         <v>18000</v>
       </c>
-      <c r="U22" s="19">
+      <c r="U22" s="23">
         <v>1</v>
       </c>
-      <c r="V22" s="19"/>
-      <c r="W22" s="19"/>
-      <c r="X22" s="19"/>
-      <c r="Y22" s="19"/>
-      <c r="Z22" s="19"/>
-      <c r="AA22" s="19"/>
-      <c r="AB22" s="19"/>
-      <c r="AC22" s="19"/>
-      <c r="AD22" s="19"/>
-      <c r="AE22" s="19"/>
-      <c r="AF22" s="19">
+      <c r="V22" s="23"/>
+      <c r="W22" s="23"/>
+      <c r="X22" s="23"/>
+      <c r="Y22" s="23"/>
+      <c r="Z22" s="23"/>
+      <c r="AA22" s="23"/>
+      <c r="AB22" s="23"/>
+      <c r="AC22" s="23"/>
+      <c r="AD22" s="23"/>
+      <c r="AE22" s="23"/>
+      <c r="AF22" s="23">
         <v>49000</v>
       </c>
-      <c r="AG22" s="19">
+      <c r="AG22" s="23">
         <v>4</v>
       </c>
     </row>
     <row r="23" spans="2:38" x14ac:dyDescent="0.25">
-      <c r="J23" s="8" t="s">
-        <v>151</v>
-      </c>
-      <c r="K23" s="9">
+      <c r="J23" s="9" t="s">
+        <v>150</v>
+      </c>
+      <c r="K23" s="10">
         <v>88600</v>
       </c>
-      <c r="M23" s="8" t="s">
-        <v>151</v>
-      </c>
-      <c r="N23" s="23">
+      <c r="M23" s="9" t="s">
+        <v>150</v>
+      </c>
+      <c r="N23" s="27">
         <v>25200</v>
       </c>
-      <c r="O23" s="23">
+      <c r="O23" s="27">
         <v>2</v>
       </c>
-      <c r="P23" s="23">
+      <c r="P23" s="27">
         <v>3000</v>
       </c>
-      <c r="Q23" s="19">
+      <c r="Q23" s="23">
         <v>1</v>
       </c>
-      <c r="R23" s="19">
+      <c r="R23" s="23">
         <v>10000</v>
       </c>
-      <c r="S23" s="19">
+      <c r="S23" s="23">
         <v>1</v>
       </c>
-      <c r="T23" s="19"/>
-      <c r="U23" s="19"/>
-      <c r="V23" s="19">
+      <c r="T23" s="23"/>
+      <c r="U23" s="23"/>
+      <c r="V23" s="23">
         <v>12600</v>
       </c>
-      <c r="W23" s="19">
+      <c r="W23" s="23">
         <v>1</v>
       </c>
-      <c r="X23" s="19">
+      <c r="X23" s="23">
         <v>12600</v>
       </c>
-      <c r="Y23" s="19">
+      <c r="Y23" s="23">
         <v>1</v>
       </c>
-      <c r="Z23" s="19">
+      <c r="Z23" s="23">
         <v>12600</v>
       </c>
-      <c r="AA23" s="19">
+      <c r="AA23" s="23">
         <v>1</v>
       </c>
-      <c r="AB23" s="19">
+      <c r="AB23" s="23">
         <v>12600</v>
       </c>
-      <c r="AC23" s="19">
+      <c r="AC23" s="23">
         <v>1</v>
       </c>
-      <c r="AD23" s="19"/>
-      <c r="AE23" s="19"/>
-      <c r="AF23" s="19">
+      <c r="AD23" s="23"/>
+      <c r="AE23" s="23"/>
+      <c r="AF23" s="23">
         <v>88600</v>
       </c>
-      <c r="AG23" s="19">
+      <c r="AG23" s="23">
         <v>8</v>
       </c>
     </row>
     <row r="24" spans="2:38" x14ac:dyDescent="0.25">
-      <c r="J24" s="8" t="s">
-        <v>167</v>
-      </c>
-      <c r="K24" s="9">
+      <c r="J24" s="9" t="s">
+        <v>166</v>
+      </c>
+      <c r="K24" s="10">
         <v>39000</v>
       </c>
-      <c r="M24" s="8" t="s">
-        <v>167</v>
-      </c>
-      <c r="N24" s="23">
+      <c r="M24" s="9" t="s">
+        <v>166</v>
+      </c>
+      <c r="N24" s="27">
         <v>18000</v>
       </c>
-      <c r="O24" s="23">
+      <c r="O24" s="27">
         <v>1</v>
       </c>
-      <c r="P24" s="23">
+      <c r="P24" s="27">
         <v>3000</v>
       </c>
-      <c r="Q24" s="19">
+      <c r="Q24" s="23">
         <v>1</v>
       </c>
-      <c r="R24" s="19"/>
-      <c r="S24" s="19"/>
-      <c r="T24" s="19"/>
-      <c r="U24" s="19"/>
-      <c r="V24" s="19"/>
-      <c r="W24" s="19"/>
-      <c r="X24" s="19"/>
-      <c r="Y24" s="19"/>
-      <c r="Z24" s="19"/>
-      <c r="AA24" s="19"/>
-      <c r="AB24" s="19"/>
-      <c r="AC24" s="19"/>
-      <c r="AD24" s="19">
+      <c r="R24" s="23"/>
+      <c r="S24" s="23"/>
+      <c r="T24" s="23"/>
+      <c r="U24" s="23"/>
+      <c r="V24" s="23"/>
+      <c r="W24" s="23"/>
+      <c r="X24" s="23"/>
+      <c r="Y24" s="23"/>
+      <c r="Z24" s="23"/>
+      <c r="AA24" s="23"/>
+      <c r="AB24" s="23"/>
+      <c r="AC24" s="23"/>
+      <c r="AD24" s="23">
         <v>18000</v>
       </c>
-      <c r="AE24" s="19">
+      <c r="AE24" s="23">
         <v>1</v>
       </c>
-      <c r="AF24" s="19">
+      <c r="AF24" s="23">
         <v>39000</v>
       </c>
-      <c r="AG24" s="19">
+      <c r="AG24" s="23">
         <v>3</v>
       </c>
     </row>
     <row r="25" spans="2:38" x14ac:dyDescent="0.25">
-      <c r="J25" s="8" t="s">
+      <c r="J25" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="K25" s="9">
+      <c r="K25" s="10">
         <v>176600</v>
       </c>
-      <c r="M25" s="8" t="s">
+      <c r="M25" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="N25" s="9">
+      <c r="N25" s="10">
         <v>61200</v>
       </c>
-      <c r="O25" s="9">
+      <c r="O25" s="10">
         <v>4</v>
       </c>
-      <c r="P25" s="9">
+      <c r="P25" s="10">
         <v>9000</v>
       </c>
-      <c r="Q25" s="9">
+      <c r="Q25" s="10">
         <v>3</v>
       </c>
-      <c r="R25" s="9">
+      <c r="R25" s="10">
         <v>20000</v>
       </c>
-      <c r="S25" s="9">
+      <c r="S25" s="10">
         <v>2</v>
       </c>
-      <c r="T25" s="9">
+      <c r="T25" s="10">
         <v>18000</v>
       </c>
-      <c r="U25" s="9">
+      <c r="U25" s="10">
         <v>1</v>
       </c>
-      <c r="V25" s="9">
+      <c r="V25" s="10">
         <v>12600</v>
       </c>
-      <c r="W25" s="9">
+      <c r="W25" s="10">
         <v>1</v>
       </c>
-      <c r="X25" s="9">
+      <c r="X25" s="10">
         <v>12600</v>
       </c>
-      <c r="Y25" s="9">
+      <c r="Y25" s="10">
         <v>1</v>
       </c>
-      <c r="Z25" s="9">
+      <c r="Z25" s="10">
         <v>12600</v>
       </c>
-      <c r="AA25" s="9">
+      <c r="AA25" s="10">
         <v>1</v>
       </c>
-      <c r="AB25" s="9">
+      <c r="AB25" s="10">
         <v>12600</v>
       </c>
-      <c r="AC25" s="9">
+      <c r="AC25" s="10">
         <v>1</v>
       </c>
-      <c r="AD25" s="9">
+      <c r="AD25" s="10">
         <v>18000</v>
       </c>
-      <c r="AE25" s="9">
+      <c r="AE25" s="10">
         <v>1</v>
       </c>
-      <c r="AF25" s="9">
+      <c r="AF25" s="10">
         <v>176600</v>
       </c>
-      <c r="AG25" s="9">
+      <c r="AG25" s="10">
         <v>15</v>
       </c>
     </row>
     <row r="26" spans="2:38" x14ac:dyDescent="0.25">
-      <c r="J26" s="24" t="s">
+      <c r="J26" s="28" t="s">
+        <v>174</v>
+      </c>
+      <c r="M26" s="31" t="s">
         <v>175</v>
-      </c>
-      <c r="M26" s="27" t="s">
-        <v>176</v>
       </c>
     </row>
     <row r="28" spans="2:38" x14ac:dyDescent="0.25">
@@ -10178,7 +10265,7 @@
         <v>1</v>
       </c>
       <c r="C1" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D1" t="s">
         <v>2</v>
@@ -10195,16 +10282,16 @@
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
+        <v>82</v>
+      </c>
+      <c r="B2" s="6">
+        <v>46149</v>
+      </c>
+      <c r="C2" t="s">
         <v>83</v>
       </c>
-      <c r="B2" s="5">
-        <v>46149</v>
-      </c>
-      <c r="C2" t="s">
+      <c r="D2" t="s">
         <v>84</v>
-      </c>
-      <c r="D2" t="s">
-        <v>85</v>
       </c>
       <c r="E2" t="s">
         <v>9</v>
@@ -10218,16 +10305,16 @@
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
+        <v>107</v>
+      </c>
+      <c r="B3" s="6">
+        <v>46151</v>
+      </c>
+      <c r="C3" t="s">
+        <v>83</v>
+      </c>
+      <c r="D3" t="s">
         <v>108</v>
-      </c>
-      <c r="B3" s="5">
-        <v>46151</v>
-      </c>
-      <c r="C3" t="s">
-        <v>84</v>
-      </c>
-      <c r="D3" t="s">
-        <v>109</v>
       </c>
       <c r="E3" t="s">
         <v>9</v>
@@ -10241,16 +10328,16 @@
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
+        <v>88</v>
+      </c>
+      <c r="B4" s="6">
+        <v>46149</v>
+      </c>
+      <c r="C4" t="s">
+        <v>83</v>
+      </c>
+      <c r="D4" t="s">
         <v>89</v>
-      </c>
-      <c r="B4" s="5">
-        <v>46149</v>
-      </c>
-      <c r="C4" t="s">
-        <v>84</v>
-      </c>
-      <c r="D4" t="s">
-        <v>90</v>
       </c>
       <c r="E4" t="s">
         <v>9</v>
@@ -10264,16 +10351,16 @@
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
+        <v>102</v>
+      </c>
+      <c r="B5" s="6">
+        <v>46150</v>
+      </c>
+      <c r="C5" t="s">
+        <v>83</v>
+      </c>
+      <c r="D5" t="s">
         <v>103</v>
-      </c>
-      <c r="B5" s="5">
-        <v>46150</v>
-      </c>
-      <c r="C5" t="s">
-        <v>84</v>
-      </c>
-      <c r="D5" t="s">
-        <v>104</v>
       </c>
       <c r="E5" t="s">
         <v>9</v>
@@ -10287,16 +10374,16 @@
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
+        <v>96</v>
+      </c>
+      <c r="B6" s="6">
+        <v>46150</v>
+      </c>
+      <c r="C6" t="s">
+        <v>83</v>
+      </c>
+      <c r="D6" t="s">
         <v>97</v>
-      </c>
-      <c r="B6" s="5">
-        <v>46150</v>
-      </c>
-      <c r="C6" t="s">
-        <v>84</v>
-      </c>
-      <c r="D6" t="s">
-        <v>98</v>
       </c>
       <c r="E6" t="s">
         <v>9</v>

--- a/Analyses Excel/Préparation_Stage_Academique_2026_(exercices_pratique).xlsx
+++ b/Analyses Excel/Préparation_Stage_Academique_2026_(exercices_pratique).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\JevainBkg\Projets\Datascience-roadmap\Analyses Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8E2A80A8-4FBA-40E7-80A4-40CE42A1091B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{63279DAA-7060-4E14-9B56-5DEE1547CC29}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13740" xr2:uid="{7D3A7277-DCDC-4547-AB5A-331124B03413}"/>
   </bookViews>

--- a/Analyses Excel/Préparation_Stage_Academique_2026_(exercices_pratique).xlsx
+++ b/Analyses Excel/Préparation_Stage_Academique_2026_(exercices_pratique).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\JevainBkg\Projets\Datascience-roadmap\Analyses Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8543D832-3090-4FF4-9DFD-79B738AAB22B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A9D179E2-7A7C-4F37-8C8F-FD0F3115AF0A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13740" activeTab="1" xr2:uid="{7D3A7277-DCDC-4547-AB5A-331124B03413}"/>
   </bookViews>
@@ -82,8 +82,30 @@
 </connections>
 </file>
 
+<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+  <metadataTypes count="1">
+    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
+  </metadataTypes>
+  <futureMetadata name="XLDAPR" count="1">
+    <bk>
+      <extLst>
+        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
+          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
+        </ext>
+      </extLst>
+    </bk>
+  </futureMetadata>
+  <cellMetadata count="1">
+    <bk>
+      <rc t="1" v="0"/>
+    </bk>
+  </cellMetadata>
+</metadata>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="683" uniqueCount="193">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="675" uniqueCount="194">
   <si>
     <t>transaction_id</t>
   </si>
@@ -708,12 +730,15 @@
   <si>
     <t>Segmentation des clients</t>
   </si>
+  <si>
+    <t xml:space="preserve">Canal fav </t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -766,8 +791,15 @@
       <name val="Aptos Display"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="16">
+  <fills count="13">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -840,26 +872,8 @@
         <bgColor theme="9" tint="0.39997558519241921"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.39997558519241921"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.79998168889431442"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="-0.249977111117893"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="4">
+  <borders count="5">
     <border>
       <left/>
       <right/>
@@ -890,6 +904,15 @@
       <diagonal/>
     </border>
     <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
       <left style="thin">
         <color indexed="64"/>
       </left>
@@ -908,7 +931,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="55">
+  <cellXfs count="56">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -964,7 +987,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1023,20 +1045,206 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="13" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="14" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="15" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="555">
+  <dxfs count="172">
+    <dxf>
+      <font>
+        <color rgb="FFFF0000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="9" tint="0.39997558519241921"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1"/>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="5"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="5"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="5" tint="0.39997558519241921"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="5" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="5" tint="-0.249977111117893"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="5" tint="0.39997558519241921"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="5" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="5" tint="-0.249977111117893"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="5" tint="0.39997558519241921"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFFF0000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFFF0000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFFF0000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFFF0000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFFF0000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFFF0000"/>
+      </font>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -1128,73 +1336,63 @@
       </fill>
     </dxf>
     <dxf>
+      <alignment horizontal="center"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center"/>
+    </dxf>
+    <dxf>
       <fill>
         <patternFill patternType="solid">
-          <bgColor theme="9" tint="0.39997558519241921"/>
+          <fgColor indexed="64"/>
+          <bgColor theme="5" tint="0.39997558519241921"/>
         </patternFill>
       </fill>
     </dxf>
     <dxf>
-      <alignment wrapText="1"/>
-    </dxf>
-    <dxf>
-      <alignment wrapText="1"/>
-    </dxf>
-    <dxf>
-      <alignment wrapText="1"/>
-    </dxf>
-    <dxf>
-      <alignment wrapText="1"/>
-    </dxf>
-    <dxf>
-      <alignment wrapText="1"/>
-    </dxf>
-    <dxf>
-      <alignment wrapText="1"/>
-    </dxf>
-    <dxf>
-      <alignment wrapText="1"/>
-    </dxf>
-    <dxf>
-      <alignment wrapText="1"/>
-    </dxf>
-    <dxf>
-      <alignment wrapText="1"/>
-    </dxf>
-    <dxf>
-      <alignment wrapText="1"/>
-    </dxf>
-    <dxf>
-      <alignment wrapText="1"/>
-    </dxf>
-    <dxf>
-      <alignment wrapText="1"/>
-    </dxf>
-    <dxf>
       <fill>
-        <patternFill>
-          <bgColor theme="0"/>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="5" tint="-0.249977111117893"/>
         </patternFill>
       </fill>
     </dxf>
     <dxf>
       <fill>
         <patternFill patternType="solid">
-          <bgColor theme="5"/>
+          <fgColor indexed="64"/>
+          <bgColor theme="5" tint="0.79998168889431442"/>
         </patternFill>
       </fill>
     </dxf>
     <dxf>
       <fill>
-        <patternFill>
-          <bgColor theme="5"/>
+        <patternFill patternType="solid">
+          <bgColor theme="5" tint="0.39997558519241921"/>
         </patternFill>
       </fill>
     </dxf>
     <dxf>
       <fill>
-        <patternFill>
-          <bgColor theme="5"/>
+        <patternFill patternType="solid">
+          <bgColor theme="5" tint="-0.249977111117893"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="5" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="5" tint="0.39997558519241921"/>
         </patternFill>
       </fill>
     </dxf>
@@ -1207,1931 +1405,10 @@
       </fill>
     </dxf>
     <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="5" tint="0.39997558519241921"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="5" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="5" tint="-0.249977111117893"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="5" tint="0.39997558519241921"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="5" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="5" tint="-0.249977111117893"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="5" tint="0.39997558519241921"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="9" tint="0.39997558519241921"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <alignment wrapText="1"/>
-    </dxf>
-    <dxf>
-      <alignment wrapText="1"/>
-    </dxf>
-    <dxf>
-      <alignment wrapText="1"/>
-    </dxf>
-    <dxf>
-      <alignment wrapText="1"/>
-    </dxf>
-    <dxf>
-      <alignment wrapText="1"/>
-    </dxf>
-    <dxf>
-      <alignment wrapText="1"/>
-    </dxf>
-    <dxf>
-      <alignment wrapText="1"/>
-    </dxf>
-    <dxf>
-      <alignment wrapText="1"/>
-    </dxf>
-    <dxf>
-      <alignment wrapText="1"/>
-    </dxf>
-    <dxf>
-      <alignment wrapText="1"/>
-    </dxf>
-    <dxf>
-      <alignment wrapText="1"/>
-    </dxf>
-    <dxf>
-      <alignment wrapText="1"/>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="5"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="5"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="5"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="5"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="5" tint="0.39997558519241921"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="5" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="5" tint="-0.249977111117893"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="5" tint="0.39997558519241921"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="5" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="5" tint="-0.249977111117893"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="5" tint="0.39997558519241921"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="9" tint="0.39997558519241921"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <alignment wrapText="1"/>
-    </dxf>
-    <dxf>
-      <alignment wrapText="1"/>
-    </dxf>
-    <dxf>
-      <alignment wrapText="1"/>
-    </dxf>
-    <dxf>
-      <alignment wrapText="1"/>
-    </dxf>
-    <dxf>
-      <alignment wrapText="1"/>
-    </dxf>
-    <dxf>
-      <alignment wrapText="1"/>
-    </dxf>
-    <dxf>
-      <alignment wrapText="1"/>
-    </dxf>
-    <dxf>
-      <alignment wrapText="1"/>
-    </dxf>
-    <dxf>
-      <alignment wrapText="1"/>
-    </dxf>
-    <dxf>
-      <alignment wrapText="1"/>
-    </dxf>
-    <dxf>
-      <alignment wrapText="1"/>
-    </dxf>
-    <dxf>
-      <alignment wrapText="1"/>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="5"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="5"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="5"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="5"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="5" tint="0.39997558519241921"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="5" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="5" tint="-0.249977111117893"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="5" tint="0.39997558519241921"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="5" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="5" tint="-0.249977111117893"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="5" tint="0.39997558519241921"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="9" tint="0.39997558519241921"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <alignment wrapText="1"/>
-    </dxf>
-    <dxf>
-      <alignment wrapText="1"/>
-    </dxf>
-    <dxf>
-      <alignment wrapText="1"/>
-    </dxf>
-    <dxf>
-      <alignment wrapText="1"/>
-    </dxf>
-    <dxf>
-      <alignment wrapText="1"/>
-    </dxf>
-    <dxf>
-      <alignment wrapText="1"/>
-    </dxf>
-    <dxf>
-      <alignment wrapText="1"/>
-    </dxf>
-    <dxf>
-      <alignment wrapText="1"/>
-    </dxf>
-    <dxf>
-      <alignment wrapText="1"/>
-    </dxf>
-    <dxf>
-      <alignment wrapText="1"/>
-    </dxf>
-    <dxf>
-      <alignment wrapText="1"/>
-    </dxf>
-    <dxf>
-      <alignment wrapText="1"/>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="5"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="5"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="5"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="5"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="5" tint="0.39997558519241921"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="5" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="5" tint="-0.249977111117893"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="5" tint="0.39997558519241921"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="5" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="5" tint="-0.249977111117893"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="5" tint="0.39997558519241921"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="5" tint="0.39997558519241921"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="5" tint="-0.249977111117893"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="9" tint="0.39997558519241921"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <alignment wrapText="1"/>
-    </dxf>
-    <dxf>
-      <alignment wrapText="1"/>
-    </dxf>
-    <dxf>
-      <alignment wrapText="1"/>
-    </dxf>
-    <dxf>
-      <alignment wrapText="1"/>
-    </dxf>
-    <dxf>
-      <alignment wrapText="1"/>
-    </dxf>
-    <dxf>
-      <alignment wrapText="1"/>
-    </dxf>
-    <dxf>
-      <alignment wrapText="1"/>
-    </dxf>
-    <dxf>
-      <alignment wrapText="1"/>
-    </dxf>
-    <dxf>
-      <alignment wrapText="1"/>
-    </dxf>
-    <dxf>
-      <alignment wrapText="1"/>
-    </dxf>
-    <dxf>
-      <alignment wrapText="1"/>
-    </dxf>
-    <dxf>
-      <alignment wrapText="1"/>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="5"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="5"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="5"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="5"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="5" tint="0.39997558519241921"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="5" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="5" tint="-0.249977111117893"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="5" tint="0.39997558519241921"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="5" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="9" tint="0.39997558519241921"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <alignment wrapText="1"/>
-    </dxf>
-    <dxf>
-      <alignment wrapText="1"/>
-    </dxf>
-    <dxf>
-      <alignment wrapText="1"/>
-    </dxf>
-    <dxf>
-      <alignment wrapText="1"/>
-    </dxf>
-    <dxf>
-      <alignment wrapText="1"/>
-    </dxf>
-    <dxf>
-      <alignment wrapText="1"/>
-    </dxf>
-    <dxf>
-      <alignment wrapText="1"/>
-    </dxf>
-    <dxf>
-      <alignment wrapText="1"/>
-    </dxf>
-    <dxf>
-      <alignment wrapText="1"/>
-    </dxf>
-    <dxf>
-      <alignment wrapText="1"/>
-    </dxf>
-    <dxf>
-      <alignment wrapText="1"/>
-    </dxf>
-    <dxf>
-      <alignment wrapText="1"/>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="5"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="5"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="5"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="5"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="5" tint="0.39997558519241921"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="5" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="5" tint="-0.249977111117893"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="5" tint="0.39997558519241921"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="5" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="5" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="9" tint="0.39997558519241921"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <alignment wrapText="1"/>
-    </dxf>
-    <dxf>
-      <alignment wrapText="1"/>
-    </dxf>
-    <dxf>
-      <alignment wrapText="1"/>
-    </dxf>
-    <dxf>
-      <alignment wrapText="1"/>
-    </dxf>
-    <dxf>
-      <alignment wrapText="1"/>
-    </dxf>
-    <dxf>
-      <alignment wrapText="1"/>
-    </dxf>
-    <dxf>
-      <alignment wrapText="1"/>
-    </dxf>
-    <dxf>
-      <alignment wrapText="1"/>
-    </dxf>
-    <dxf>
-      <alignment wrapText="1"/>
-    </dxf>
-    <dxf>
-      <alignment wrapText="1"/>
-    </dxf>
-    <dxf>
-      <alignment wrapText="1"/>
-    </dxf>
-    <dxf>
-      <alignment wrapText="1"/>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="5"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="5"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="5"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="5"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="5" tint="0.39997558519241921"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="5" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="5" tint="-0.249977111117893"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="5" tint="0.39997558519241921"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="5" tint="0.39997558519241921"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="9" tint="0.39997558519241921"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <alignment wrapText="1"/>
-    </dxf>
-    <dxf>
-      <alignment wrapText="1"/>
-    </dxf>
-    <dxf>
-      <alignment wrapText="1"/>
-    </dxf>
-    <dxf>
-      <alignment wrapText="1"/>
-    </dxf>
-    <dxf>
-      <alignment wrapText="1"/>
-    </dxf>
-    <dxf>
-      <alignment wrapText="1"/>
-    </dxf>
-    <dxf>
-      <alignment wrapText="1"/>
-    </dxf>
-    <dxf>
-      <alignment wrapText="1"/>
-    </dxf>
-    <dxf>
-      <alignment wrapText="1"/>
-    </dxf>
-    <dxf>
-      <alignment wrapText="1"/>
-    </dxf>
-    <dxf>
-      <alignment wrapText="1"/>
-    </dxf>
-    <dxf>
-      <alignment wrapText="1"/>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="5"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="5"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="5"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="5"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="5" tint="0.39997558519241921"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="5" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="5" tint="-0.249977111117893"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="5" tint="-0.249977111117893"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="9" tint="0.39997558519241921"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <alignment wrapText="1"/>
-    </dxf>
-    <dxf>
-      <alignment wrapText="1"/>
-    </dxf>
-    <dxf>
-      <alignment wrapText="1"/>
-    </dxf>
-    <dxf>
-      <alignment wrapText="1"/>
-    </dxf>
-    <dxf>
-      <alignment wrapText="1"/>
-    </dxf>
-    <dxf>
-      <alignment wrapText="1"/>
-    </dxf>
-    <dxf>
-      <alignment wrapText="1"/>
-    </dxf>
-    <dxf>
-      <alignment wrapText="1"/>
-    </dxf>
-    <dxf>
-      <alignment wrapText="1"/>
-    </dxf>
-    <dxf>
-      <alignment wrapText="1"/>
-    </dxf>
-    <dxf>
-      <alignment wrapText="1"/>
-    </dxf>
-    <dxf>
-      <alignment wrapText="1"/>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="5"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="5"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="5"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="5"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="5" tint="0.39997558519241921"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="5" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="5" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="9" tint="0.39997558519241921"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <alignment wrapText="1"/>
-    </dxf>
-    <dxf>
-      <alignment wrapText="1"/>
-    </dxf>
-    <dxf>
-      <alignment wrapText="1"/>
-    </dxf>
-    <dxf>
-      <alignment wrapText="1"/>
-    </dxf>
-    <dxf>
-      <alignment wrapText="1"/>
-    </dxf>
-    <dxf>
-      <alignment wrapText="1"/>
-    </dxf>
-    <dxf>
-      <alignment wrapText="1"/>
-    </dxf>
-    <dxf>
-      <alignment wrapText="1"/>
-    </dxf>
-    <dxf>
-      <alignment wrapText="1"/>
-    </dxf>
-    <dxf>
-      <alignment wrapText="1"/>
-    </dxf>
-    <dxf>
-      <alignment wrapText="1"/>
-    </dxf>
-    <dxf>
-      <alignment wrapText="1"/>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="5"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="5"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="5"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="5"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="5" tint="0.39997558519241921"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="5" tint="0.39997558519241921"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="9" tint="0.39997558519241921"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <alignment wrapText="1"/>
-    </dxf>
-    <dxf>
-      <alignment wrapText="1"/>
-    </dxf>
-    <dxf>
-      <alignment wrapText="1"/>
-    </dxf>
-    <dxf>
-      <alignment wrapText="1"/>
-    </dxf>
-    <dxf>
-      <alignment wrapText="1"/>
-    </dxf>
-    <dxf>
-      <alignment wrapText="1"/>
-    </dxf>
-    <dxf>
-      <alignment wrapText="1"/>
-    </dxf>
-    <dxf>
-      <alignment wrapText="1"/>
-    </dxf>
-    <dxf>
-      <alignment wrapText="1"/>
-    </dxf>
-    <dxf>
-      <alignment wrapText="1"/>
-    </dxf>
-    <dxf>
-      <alignment wrapText="1"/>
-    </dxf>
-    <dxf>
-      <alignment wrapText="1"/>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="5"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="5"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="5"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="5"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="9" tint="0.39997558519241921"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <alignment wrapText="1"/>
-    </dxf>
-    <dxf>
-      <alignment wrapText="1"/>
-    </dxf>
-    <dxf>
-      <alignment wrapText="1"/>
-    </dxf>
-    <dxf>
-      <alignment wrapText="1"/>
-    </dxf>
-    <dxf>
-      <alignment wrapText="1"/>
-    </dxf>
-    <dxf>
-      <alignment wrapText="1"/>
-    </dxf>
-    <dxf>
-      <alignment wrapText="1"/>
-    </dxf>
-    <dxf>
-      <alignment wrapText="1"/>
-    </dxf>
-    <dxf>
-      <alignment wrapText="1"/>
-    </dxf>
-    <dxf>
-      <alignment wrapText="1"/>
-    </dxf>
-    <dxf>
-      <alignment wrapText="1"/>
-    </dxf>
-    <dxf>
-      <alignment wrapText="1"/>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="5"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="5"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="5"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="5"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="9" tint="0.39997558519241921"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <alignment wrapText="1"/>
-    </dxf>
-    <dxf>
-      <alignment wrapText="1"/>
-    </dxf>
-    <dxf>
-      <alignment wrapText="1"/>
-    </dxf>
-    <dxf>
-      <alignment wrapText="1"/>
-    </dxf>
-    <dxf>
-      <alignment wrapText="1"/>
-    </dxf>
-    <dxf>
-      <alignment wrapText="1"/>
-    </dxf>
-    <dxf>
-      <alignment wrapText="1"/>
-    </dxf>
-    <dxf>
-      <alignment wrapText="1"/>
-    </dxf>
-    <dxf>
-      <alignment wrapText="1"/>
-    </dxf>
-    <dxf>
-      <alignment wrapText="1"/>
-    </dxf>
-    <dxf>
-      <alignment wrapText="1"/>
-    </dxf>
-    <dxf>
-      <alignment wrapText="1"/>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="5"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="5"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="5"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="5"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="9" tint="0.39997558519241921"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <alignment wrapText="1"/>
-    </dxf>
-    <dxf>
-      <alignment wrapText="1"/>
-    </dxf>
-    <dxf>
-      <alignment wrapText="1"/>
-    </dxf>
-    <dxf>
-      <alignment wrapText="1"/>
-    </dxf>
-    <dxf>
-      <alignment wrapText="1"/>
-    </dxf>
-    <dxf>
-      <alignment wrapText="1"/>
-    </dxf>
-    <dxf>
-      <alignment wrapText="1"/>
-    </dxf>
-    <dxf>
-      <alignment wrapText="1"/>
-    </dxf>
-    <dxf>
-      <alignment wrapText="1"/>
-    </dxf>
-    <dxf>
-      <alignment wrapText="1"/>
-    </dxf>
-    <dxf>
-      <alignment wrapText="1"/>
-    </dxf>
-    <dxf>
-      <alignment wrapText="1"/>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="5"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="5"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="5"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="5"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="9" tint="0.39997558519241921"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <alignment wrapText="1"/>
-    </dxf>
-    <dxf>
-      <alignment wrapText="1"/>
-    </dxf>
-    <dxf>
-      <alignment wrapText="1"/>
-    </dxf>
-    <dxf>
-      <alignment wrapText="1"/>
-    </dxf>
-    <dxf>
-      <alignment wrapText="1"/>
-    </dxf>
-    <dxf>
-      <alignment wrapText="1"/>
-    </dxf>
-    <dxf>
-      <alignment wrapText="1"/>
-    </dxf>
-    <dxf>
-      <alignment wrapText="1"/>
-    </dxf>
-    <dxf>
-      <alignment wrapText="1"/>
-    </dxf>
-    <dxf>
-      <alignment wrapText="1"/>
-    </dxf>
-    <dxf>
-      <alignment wrapText="1"/>
-    </dxf>
-    <dxf>
-      <alignment wrapText="1"/>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="5"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="5"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="5"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="5"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="9" tint="0.39997558519241921"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <alignment wrapText="1"/>
-    </dxf>
-    <dxf>
-      <alignment wrapText="1"/>
-    </dxf>
-    <dxf>
-      <alignment wrapText="1"/>
-    </dxf>
-    <dxf>
-      <alignment wrapText="1"/>
-    </dxf>
-    <dxf>
-      <alignment wrapText="1"/>
-    </dxf>
-    <dxf>
-      <alignment wrapText="1"/>
-    </dxf>
-    <dxf>
-      <alignment wrapText="1"/>
-    </dxf>
-    <dxf>
-      <alignment wrapText="1"/>
-    </dxf>
-    <dxf>
-      <alignment wrapText="1"/>
-    </dxf>
-    <dxf>
-      <alignment wrapText="1"/>
-    </dxf>
-    <dxf>
-      <alignment wrapText="1"/>
-    </dxf>
-    <dxf>
-      <alignment wrapText="1"/>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="5"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="5"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="5"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="5"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="5"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
       <alignment horizontal="center"/>
     </dxf>
     <dxf>
       <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="9" tint="0.39997558519241921"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <alignment wrapText="1"/>
-    </dxf>
-    <dxf>
-      <alignment wrapText="1"/>
-    </dxf>
-    <dxf>
-      <alignment wrapText="1"/>
-    </dxf>
-    <dxf>
-      <alignment wrapText="1"/>
-    </dxf>
-    <dxf>
-      <alignment wrapText="1"/>
-    </dxf>
-    <dxf>
-      <alignment wrapText="1"/>
-    </dxf>
-    <dxf>
-      <alignment wrapText="1"/>
-    </dxf>
-    <dxf>
-      <alignment wrapText="1"/>
-    </dxf>
-    <dxf>
-      <alignment wrapText="1"/>
-    </dxf>
-    <dxf>
-      <alignment wrapText="1"/>
-    </dxf>
-    <dxf>
-      <alignment wrapText="1"/>
-    </dxf>
-    <dxf>
-      <alignment wrapText="1"/>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="5"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="5"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="5"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="9" tint="0.39997558519241921"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <alignment wrapText="1"/>
-    </dxf>
-    <dxf>
-      <alignment wrapText="1"/>
-    </dxf>
-    <dxf>
-      <alignment wrapText="1"/>
-    </dxf>
-    <dxf>
-      <alignment wrapText="1"/>
-    </dxf>
-    <dxf>
-      <alignment wrapText="1"/>
-    </dxf>
-    <dxf>
-      <alignment wrapText="1"/>
-    </dxf>
-    <dxf>
-      <alignment wrapText="1"/>
-    </dxf>
-    <dxf>
-      <alignment wrapText="1"/>
-    </dxf>
-    <dxf>
-      <alignment wrapText="1"/>
-    </dxf>
-    <dxf>
-      <alignment wrapText="1"/>
-    </dxf>
-    <dxf>
-      <alignment wrapText="1"/>
-    </dxf>
-    <dxf>
-      <alignment wrapText="1"/>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="5"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="5"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="5"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="9" tint="0.39997558519241921"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <alignment wrapText="1"/>
-    </dxf>
-    <dxf>
-      <alignment wrapText="1"/>
-    </dxf>
-    <dxf>
-      <alignment wrapText="1"/>
-    </dxf>
-    <dxf>
-      <alignment wrapText="1"/>
-    </dxf>
-    <dxf>
-      <alignment wrapText="1"/>
-    </dxf>
-    <dxf>
-      <alignment wrapText="1"/>
-    </dxf>
-    <dxf>
-      <alignment wrapText="1"/>
-    </dxf>
-    <dxf>
-      <alignment wrapText="1"/>
-    </dxf>
-    <dxf>
-      <alignment wrapText="1"/>
-    </dxf>
-    <dxf>
-      <alignment wrapText="1"/>
-    </dxf>
-    <dxf>
-      <alignment wrapText="1"/>
-    </dxf>
-    <dxf>
-      <alignment wrapText="1"/>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="5"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="5"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="5"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="9" tint="0.39997558519241921"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <alignment wrapText="1"/>
-    </dxf>
-    <dxf>
-      <alignment wrapText="1"/>
-    </dxf>
-    <dxf>
-      <alignment wrapText="1"/>
-    </dxf>
-    <dxf>
-      <alignment wrapText="1"/>
-    </dxf>
-    <dxf>
-      <alignment wrapText="1"/>
-    </dxf>
-    <dxf>
-      <alignment wrapText="1"/>
-    </dxf>
-    <dxf>
-      <alignment wrapText="1"/>
-    </dxf>
-    <dxf>
-      <alignment wrapText="1"/>
-    </dxf>
-    <dxf>
-      <alignment wrapText="1"/>
-    </dxf>
-    <dxf>
-      <alignment wrapText="1"/>
-    </dxf>
-    <dxf>
-      <alignment wrapText="1"/>
-    </dxf>
-    <dxf>
-      <alignment wrapText="1"/>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="5"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="5"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="5"/>
-        </patternFill>
-      </fill>
     </dxf>
     <dxf>
       <numFmt numFmtId="19" formatCode="dd/mm/yyyy"/>
@@ -3473,20 +1750,6 @@
     </dxf>
     <dxf>
       <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="5"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="5"/>
-        </patternFill>
-      </fill>
     </dxf>
     <dxf>
       <fill>
@@ -3695,7 +1958,7 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>7</xdr:col>
-      <xdr:colOff>730249</xdr:colOff>
+      <xdr:colOff>698499</xdr:colOff>
       <xdr:row>83</xdr:row>
       <xdr:rowOff>179917</xdr:rowOff>
     </xdr:to>
@@ -3735,7 +1998,7 @@
           </xdr:nvSpPr>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="476250" y="19547417"/>
+              <a:off x="476250" y="18796000"/>
               <a:ext cx="6117166" cy="941917"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
@@ -4825,7 +3088,7 @@
     <dataField name="Somme de montant_fc" fld="5" baseField="0" baseItem="0"/>
   </dataFields>
   <formats count="6">
-    <format dxfId="550">
+    <format dxfId="167">
       <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
         <references count="1">
           <reference field="3" count="1">
@@ -4834,7 +3097,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="549">
+    <format dxfId="166">
       <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
         <references count="1">
           <reference field="3" count="1">
@@ -4843,7 +3106,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="548">
+    <format dxfId="165">
       <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
         <references count="1">
           <reference field="3" count="1">
@@ -4852,7 +3115,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="547">
+    <format dxfId="164">
       <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
         <references count="1">
           <reference field="3" count="1">
@@ -4861,7 +3124,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="546">
+    <format dxfId="163">
       <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
         <references count="1">
           <reference field="3" count="1">
@@ -4870,7 +3133,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="545">
+    <format dxfId="162">
       <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
         <references count="1">
           <reference field="3" count="1">
@@ -4981,10 +3244,10 @@
     <dataField name="Somme de montant_fc" fld="6" baseField="0" baseItem="0"/>
   </dataFields>
   <formats count="2">
-    <format dxfId="507">
+    <format dxfId="126">
       <pivotArea field="4" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
     </format>
-    <format dxfId="506">
+    <format dxfId="125">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="1">
           <reference field="4294967294" count="2">
@@ -5107,10 +3370,10 @@
     <dataField name="Somme de montant_fc" fld="6" baseField="0" baseItem="0"/>
   </dataFields>
   <formats count="5">
-    <format dxfId="512">
+    <format dxfId="131">
       <pivotArea field="2" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
     </format>
-    <format dxfId="511">
+    <format dxfId="130">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="1">
           <reference field="4294967294" count="2">
@@ -5120,7 +3383,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="510">
+    <format dxfId="129">
       <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
         <references count="1">
           <reference field="2" count="2">
@@ -5130,7 +3393,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="509">
+    <format dxfId="128">
       <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
         <references count="1">
           <reference field="2" count="2">
@@ -5140,7 +3403,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="508">
+    <format dxfId="127">
       <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
         <references count="1">
           <reference field="2" count="2">
@@ -5322,10 +3585,10 @@
     <dataField name="Somme de montant_fc" fld="5" baseField="0" baseItem="0"/>
   </dataFields>
   <formats count="2">
-    <format dxfId="492">
+    <format dxfId="111">
       <pivotArea field="2" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
     </format>
-    <format dxfId="491">
+    <format dxfId="110">
       <pivotArea dataOnly="0" labelOnly="1" grandCol="1" outline="0" fieldPosition="0"/>
     </format>
   </formats>
@@ -5406,13 +3669,13 @@
     <dataField name="Nombre de transaction_id" fld="0" subtotal="count" baseField="0" baseItem="0"/>
   </dataFields>
   <formats count="3">
-    <format dxfId="495">
+    <format dxfId="114">
       <pivotArea field="4" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
     </format>
-    <format dxfId="494">
+    <format dxfId="113">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
     </format>
-    <format dxfId="493">
+    <format dxfId="112">
       <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
         <references count="1">
           <reference field="4" count="1">
@@ -5503,10 +3766,10 @@
     <dataField name="Nombre de transaction_id" fld="0" subtotal="count" baseField="0" baseItem="0"/>
   </dataFields>
   <formats count="2">
-    <format dxfId="497">
+    <format dxfId="116">
       <pivotArea field="3" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
     </format>
-    <format dxfId="496">
+    <format dxfId="115">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
     </format>
   </formats>
@@ -5649,10 +3912,10 @@
     <dataField name="Nombre de transaction_id" fld="0" subtotal="count" baseField="0" baseItem="0"/>
   </dataFields>
   <formats count="2">
-    <format dxfId="499">
+    <format dxfId="118">
       <pivotArea field="2" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
     </format>
-    <format dxfId="498">
+    <format dxfId="117">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
     </format>
   </formats>
@@ -5737,10 +4000,10 @@
     <dataField name="CA" fld="5" baseField="6" baseItem="0"/>
   </dataFields>
   <formats count="2">
-    <format dxfId="446">
+    <format dxfId="65">
       <pivotArea field="6" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
     </format>
-    <format dxfId="445">
+    <format dxfId="64">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
     </format>
   </formats>
@@ -5875,7 +4138,7 @@
     <dataField name="Nombre de transaction_id" fld="0" subtotal="count" baseField="0" baseItem="0"/>
   </dataFields>
   <formats count="8">
-    <format dxfId="454">
+    <format dxfId="73">
       <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
         <references count="2">
           <reference field="3" count="1" selected="0">
@@ -5887,7 +4150,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="453">
+    <format dxfId="72">
       <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
         <references count="2">
           <reference field="3" count="1" selected="0">
@@ -5899,7 +4162,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="452">
+    <format dxfId="71">
       <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
         <references count="2">
           <reference field="3" count="1" selected="0">
@@ -5911,7 +4174,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="451">
+    <format dxfId="70">
       <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
         <references count="2">
           <reference field="3" count="1" selected="0">
@@ -5923,20 +4186,20 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="450">
+    <format dxfId="69">
       <pivotArea field="6" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
     </format>
-    <format dxfId="449">
+    <format dxfId="68">
       <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
         <references count="1">
           <reference field="3" count="0"/>
         </references>
       </pivotArea>
     </format>
-    <format dxfId="448">
+    <format dxfId="67">
       <pivotArea dataOnly="0" labelOnly="1" grandCol="1" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="447">
+    <format dxfId="66">
       <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
         <references count="2">
           <reference field="3" count="1" selected="0">
@@ -6049,7 +4312,7 @@
     <dataField name="Nombre de transaction_id" fld="0" subtotal="count" baseField="0" baseItem="0"/>
   </dataFields>
   <formats count="6">
-    <format dxfId="460">
+    <format dxfId="79">
       <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
         <references count="2">
           <reference field="2" count="4" selected="0">
@@ -6064,7 +4327,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="459">
+    <format dxfId="78">
       <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
         <references count="2">
           <reference field="2" count="1" selected="0">
@@ -6076,7 +4339,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="458">
+    <format dxfId="77">
       <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
         <references count="2">
           <reference field="2" count="1" selected="0">
@@ -6088,13 +4351,13 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="457">
+    <format dxfId="76">
       <pivotArea type="origin" dataOnly="0" labelOnly="1" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="456">
+    <format dxfId="75">
       <pivotArea field="2" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisCol" fieldPosition="0"/>
     </format>
-    <format dxfId="455">
+    <format dxfId="74">
       <pivotArea type="topRight" dataOnly="0" labelOnly="1" outline="0" fieldPosition="0"/>
     </format>
   </formats>
@@ -6271,29 +4534,29 @@
     <dataField name="Nombre de transaction_id" fld="0" subtotal="count" baseField="0" baseItem="0"/>
   </dataFields>
   <formats count="24">
-    <format dxfId="484">
+    <format dxfId="103">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
     </format>
-    <format dxfId="483">
+    <format dxfId="102">
       <pivotArea type="origin" dataOnly="0" labelOnly="1" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="482">
+    <format dxfId="101">
       <pivotArea field="2" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisCol" fieldPosition="0"/>
     </format>
-    <format dxfId="481">
+    <format dxfId="100">
       <pivotArea type="topRight" dataOnly="0" labelOnly="1" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="480">
+    <format dxfId="99">
       <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
         <references count="1">
           <reference field="6" count="0"/>
         </references>
       </pivotArea>
     </format>
-    <format dxfId="479">
+    <format dxfId="98">
       <pivotArea field="6" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
     </format>
-    <format dxfId="478">
+    <format dxfId="97">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="2">
           <reference field="4294967294" count="2">
@@ -6306,7 +4569,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="477">
+    <format dxfId="96">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="2">
           <reference field="4294967294" count="2">
@@ -6319,7 +4582,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="476">
+    <format dxfId="95">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="2">
           <reference field="4294967294" count="2">
@@ -6332,7 +4595,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="475">
+    <format dxfId="94">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="2">
           <reference field="4294967294" count="2">
@@ -6345,7 +4608,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="474">
+    <format dxfId="93">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="2">
           <reference field="4294967294" count="2">
@@ -6358,7 +4621,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="473">
+    <format dxfId="92">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="2">
           <reference field="4294967294" count="2">
@@ -6371,7 +4634,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="472">
+    <format dxfId="91">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="2">
           <reference field="4294967294" count="2">
@@ -6384,7 +4647,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="471">
+    <format dxfId="90">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="2">
           <reference field="4294967294" count="2">
@@ -6397,7 +4660,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="470">
+    <format dxfId="89">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="2">
           <reference field="4294967294" count="2">
@@ -6410,7 +4673,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="469">
+    <format dxfId="88">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="2">
           <reference field="4294967294" count="1">
@@ -6422,7 +4685,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="468">
+    <format dxfId="87">
       <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
         <references count="1">
           <reference field="2" count="1">
@@ -6431,7 +4694,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="467">
+    <format dxfId="86">
       <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
         <references count="1">
           <reference field="2" count="1">
@@ -6440,7 +4703,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="466">
+    <format dxfId="85">
       <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
         <references count="1">
           <reference field="2" count="7">
@@ -6455,7 +4718,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="465">
+    <format dxfId="84">
       <pivotArea field="2" dataOnly="0" labelOnly="1" grandCol="1" outline="0" axis="axisCol" fieldPosition="0">
         <references count="1">
           <reference field="4294967294" count="1" selected="0">
@@ -6464,7 +4727,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="464">
+    <format dxfId="83">
       <pivotArea field="2" dataOnly="0" labelOnly="1" grandCol="1" outline="0" axis="axisCol" fieldPosition="0">
         <references count="1">
           <reference field="4294967294" count="1" selected="0">
@@ -6473,7 +4736,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="463">
+    <format dxfId="82">
       <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
         <references count="3">
           <reference field="4294967294" count="1" selected="0">
@@ -6486,7 +4749,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="462">
+    <format dxfId="81">
       <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
         <references count="3">
           <reference field="4294967294" count="1" selected="0">
@@ -6499,7 +4762,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="461">
+    <format dxfId="80">
       <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
         <references count="3">
           <reference field="4294967294" count="1" selected="0">
@@ -6659,7 +4922,7 @@
     <dataField name="Nombre de transaction_id" fld="0" subtotal="count" baseField="0" baseItem="0"/>
   </dataFields>
   <formats count="2">
-    <format dxfId="552">
+    <format dxfId="169">
       <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
         <references count="1">
           <reference field="6" count="1">
@@ -6668,7 +4931,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="551">
+    <format dxfId="168">
       <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
         <references count="1">
           <reference field="6" count="1">
@@ -6746,7 +5009,7 @@
     <dataField name="Somme de montant_fc" fld="5" baseField="0" baseItem="0"/>
   </dataFields>
   <formats count="2">
-    <format dxfId="554">
+    <format dxfId="171">
       <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
         <references count="1">
           <reference field="4" count="1">
@@ -6755,7 +5018,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="553">
+    <format dxfId="170">
       <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
         <references count="1">
           <reference field="4" count="1">
@@ -6885,10 +5148,10 @@
     <dataField name="Somme de montant_fc" fld="5" baseField="0" baseItem="0"/>
   </dataFields>
   <formats count="2">
-    <format dxfId="367">
+    <format dxfId="54">
       <pivotArea field="2" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
     </format>
-    <format dxfId="368">
+    <format dxfId="55">
       <pivotArea dataOnly="0" labelOnly="1" grandCol="1" outline="0" fieldPosition="0"/>
     </format>
   </formats>
@@ -7010,7 +5273,7 @@
 
 <file path=xl/pivotTables/pivotTable7.xml><?xml version="1.0" encoding="utf-8"?>
 <pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{307774D1-06E3-4866-B6C8-A311F7479B8C}" name="Tableau croisé dynamique25" cacheId="5" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valeurs" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
-  <location ref="B71:L77" firstHeaderRow="1" firstDataRow="3" firstDataCol="1"/>
+  <location ref="B71:F77" firstHeaderRow="1" firstDataRow="3" firstDataCol="1"/>
   <pivotFields count="7">
     <pivotField dataField="1" showAll="0"/>
     <pivotField axis="axisRow" numFmtId="14" showAll="0">
@@ -7024,9 +5287,9 @@
     <pivotField axis="axisCol" showAll="0">
       <items count="9">
         <item x="0"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item x="3"/>
+        <item h="1" x="1"/>
+        <item h="1" x="2"/>
+        <item h="1" x="3"/>
         <item h="1" x="4"/>
         <item h="1" x="5"/>
         <item h="1" x="6"/>
@@ -7068,30 +5331,9 @@
     <field x="2"/>
     <field x="-2"/>
   </colFields>
-  <colItems count="10">
+  <colItems count="4">
     <i>
       <x/>
-      <x/>
-    </i>
-    <i r="1" i="1">
-      <x v="1"/>
-    </i>
-    <i>
-      <x v="1"/>
-      <x/>
-    </i>
-    <i r="1" i="1">
-      <x v="1"/>
-    </i>
-    <i>
-      <x v="2"/>
-      <x/>
-    </i>
-    <i r="1" i="1">
-      <x v="1"/>
-    </i>
-    <i>
-      <x v="3"/>
       <x/>
     </i>
     <i r="1" i="1">
@@ -7108,8 +5350,8 @@
     <dataField name="Nombre de transaction_id" fld="0" subtotal="count" baseField="0" baseItem="0"/>
     <dataField name="Somme de montant_fc" fld="5" baseField="0" baseItem="0"/>
   </dataFields>
-  <formats count="25">
-    <format dxfId="535">
+  <formats count="28">
+    <format dxfId="152">
       <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
         <references count="2">
           <reference field="1" count="2">
@@ -7122,10 +5364,10 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="534">
+    <format dxfId="151">
       <pivotArea field="1" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
     </format>
-    <format dxfId="533">
+    <format dxfId="150">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="2">
           <reference field="4294967294" count="2">
@@ -7138,7 +5380,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="532">
+    <format dxfId="149">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="2">
           <reference field="4294967294" count="2">
@@ -7151,7 +5393,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="531">
+    <format dxfId="148">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="2">
           <reference field="4294967294" count="2">
@@ -7164,7 +5406,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="530">
+    <format dxfId="147">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="2">
           <reference field="4294967294" count="2">
@@ -7177,7 +5419,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="529">
+    <format dxfId="146">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="2">
           <reference field="4294967294" count="2">
@@ -7190,7 +5432,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="528">
+    <format dxfId="145">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="2">
           <reference field="4294967294" count="2">
@@ -7203,7 +5445,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="527">
+    <format dxfId="144">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="2">
           <reference field="4294967294" count="2">
@@ -7216,7 +5458,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="526">
+    <format dxfId="143">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="2">
           <reference field="4294967294" count="2">
@@ -7229,7 +5471,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="525">
+    <format dxfId="142">
       <pivotArea field="2" dataOnly="0" labelOnly="1" grandCol="1" outline="0" axis="axisCol" fieldPosition="0">
         <references count="1">
           <reference field="4294967294" count="1" selected="0">
@@ -7238,7 +5480,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="524">
+    <format dxfId="141">
       <pivotArea field="2" dataOnly="0" labelOnly="1" grandCol="1" outline="0" axis="axisCol" fieldPosition="0">
         <references count="1">
           <reference field="4294967294" count="1" selected="0">
@@ -7247,10 +5489,10 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="523">
+    <format dxfId="140">
       <pivotArea field="2" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisCol" fieldPosition="0"/>
     </format>
-    <format dxfId="522">
+    <format dxfId="139">
       <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
         <references count="3">
           <reference field="4294967294" count="2" selected="0">
@@ -7267,7 +5509,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="521">
+    <format dxfId="138">
       <pivotArea dataOnly="0" labelOnly="1" offset="A256" fieldPosition="0">
         <references count="1">
           <reference field="2" count="1">
@@ -7276,7 +5518,113 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="520">
+    <format dxfId="53">
+      <pivotArea dataOnly="0" labelOnly="1" offset="IV256" fieldPosition="0">
+        <references count="1">
+          <reference field="2" count="1">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="52">
+      <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
+        <references count="1">
+          <reference field="2" count="1">
+            <x v="1"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="51">
+      <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
+        <references count="1">
+          <reference field="2" count="1">
+            <x v="2"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="50">
+      <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
+        <references count="1">
+          <reference field="2" count="1">
+            <x v="3"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="49">
+      <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
+        <references count="1">
+          <reference field="2" count="1">
+            <x v="4"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="48">
+      <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
+        <references count="1">
+          <reference field="2" count="1">
+            <x v="5"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="47">
+      <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
+        <references count="1">
+          <reference field="2" count="1">
+            <x v="6"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="46">
+      <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
+        <references count="1">
+          <reference field="2" count="1">
+            <x v="7"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="33">
+      <pivotArea field="2" grandRow="1" outline="0" collapsedLevelsAreSubtotals="1" axis="axisCol" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+          <reference field="2" count="0" selected="0"/>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="32">
+      <pivotArea field="2" grandRow="1" outline="0" collapsedLevelsAreSubtotals="1" axis="axisCol" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="2" count="0" selected="0"/>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="31">
+      <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
+        <references count="3">
+          <reference field="4294967294" count="2" selected="0">
+            <x v="0"/>
+            <x v="1"/>
+          </reference>
+          <reference field="1" count="1">
+            <x v="1"/>
+          </reference>
+          <reference field="2" count="0" selected="0"/>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="28">
       <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
         <references count="3">
           <reference field="4294967294" count="1" selected="0">
@@ -7285,13 +5633,11 @@
           <reference field="1" count="1">
             <x v="1"/>
           </reference>
-          <reference field="2" count="1" selected="0">
-            <x v="0"/>
-          </reference>
+          <reference field="2" count="0" selected="0"/>
         </references>
       </pivotArea>
     </format>
-    <format dxfId="519">
+    <format dxfId="0">
       <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
         <references count="3">
           <reference field="4294967294" count="1" selected="0">
@@ -7300,81 +5646,7 @@
           <reference field="1" count="1">
             <x v="1"/>
           </reference>
-          <reference field="2" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </format>
-    <format dxfId="352">
-      <pivotArea dataOnly="0" labelOnly="1" offset="IV256" fieldPosition="0">
-        <references count="1">
-          <reference field="2" count="1">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </format>
-    <format dxfId="243">
-      <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
-        <references count="1">
-          <reference field="2" count="1">
-            <x v="1"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </format>
-    <format dxfId="223">
-      <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
-        <references count="1">
-          <reference field="2" count="1">
-            <x v="2"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </format>
-    <format dxfId="202">
-      <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
-        <references count="1">
-          <reference field="2" count="1">
-            <x v="3"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </format>
-    <format dxfId="180">
-      <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
-        <references count="1">
-          <reference field="2" count="1">
-            <x v="4"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </format>
-    <format dxfId="157">
-      <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
-        <references count="1">
-          <reference field="2" count="1">
-            <x v="5"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </format>
-    <format dxfId="110">
-      <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
-        <references count="1">
-          <reference field="2" count="1">
-            <x v="6"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </format>
-    <format dxfId="109">
-      <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
-        <references count="1">
-          <reference field="2" count="1">
-            <x v="7"/>
-          </reference>
+          <reference field="2" count="0" selected="0"/>
         </references>
       </pivotArea>
     </format>
@@ -7494,17 +5766,17 @@
     <dataField name="Canal preferé par client" fld="0" subtotal="count" baseField="0" baseItem="0"/>
   </dataFields>
   <formats count="3">
-    <format dxfId="364">
+    <format dxfId="43">
       <pivotArea field="2" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
     </format>
-    <format dxfId="365">
+    <format dxfId="44">
       <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
         <references count="1">
           <reference field="6" count="0"/>
         </references>
       </pivotArea>
     </format>
-    <format dxfId="366">
+    <format dxfId="45">
       <pivotArea dataOnly="0" labelOnly="1" grandCol="1" outline="0" fieldPosition="0"/>
     </format>
   </formats>
@@ -7664,9 +5936,9 @@
     <tabular pivotCacheId="1733318224">
       <items count="8">
         <i x="0" s="1"/>
-        <i x="1" s="1"/>
-        <i x="2" s="1"/>
-        <i x="3" s="1"/>
+        <i x="1"/>
+        <i x="2"/>
+        <i x="3"/>
         <i x="4"/>
         <i x="5"/>
         <i x="6"/>
@@ -7684,16 +5956,16 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{6EC83A65-D9A6-475F-8D16-1CE811FFF2E9}" name="Tableau1" displayName="Tableau1" ref="B3:H13" totalsRowShown="0" headerRowDxfId="544" dataDxfId="543">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{6EC83A65-D9A6-475F-8D16-1CE811FFF2E9}" name="Tableau1" displayName="Tableau1" ref="B3:H13" totalsRowShown="0" headerRowDxfId="161" dataDxfId="160">
   <autoFilter ref="B3:H13" xr:uid="{6EC83A65-D9A6-475F-8D16-1CE811FFF2E9}"/>
   <tableColumns count="7">
-    <tableColumn id="1" xr3:uid="{54537CD7-847D-4C04-9BD6-B993FB8C0924}" name="transaction_id" dataDxfId="542"/>
-    <tableColumn id="2" xr3:uid="{7DFAA592-DC98-463C-A6AF-A94A0F915646}" name="date" dataDxfId="541"/>
-    <tableColumn id="3" xr3:uid="{122DF7BD-714F-4B55-830F-7573F364E80A}" name="client_id" dataDxfId="540"/>
-    <tableColumn id="4" xr3:uid="{1B94713D-DD23-416E-B23B-98EF629AFCBE}" name="commune" dataDxfId="539"/>
-    <tableColumn id="5" xr3:uid="{084E48D7-3EDD-4FC4-B38B-BD3872EDFF23}" name="produit" dataDxfId="538"/>
-    <tableColumn id="6" xr3:uid="{D1BF92F6-B520-4D49-B97E-C1395DDE5A98}" name="montant_fc" dataDxfId="537"/>
-    <tableColumn id="7" xr3:uid="{21C18558-D71D-47B7-B0D0-001594508953}" name="canal" dataDxfId="536"/>
+    <tableColumn id="1" xr3:uid="{54537CD7-847D-4C04-9BD6-B993FB8C0924}" name="transaction_id" dataDxfId="159"/>
+    <tableColumn id="2" xr3:uid="{7DFAA592-DC98-463C-A6AF-A94A0F915646}" name="date" dataDxfId="158"/>
+    <tableColumn id="3" xr3:uid="{122DF7BD-714F-4B55-830F-7573F364E80A}" name="client_id" dataDxfId="157"/>
+    <tableColumn id="4" xr3:uid="{1B94713D-DD23-416E-B23B-98EF629AFCBE}" name="commune" dataDxfId="156"/>
+    <tableColumn id="5" xr3:uid="{084E48D7-3EDD-4FC4-B38B-BD3872EDFF23}" name="produit" dataDxfId="155"/>
+    <tableColumn id="6" xr3:uid="{D1BF92F6-B520-4D49-B97E-C1395DDE5A98}" name="montant_fc" dataDxfId="154"/>
+    <tableColumn id="7" xr3:uid="{21C18558-D71D-47B7-B0D0-001594508953}" name="canal" dataDxfId="153"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -7703,13 +5975,13 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{5B43BC6D-66A6-432F-982F-C406FA282078}" name="Dataset_day2__2" displayName="Dataset_day2__2" ref="B2:H17" tableType="queryTable" totalsRowShown="0">
   <autoFilter ref="B2:H17" xr:uid="{5B43BC6D-66A6-432F-982F-C406FA282078}"/>
   <tableColumns count="7">
-    <tableColumn id="1" xr3:uid="{F0363F15-00D8-44D9-B9E8-73E1201A36E6}" uniqueName="1" name="transaction_id" queryTableFieldId="1" dataDxfId="518"/>
-    <tableColumn id="2" xr3:uid="{85F76B94-3323-41EB-B99E-F9DE7DD9EF5D}" uniqueName="2" name="date" queryTableFieldId="2" dataDxfId="517"/>
-    <tableColumn id="3" xr3:uid="{90258075-E8BA-4181-AEBF-14DCE9CF1AC4}" uniqueName="3" name="client_id" queryTableFieldId="3" dataDxfId="516"/>
-    <tableColumn id="4" xr3:uid="{3B088930-C813-470C-9790-11DA318C42A1}" uniqueName="4" name="commune" queryTableFieldId="4" dataDxfId="515"/>
-    <tableColumn id="5" xr3:uid="{E074DF00-E0E7-41D6-B91A-ABE22CB1881A}" uniqueName="5" name="produit" queryTableFieldId="5" dataDxfId="514"/>
+    <tableColumn id="1" xr3:uid="{F0363F15-00D8-44D9-B9E8-73E1201A36E6}" uniqueName="1" name="transaction_id" queryTableFieldId="1" dataDxfId="137"/>
+    <tableColumn id="2" xr3:uid="{85F76B94-3323-41EB-B99E-F9DE7DD9EF5D}" uniqueName="2" name="date" queryTableFieldId="2" dataDxfId="136"/>
+    <tableColumn id="3" xr3:uid="{90258075-E8BA-4181-AEBF-14DCE9CF1AC4}" uniqueName="3" name="client_id" queryTableFieldId="3" dataDxfId="135"/>
+    <tableColumn id="4" xr3:uid="{3B088930-C813-470C-9790-11DA318C42A1}" uniqueName="4" name="commune" queryTableFieldId="4" dataDxfId="134"/>
+    <tableColumn id="5" xr3:uid="{E074DF00-E0E7-41D6-B91A-ABE22CB1881A}" uniqueName="5" name="produit" queryTableFieldId="5" dataDxfId="133"/>
     <tableColumn id="6" xr3:uid="{7C01ABE9-F9C0-40F6-9F95-D610FB820086}" uniqueName="6" name="montant_fc" queryTableFieldId="6"/>
-    <tableColumn id="7" xr3:uid="{30F6D1BA-4065-4D54-BF94-1BE05C99AC63}" uniqueName="7" name="canal" queryTableFieldId="7" dataDxfId="513"/>
+    <tableColumn id="7" xr3:uid="{30F6D1BA-4065-4D54-BF94-1BE05C99AC63}" uniqueName="7" name="canal" queryTableFieldId="7" dataDxfId="132"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -7719,12 +5991,12 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{A4A0DCA2-C1C4-44D4-AD45-BDA248A44995}" name="Dataset_day3" displayName="Dataset_day3" ref="B2:H17" tableType="queryTable" totalsRowShown="0">
   <autoFilter ref="B2:H17" xr:uid="{A4A0DCA2-C1C4-44D4-AD45-BDA248A44995}"/>
   <tableColumns count="7">
-    <tableColumn id="1" xr3:uid="{A0067E32-0369-4D8A-BDF1-C8B907B86BD0}" uniqueName="1" name="transaction_id" queryTableFieldId="1" dataDxfId="505"/>
-    <tableColumn id="2" xr3:uid="{C68FAFFA-BEA0-4F94-BA99-6450F477971E}" uniqueName="2" name="date" queryTableFieldId="2" dataDxfId="504"/>
-    <tableColumn id="3" xr3:uid="{CDF65428-BE02-471D-A8F7-90F1D8454251}" uniqueName="3" name="agent_id" queryTableFieldId="3" dataDxfId="503"/>
-    <tableColumn id="4" xr3:uid="{22F84FAA-57F1-425F-B37C-F8428C49E033}" uniqueName="4" name="client_id" queryTableFieldId="4" dataDxfId="502"/>
-    <tableColumn id="5" xr3:uid="{93A8CFD1-D585-478D-9AFB-02301838500E}" uniqueName="5" name="commune" queryTableFieldId="5" dataDxfId="501"/>
-    <tableColumn id="6" xr3:uid="{956E7CEA-E833-4F96-9E51-2D67194B8C61}" uniqueName="6" name="produit" queryTableFieldId="6" dataDxfId="500"/>
+    <tableColumn id="1" xr3:uid="{A0067E32-0369-4D8A-BDF1-C8B907B86BD0}" uniqueName="1" name="transaction_id" queryTableFieldId="1" dataDxfId="124"/>
+    <tableColumn id="2" xr3:uid="{C68FAFFA-BEA0-4F94-BA99-6450F477971E}" uniqueName="2" name="date" queryTableFieldId="2" dataDxfId="123"/>
+    <tableColumn id="3" xr3:uid="{CDF65428-BE02-471D-A8F7-90F1D8454251}" uniqueName="3" name="agent_id" queryTableFieldId="3" dataDxfId="122"/>
+    <tableColumn id="4" xr3:uid="{22F84FAA-57F1-425F-B37C-F8428C49E033}" uniqueName="4" name="client_id" queryTableFieldId="4" dataDxfId="121"/>
+    <tableColumn id="5" xr3:uid="{93A8CFD1-D585-478D-9AFB-02301838500E}" uniqueName="5" name="commune" queryTableFieldId="5" dataDxfId="120"/>
+    <tableColumn id="6" xr3:uid="{956E7CEA-E833-4F96-9E51-2D67194B8C61}" uniqueName="6" name="produit" queryTableFieldId="6" dataDxfId="119"/>
     <tableColumn id="7" xr3:uid="{E636C8A0-3C3C-48BE-AFE5-1B3DB129CA7E}" uniqueName="7" name="montant_fc" queryTableFieldId="7"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
@@ -7735,11 +6007,11 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{AB24B926-8F3E-4EE6-9138-D47BB2378B02}" name="Dataset_day4" displayName="Dataset_day4" ref="B2:G17" totalsRowShown="0">
   <autoFilter ref="B2:G17" xr:uid="{AB24B926-8F3E-4EE6-9138-D47BB2378B02}"/>
   <tableColumns count="6">
-    <tableColumn id="1" xr3:uid="{2FA77349-5B7D-430C-A299-CA8EF8B94F8F}" name="transaction_id" dataDxfId="490"/>
-    <tableColumn id="2" xr3:uid="{EA88A0A8-EDC4-468E-80F4-EF0578FE9A03}" name="date" dataDxfId="489"/>
-    <tableColumn id="3" xr3:uid="{811F8411-B146-492E-A697-2D905854F94D}" name="client_id" dataDxfId="488"/>
-    <tableColumn id="4" xr3:uid="{7B37CE19-01A8-4470-8A2B-849B751FB37D}" name="commune" dataDxfId="487"/>
-    <tableColumn id="5" xr3:uid="{863A1A63-AC11-4715-82E2-F6EC444E5B51}" name="produit" dataDxfId="486"/>
+    <tableColumn id="1" xr3:uid="{2FA77349-5B7D-430C-A299-CA8EF8B94F8F}" name="transaction_id" dataDxfId="109"/>
+    <tableColumn id="2" xr3:uid="{EA88A0A8-EDC4-468E-80F4-EF0578FE9A03}" name="date" dataDxfId="108"/>
+    <tableColumn id="3" xr3:uid="{811F8411-B146-492E-A697-2D905854F94D}" name="client_id" dataDxfId="107"/>
+    <tableColumn id="4" xr3:uid="{7B37CE19-01A8-4470-8A2B-849B751FB37D}" name="commune" dataDxfId="106"/>
+    <tableColumn id="5" xr3:uid="{863A1A63-AC11-4715-82E2-F6EC444E5B51}" name="produit" dataDxfId="105"/>
     <tableColumn id="6" xr3:uid="{DDFB738A-4C05-4F97-882D-16FE65EF8A7E}" name="montant_fc"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
@@ -7747,7 +6019,7 @@
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="9" xr:uid="{B1C5B688-9C67-4CAD-9DAE-7207D5E5E850}" name="Tableau9" displayName="Tableau9" ref="AA3:AA11" totalsRowShown="0" headerRowDxfId="485">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="9" xr:uid="{B1C5B688-9C67-4CAD-9DAE-7207D5E5E850}" name="Tableau9" displayName="Tableau9" ref="AA3:AA11" totalsRowShown="0" headerRowDxfId="104">
   <autoFilter ref="AA3:AA11" xr:uid="{B1C5B688-9C67-4CAD-9DAE-7207D5E5E850}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="AA4:AA11">
     <sortCondition ref="AA3:AA11"/>
@@ -7762,16 +6034,16 @@
 </file>
 
 <file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="10" xr:uid="{C4A92EC0-501A-4751-9A16-2163E0BD39EA}" name="Dataset_day5" displayName="Dataset_day5" ref="B2:H17" tableType="queryTable" totalsRowShown="0" headerRowDxfId="444">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="10" xr:uid="{C4A92EC0-501A-4751-9A16-2163E0BD39EA}" name="Dataset_day5" displayName="Dataset_day5" ref="B2:H17" tableType="queryTable" totalsRowShown="0" headerRowDxfId="63">
   <autoFilter ref="B2:H17" xr:uid="{C4A92EC0-501A-4751-9A16-2163E0BD39EA}"/>
   <tableColumns count="7">
-    <tableColumn id="1" xr3:uid="{FBC21564-1B48-423F-AFDB-04B5AE20CF75}" uniqueName="1" name="transaction_id" queryTableFieldId="1" dataDxfId="443"/>
-    <tableColumn id="2" xr3:uid="{CA4A50D7-5720-4F71-ACD1-3781681C0231}" uniqueName="2" name="date" queryTableFieldId="2" dataDxfId="442"/>
-    <tableColumn id="3" xr3:uid="{A265E5F8-50A6-4DD3-8C5E-10BB05E3F126}" uniqueName="3" name="client_id" queryTableFieldId="3" dataDxfId="441"/>
-    <tableColumn id="4" xr3:uid="{0E595B89-2727-474B-B4A6-66BC0AC0864A}" uniqueName="4" name="commune" queryTableFieldId="4" dataDxfId="440"/>
-    <tableColumn id="5" xr3:uid="{4D992877-9744-466D-982E-E1F06CDEF762}" uniqueName="5" name="produit" queryTableFieldId="5" dataDxfId="439"/>
+    <tableColumn id="1" xr3:uid="{FBC21564-1B48-423F-AFDB-04B5AE20CF75}" uniqueName="1" name="transaction_id" queryTableFieldId="1" dataDxfId="62"/>
+    <tableColumn id="2" xr3:uid="{CA4A50D7-5720-4F71-ACD1-3781681C0231}" uniqueName="2" name="date" queryTableFieldId="2" dataDxfId="61"/>
+    <tableColumn id="3" xr3:uid="{A265E5F8-50A6-4DD3-8C5E-10BB05E3F126}" uniqueName="3" name="client_id" queryTableFieldId="3" dataDxfId="60"/>
+    <tableColumn id="4" xr3:uid="{0E595B89-2727-474B-B4A6-66BC0AC0864A}" uniqueName="4" name="commune" queryTableFieldId="4" dataDxfId="59"/>
+    <tableColumn id="5" xr3:uid="{4D992877-9744-466D-982E-E1F06CDEF762}" uniqueName="5" name="produit" queryTableFieldId="5" dataDxfId="58"/>
     <tableColumn id="6" xr3:uid="{D10FAE6E-7969-4551-94AB-82C2D27DFD50}" uniqueName="6" name="montant_fc" queryTableFieldId="6"/>
-    <tableColumn id="7" xr3:uid="{7306D68B-3C9A-40F7-A0D9-E00CC8C73541}" uniqueName="7" name="periode" queryTableFieldId="7" dataDxfId="438"/>
+    <tableColumn id="7" xr3:uid="{7306D68B-3C9A-40F7-A0D9-E00CC8C73541}" uniqueName="7" name="periode" queryTableFieldId="7" dataDxfId="57"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -7782,7 +6054,7 @@
   <autoFilter ref="A1:G6" xr:uid="{68E59C74-D329-4B48-A967-CC868365949C}"/>
   <tableColumns count="7">
     <tableColumn id="1" xr3:uid="{C102BD58-3DF8-48B7-9114-2067608D3DB4}" name="transaction_id"/>
-    <tableColumn id="2" xr3:uid="{998F6E83-476D-414D-8353-8E6146354739}" name="date" dataDxfId="437"/>
+    <tableColumn id="2" xr3:uid="{998F6E83-476D-414D-8353-8E6146354739}" name="date" dataDxfId="56"/>
     <tableColumn id="3" xr3:uid="{1ACC5CD9-2A0F-4DB2-B7B7-A25781DA1795}" name="agent_id"/>
     <tableColumn id="4" xr3:uid="{D4B111D2-01DE-4AFC-91B0-641E23172B8C}" name="client_id"/>
     <tableColumn id="5" xr3:uid="{C0E2906A-2633-4FB3-89D8-883ADDF86D4F}" name="commune"/>
@@ -8121,15 +6393,15 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="B2" s="47" t="s">
+      <c r="B2" s="46" t="s">
         <v>43</v>
       </c>
-      <c r="C2" s="47"/>
-      <c r="D2" s="47"/>
-      <c r="E2" s="47"/>
-      <c r="F2" s="47"/>
-      <c r="G2" s="47"/>
-      <c r="H2" s="47"/>
+      <c r="C2" s="46"/>
+      <c r="D2" s="46"/>
+      <c r="E2" s="46"/>
+      <c r="F2" s="46"/>
+      <c r="G2" s="46"/>
+      <c r="H2" s="46"/>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" s="12" t="s">
@@ -8428,18 +6700,18 @@
       <c r="H14" s="5"/>
     </row>
     <row r="15" spans="1:9" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B15" s="44" t="s">
+      <c r="B15" s="43" t="s">
         <v>171</v>
       </c>
-      <c r="C15" s="49"/>
-      <c r="D15" s="49"/>
-      <c r="E15" s="49"/>
-      <c r="F15" s="49"/>
-      <c r="G15" s="49"/>
-      <c r="H15" s="49"/>
+      <c r="C15" s="48"/>
+      <c r="D15" s="48"/>
+      <c r="E15" s="48"/>
+      <c r="F15" s="48"/>
+      <c r="G15" s="48"/>
+      <c r="H15" s="48"/>
     </row>
     <row r="16" spans="1:9" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B16" s="37"/>
+      <c r="B16" s="36"/>
       <c r="C16" s="1"/>
       <c r="D16" s="1"/>
       <c r="E16" s="1"/>
@@ -8448,18 +6720,18 @@
       <c r="H16" s="1"/>
     </row>
     <row r="17" spans="2:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B17" s="44" t="s">
+      <c r="B17" s="43" t="s">
         <v>172</v>
       </c>
-      <c r="C17" s="44"/>
-      <c r="D17" s="44"/>
-      <c r="E17" s="38"/>
+      <c r="C17" s="43"/>
+      <c r="D17" s="43"/>
+      <c r="E17" s="37"/>
     </row>
     <row r="19" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B19" s="47" t="s">
+      <c r="B19" s="46" t="s">
         <v>44</v>
       </c>
-      <c r="C19" s="47"/>
+      <c r="C19" s="46"/>
     </row>
     <row r="20" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B20" s="8" t="s">
@@ -8506,20 +6778,20 @@
       <c r="C26" s="10"/>
     </row>
     <row r="27" spans="2:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B27" s="44" t="s">
+      <c r="B27" s="43" t="s">
         <v>173</v>
       </c>
-      <c r="C27" s="44"/>
-      <c r="D27" s="44"/>
-      <c r="E27" s="38"/>
+      <c r="C27" s="43"/>
+      <c r="D27" s="43"/>
+      <c r="E27" s="37"/>
       <c r="F27" s="1"/>
       <c r="G27" s="1"/>
     </row>
     <row r="30" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B30" s="47" t="s">
+      <c r="B30" s="46" t="s">
         <v>45</v>
       </c>
-      <c r="C30" s="47"/>
+      <c r="C30" s="46"/>
     </row>
     <row r="31" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B31" s="8" t="s">
@@ -8530,7 +6802,7 @@
       </c>
     </row>
     <row r="32" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B32" s="39" t="s">
+      <c r="B32" s="38" t="s">
         <v>9</v>
       </c>
       <c r="C32" s="21">
@@ -8578,17 +6850,17 @@
       </c>
     </row>
     <row r="40" spans="2:4" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B40" s="44" t="s">
+      <c r="B40" s="43" t="s">
         <v>174</v>
       </c>
-      <c r="C40" s="44"/>
-      <c r="D40" s="44"/>
+      <c r="C40" s="43"/>
+      <c r="D40" s="43"/>
     </row>
     <row r="42" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B42" s="47" t="s">
+      <c r="B42" s="46" t="s">
         <v>46</v>
       </c>
-      <c r="C42" s="47"/>
+      <c r="C42" s="46"/>
     </row>
     <row r="43" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B43" s="8" t="s">
@@ -8639,17 +6911,17 @@
       </c>
     </row>
     <row r="50" spans="2:5" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B50" s="44" t="s">
+      <c r="B50" s="43" t="s">
         <v>175</v>
       </c>
-      <c r="C50" s="44"/>
-      <c r="D50" s="44"/>
+      <c r="C50" s="43"/>
+      <c r="D50" s="43"/>
     </row>
     <row r="52" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B52" s="47" t="s">
+      <c r="B52" s="46" t="s">
         <v>47</v>
       </c>
-      <c r="C52" s="48"/>
+      <c r="C52" s="47"/>
     </row>
     <row r="53" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B53" s="8" t="s">
@@ -8692,56 +6964,56 @@
       </c>
     </row>
     <row r="60" spans="2:5" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="B60" s="45" t="s">
+      <c r="B60" s="44" t="s">
         <v>182</v>
       </c>
-      <c r="C60" s="45"/>
+      <c r="C60" s="44"/>
     </row>
     <row r="62" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B62" s="46" t="s">
+      <c r="B62" s="45" t="s">
         <v>183</v>
       </c>
-      <c r="C62" s="46"/>
-      <c r="D62" s="46"/>
-      <c r="E62" s="46"/>
+      <c r="C62" s="45"/>
+      <c r="D62" s="45"/>
+      <c r="E62" s="45"/>
     </row>
     <row r="63" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B63" s="46"/>
-      <c r="C63" s="46"/>
-      <c r="D63" s="46"/>
-      <c r="E63" s="46"/>
+      <c r="B63" s="45"/>
+      <c r="C63" s="45"/>
+      <c r="D63" s="45"/>
+      <c r="E63" s="45"/>
     </row>
     <row r="64" spans="2:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B64" s="41"/>
-      <c r="C64" s="41"/>
-      <c r="D64" s="41"/>
-      <c r="E64" s="41"/>
+      <c r="B64" s="40"/>
+      <c r="C64" s="40"/>
+      <c r="D64" s="40"/>
+      <c r="E64" s="40"/>
     </row>
     <row r="65" spans="2:2" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="B65" s="42" t="s">
+      <c r="B65" s="41" t="s">
         <v>177</v>
       </c>
     </row>
     <row r="66" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B66" s="40"/>
+      <c r="B66" s="39"/>
     </row>
     <row r="67" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B67" s="43" t="s">
+      <c r="B67" s="42" t="s">
         <v>178</v>
       </c>
     </row>
     <row r="68" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B68" s="43" t="s">
+      <c r="B68" s="42" t="s">
         <v>179</v>
       </c>
     </row>
     <row r="69" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B69" s="43" t="s">
+      <c r="B69" s="42" t="s">
         <v>180</v>
       </c>
     </row>
     <row r="70" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B70" s="43" t="s">
+      <c r="B70" s="42" t="s">
         <v>181</v>
       </c>
     </row>
@@ -8813,9 +7085,9 @@
     <col min="2" max="2" width="15.42578125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="24.42578125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="11.140625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="5.7109375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="5.5703125" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="11.140625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="13" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="13.7109375" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="11.140625" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="13.7109375" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="11.140625" customWidth="1"/>
@@ -9200,47 +7472,47 @@
       </c>
     </row>
     <row r="19" spans="2:8" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B19" s="44" t="s">
+      <c r="B19" s="43" t="s">
         <v>171</v>
       </c>
-      <c r="C19" s="49"/>
-      <c r="D19" s="49"/>
-      <c r="E19" s="49"/>
-      <c r="F19" s="49"/>
-      <c r="G19" s="49"/>
-      <c r="H19" s="49"/>
+      <c r="C19" s="48"/>
+      <c r="D19" s="48"/>
+      <c r="E19" s="48"/>
+      <c r="F19" s="48"/>
+      <c r="G19" s="48"/>
+      <c r="H19" s="48"/>
     </row>
     <row r="20" spans="2:8" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B20" s="37"/>
-      <c r="C20" s="36"/>
-      <c r="D20" s="36"/>
-      <c r="E20" s="36"/>
-      <c r="F20" s="36"/>
-      <c r="G20" s="36"/>
-      <c r="H20" s="36"/>
+      <c r="B20" s="36"/>
+      <c r="C20" s="35"/>
+      <c r="D20" s="35"/>
+      <c r="E20" s="35"/>
+      <c r="F20" s="35"/>
+      <c r="G20" s="35"/>
+      <c r="H20" s="35"/>
     </row>
     <row r="21" spans="2:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B21" s="44" t="s">
+      <c r="B21" s="43" t="s">
         <v>184</v>
       </c>
-      <c r="C21" s="44"/>
-      <c r="D21" s="44"/>
-      <c r="E21" s="44"/>
+      <c r="C21" s="43"/>
+      <c r="D21" s="43"/>
+      <c r="E21" s="43"/>
     </row>
     <row r="22" spans="2:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B22" s="37"/>
-      <c r="C22" s="37"/>
-      <c r="D22" s="37"/>
-      <c r="E22" s="37"/>
+      <c r="B22" s="36"/>
+      <c r="C22" s="36"/>
+      <c r="D22" s="36"/>
+      <c r="E22" s="36"/>
     </row>
     <row r="23" spans="2:8" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B23" s="44" t="s">
+      <c r="B23" s="43" t="s">
         <v>185</v>
       </c>
-      <c r="C23" s="44"/>
-      <c r="D23" s="38"/>
-      <c r="E23" s="38"/>
-      <c r="F23" s="38"/>
+      <c r="C23" s="43"/>
+      <c r="D23" s="37"/>
+      <c r="E23" s="37"/>
+      <c r="F23" s="37"/>
     </row>
     <row r="24" spans="2:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B24" s="8" t="s">
@@ -9331,26 +7603,26 @@
       <c r="C35" s="10"/>
     </row>
     <row r="36" spans="2:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B36" s="44" t="s">
+      <c r="B36" s="43" t="s">
         <v>186</v>
       </c>
-      <c r="C36" s="44"/>
-      <c r="D36" s="44"/>
-      <c r="E36" s="44"/>
+      <c r="C36" s="43"/>
+      <c r="D36" s="43"/>
+      <c r="E36" s="43"/>
     </row>
     <row r="37" spans="2:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B37" s="37"/>
-      <c r="C37" s="37"/>
-      <c r="D37" s="37"/>
-      <c r="E37" s="37"/>
+      <c r="B37" s="36"/>
+      <c r="C37" s="36"/>
+      <c r="D37" s="36"/>
+      <c r="E37" s="36"/>
     </row>
     <row r="38" spans="2:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B38" s="44" t="s">
+      <c r="B38" s="43" t="s">
         <v>189</v>
       </c>
-      <c r="C38" s="44"/>
-      <c r="D38" s="37"/>
-      <c r="E38" s="37"/>
+      <c r="C38" s="43"/>
+      <c r="D38" s="36"/>
+      <c r="E38" s="36"/>
     </row>
     <row r="39" spans="2:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B39" s="18" t="s">
@@ -9432,39 +7704,40 @@
         <v>167000</v>
       </c>
     </row>
-    <row r="49" spans="2:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="50" spans="2:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="51" spans="2:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B51" s="44" t="s">
+    <row r="49" spans="2:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="50" spans="2:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="51" spans="2:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B51" s="43" t="s">
         <v>188</v>
       </c>
-      <c r="C51" s="44"/>
-      <c r="D51" s="44"/>
-      <c r="E51" s="44"/>
-    </row>
-    <row r="52" spans="2:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B52" s="37"/>
-      <c r="C52" s="37"/>
-      <c r="D52" s="37"/>
-      <c r="E52" s="37"/>
-    </row>
-    <row r="53" spans="2:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B53" s="37" t="s">
+      <c r="C51" s="43"/>
+      <c r="D51" s="43"/>
+      <c r="E51" s="43"/>
+    </row>
+    <row r="52" spans="2:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B52" s="36"/>
+      <c r="C52" s="36"/>
+      <c r="D52" s="36"/>
+      <c r="E52" s="36"/>
+    </row>
+    <row r="53" spans="2:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B53" s="36" t="s">
         <v>187</v>
       </c>
-      <c r="C53" s="37"/>
-      <c r="D53" s="37"/>
-      <c r="E53" s="37"/>
-    </row>
-    <row r="54" spans="2:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C53" s="36"/>
+      <c r="D53" s="36"/>
+      <c r="E53" s="36"/>
+    </row>
+    <row r="54" spans="2:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B54" s="8" t="s">
         <v>72</v>
       </c>
       <c r="C54" s="8" t="s">
         <v>42</v>
       </c>
-    </row>
-    <row r="55" spans="2:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="G54" s="49"/>
+    </row>
+    <row r="55" spans="2:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B55" s="18" t="s">
         <v>74</v>
       </c>
@@ -9480,8 +7753,11 @@
       <c r="F55" s="11" t="s">
         <v>40</v>
       </c>
-    </row>
-    <row r="56" spans="2:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="G55" s="52" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="56" spans="2:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B56" s="9" t="s">
         <v>8</v>
       </c>
@@ -9493,8 +7769,12 @@
       <c r="F56" s="10">
         <v>7</v>
       </c>
-    </row>
-    <row r="57" spans="2:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="G56" s="10" t="str" cm="1">
+        <f t="array" ref="G56">_xlfn.IFS(MAX(C56:E56)=C56,"Agent",MAX(C56:E56)=D56,"Mobile Money",MAX(C56:E56)=E56,"USSD")</f>
+        <v>Mobile Money</v>
+      </c>
+    </row>
+    <row r="57" spans="2:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B57" s="9" t="s">
         <v>13</v>
       </c>
@@ -9506,8 +7786,12 @@
       <c r="F57" s="10">
         <v>2</v>
       </c>
-    </row>
-    <row r="58" spans="2:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="G57" s="10" t="str" cm="1">
+        <f t="array" ref="G57">_xlfn.IFS(MAX(C57:E57)=C57,"Agent",MAX(C57:E57)=D57,"Mobile Money",MAX(C57:E57)=E57,"USSD")</f>
+        <v>USSD</v>
+      </c>
+    </row>
+    <row r="58" spans="2:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B58" s="9" t="s">
         <v>52</v>
       </c>
@@ -9519,8 +7803,12 @@
       <c r="F58" s="10">
         <v>1</v>
       </c>
-    </row>
-    <row r="59" spans="2:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="G58" s="10" t="str" cm="1">
+        <f t="array" ref="G58">_xlfn.IFS(MAX(C58:E58)=C58,"Agent",MAX(C58:E58)=D58,"Mobile Money",MAX(C58:E58)=E58,"USSD")</f>
+        <v>Agent</v>
+      </c>
+    </row>
+    <row r="59" spans="2:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B59" s="9" t="s">
         <v>54</v>
       </c>
@@ -9532,8 +7820,12 @@
       <c r="F59" s="10">
         <v>1</v>
       </c>
-    </row>
-    <row r="60" spans="2:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="G59" s="10" t="str" cm="1">
+        <f t="array" ref="G59">_xlfn.IFS(MAX(C59:E59)=C59,"Agent",MAX(C59:E59)=D59,"Mobile Money",MAX(C59:E59)=E59,"USSD")</f>
+        <v>Agent</v>
+      </c>
+    </row>
+    <row r="60" spans="2:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B60" s="9" t="s">
         <v>58</v>
       </c>
@@ -9545,8 +7837,12 @@
       <c r="F60" s="10">
         <v>1</v>
       </c>
-    </row>
-    <row r="61" spans="2:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="G60" s="10" t="str" cm="1">
+        <f t="array" ref="G60">_xlfn.IFS(MAX(C60:E60)=C60,"Agent",MAX(C60:E60)=D60,"Mobile Money",MAX(C60:E60)=E60,"USSD")</f>
+        <v>Agent</v>
+      </c>
+    </row>
+    <row r="61" spans="2:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B61" s="9" t="s">
         <v>61</v>
       </c>
@@ -9558,8 +7854,12 @@
       <c r="F61" s="10">
         <v>1</v>
       </c>
-    </row>
-    <row r="62" spans="2:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="G61" s="10" t="str" cm="1">
+        <f t="array" ref="G61">_xlfn.IFS(MAX(C61:E61)=C61,"Agent",MAX(C61:E61)=D61,"Mobile Money",MAX(C61:E61)=E61,"USSD")</f>
+        <v>Mobile Money</v>
+      </c>
+    </row>
+    <row r="62" spans="2:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B62" s="9" t="s">
         <v>64</v>
       </c>
@@ -9571,8 +7871,12 @@
       <c r="F62" s="10">
         <v>1</v>
       </c>
-    </row>
-    <row r="63" spans="2:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="G62" s="10" t="str" cm="1">
+        <f t="array" ref="G62">_xlfn.IFS(MAX(C62:E62)=C62,"Agent",MAX(C62:E62)=D62,"Mobile Money",MAX(C62:E62)=E62,"USSD")</f>
+        <v>USSD</v>
+      </c>
+    </row>
+    <row r="63" spans="2:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B63" s="9" t="s">
         <v>67</v>
       </c>
@@ -9584,56 +7888,61 @@
       <c r="F63" s="10">
         <v>1</v>
       </c>
-    </row>
-    <row r="64" spans="2:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="G63" s="10" t="str" cm="1">
+        <f t="array" ref="G63">_xlfn.IFS(MAX(C63:E63)=C63,"Agent",MAX(C63:E63)=D63,"Mobile Money",MAX(C63:E63)=E63,"USSD")</f>
+        <v>Agent</v>
+      </c>
+    </row>
+    <row r="64" spans="2:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B64" s="9" t="s">
         <v>40</v>
       </c>
       <c r="C64" s="10">
         <v>4</v>
       </c>
-      <c r="E64" s="37"/>
-      <c r="F64" s="37"/>
+      <c r="E64" s="36"/>
+      <c r="F64" s="36"/>
+      <c r="G64" s="53"/>
     </row>
     <row r="65" spans="2:20" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B65" s="37"/>
-      <c r="C65" s="37"/>
-      <c r="D65" s="37"/>
-      <c r="E65" s="37"/>
+      <c r="B65" s="36"/>
+      <c r="C65" s="36"/>
+      <c r="D65" s="36"/>
+      <c r="E65" s="36"/>
     </row>
     <row r="66" spans="2:20" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B66" s="37"/>
-      <c r="C66" s="37"/>
-      <c r="D66" s="37"/>
-      <c r="E66" s="37"/>
+      <c r="B66" s="36"/>
+      <c r="C66" s="36"/>
+      <c r="D66" s="36"/>
+      <c r="E66" s="36"/>
     </row>
     <row r="67" spans="2:20" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B67" s="44" t="s">
+      <c r="B67" s="43" t="s">
         <v>190</v>
       </c>
-      <c r="C67" s="44"/>
-      <c r="D67" s="44"/>
-      <c r="E67" s="44"/>
+      <c r="C67" s="43"/>
+      <c r="D67" s="43"/>
+      <c r="E67" s="43"/>
     </row>
     <row r="68" spans="2:20" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B68" s="37"/>
-      <c r="C68" s="37"/>
-      <c r="D68" s="37"/>
-      <c r="E68" s="37"/>
+      <c r="B68" s="36"/>
+      <c r="C68" s="36"/>
+      <c r="D68" s="36"/>
+      <c r="E68" s="36"/>
     </row>
     <row r="69" spans="2:20" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B69" s="44" t="s">
+      <c r="B69" s="43" t="s">
         <v>191</v>
       </c>
-      <c r="C69" s="44"/>
-      <c r="D69" s="44"/>
-      <c r="E69" s="44"/>
-      <c r="F69" s="44"/>
-      <c r="G69" s="44"/>
+      <c r="C69" s="43"/>
+      <c r="D69" s="43"/>
+      <c r="E69" s="43"/>
+      <c r="F69" s="43"/>
+      <c r="G69" s="43"/>
     </row>
     <row r="70" spans="2:20" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B70" s="44"/>
-      <c r="C70" s="44"/>
+      <c r="B70" s="43"/>
+      <c r="C70" s="43"/>
       <c r="F70" s="9"/>
       <c r="G70" s="10"/>
       <c r="H70" s="10"/>
@@ -9645,31 +7954,19 @@
         <v>42</v>
       </c>
     </row>
-    <row r="72" spans="2:20" ht="60" x14ac:dyDescent="0.25">
+    <row r="72" spans="2:20" ht="60.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C72" s="22" t="s">
         <v>8</v>
       </c>
       <c r="D72" s="22"/>
-      <c r="E72" s="50" t="s">
-        <v>13</v>
-      </c>
-      <c r="F72" s="50"/>
-      <c r="G72" s="51" t="s">
-        <v>52</v>
-      </c>
-      <c r="H72" s="51"/>
-      <c r="I72" s="52" t="s">
-        <v>54</v>
-      </c>
-      <c r="J72" s="52"/>
-      <c r="K72" s="19" t="s">
+      <c r="E72" s="19" t="s">
         <v>69</v>
       </c>
-      <c r="L72" s="19" t="s">
+      <c r="F72" s="19" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="73" spans="2:20" s="19" customFormat="1" ht="90" x14ac:dyDescent="0.25">
+    <row r="73" spans="2:20" s="19" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="B73" s="20" t="s">
         <v>38</v>
       </c>
@@ -9679,24 +7976,12 @@
       <c r="D73" s="19" t="s">
         <v>41</v>
       </c>
-      <c r="E73" s="19" t="s">
-        <v>39</v>
-      </c>
-      <c r="F73" s="19" t="s">
-        <v>41</v>
-      </c>
-      <c r="G73" s="19" t="s">
-        <v>39</v>
-      </c>
-      <c r="H73" s="19" t="s">
-        <v>41</v>
-      </c>
-      <c r="I73" s="19" t="s">
-        <v>39</v>
-      </c>
-      <c r="J73" s="19" t="s">
-        <v>41</v>
-      </c>
+      <c r="G73"/>
+      <c r="H73"/>
+      <c r="I73"/>
+      <c r="J73"/>
+      <c r="K73"/>
+      <c r="L73"/>
       <c r="M73"/>
       <c r="N73"/>
       <c r="O73"/>
@@ -9717,55 +8002,27 @@
         <v>28000</v>
       </c>
       <c r="E74" s="10">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F74" s="10">
-        <v>3000</v>
-      </c>
-      <c r="G74" s="10">
-        <v>1</v>
-      </c>
-      <c r="H74" s="10">
-        <v>1000</v>
-      </c>
-      <c r="I74" s="10">
-        <v>1</v>
-      </c>
-      <c r="J74" s="10">
-        <v>18000</v>
-      </c>
-      <c r="K74" s="10">
-        <v>5</v>
-      </c>
-      <c r="L74" s="10">
-        <v>50000</v>
+        <v>28000</v>
       </c>
     </row>
     <row r="75" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B75" s="17">
         <v>46147</v>
       </c>
-      <c r="C75" s="23">
+      <c r="C75" s="55">
         <v>4</v>
       </c>
-      <c r="D75" s="23">
+      <c r="D75" s="55">
         <v>64000</v>
       </c>
       <c r="E75" s="10">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F75" s="10">
-        <v>3000</v>
-      </c>
-      <c r="G75" s="10"/>
-      <c r="H75" s="10"/>
-      <c r="I75" s="10"/>
-      <c r="J75" s="10"/>
-      <c r="K75" s="10">
-        <v>5</v>
-      </c>
-      <c r="L75" s="10">
-        <v>67000</v>
+        <v>64000</v>
       </c>
     </row>
     <row r="76" spans="2:20" x14ac:dyDescent="0.25">
@@ -9778,16 +8035,10 @@
       <c r="D76" s="10">
         <v>18000</v>
       </c>
-      <c r="E76" s="10"/>
-      <c r="F76" s="10"/>
-      <c r="G76" s="10"/>
-      <c r="H76" s="10"/>
-      <c r="I76" s="10"/>
-      <c r="J76" s="10"/>
-      <c r="K76" s="10">
+      <c r="E76" s="10">
         <v>1</v>
       </c>
-      <c r="L76" s="10">
+      <c r="F76" s="10">
         <v>18000</v>
       </c>
     </row>
@@ -9795,35 +8046,17 @@
       <c r="B77" s="17" t="s">
         <v>40</v>
       </c>
-      <c r="C77" s="10">
+      <c r="C77" s="54">
         <v>7</v>
       </c>
-      <c r="D77" s="10">
+      <c r="D77" s="54">
         <v>110000</v>
       </c>
       <c r="E77" s="10">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="F77" s="10">
-        <v>6000</v>
-      </c>
-      <c r="G77" s="10">
-        <v>1</v>
-      </c>
-      <c r="H77" s="10">
-        <v>1000</v>
-      </c>
-      <c r="I77" s="10">
-        <v>1</v>
-      </c>
-      <c r="J77" s="10">
-        <v>18000</v>
-      </c>
-      <c r="K77" s="10">
-        <v>11</v>
-      </c>
-      <c r="L77" s="10">
-        <v>135000</v>
+        <v>110000</v>
       </c>
     </row>
     <row r="78" spans="2:20" x14ac:dyDescent="0.25">
@@ -9840,10 +8073,10 @@
       <c r="L78" s="10"/>
     </row>
     <row r="79" spans="2:20" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="B79" s="53" t="s">
+      <c r="B79" s="50" t="s">
         <v>192</v>
       </c>
-      <c r="C79" s="54"/>
+      <c r="C79" s="51"/>
     </row>
   </sheetData>
   <mergeCells count="10">
@@ -9871,14 +8104,15 @@
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId5"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId5"/>
+  <drawing r:id="rId6"/>
   <tableParts count="1">
-    <tablePart r:id="rId6"/>
+    <tablePart r:id="rId7"/>
   </tableParts>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{A8765BA9-456A-4dab-B4F3-ACF838C121DE}">
       <x14:slicerList>
-        <x14:slicer r:id="rId7"/>
+        <x14:slicer r:id="rId8"/>
       </x14:slicerList>
     </ext>
   </extLst>
@@ -9925,16 +8159,16 @@
       <c r="H2" t="s">
         <v>5</v>
       </c>
-      <c r="J2" s="47" t="s">
+      <c r="J2" s="46" t="s">
         <v>111</v>
       </c>
-      <c r="K2" s="47"/>
-      <c r="L2" s="47"/>
-      <c r="N2" s="47" t="s">
+      <c r="K2" s="46"/>
+      <c r="L2" s="46"/>
+      <c r="N2" s="46" t="s">
         <v>112</v>
       </c>
-      <c r="O2" s="47"/>
-      <c r="P2" s="47"/>
+      <c r="O2" s="46"/>
+      <c r="P2" s="46"/>
     </row>
     <row r="3" spans="2:16" ht="45" x14ac:dyDescent="0.25">
       <c r="B3" s="10" t="s">
@@ -10123,7 +8357,7 @@
       <c r="H7">
         <v>18000</v>
       </c>
-      <c r="J7" s="24" t="s">
+      <c r="J7" s="23" t="s">
         <v>80</v>
       </c>
       <c r="K7" s="10">
@@ -10164,7 +8398,7 @@
       <c r="H8">
         <v>18000</v>
       </c>
-      <c r="J8" s="24" t="s">
+      <c r="J8" s="23" t="s">
         <v>85</v>
       </c>
       <c r="K8" s="10">
@@ -10523,22 +8757,22 @@
     <mergeCell ref="N2:P2"/>
   </mergeCells>
   <conditionalFormatting pivot="1" sqref="L4:L8">
-    <cfRule type="cellIs" dxfId="8" priority="5" operator="lessThan">
+    <cfRule type="cellIs" dxfId="42" priority="5" operator="lessThan">
       <formula>10000</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting pivot="1" sqref="P4:P8">
-    <cfRule type="cellIs" dxfId="7" priority="4" operator="lessThan">
+    <cfRule type="cellIs" dxfId="41" priority="4" operator="lessThan">
       <formula>$Q$4</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting pivot="1" sqref="P4:P9">
-    <cfRule type="cellIs" dxfId="6" priority="3" operator="lessThan">
+    <cfRule type="cellIs" dxfId="40" priority="3" operator="lessThan">
       <formula>30000</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J7:J8">
-    <cfRule type="cellIs" dxfId="5" priority="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="39" priority="1" operator="lessThan">
       <formula>10000</formula>
     </cfRule>
   </conditionalFormatting>
@@ -10676,7 +8910,7 @@
       <c r="Y3" s="19" t="s">
         <v>40</v>
       </c>
-      <c r="AA3" s="27" t="s">
+      <c r="AA3" s="26" t="s">
         <v>136</v>
       </c>
     </row>
@@ -11278,7 +9512,7 @@
       <c r="H21" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="I21" s="25">
+      <c r="I21" s="24">
         <v>6</v>
       </c>
     </row>
@@ -11402,23 +9636,23 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B20:C29">
-    <cfRule type="cellIs" dxfId="4" priority="5" operator="lessThan">
+    <cfRule type="cellIs" dxfId="38" priority="5" operator="lessThan">
       <formula>2</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting pivot="1" sqref="F21:F25">
-    <cfRule type="cellIs" dxfId="3" priority="4" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="37" priority="4" operator="greaterThan">
       <formula>5</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting pivot="1" sqref="F21:F25">
-    <cfRule type="cellIs" dxfId="2" priority="3" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="36" priority="3" operator="greaterThan">
       <formula>5</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AA4:AA11">
-    <cfRule type="top10" dxfId="1" priority="1" rank="2"/>
-    <cfRule type="top10" dxfId="0" priority="2" rank="2"/>
+    <cfRule type="top10" dxfId="35" priority="1" rank="2"/>
+    <cfRule type="top10" dxfId="34" priority="2" rank="2"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="2">
@@ -11629,7 +9863,7 @@
       <c r="J5" s="9" t="s">
         <v>144</v>
       </c>
-      <c r="K5" s="30">
+      <c r="K5" s="29">
         <v>2</v>
       </c>
       <c r="L5" s="10">
@@ -11639,16 +9873,16 @@
         <v>1</v>
       </c>
       <c r="N5" s="10"/>
-      <c r="O5" s="25">
+      <c r="O5" s="24">
         <v>1</v>
       </c>
-      <c r="P5" s="25">
+      <c r="P5" s="24">
         <v>1</v>
       </c>
-      <c r="Q5" s="25">
+      <c r="Q5" s="24">
         <v>1</v>
       </c>
-      <c r="R5" s="25">
+      <c r="R5" s="24">
         <v>1</v>
       </c>
       <c r="S5" s="10"/>
@@ -11693,7 +9927,7 @@
       <c r="P6" s="10"/>
       <c r="Q6" s="10"/>
       <c r="R6" s="10"/>
-      <c r="S6" s="25">
+      <c r="S6" s="24">
         <v>1</v>
       </c>
       <c r="T6" s="10">
@@ -11778,22 +10012,22 @@
       <c r="H8" s="10" t="s">
         <v>144</v>
       </c>
-      <c r="J8" s="29" t="s">
+      <c r="J8" s="28" t="s">
         <v>165</v>
       </c>
-      <c r="K8" s="35" t="s">
+      <c r="K8" s="34" t="s">
         <v>147</v>
       </c>
-      <c r="L8" s="35" t="s">
+      <c r="L8" s="34" t="s">
         <v>149</v>
       </c>
-      <c r="M8" s="35" t="s">
+      <c r="M8" s="34" t="s">
         <v>153</v>
       </c>
-      <c r="N8" s="35" t="s">
+      <c r="N8" s="34" t="s">
         <v>157</v>
       </c>
-      <c r="O8" s="35" t="s">
+      <c r="O8" s="34" t="s">
         <v>163</v>
       </c>
     </row>
@@ -11819,10 +10053,10 @@
       <c r="H9" s="10" t="s">
         <v>144</v>
       </c>
-      <c r="J9" s="31" t="s">
+      <c r="J9" s="30" t="s">
         <v>166</v>
       </c>
-      <c r="K9" s="31" t="s">
+      <c r="K9" s="30" t="s">
         <v>114</v>
       </c>
     </row>
@@ -11902,25 +10136,25 @@
       </c>
     </row>
     <row r="13" spans="2:20" s="19" customFormat="1" ht="27" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B13" s="32" t="s">
+      <c r="B13" s="31" t="s">
         <v>155</v>
       </c>
-      <c r="C13" s="33">
+      <c r="C13" s="32">
         <v>46159</v>
       </c>
-      <c r="D13" s="32" t="s">
+      <c r="D13" s="31" t="s">
         <v>118</v>
       </c>
-      <c r="E13" s="32" t="s">
+      <c r="E13" s="31" t="s">
         <v>19</v>
       </c>
-      <c r="F13" s="32" t="s">
+      <c r="F13" s="31" t="s">
         <v>10</v>
       </c>
       <c r="G13" s="19">
         <v>10000</v>
       </c>
-      <c r="H13" s="32" t="s">
+      <c r="H13" s="31" t="s">
         <v>144</v>
       </c>
       <c r="J13" s="20" t="s">
@@ -12028,26 +10262,26 @@
       <c r="J15" s="9" t="s">
         <v>144</v>
       </c>
-      <c r="K15" s="25">
+      <c r="K15" s="24">
         <v>1</v>
       </c>
       <c r="L15" s="10">
         <v>2</v>
       </c>
-      <c r="M15" s="25">
+      <c r="M15" s="24">
         <v>1</v>
       </c>
       <c r="N15" s="10">
         <v>1</v>
       </c>
-      <c r="O15" s="25">
+      <c r="O15" s="24">
         <v>1</v>
       </c>
       <c r="P15" s="10">
         <v>1</v>
       </c>
       <c r="Q15" s="10"/>
-      <c r="R15" s="25">
+      <c r="R15" s="24">
         <v>1</v>
       </c>
       <c r="S15" s="10"/>
@@ -12092,7 +10326,7 @@
       <c r="P16" s="10"/>
       <c r="Q16" s="10"/>
       <c r="R16" s="10"/>
-      <c r="S16" s="25">
+      <c r="S16" s="24">
         <v>1</v>
       </c>
       <c r="T16" s="10">
@@ -12156,7 +10390,7 @@
       </c>
     </row>
     <row r="18" spans="2:38" x14ac:dyDescent="0.25">
-      <c r="J18" s="29" t="s">
+      <c r="J18" s="28" t="s">
         <v>167</v>
       </c>
     </row>
@@ -12185,42 +10419,42 @@
       <c r="AG19" s="19"/>
     </row>
     <row r="20" spans="2:38" s="19" customFormat="1" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="N20" s="34" t="s">
+      <c r="N20" s="33" t="s">
         <v>114</v>
       </c>
-      <c r="O20" s="34"/>
-      <c r="P20" s="28" t="s">
+      <c r="O20" s="33"/>
+      <c r="P20" s="27" t="s">
         <v>116</v>
       </c>
-      <c r="Q20" s="28"/>
-      <c r="R20" s="34" t="s">
+      <c r="Q20" s="27"/>
+      <c r="R20" s="33" t="s">
         <v>118</v>
       </c>
-      <c r="S20" s="34"/>
-      <c r="T20" s="28" t="s">
+      <c r="S20" s="33"/>
+      <c r="T20" s="27" t="s">
         <v>123</v>
       </c>
-      <c r="U20" s="28"/>
-      <c r="V20" s="34" t="s">
+      <c r="U20" s="27"/>
+      <c r="V20" s="33" t="s">
         <v>147</v>
       </c>
-      <c r="W20" s="34"/>
-      <c r="X20" s="28" t="s">
+      <c r="W20" s="33"/>
+      <c r="X20" s="27" t="s">
         <v>149</v>
       </c>
-      <c r="Y20" s="28"/>
-      <c r="Z20" s="34" t="s">
+      <c r="Y20" s="27"/>
+      <c r="Z20" s="33" t="s">
         <v>153</v>
       </c>
-      <c r="AA20" s="34"/>
-      <c r="AB20" s="28" t="s">
+      <c r="AA20" s="33"/>
+      <c r="AB20" s="27" t="s">
         <v>157</v>
       </c>
-      <c r="AC20" s="28"/>
-      <c r="AD20" s="34" t="s">
+      <c r="AC20" s="27"/>
+      <c r="AD20" s="33" t="s">
         <v>163</v>
       </c>
-      <c r="AE20" s="34"/>
+      <c r="AE20" s="33"/>
       <c r="AF20" s="19" t="s">
         <v>70</v>
       </c>
@@ -12308,13 +10542,13 @@
       <c r="M22" s="9" t="s">
         <v>139</v>
       </c>
-      <c r="N22" s="25">
+      <c r="N22" s="24">
         <v>18000</v>
       </c>
-      <c r="O22" s="25">
+      <c r="O22" s="24">
         <v>1</v>
       </c>
-      <c r="P22" s="25">
+      <c r="P22" s="24">
         <v>3000</v>
       </c>
       <c r="Q22" s="21">
@@ -12359,13 +10593,13 @@
       <c r="M23" s="9" t="s">
         <v>144</v>
       </c>
-      <c r="N23" s="25">
+      <c r="N23" s="24">
         <v>25200</v>
       </c>
-      <c r="O23" s="25">
+      <c r="O23" s="24">
         <v>2</v>
       </c>
-      <c r="P23" s="25">
+      <c r="P23" s="24">
         <v>3000</v>
       </c>
       <c r="Q23" s="21">
@@ -12422,13 +10656,13 @@
       <c r="M24" s="9" t="s">
         <v>160</v>
       </c>
-      <c r="N24" s="25">
+      <c r="N24" s="24">
         <v>18000</v>
       </c>
-      <c r="O24" s="25">
+      <c r="O24" s="24">
         <v>1</v>
       </c>
-      <c r="P24" s="25">
+      <c r="P24" s="24">
         <v>3000</v>
       </c>
       <c r="Q24" s="21">
@@ -12531,10 +10765,10 @@
       </c>
     </row>
     <row r="26" spans="2:38" x14ac:dyDescent="0.25">
-      <c r="J26" s="26" t="s">
+      <c r="J26" s="25" t="s">
         <v>168</v>
       </c>
-      <c r="M26" s="29" t="s">
+      <c r="M26" s="28" t="s">
         <v>169</v>
       </c>
     </row>

--- a/Analyses Excel/Préparation_Stage_Academique_2026_(exercices_pratique).xlsx
+++ b/Analyses Excel/Préparation_Stage_Academique_2026_(exercices_pratique).xlsx
@@ -2,15 +2,15 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27932"/>
-  <workbookPr defaultThemeVersion="202300"/>
+  <workbookPr hidePivotFieldList="1" defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\JevainBkg\Projets\Datascience-roadmap\Analyses Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A9D179E2-7A7C-4F37-8C8F-FD0F3115AF0A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F8C1A734-BDA7-4378-8725-97A2C2A990CE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13740" activeTab="1" xr2:uid="{7D3A7277-DCDC-4547-AB5A-331124B03413}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13740" activeTab="3" xr2:uid="{7D3A7277-DCDC-4547-AB5A-331124B03413}"/>
   </bookViews>
   <sheets>
     <sheet name="Dataset_day1" sheetId="1" r:id="rId1"/>
@@ -30,7 +30,7 @@
   <calcPr calcId="191029"/>
   <pivotCaches>
     <pivotCache cacheId="0" r:id="rId8"/>
-    <pivotCache cacheId="5" r:id="rId9"/>
+    <pivotCache cacheId="1" r:id="rId9"/>
     <pivotCache cacheId="2" r:id="rId10"/>
     <pivotCache cacheId="3" r:id="rId11"/>
     <pivotCache cacheId="4" r:id="rId12"/>
@@ -105,7 +105,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="675" uniqueCount="194">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="691" uniqueCount="210">
   <si>
     <t>transaction_id</t>
   </si>
@@ -438,12 +438,6 @@
   </si>
   <si>
     <t>C115</t>
-  </si>
-  <si>
-    <t>Best agent</t>
-  </si>
-  <si>
-    <t>Best zone</t>
   </si>
   <si>
     <t>F001</t>
@@ -733,12 +727,266 @@
   <si>
     <t xml:space="preserve">Canal fav </t>
   </si>
+  <si>
+    <t>Dataset</t>
+  </si>
+  <si>
+    <t>Question 1 : Pérformance agents</t>
+  </si>
+  <si>
+    <t>Question 2 : Quelle zone rapporte le plus ?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Performance communes			</t>
+  </si>
+  <si>
+    <t>Question 3 : Quel produit fonctionne selon la zone ?</t>
+  </si>
+  <si>
+    <t>Produit par zone</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">Note : </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">Nous avons en vert l'(es) agent(s) performant(s) et plus nous tendons vers le rouge moins pérformant est l'agent </t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">Note : </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">Nous avons en vert la(es) commune(s) performante(s) et plus nous tendons vers le rouge moins pérformant est la commune </t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">Note : </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Nous constatons que nos client de la commune de ndjili ainsi qu'une partie de la Gombe sont plus attirés par notre offre Data 10GB , Matete et une petite partie de la Gombe par Data 5GB , nos clients de masina ne jure que sur l'offr e SMS et Limete sur L'offre Voice</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">Note : </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">Nous avons en vert le client C001 qui est très active et plus nous tendons vers le blanc moins active est le client </t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">Note : </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">Le client C001 est aussi celui qui nous depense le plus </t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">Note : </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>La plupart de nos clients préfèrent payer leurs forfaits auprès de nos agents</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">Note : </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Seul le client C001 présente des suspicions mais une analyse approfondie s'impose avant une quelconque conclusion</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">Note : </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Notre chiffre d'affaires est à hauteur de 77000 FC et nous constatons par la même occasion que la dernière journée de vente aurait été très fructueuse</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">Note : </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>La commune de la Gombe est celle qui fait le plus grand CA</t>
+    </r>
+  </si>
+  <si>
+    <t>Chiffre d'affaire</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">Note :  </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Notre offre Data 10GB est la plus rentable de tous</t>
+    </r>
+  </si>
+  <si>
+    <t>Classement agents</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="8" x14ac:knownFonts="1">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -798,8 +1046,15 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="13">
+  <fills count="12">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -833,12 +1088,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2C4CB"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -931,7 +1180,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="56">
+  <cellXfs count="61">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -988,15 +1237,14 @@
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="2" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
@@ -1005,8 +1253,8 @@
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="2" fillId="11" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="10" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1016,7 +1264,7 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="0" xfId="0" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="0" xfId="0" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
@@ -1030,28 +1278,7 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1060,191 +1287,48 @@
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="7" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="172">
-    <dxf>
-      <font>
-        <color rgb="FFFF0000"/>
-      </font>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="9" tint="0.39997558519241921"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <alignment wrapText="1"/>
-    </dxf>
-    <dxf>
-      <alignment wrapText="1"/>
-    </dxf>
-    <dxf>
-      <alignment wrapText="1"/>
-    </dxf>
-    <dxf>
-      <alignment wrapText="1"/>
-    </dxf>
-    <dxf>
-      <alignment wrapText="1"/>
-    </dxf>
-    <dxf>
-      <alignment wrapText="1"/>
-    </dxf>
-    <dxf>
-      <alignment wrapText="1"/>
-    </dxf>
-    <dxf>
-      <alignment wrapText="1"/>
-    </dxf>
-    <dxf>
-      <alignment wrapText="1"/>
-    </dxf>
-    <dxf>
-      <alignment wrapText="1"/>
-    </dxf>
-    <dxf>
-      <alignment wrapText="1"/>
-    </dxf>
-    <dxf>
-      <alignment wrapText="1"/>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="5"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="5"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="5" tint="0.39997558519241921"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="5" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="5" tint="-0.249977111117893"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="5" tint="0.39997558519241921"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="5" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="5" tint="-0.249977111117893"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="5" tint="0.39997558519241921"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFFF0000"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFFF0000"/>
-      </font>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFFF0000"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFFF0000"/>
-      </font>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="5"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="5"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFFF0000"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFFF0000"/>
-      </font>
-    </dxf>
+  <dxfs count="164">
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -1336,19 +1420,50 @@
       </fill>
     </dxf>
     <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
     </dxf>
     <dxf>
       <fill>
         <patternFill patternType="solid">
           <fgColor indexed="64"/>
-          <bgColor theme="5" tint="0.39997558519241921"/>
+          <bgColor theme="9" tint="0.39997558519241921"/>
         </patternFill>
       </fill>
     </dxf>
@@ -1356,59 +1471,124 @@
       <fill>
         <patternFill patternType="solid">
           <fgColor indexed="64"/>
-          <bgColor theme="5" tint="-0.249977111117893"/>
+          <bgColor theme="9" tint="0.39997558519241921"/>
         </patternFill>
       </fill>
     </dxf>
     <dxf>
       <fill>
         <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="5" tint="0.79998168889431442"/>
+          <bgColor theme="9" tint="0.39997558519241921"/>
         </patternFill>
       </fill>
     </dxf>
     <dxf>
       <fill>
         <patternFill patternType="solid">
-          <bgColor theme="5" tint="0.39997558519241921"/>
+          <bgColor theme="9" tint="0.39997558519241921"/>
         </patternFill>
       </fill>
     </dxf>
     <dxf>
       <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="5" tint="-0.249977111117893"/>
+        <patternFill>
+          <bgColor theme="9" tint="0.79998168889431442"/>
         </patternFill>
       </fill>
     </dxf>
     <dxf>
       <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="5" tint="0.79998168889431442"/>
+        <patternFill>
+          <fgColor theme="9" tint="0.39997558519241921"/>
         </patternFill>
       </fill>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF4DD36D"/>
+        </patternFill>
+      </fill>
     </dxf>
     <dxf>
       <fill>
         <patternFill patternType="solid">
-          <bgColor theme="5" tint="0.39997558519241921"/>
+          <bgColor theme="9" tint="0.39997558519241921"/>
         </patternFill>
       </fill>
     </dxf>
     <dxf>
       <fill>
         <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="5"/>
+          <bgColor theme="9" tint="0.39997558519241921"/>
         </patternFill>
       </fill>
     </dxf>
     <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <fgColor theme="9" tint="0.39997558519241921"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF4DD36D"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <numFmt numFmtId="19" formatCode="dd/mm/yyyy"/>
@@ -1433,12 +1613,6 @@
     </dxf>
     <dxf>
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment wrapText="1"/>
-    </dxf>
-    <dxf>
-      <alignment wrapText="1"/>
     </dxf>
     <dxf>
       <fill>
@@ -1602,6 +1776,12 @@
           <bgColor theme="0"/>
         </patternFill>
       </fill>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1"/>
     </dxf>
     <dxf>
       <alignment wrapText="1"/>
@@ -1699,12 +1879,6 @@
       <numFmt numFmtId="0" formatCode="General"/>
     </dxf>
     <dxf>
-      <alignment wrapText="1"/>
-    </dxf>
-    <dxf>
-      <alignment wrapText="1"/>
-    </dxf>
-    <dxf>
       <fill>
         <patternFill>
           <bgColor rgb="FFF2C4CB"/>
@@ -1752,6 +1926,99 @@
       <numFmt numFmtId="0" formatCode="General"/>
     </dxf>
     <dxf>
+      <alignment horizontal="center"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center"/>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFFF0000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFFF0000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFFF0000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFFF0000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="5" tint="0.39997558519241921"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="5" tint="-0.249977111117893"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="5" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="5" tint="0.39997558519241921"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="5" tint="-0.249977111117893"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="5" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="5" tint="0.39997558519241921"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="5"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
       <fill>
         <patternFill patternType="solid">
           <bgColor theme="5"/>
@@ -1807,6 +2074,15 @@
           <bgColor theme="9" tint="0.39997558519241921"/>
         </patternFill>
       </fill>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center"/>
     </dxf>
     <dxf>
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
@@ -1854,6 +2130,38 @@
     </dxf>
     <dxf>
       <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="9" tint="0.39997558519241921"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="9" tint="0.39997558519241921"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="9" tint="0.39997558519241921"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="9" tint="0.39997558519241921"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
         <patternFill>
           <bgColor rgb="FF4DD36D"/>
         </patternFill>
@@ -1891,38 +2199,6 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
-          <bgColor theme="9" tint="0.39997558519241921"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="9" tint="0.39997558519241921"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="9" tint="0.39997558519241921"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="9" tint="0.39997558519241921"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
           <bgColor theme="9" tint="0.39997558519241921"/>
         </patternFill>
       </fill>
@@ -1953,17 +2229,17 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>79</xdr:row>
+      <xdr:row>85</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>7</xdr:col>
-      <xdr:colOff>698499</xdr:colOff>
-      <xdr:row>83</xdr:row>
+      <xdr:colOff>250824</xdr:colOff>
+      <xdr:row>89</xdr:row>
       <xdr:rowOff>179917</xdr:rowOff>
     </xdr:to>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+      <mc:Choice Requires="a14">
         <xdr:graphicFrame macro="">
           <xdr:nvGraphicFramePr>
             <xdr:cNvPr id="3" name="client_id">
@@ -1988,7 +2264,7 @@
           </a:graphic>
         </xdr:graphicFrame>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="0" name=""/>
@@ -3016,10 +3292,10 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{0489F5AA-4386-45E5-9C54-88F4AB4B8C8B}" name="Tableau croisé dynamique8" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valeurs" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
-  <location ref="B31:C37" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{0A94A5AA-7939-49B7-A6DD-E9354366584E}" name="Tableau croisé dynamique11" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valeurs" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+  <location ref="B60:C64" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="7">
-    <pivotField showAll="0">
+    <pivotField dataField="1" showAll="0">
       <items count="11">
         <item x="0"/>
         <item x="1"/>
@@ -3036,32 +3312,22 @@
     </pivotField>
     <pivotField numFmtId="14" showAll="0"/>
     <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
     <pivotField axis="axisRow" showAll="0">
-      <items count="6">
+      <items count="4">
+        <item x="2"/>
         <item x="0"/>
         <item x="1"/>
-        <item x="4"/>
-        <item x="2"/>
-        <item x="3"/>
         <item t="default"/>
       </items>
     </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField dataField="1" showAll="0" sumSubtotal="1">
-      <items count="5">
-        <item x="2"/>
-        <item x="1"/>
-        <item x="0"/>
-        <item x="3"/>
-        <item t="sum"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
   </pivotFields>
   <rowFields count="1">
-    <field x="3"/>
+    <field x="6"/>
   </rowFields>
-  <rowItems count="6">
+  <rowItems count="4">
     <i>
       <x/>
     </i>
@@ -3070,12 +3336,6 @@
     </i>
     <i>
       <x v="2"/>
-    </i>
-    <i>
-      <x v="3"/>
-    </i>
-    <i>
-      <x v="4"/>
     </i>
     <i t="grand">
       <x/>
@@ -3085,84 +3345,28 @@
     <i/>
   </colItems>
   <dataFields count="1">
-    <dataField name="Somme de montant_fc" fld="5" baseField="0" baseItem="0"/>
+    <dataField name="Nombre de transaction_id" fld="0" subtotal="count" baseField="0" baseItem="0"/>
   </dataFields>
-  <formats count="6">
-    <format dxfId="167">
+  <formats count="2">
+    <format dxfId="155">
       <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
         <references count="1">
-          <reference field="3" count="1">
+          <reference field="6" count="1">
             <x v="0"/>
           </reference>
         </references>
       </pivotArea>
     </format>
-    <format dxfId="166">
+    <format dxfId="154">
       <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
         <references count="1">
-          <reference field="3" count="1">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </format>
-    <format dxfId="165">
-      <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
-        <references count="1">
-          <reference field="3" count="1">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </format>
-    <format dxfId="164">
-      <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
-        <references count="1">
-          <reference field="3" count="1">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </format>
-    <format dxfId="163">
-      <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
-        <references count="1">
-          <reference field="3" count="1">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </format>
-    <format dxfId="162">
-      <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
-        <references count="1">
-          <reference field="3" count="1">
+          <reference field="6" count="1">
             <x v="0"/>
           </reference>
         </references>
       </pivotArea>
     </format>
   </formats>
-  <conditionalFormats count="1">
-    <conditionalFormat priority="3">
-      <pivotAreas count="1">
-        <pivotArea type="data" collapsedLevelsAreSubtotals="1" fieldPosition="0">
-          <references count="2">
-            <reference field="4294967294" count="1" selected="0">
-              <x v="0"/>
-            </reference>
-            <reference field="3" count="5">
-              <x v="0"/>
-              <x v="1"/>
-              <x v="2"/>
-              <x v="3"/>
-              <x v="4"/>
-            </reference>
-          </references>
-        </pivotArea>
-      </pivotAreas>
-    </conditionalFormat>
-  </conditionalFormats>
   <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
@@ -3176,14 +3380,14 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable10.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{ED04ABC1-CC07-43AE-8AC6-404199804ABF}" name="Tableau croisé dynamique27" cacheId="2" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valeurs" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
-  <location ref="N3:P9" firstHeaderRow="0" firstDataRow="1" firstDataCol="1"/>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{B6B3D1A4-0B77-482E-9D3E-CEB1DCD7B445}" name="Tableau croisé dynamique28" cacheId="2" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valeurs" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+  <location ref="B49:H55" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
   <pivotFields count="7">
-    <pivotField dataField="1" showAll="0"/>
+    <pivotField showAll="0"/>
     <pivotField numFmtId="14" showAll="0"/>
     <pivotField showAll="0"/>
     <pivotField showAll="0"/>
-    <pivotField axis="axisRow" showAll="0" sortType="descending">
+    <pivotField axis="axisCol" showAll="0">
       <items count="6">
         <item x="0"/>
         <item x="1"/>
@@ -3192,103 +3396,64 @@
         <item x="3"/>
         <item t="default"/>
       </items>
-      <autoSortScope>
-        <pivotArea dataOnly="0" outline="0" fieldPosition="0">
-          <references count="1">
-            <reference field="4294967294" count="1" selected="0">
-              <x v="1"/>
-            </reference>
-          </references>
-        </pivotArea>
-      </autoSortScope>
     </pivotField>
-    <pivotField showAll="0"/>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="5">
+        <item x="0"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="1"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
     <pivotField dataField="1" showAll="0"/>
   </pivotFields>
   <rowFields count="1">
-    <field x="4"/>
+    <field x="5"/>
   </rowFields>
-  <rowItems count="6">
+  <rowItems count="5">
     <i>
       <x/>
     </i>
     <i>
-      <x v="4"/>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
     </i>
     <i>
       <x v="3"/>
-    </i>
-    <i>
-      <x v="1"/>
-    </i>
-    <i>
-      <x v="2"/>
     </i>
     <i t="grand">
       <x/>
     </i>
   </rowItems>
   <colFields count="1">
-    <field x="-2"/>
+    <field x="4"/>
   </colFields>
-  <colItems count="2">
+  <colItems count="6">
     <i>
       <x/>
     </i>
-    <i i="1">
+    <i>
       <x v="1"/>
     </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i>
+      <x v="4"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
   </colItems>
-  <dataFields count="2">
-    <dataField name="Nombre de transaction_id" fld="0" subtotal="count" baseField="0" baseItem="0"/>
+  <dataFields count="1">
     <dataField name="Somme de montant_fc" fld="6" baseField="0" baseItem="0"/>
   </dataFields>
-  <formats count="2">
-    <format dxfId="126">
-      <pivotArea field="4" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
-    </format>
-    <format dxfId="125">
-      <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="2">
-            <x v="0"/>
-            <x v="1"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </format>
-  </formats>
-  <conditionalFormats count="2">
-    <conditionalFormat priority="3">
-      <pivotAreas count="1">
-        <pivotArea type="data" outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0">
-          <references count="1">
-            <reference field="4294967294" count="1" selected="0">
-              <x v="1"/>
-            </reference>
-          </references>
-        </pivotArea>
-      </pivotAreas>
-    </conditionalFormat>
-    <conditionalFormat priority="4">
-      <pivotAreas count="1">
-        <pivotArea type="data" collapsedLevelsAreSubtotals="1" fieldPosition="0">
-          <references count="2">
-            <reference field="4294967294" count="1" selected="0">
-              <x v="1"/>
-            </reference>
-            <reference field="4" count="5">
-              <x v="0"/>
-              <x v="1"/>
-              <x v="2"/>
-              <x v="3"/>
-              <x v="4"/>
-            </reference>
-          </references>
-        </pivotArea>
-      </pivotAreas>
-    </conditionalFormat>
-  </conditionalFormats>
   <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
@@ -3303,7 +3468,7 @@
 
 <file path=xl/pivotTables/pivotTable11.xml><?xml version="1.0" encoding="utf-8"?>
 <pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{977B8F9E-FB0D-490A-8AEA-204AC7739D25}" name="Tableau croisé dynamique26" cacheId="2" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valeurs" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
-  <location ref="J3:L9" firstHeaderRow="0" firstDataRow="1" firstDataCol="1"/>
+  <location ref="B23:D29" firstHeaderRow="0" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="7">
     <pivotField dataField="1" showAll="0"/>
     <pivotField numFmtId="14" showAll="0"/>
@@ -3369,11 +3534,11 @@
     <dataField name="Nombre de transaction_id" fld="0" subtotal="count" baseField="0" baseItem="0"/>
     <dataField name="Somme de montant_fc" fld="6" baseField="0" baseItem="0"/>
   </dataFields>
-  <formats count="5">
-    <format dxfId="131">
+  <formats count="6">
+    <format dxfId="105">
       <pivotArea field="2" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
     </format>
-    <format dxfId="130">
+    <format dxfId="104">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="1">
           <reference field="4294967294" count="2">
@@ -3383,7 +3548,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="129">
+    <format dxfId="103">
       <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
         <references count="1">
           <reference field="2" count="2">
@@ -3393,7 +3558,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="128">
+    <format dxfId="102">
       <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
         <references count="1">
           <reference field="2" count="2">
@@ -3403,7 +3568,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="127">
+    <format dxfId="101">
       <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
         <references count="1">
           <reference field="2" count="2">
@@ -3413,9 +3578,34 @@
         </references>
       </pivotArea>
     </format>
+    <format dxfId="31">
+      <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
+        <references count="1">
+          <reference field="2" count="0"/>
+        </references>
+      </pivotArea>
+    </format>
   </formats>
-  <conditionalFormats count="1">
-    <conditionalFormat priority="5">
+  <conditionalFormats count="2">
+    <conditionalFormat priority="11">
+      <pivotAreas count="1">
+        <pivotArea type="data" collapsedLevelsAreSubtotals="1" fieldPosition="0">
+          <references count="2">
+            <reference field="4294967294" count="1" selected="0">
+              <x v="1"/>
+            </reference>
+            <reference field="2" count="5">
+              <x v="0"/>
+              <x v="1"/>
+              <x v="2"/>
+              <x v="3"/>
+              <x v="4"/>
+            </reference>
+          </references>
+        </pivotArea>
+      </pivotAreas>
+    </conditionalFormat>
+    <conditionalFormat priority="6">
       <pivotAreas count="1">
         <pivotArea type="data" collapsedLevelsAreSubtotals="1" fieldPosition="0">
           <references count="2">
@@ -3585,10 +3775,10 @@
     <dataField name="Somme de montant_fc" fld="5" baseField="0" baseItem="0"/>
   </dataFields>
   <formats count="2">
-    <format dxfId="111">
+    <format dxfId="87">
       <pivotArea field="2" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
     </format>
-    <format dxfId="110">
+    <format dxfId="86">
       <pivotArea dataOnly="0" labelOnly="1" grandCol="1" outline="0" fieldPosition="0"/>
     </format>
   </formats>
@@ -3669,13 +3859,13 @@
     <dataField name="Nombre de transaction_id" fld="0" subtotal="count" baseField="0" baseItem="0"/>
   </dataFields>
   <formats count="3">
-    <format dxfId="114">
+    <format dxfId="90">
       <pivotArea field="4" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
     </format>
-    <format dxfId="113">
+    <format dxfId="89">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
     </format>
-    <format dxfId="112">
+    <format dxfId="88">
       <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
         <references count="1">
           <reference field="4" count="1">
@@ -3766,15 +3956,15 @@
     <dataField name="Nombre de transaction_id" fld="0" subtotal="count" baseField="0" baseItem="0"/>
   </dataFields>
   <formats count="2">
-    <format dxfId="116">
+    <format dxfId="92">
       <pivotArea field="3" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
     </format>
-    <format dxfId="115">
+    <format dxfId="91">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
     </format>
   </formats>
   <conditionalFormats count="2">
-    <conditionalFormat priority="3">
+    <conditionalFormat priority="4">
       <pivotAreas count="1">
         <pivotArea type="data" collapsedLevelsAreSubtotals="1" fieldPosition="0">
           <references count="2">
@@ -3792,7 +3982,7 @@
         </pivotArea>
       </pivotAreas>
     </conditionalFormat>
-    <conditionalFormat priority="4">
+    <conditionalFormat priority="3">
       <pivotAreas count="1">
         <pivotArea type="data" collapsedLevelsAreSubtotals="1" fieldPosition="0">
           <references count="2">
@@ -3912,10 +4102,10 @@
     <dataField name="Nombre de transaction_id" fld="0" subtotal="count" baseField="0" baseItem="0"/>
   </dataFields>
   <formats count="2">
-    <format dxfId="118">
+    <format dxfId="94">
       <pivotArea field="2" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
     </format>
-    <format dxfId="117">
+    <format dxfId="93">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
     </format>
   </formats>
@@ -3932,112 +4122,6 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable16.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{19B725E5-E44B-4C51-9E5D-DFB5B7840FB2}" name="Tableau croisé dynamique38" cacheId="4" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valeurs" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" rowHeaderCaption="Periodes">
-  <location ref="J21:K25" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
-  <pivotFields count="7">
-    <pivotField showAll="0"/>
-    <pivotField numFmtId="14" showAll="0"/>
-    <pivotField showAll="0">
-      <items count="10">
-        <item x="0"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item x="3"/>
-        <item x="4"/>
-        <item x="5"/>
-        <item x="6"/>
-        <item x="7"/>
-        <item x="8"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0">
-      <items count="10">
-        <item x="6"/>
-        <item x="0"/>
-        <item x="5"/>
-        <item x="1"/>
-        <item x="4"/>
-        <item x="2"/>
-        <item x="3"/>
-        <item x="7"/>
-        <item x="8"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField dataField="1" showAll="0"/>
-    <pivotField axis="axisRow" showAll="0">
-      <items count="4">
-        <item x="0"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-  </pivotFields>
-  <rowFields count="1">
-    <field x="6"/>
-  </rowFields>
-  <rowItems count="4">
-    <i>
-      <x/>
-    </i>
-    <i>
-      <x v="1"/>
-    </i>
-    <i>
-      <x v="2"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </rowItems>
-  <colItems count="1">
-    <i/>
-  </colItems>
-  <dataFields count="1">
-    <dataField name="CA" fld="5" baseField="6" baseItem="0"/>
-  </dataFields>
-  <formats count="2">
-    <format dxfId="65">
-      <pivotArea field="6" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
-    </format>
-    <format dxfId="64">
-      <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
-    </format>
-  </formats>
-  <conditionalFormats count="1">
-    <conditionalFormat priority="2">
-      <pivotAreas count="1">
-        <pivotArea type="data" collapsedLevelsAreSubtotals="1" fieldPosition="0">
-          <references count="2">
-            <reference field="4294967294" count="1" selected="0">
-              <x v="0"/>
-            </reference>
-            <reference field="6" count="3">
-              <x v="0"/>
-              <x v="1"/>
-              <x v="2"/>
-            </reference>
-          </references>
-        </pivotArea>
-      </pivotAreas>
-    </conditionalFormat>
-  </conditionalFormats>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable17.xml><?xml version="1.0" encoding="utf-8"?>
 <pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{5F47745C-4696-420B-92A1-AB6748DDECE4}" name="Tableau croisé dynamique37" cacheId="4" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valeurs" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" rowHeaderCaption="Periodes">
   <location ref="J12:T17" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
   <pivotFields count="7">
@@ -4138,7 +4222,7 @@
     <dataField name="Nombre de transaction_id" fld="0" subtotal="count" baseField="0" baseItem="0"/>
   </dataFields>
   <formats count="8">
-    <format dxfId="73">
+    <format dxfId="47">
       <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
         <references count="2">
           <reference field="3" count="1" selected="0">
@@ -4150,7 +4234,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="72">
+    <format dxfId="46">
       <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
         <references count="2">
           <reference field="3" count="1" selected="0">
@@ -4162,7 +4246,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="71">
+    <format dxfId="45">
       <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
         <references count="2">
           <reference field="3" count="1" selected="0">
@@ -4174,7 +4258,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="70">
+    <format dxfId="44">
       <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
         <references count="2">
           <reference field="3" count="1" selected="0">
@@ -4186,20 +4270,20 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="69">
+    <format dxfId="43">
       <pivotArea field="6" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
     </format>
-    <format dxfId="68">
+    <format dxfId="42">
       <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
         <references count="1">
           <reference field="3" count="0"/>
         </references>
       </pivotArea>
     </format>
-    <format dxfId="67">
+    <format dxfId="41">
       <pivotArea dataOnly="0" labelOnly="1" grandCol="1" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="66">
+    <format dxfId="40">
       <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
         <references count="2">
           <reference field="3" count="1" selected="0">
@@ -4224,7 +4308,7 @@
 </pivotTableDefinition>
 </file>
 
-<file path=xl/pivotTables/pivotTable18.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/pivotTables/pivotTable17.xml><?xml version="1.0" encoding="utf-8"?>
 <pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{1E2F9B57-B688-4923-9689-D300C6FD2A2D}" name="Tableau croisé dynamique36" cacheId="4" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valeurs" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" rowHeaderCaption="Periodes">
   <location ref="J2:T7" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
   <pivotFields count="7">
@@ -4312,7 +4396,7 @@
     <dataField name="Nombre de transaction_id" fld="0" subtotal="count" baseField="0" baseItem="0"/>
   </dataFields>
   <formats count="6">
-    <format dxfId="79">
+    <format dxfId="53">
       <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
         <references count="2">
           <reference field="2" count="4" selected="0">
@@ -4327,7 +4411,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="78">
+    <format dxfId="52">
       <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
         <references count="2">
           <reference field="2" count="1" selected="0">
@@ -4339,7 +4423,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="77">
+    <format dxfId="51">
       <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
         <references count="2">
           <reference field="2" count="1" selected="0">
@@ -4351,13 +4435,13 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="76">
+    <format dxfId="50">
       <pivotArea type="origin" dataOnly="0" labelOnly="1" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="75">
+    <format dxfId="49">
       <pivotArea field="2" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisCol" fieldPosition="0"/>
     </format>
-    <format dxfId="74">
+    <format dxfId="48">
       <pivotArea type="topRight" dataOnly="0" labelOnly="1" outline="0" fieldPosition="0"/>
     </format>
   </formats>
@@ -4373,7 +4457,7 @@
 </pivotTableDefinition>
 </file>
 
-<file path=xl/pivotTables/pivotTable19.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/pivotTables/pivotTable18.xml><?xml version="1.0" encoding="utf-8"?>
 <pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{1508B158-EB77-4324-A140-92124BCC4586}" name="Tableau croisé dynamique39" cacheId="4" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valeurs" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" rowHeaderCaption="Periodes">
   <location ref="M19:AG25" firstHeaderRow="1" firstDataRow="3" firstDataCol="1"/>
   <pivotFields count="7">
@@ -4534,29 +4618,29 @@
     <dataField name="Nombre de transaction_id" fld="0" subtotal="count" baseField="0" baseItem="0"/>
   </dataFields>
   <formats count="24">
-    <format dxfId="103">
+    <format dxfId="77">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
     </format>
-    <format dxfId="102">
+    <format dxfId="76">
       <pivotArea type="origin" dataOnly="0" labelOnly="1" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="101">
+    <format dxfId="75">
       <pivotArea field="2" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisCol" fieldPosition="0"/>
     </format>
-    <format dxfId="100">
+    <format dxfId="74">
       <pivotArea type="topRight" dataOnly="0" labelOnly="1" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="99">
+    <format dxfId="73">
       <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
         <references count="1">
           <reference field="6" count="0"/>
         </references>
       </pivotArea>
     </format>
-    <format dxfId="98">
+    <format dxfId="72">
       <pivotArea field="6" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
     </format>
-    <format dxfId="97">
+    <format dxfId="71">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="2">
           <reference field="4294967294" count="2">
@@ -4569,7 +4653,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="96">
+    <format dxfId="70">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="2">
           <reference field="4294967294" count="2">
@@ -4582,7 +4666,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="95">
+    <format dxfId="69">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="2">
           <reference field="4294967294" count="2">
@@ -4595,7 +4679,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="94">
+    <format dxfId="68">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="2">
           <reference field="4294967294" count="2">
@@ -4608,7 +4692,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="93">
+    <format dxfId="67">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="2">
           <reference field="4294967294" count="2">
@@ -4621,7 +4705,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="92">
+    <format dxfId="66">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="2">
           <reference field="4294967294" count="2">
@@ -4634,7 +4718,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="91">
+    <format dxfId="65">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="2">
           <reference field="4294967294" count="2">
@@ -4647,7 +4731,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="90">
+    <format dxfId="64">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="2">
           <reference field="4294967294" count="2">
@@ -4660,7 +4744,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="89">
+    <format dxfId="63">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="2">
           <reference field="4294967294" count="2">
@@ -4673,7 +4757,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="88">
+    <format dxfId="62">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="2">
           <reference field="4294967294" count="1">
@@ -4685,7 +4769,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="87">
+    <format dxfId="61">
       <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
         <references count="1">
           <reference field="2" count="1">
@@ -4694,7 +4778,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="86">
+    <format dxfId="60">
       <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
         <references count="1">
           <reference field="2" count="1">
@@ -4703,7 +4787,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="85">
+    <format dxfId="59">
       <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
         <references count="1">
           <reference field="2" count="7">
@@ -4718,7 +4802,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="84">
+    <format dxfId="58">
       <pivotArea field="2" dataOnly="0" labelOnly="1" grandCol="1" outline="0" axis="axisCol" fieldPosition="0">
         <references count="1">
           <reference field="4294967294" count="1" selected="0">
@@ -4727,7 +4811,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="83">
+    <format dxfId="57">
       <pivotArea field="2" dataOnly="0" labelOnly="1" grandCol="1" outline="0" axis="axisCol" fieldPosition="0">
         <references count="1">
           <reference field="4294967294" count="1" selected="0">
@@ -4736,7 +4820,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="82">
+    <format dxfId="56">
       <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
         <references count="3">
           <reference field="4294967294" count="1" selected="0">
@@ -4749,7 +4833,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="81">
+    <format dxfId="55">
       <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
         <references count="3">
           <reference field="4294967294" count="1" selected="0">
@@ -4762,7 +4846,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="80">
+    <format dxfId="54">
       <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
         <references count="3">
           <reference field="4294967294" count="1" selected="0">
@@ -4788,7 +4872,388 @@
 </pivotTableDefinition>
 </file>
 
+<file path=xl/pivotTables/pivotTable19.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{19B725E5-E44B-4C51-9E5D-DFB5B7840FB2}" name="Tableau croisé dynamique38" cacheId="4" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valeurs" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" rowHeaderCaption="Periodes">
+  <location ref="J21:K25" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+  <pivotFields count="7">
+    <pivotField showAll="0"/>
+    <pivotField numFmtId="14" showAll="0"/>
+    <pivotField showAll="0">
+      <items count="10">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item x="6"/>
+        <item x="7"/>
+        <item x="8"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0">
+      <items count="10">
+        <item x="6"/>
+        <item x="0"/>
+        <item x="5"/>
+        <item x="1"/>
+        <item x="4"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="7"/>
+        <item x="8"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField dataField="1" showAll="0"/>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="4">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="6"/>
+  </rowFields>
+  <rowItems count="4">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="CA" fld="5" baseField="6" baseItem="0"/>
+  </dataFields>
+  <formats count="2">
+    <format dxfId="79">
+      <pivotArea field="6" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
+    </format>
+    <format dxfId="78">
+      <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
+    </format>
+  </formats>
+  <conditionalFormats count="1">
+    <conditionalFormat priority="2">
+      <pivotAreas count="1">
+        <pivotArea type="data" collapsedLevelsAreSubtotals="1" fieldPosition="0">
+          <references count="2">
+            <reference field="4294967294" count="1" selected="0">
+              <x v="0"/>
+            </reference>
+            <reference field="6" count="3">
+              <x v="0"/>
+              <x v="1"/>
+              <x v="2"/>
+            </reference>
+          </references>
+        </pivotArea>
+      </pivotAreas>
+    </conditionalFormat>
+  </conditionalFormats>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
 <file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{0E420E65-FA27-4856-B341-2B171A7E7366}" name="Tableau croisé dynamique10" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valeurs" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+  <location ref="B47:C52" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+  <pivotFields count="7">
+    <pivotField showAll="0"/>
+    <pivotField numFmtId="14" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField axis="axisRow" showAll="0" sortType="descending">
+      <items count="5">
+        <item x="3"/>
+        <item x="0"/>
+        <item x="2"/>
+        <item x="1"/>
+        <item t="default"/>
+      </items>
+      <autoSortScope>
+        <pivotArea dataOnly="0" outline="0" fieldPosition="0">
+          <references count="1">
+            <reference field="4294967294" count="1" selected="0">
+              <x v="0"/>
+            </reference>
+          </references>
+        </pivotArea>
+      </autoSortScope>
+    </pivotField>
+    <pivotField dataField="1" showAll="0"/>
+    <pivotField showAll="0"/>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="4"/>
+  </rowFields>
+  <rowItems count="5">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Chiffre d'affaire" fld="5" baseField="0" baseItem="0"/>
+  </dataFields>
+  <formats count="2">
+    <format dxfId="157">
+      <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
+        <references count="1">
+          <reference field="4" count="1">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="156">
+      <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
+        <references count="1">
+          <reference field="4" count="1">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+  </formats>
+  <conditionalFormats count="1">
+    <conditionalFormat priority="1">
+      <pivotAreas count="1">
+        <pivotArea type="data" collapsedLevelsAreSubtotals="1" fieldPosition="0">
+          <references count="2">
+            <reference field="4294967294" count="1" selected="0">
+              <x v="0"/>
+            </reference>
+            <reference field="4" count="4">
+              <x v="0"/>
+              <x v="1"/>
+              <x v="2"/>
+              <x v="3"/>
+            </reference>
+          </references>
+        </pivotArea>
+      </pivotAreas>
+    </conditionalFormat>
+  </conditionalFormats>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable3.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{0489F5AA-4386-45E5-9C54-88F4AB4B8C8B}" name="Tableau croisé dynamique8" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valeurs" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+  <location ref="B33:C39" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+  <pivotFields count="7">
+    <pivotField showAll="0">
+      <items count="11">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item x="6"/>
+        <item x="7"/>
+        <item x="8"/>
+        <item x="9"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField numFmtId="14" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField axis="axisRow" showAll="0" sortType="descending">
+      <items count="6">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="4"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item t="default"/>
+      </items>
+      <autoSortScope>
+        <pivotArea dataOnly="0" outline="0" fieldPosition="0">
+          <references count="1">
+            <reference field="4294967294" count="1" selected="0">
+              <x v="0"/>
+            </reference>
+          </references>
+        </pivotArea>
+      </autoSortScope>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField dataField="1" showAll="0" sumSubtotal="1">
+      <items count="5">
+        <item x="2"/>
+        <item x="1"/>
+        <item x="0"/>
+        <item x="3"/>
+        <item t="sum"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="3"/>
+  </rowFields>
+  <rowItems count="6">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="4"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Chiffre d'affaire" fld="5" baseField="0" baseItem="0"/>
+  </dataFields>
+  <formats count="6">
+    <format dxfId="163">
+      <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
+        <references count="1">
+          <reference field="3" count="1">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="162">
+      <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
+        <references count="1">
+          <reference field="3" count="1">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="161">
+      <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
+        <references count="1">
+          <reference field="3" count="1">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="160">
+      <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
+        <references count="1">
+          <reference field="3" count="1">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="159">
+      <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
+        <references count="1">
+          <reference field="3" count="1">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="158">
+      <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
+        <references count="1">
+          <reference field="3" count="1">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+  </formats>
+  <conditionalFormats count="1">
+    <conditionalFormat priority="3">
+      <pivotAreas count="1">
+        <pivotArea type="data" collapsedLevelsAreSubtotals="1" fieldPosition="0">
+          <references count="2">
+            <reference field="4294967294" count="1" selected="0">
+              <x v="0"/>
+            </reference>
+            <reference field="3" count="5">
+              <x v="0"/>
+              <x v="1"/>
+              <x v="2"/>
+              <x v="3"/>
+              <x v="4"/>
+            </reference>
+          </references>
+        </pivotArea>
+      </pivotAreas>
+    </conditionalFormat>
+  </conditionalFormats>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable4.xml><?xml version="1.0" encoding="utf-8"?>
 <pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{7B72621D-595A-4AC1-AE02-1074C41FD4EA}" name="Tableau croisé dynamique7" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valeurs" grandTotalCaption="CA" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="B20:C24" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="7">
@@ -4865,203 +5330,9 @@
 </pivotTableDefinition>
 </file>
 
-<file path=xl/pivotTables/pivotTable3.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{0A94A5AA-7939-49B7-A6DD-E9354366584E}" name="Tableau croisé dynamique11" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valeurs" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
-  <location ref="B53:C57" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
-  <pivotFields count="7">
-    <pivotField dataField="1" showAll="0">
-      <items count="11">
-        <item x="0"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item x="3"/>
-        <item x="4"/>
-        <item x="5"/>
-        <item x="6"/>
-        <item x="7"/>
-        <item x="8"/>
-        <item x="9"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField numFmtId="14" showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField axis="axisRow" showAll="0">
-      <items count="4">
-        <item x="2"/>
-        <item x="0"/>
-        <item x="1"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-  </pivotFields>
-  <rowFields count="1">
-    <field x="6"/>
-  </rowFields>
-  <rowItems count="4">
-    <i>
-      <x/>
-    </i>
-    <i>
-      <x v="1"/>
-    </i>
-    <i>
-      <x v="2"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </rowItems>
-  <colItems count="1">
-    <i/>
-  </colItems>
-  <dataFields count="1">
-    <dataField name="Nombre de transaction_id" fld="0" subtotal="count" baseField="0" baseItem="0"/>
-  </dataFields>
-  <formats count="2">
-    <format dxfId="169">
-      <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
-        <references count="1">
-          <reference field="6" count="1">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </format>
-    <format dxfId="168">
-      <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
-        <references count="1">
-          <reference field="6" count="1">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </format>
-  </formats>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable4.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{0E420E65-FA27-4856-B341-2B171A7E7366}" name="Tableau croisé dynamique10" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valeurs" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
-  <location ref="B43:C48" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
-  <pivotFields count="7">
-    <pivotField showAll="0"/>
-    <pivotField numFmtId="14" showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField axis="axisRow" showAll="0" sortType="descending">
-      <items count="5">
-        <item x="3"/>
-        <item x="0"/>
-        <item x="2"/>
-        <item x="1"/>
-        <item t="default"/>
-      </items>
-      <autoSortScope>
-        <pivotArea dataOnly="0" outline="0" fieldPosition="0">
-          <references count="1">
-            <reference field="4294967294" count="1" selected="0">
-              <x v="0"/>
-            </reference>
-          </references>
-        </pivotArea>
-      </autoSortScope>
-    </pivotField>
-    <pivotField dataField="1" showAll="0"/>
-    <pivotField showAll="0"/>
-  </pivotFields>
-  <rowFields count="1">
-    <field x="4"/>
-  </rowFields>
-  <rowItems count="5">
-    <i>
-      <x/>
-    </i>
-    <i>
-      <x v="1"/>
-    </i>
-    <i>
-      <x v="3"/>
-    </i>
-    <i>
-      <x v="2"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </rowItems>
-  <colItems count="1">
-    <i/>
-  </colItems>
-  <dataFields count="1">
-    <dataField name="Somme de montant_fc" fld="5" baseField="0" baseItem="0"/>
-  </dataFields>
-  <formats count="2">
-    <format dxfId="171">
-      <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
-        <references count="1">
-          <reference field="4" count="1">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </format>
-    <format dxfId="170">
-      <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
-        <references count="1">
-          <reference field="4" count="1">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </format>
-  </formats>
-  <conditionalFormats count="1">
-    <conditionalFormat priority="1">
-      <pivotAreas count="1">
-        <pivotArea type="data" collapsedLevelsAreSubtotals="1" fieldPosition="0">
-          <references count="2">
-            <reference field="4294967294" count="1" selected="0">
-              <x v="0"/>
-            </reference>
-            <reference field="4" count="4">
-              <x v="0"/>
-              <x v="1"/>
-              <x v="2"/>
-              <x v="3"/>
-            </reference>
-          </references>
-        </pivotArea>
-      </pivotAreas>
-    </conditionalFormat>
-  </conditionalFormats>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
 <file path=xl/pivotTables/pivotTable5.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{E629A829-0601-4384-AE7B-9BD574CFE933}" name="Tableau croisé dynamique2" cacheId="5" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valeurs" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" rowHeaderCaption="Clients/canal">
-  <location ref="B39:C48" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{E629A829-0601-4384-AE7B-9BD574CFE933}" name="Tableau croisé dynamique2" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valeurs" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" rowHeaderCaption="Clients/canal">
+  <location ref="B41:C50" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="7">
     <pivotField showAll="0">
       <items count="16">
@@ -5148,13 +5419,117 @@
     <dataField name="Somme de montant_fc" fld="5" baseField="0" baseItem="0"/>
   </dataFields>
   <formats count="2">
-    <format dxfId="54">
+    <format dxfId="113">
       <pivotArea field="2" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
     </format>
-    <format dxfId="55">
+    <format dxfId="112">
       <pivotArea dataOnly="0" labelOnly="1" grandCol="1" outline="0" fieldPosition="0"/>
     </format>
   </formats>
+  <conditionalFormats count="1">
+    <conditionalFormat priority="4">
+      <pivotAreas count="1">
+        <pivotArea type="data" collapsedLevelsAreSubtotals="1" fieldPosition="0">
+          <references count="2">
+            <reference field="4294967294" count="1" selected="0">
+              <x v="0"/>
+            </reference>
+            <reference field="2" count="8">
+              <x v="0"/>
+              <x v="1"/>
+              <x v="2"/>
+              <x v="3"/>
+              <x v="4"/>
+              <x v="5"/>
+              <x v="6"/>
+              <x v="7"/>
+            </reference>
+          </references>
+        </pivotArea>
+      </pivotAreas>
+    </conditionalFormat>
+  </conditionalFormats>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable6.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{9BDC4D3E-6E87-4F60-A0F8-9C65B558BC36}" name="Tableau croisé dynamique1" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valeurs" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" rowHeaderCaption="Clients">
+  <location ref="B24:C33" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+  <pivotFields count="7">
+    <pivotField dataField="1" showAll="0"/>
+    <pivotField numFmtId="14" showAll="0"/>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="9">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item x="6"/>
+        <item x="7"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0">
+      <items count="4">
+        <item x="2"/>
+        <item x="0"/>
+        <item x="1"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="2"/>
+  </rowFields>
+  <rowItems count="9">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i>
+      <x v="4"/>
+    </i>
+    <i>
+      <x v="5"/>
+    </i>
+    <i>
+      <x v="6"/>
+    </i>
+    <i>
+      <x v="7"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Frequence par client" fld="0" subtotal="count" baseField="2" baseItem="0"/>
+  </dataFields>
   <conditionalFormats count="1">
     <conditionalFormat priority="1">
       <pivotAreas count="1">
@@ -5190,90 +5565,9 @@
 </pivotTableDefinition>
 </file>
 
-<file path=xl/pivotTables/pivotTable6.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{9BDC4D3E-6E87-4F60-A0F8-9C65B558BC36}" name="Tableau croisé dynamique1" cacheId="5" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valeurs" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" rowHeaderCaption="Clients">
-  <location ref="B24:C33" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
-  <pivotFields count="7">
-    <pivotField dataField="1" showAll="0"/>
-    <pivotField numFmtId="14" showAll="0"/>
-    <pivotField axis="axisRow" showAll="0">
-      <items count="9">
-        <item x="0"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item x="3"/>
-        <item x="4"/>
-        <item x="5"/>
-        <item x="6"/>
-        <item x="7"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0">
-      <items count="4">
-        <item x="2"/>
-        <item x="0"/>
-        <item x="1"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-  </pivotFields>
-  <rowFields count="1">
-    <field x="2"/>
-  </rowFields>
-  <rowItems count="9">
-    <i>
-      <x/>
-    </i>
-    <i>
-      <x v="1"/>
-    </i>
-    <i>
-      <x v="2"/>
-    </i>
-    <i>
-      <x v="3"/>
-    </i>
-    <i>
-      <x v="4"/>
-    </i>
-    <i>
-      <x v="5"/>
-    </i>
-    <i>
-      <x v="6"/>
-    </i>
-    <i>
-      <x v="7"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </rowItems>
-  <colItems count="1">
-    <i/>
-  </colItems>
-  <dataFields count="1">
-    <dataField name="Frequence par client" fld="0" subtotal="count" baseField="2" baseItem="0"/>
-  </dataFields>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
 <file path=xl/pivotTables/pivotTable7.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{307774D1-06E3-4866-B6C8-A311F7479B8C}" name="Tableau croisé dynamique25" cacheId="5" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valeurs" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
-  <location ref="B71:F77" firstHeaderRow="1" firstDataRow="3" firstDataCol="1"/>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{307774D1-06E3-4866-B6C8-A311F7479B8C}" name="Tableau croisé dynamique25" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valeurs" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+  <location ref="B77:F83" firstHeaderRow="1" firstDataRow="3" firstDataCol="1"/>
   <pivotFields count="7">
     <pivotField dataField="1" showAll="0"/>
     <pivotField axis="axisRow" numFmtId="14" showAll="0">
@@ -5351,7 +5645,7 @@
     <dataField name="Somme de montant_fc" fld="5" baseField="0" baseItem="0"/>
   </dataFields>
   <formats count="28">
-    <format dxfId="152">
+    <format dxfId="141">
       <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
         <references count="2">
           <reference field="1" count="2">
@@ -5364,10 +5658,10 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="151">
+    <format dxfId="140">
       <pivotArea field="1" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
     </format>
-    <format dxfId="150">
+    <format dxfId="139">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="2">
           <reference field="4294967294" count="2">
@@ -5380,7 +5674,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="149">
+    <format dxfId="138">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="2">
           <reference field="4294967294" count="2">
@@ -5393,7 +5687,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="148">
+    <format dxfId="137">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="2">
           <reference field="4294967294" count="2">
@@ -5406,7 +5700,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="147">
+    <format dxfId="136">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="2">
           <reference field="4294967294" count="2">
@@ -5419,7 +5713,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="146">
+    <format dxfId="135">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="2">
           <reference field="4294967294" count="2">
@@ -5432,7 +5726,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="145">
+    <format dxfId="134">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="2">
           <reference field="4294967294" count="2">
@@ -5445,7 +5739,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="144">
+    <format dxfId="133">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="2">
           <reference field="4294967294" count="2">
@@ -5458,7 +5752,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="143">
+    <format dxfId="132">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="2">
           <reference field="4294967294" count="2">
@@ -5471,7 +5765,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="142">
+    <format dxfId="131">
       <pivotArea field="2" dataOnly="0" labelOnly="1" grandCol="1" outline="0" axis="axisCol" fieldPosition="0">
         <references count="1">
           <reference field="4294967294" count="1" selected="0">
@@ -5480,7 +5774,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="141">
+    <format dxfId="130">
       <pivotArea field="2" dataOnly="0" labelOnly="1" grandCol="1" outline="0" axis="axisCol" fieldPosition="0">
         <references count="1">
           <reference field="4294967294" count="1" selected="0">
@@ -5489,10 +5783,10 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="140">
+    <format dxfId="129">
       <pivotArea field="2" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisCol" fieldPosition="0"/>
     </format>
-    <format dxfId="139">
+    <format dxfId="128">
       <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
         <references count="3">
           <reference field="4294967294" count="2" selected="0">
@@ -5509,7 +5803,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="138">
+    <format dxfId="127">
       <pivotArea dataOnly="0" labelOnly="1" offset="A256" fieldPosition="0">
         <references count="1">
           <reference field="2" count="1">
@@ -5518,7 +5812,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="53">
+    <format dxfId="126">
       <pivotArea dataOnly="0" labelOnly="1" offset="IV256" fieldPosition="0">
         <references count="1">
           <reference field="2" count="1">
@@ -5527,7 +5821,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="52">
+    <format dxfId="125">
       <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
         <references count="1">
           <reference field="2" count="1">
@@ -5536,7 +5830,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="51">
+    <format dxfId="124">
       <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
         <references count="1">
           <reference field="2" count="1">
@@ -5545,7 +5839,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="50">
+    <format dxfId="123">
       <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
         <references count="1">
           <reference field="2" count="1">
@@ -5554,7 +5848,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="49">
+    <format dxfId="122">
       <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
         <references count="1">
           <reference field="2" count="1">
@@ -5563,7 +5857,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="48">
+    <format dxfId="121">
       <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
         <references count="1">
           <reference field="2" count="1">
@@ -5572,7 +5866,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="47">
+    <format dxfId="120">
       <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
         <references count="1">
           <reference field="2" count="1">
@@ -5581,7 +5875,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="46">
+    <format dxfId="119">
       <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
         <references count="1">
           <reference field="2" count="1">
@@ -5590,7 +5884,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="33">
+    <format dxfId="118">
       <pivotArea field="2" grandRow="1" outline="0" collapsedLevelsAreSubtotals="1" axis="axisCol" fieldPosition="0">
         <references count="2">
           <reference field="4294967294" count="1" selected="0">
@@ -5600,7 +5894,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="32">
+    <format dxfId="117">
       <pivotArea field="2" grandRow="1" outline="0" collapsedLevelsAreSubtotals="1" axis="axisCol" fieldPosition="0">
         <references count="2">
           <reference field="4294967294" count="1" selected="0">
@@ -5610,7 +5904,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="31">
+    <format dxfId="116">
       <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
         <references count="3">
           <reference field="4294967294" count="2" selected="0">
@@ -5624,7 +5918,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="28">
+    <format dxfId="115">
       <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
         <references count="3">
           <reference field="4294967294" count="1" selected="0">
@@ -5637,7 +5931,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="0">
+    <format dxfId="114">
       <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
         <references count="3">
           <reference field="4294967294" count="1" selected="0">
@@ -5651,6 +5945,44 @@
       </pivotArea>
     </format>
   </formats>
+  <conditionalFormats count="2">
+    <conditionalFormat priority="3">
+      <pivotAreas count="1">
+        <pivotArea type="data" collapsedLevelsAreSubtotals="1" fieldPosition="0">
+          <references count="3">
+            <reference field="4294967294" count="1" selected="0">
+              <x v="0"/>
+            </reference>
+            <reference field="1" count="2">
+              <x v="0"/>
+              <x v="1"/>
+            </reference>
+            <reference field="2" count="1" selected="0">
+              <x v="0"/>
+            </reference>
+          </references>
+        </pivotArea>
+      </pivotAreas>
+    </conditionalFormat>
+    <conditionalFormat priority="2">
+      <pivotAreas count="1">
+        <pivotArea type="data" collapsedLevelsAreSubtotals="1" fieldPosition="0">
+          <references count="3">
+            <reference field="4294967294" count="1" selected="0">
+              <x v="0"/>
+            </reference>
+            <reference field="1" count="2">
+              <x v="0"/>
+              <x v="1"/>
+            </reference>
+            <reference field="2" count="1" selected="0">
+              <x v="0"/>
+            </reference>
+          </references>
+        </pivotArea>
+      </pivotAreas>
+    </conditionalFormat>
+  </conditionalFormats>
   <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
@@ -5664,8 +5996,8 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable8.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{E03AB932-5DD7-4CAF-BF0A-30F67C3B60D8}" name="Tableau croisé dynamique17" cacheId="5" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valeurs" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" rowHeaderCaption="Clients/canal">
-  <location ref="B54:F64" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{E03AB932-5DD7-4CAF-BF0A-30F67C3B60D8}" name="Tableau croisé dynamique17" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valeurs" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" rowHeaderCaption="Clients/canal">
+  <location ref="B58:F68" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
   <pivotFields count="7">
     <pivotField dataField="1" showAll="0">
       <items count="16">
@@ -5766,17 +6098,17 @@
     <dataField name="Canal preferé par client" fld="0" subtotal="count" baseField="0" baseItem="0"/>
   </dataFields>
   <formats count="3">
-    <format dxfId="43">
+    <format dxfId="144">
       <pivotArea field="2" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
     </format>
-    <format dxfId="44">
+    <format dxfId="143">
       <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
         <references count="1">
           <reference field="6" count="0"/>
         </references>
       </pivotArea>
     </format>
-    <format dxfId="45">
+    <format dxfId="142">
       <pivotArea dataOnly="0" labelOnly="1" grandCol="1" outline="0" fieldPosition="0"/>
     </format>
   </formats>
@@ -5793,14 +6125,14 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable9.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{B6B3D1A4-0B77-482E-9D3E-CEB1DCD7B445}" name="Tableau croisé dynamique28" cacheId="2" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valeurs" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
-  <location ref="J11:P17" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{61DDDF72-4F90-487F-8CBD-C2BF23835112}" name="Tableau croisé dynamique1" cacheId="2" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valeurs" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+  <location ref="B36:D42" firstHeaderRow="0" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="7">
-    <pivotField showAll="0"/>
+    <pivotField dataField="1" showAll="0"/>
     <pivotField numFmtId="14" showAll="0"/>
     <pivotField showAll="0"/>
     <pivotField showAll="0"/>
-    <pivotField axis="axisCol" showAll="0">
+    <pivotField axis="axisRow" showAll="0" sortType="descending">
       <items count="6">
         <item x="0"/>
         <item x="1"/>
@@ -5809,64 +6141,121 @@
         <item x="3"/>
         <item t="default"/>
       </items>
+      <autoSortScope>
+        <pivotArea dataOnly="0" outline="0" fieldPosition="0">
+          <references count="1">
+            <reference field="4294967294" count="1" selected="0">
+              <x v="1"/>
+            </reference>
+          </references>
+        </pivotArea>
+      </autoSortScope>
     </pivotField>
-    <pivotField axis="axisRow" showAll="0">
-      <items count="5">
-        <item x="0"/>
-        <item x="2"/>
-        <item x="3"/>
-        <item x="1"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
+    <pivotField showAll="0"/>
     <pivotField dataField="1" showAll="0"/>
   </pivotFields>
   <rowFields count="1">
-    <field x="5"/>
+    <field x="4"/>
   </rowFields>
-  <rowItems count="5">
+  <rowItems count="6">
     <i>
       <x/>
     </i>
     <i>
+      <x v="4"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i>
       <x v="1"/>
     </i>
     <i>
       <x v="2"/>
-    </i>
-    <i>
-      <x v="3"/>
     </i>
     <i t="grand">
       <x/>
     </i>
   </rowItems>
   <colFields count="1">
-    <field x="4"/>
+    <field x="-2"/>
   </colFields>
-  <colItems count="6">
+  <colItems count="2">
     <i>
       <x/>
     </i>
-    <i>
+    <i i="1">
       <x v="1"/>
     </i>
-    <i>
-      <x v="2"/>
-    </i>
-    <i>
-      <x v="3"/>
-    </i>
-    <i>
-      <x v="4"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
   </colItems>
-  <dataFields count="1">
+  <dataFields count="2">
+    <dataField name="Nombre de transaction_id" fld="0" subtotal="count" baseField="0" baseItem="0"/>
     <dataField name="Somme de montant_fc" fld="6" baseField="0" baseItem="0"/>
   </dataFields>
+  <formats count="2">
+    <format dxfId="29">
+      <pivotArea field="4" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
+    </format>
+    <format dxfId="30">
+      <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="2">
+            <x v="0"/>
+            <x v="1"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+  </formats>
+  <conditionalFormats count="3">
+    <conditionalFormat priority="3">
+      <pivotAreas count="1">
+        <pivotArea type="data" collapsedLevelsAreSubtotals="1" fieldPosition="0">
+          <references count="2">
+            <reference field="4294967294" count="1" selected="0">
+              <x v="1"/>
+            </reference>
+            <reference field="4" count="5">
+              <x v="0"/>
+              <x v="1"/>
+              <x v="2"/>
+              <x v="3"/>
+              <x v="4"/>
+            </reference>
+          </references>
+        </pivotArea>
+      </pivotAreas>
+    </conditionalFormat>
+    <conditionalFormat priority="2">
+      <pivotAreas count="1">
+        <pivotArea type="data" outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0">
+          <references count="1">
+            <reference field="4294967294" count="1" selected="0">
+              <x v="1"/>
+            </reference>
+          </references>
+        </pivotArea>
+      </pivotAreas>
+    </conditionalFormat>
+    <conditionalFormat priority="1">
+      <pivotAreas count="1">
+        <pivotArea type="data" collapsedLevelsAreSubtotals="1" fieldPosition="0">
+          <references count="2">
+            <reference field="4294967294" count="1" selected="0">
+              <x v="1"/>
+            </reference>
+            <reference field="4" count="5">
+              <x v="0"/>
+              <x v="1"/>
+              <x v="2"/>
+              <x v="3"/>
+              <x v="4"/>
+            </reference>
+          </references>
+        </pivotArea>
+      </pivotAreas>
+    </conditionalFormat>
+  </conditionalFormats>
   <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
@@ -5956,16 +6345,16 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{6EC83A65-D9A6-475F-8D16-1CE811FFF2E9}" name="Tableau1" displayName="Tableau1" ref="B3:H13" totalsRowShown="0" headerRowDxfId="161" dataDxfId="160">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{6EC83A65-D9A6-475F-8D16-1CE811FFF2E9}" name="Tableau1" displayName="Tableau1" ref="B3:H13" totalsRowShown="0" headerRowDxfId="153" dataDxfId="152">
   <autoFilter ref="B3:H13" xr:uid="{6EC83A65-D9A6-475F-8D16-1CE811FFF2E9}"/>
   <tableColumns count="7">
-    <tableColumn id="1" xr3:uid="{54537CD7-847D-4C04-9BD6-B993FB8C0924}" name="transaction_id" dataDxfId="159"/>
-    <tableColumn id="2" xr3:uid="{7DFAA592-DC98-463C-A6AF-A94A0F915646}" name="date" dataDxfId="158"/>
-    <tableColumn id="3" xr3:uid="{122DF7BD-714F-4B55-830F-7573F364E80A}" name="client_id" dataDxfId="157"/>
-    <tableColumn id="4" xr3:uid="{1B94713D-DD23-416E-B23B-98EF629AFCBE}" name="commune" dataDxfId="156"/>
-    <tableColumn id="5" xr3:uid="{084E48D7-3EDD-4FC4-B38B-BD3872EDFF23}" name="produit" dataDxfId="155"/>
-    <tableColumn id="6" xr3:uid="{D1BF92F6-B520-4D49-B97E-C1395DDE5A98}" name="montant_fc" dataDxfId="154"/>
-    <tableColumn id="7" xr3:uid="{21C18558-D71D-47B7-B0D0-001594508953}" name="canal" dataDxfId="153"/>
+    <tableColumn id="1" xr3:uid="{54537CD7-847D-4C04-9BD6-B993FB8C0924}" name="transaction_id" dataDxfId="151"/>
+    <tableColumn id="2" xr3:uid="{7DFAA592-DC98-463C-A6AF-A94A0F915646}" name="date" dataDxfId="150"/>
+    <tableColumn id="3" xr3:uid="{122DF7BD-714F-4B55-830F-7573F364E80A}" name="client_id" dataDxfId="149"/>
+    <tableColumn id="4" xr3:uid="{1B94713D-DD23-416E-B23B-98EF629AFCBE}" name="commune" dataDxfId="148"/>
+    <tableColumn id="5" xr3:uid="{084E48D7-3EDD-4FC4-B38B-BD3872EDFF23}" name="produit" dataDxfId="147"/>
+    <tableColumn id="6" xr3:uid="{D1BF92F6-B520-4D49-B97E-C1395DDE5A98}" name="montant_fc" dataDxfId="146"/>
+    <tableColumn id="7" xr3:uid="{21C18558-D71D-47B7-B0D0-001594508953}" name="canal" dataDxfId="145"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -5975,13 +6364,13 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{5B43BC6D-66A6-432F-982F-C406FA282078}" name="Dataset_day2__2" displayName="Dataset_day2__2" ref="B2:H17" tableType="queryTable" totalsRowShown="0">
   <autoFilter ref="B2:H17" xr:uid="{5B43BC6D-66A6-432F-982F-C406FA282078}"/>
   <tableColumns count="7">
-    <tableColumn id="1" xr3:uid="{F0363F15-00D8-44D9-B9E8-73E1201A36E6}" uniqueName="1" name="transaction_id" queryTableFieldId="1" dataDxfId="137"/>
-    <tableColumn id="2" xr3:uid="{85F76B94-3323-41EB-B99E-F9DE7DD9EF5D}" uniqueName="2" name="date" queryTableFieldId="2" dataDxfId="136"/>
-    <tableColumn id="3" xr3:uid="{90258075-E8BA-4181-AEBF-14DCE9CF1AC4}" uniqueName="3" name="client_id" queryTableFieldId="3" dataDxfId="135"/>
-    <tableColumn id="4" xr3:uid="{3B088930-C813-470C-9790-11DA318C42A1}" uniqueName="4" name="commune" queryTableFieldId="4" dataDxfId="134"/>
-    <tableColumn id="5" xr3:uid="{E074DF00-E0E7-41D6-B91A-ABE22CB1881A}" uniqueName="5" name="produit" queryTableFieldId="5" dataDxfId="133"/>
+    <tableColumn id="1" xr3:uid="{F0363F15-00D8-44D9-B9E8-73E1201A36E6}" uniqueName="1" name="transaction_id" queryTableFieldId="1" dataDxfId="111"/>
+    <tableColumn id="2" xr3:uid="{85F76B94-3323-41EB-B99E-F9DE7DD9EF5D}" uniqueName="2" name="date" queryTableFieldId="2" dataDxfId="110"/>
+    <tableColumn id="3" xr3:uid="{90258075-E8BA-4181-AEBF-14DCE9CF1AC4}" uniqueName="3" name="client_id" queryTableFieldId="3" dataDxfId="109"/>
+    <tableColumn id="4" xr3:uid="{3B088930-C813-470C-9790-11DA318C42A1}" uniqueName="4" name="commune" queryTableFieldId="4" dataDxfId="108"/>
+    <tableColumn id="5" xr3:uid="{E074DF00-E0E7-41D6-B91A-ABE22CB1881A}" uniqueName="5" name="produit" queryTableFieldId="5" dataDxfId="107"/>
     <tableColumn id="6" xr3:uid="{7C01ABE9-F9C0-40F6-9F95-D610FB820086}" uniqueName="6" name="montant_fc" queryTableFieldId="6"/>
-    <tableColumn id="7" xr3:uid="{30F6D1BA-4065-4D54-BF94-1BE05C99AC63}" uniqueName="7" name="canal" queryTableFieldId="7" dataDxfId="132"/>
+    <tableColumn id="7" xr3:uid="{30F6D1BA-4065-4D54-BF94-1BE05C99AC63}" uniqueName="7" name="canal" queryTableFieldId="7" dataDxfId="106"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -5991,12 +6380,12 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{A4A0DCA2-C1C4-44D4-AD45-BDA248A44995}" name="Dataset_day3" displayName="Dataset_day3" ref="B2:H17" tableType="queryTable" totalsRowShown="0">
   <autoFilter ref="B2:H17" xr:uid="{A4A0DCA2-C1C4-44D4-AD45-BDA248A44995}"/>
   <tableColumns count="7">
-    <tableColumn id="1" xr3:uid="{A0067E32-0369-4D8A-BDF1-C8B907B86BD0}" uniqueName="1" name="transaction_id" queryTableFieldId="1" dataDxfId="124"/>
-    <tableColumn id="2" xr3:uid="{C68FAFFA-BEA0-4F94-BA99-6450F477971E}" uniqueName="2" name="date" queryTableFieldId="2" dataDxfId="123"/>
-    <tableColumn id="3" xr3:uid="{CDF65428-BE02-471D-A8F7-90F1D8454251}" uniqueName="3" name="agent_id" queryTableFieldId="3" dataDxfId="122"/>
-    <tableColumn id="4" xr3:uid="{22F84FAA-57F1-425F-B37C-F8428C49E033}" uniqueName="4" name="client_id" queryTableFieldId="4" dataDxfId="121"/>
-    <tableColumn id="5" xr3:uid="{93A8CFD1-D585-478D-9AFB-02301838500E}" uniqueName="5" name="commune" queryTableFieldId="5" dataDxfId="120"/>
-    <tableColumn id="6" xr3:uid="{956E7CEA-E833-4F96-9E51-2D67194B8C61}" uniqueName="6" name="produit" queryTableFieldId="6" dataDxfId="119"/>
+    <tableColumn id="1" xr3:uid="{A0067E32-0369-4D8A-BDF1-C8B907B86BD0}" uniqueName="1" name="transaction_id" queryTableFieldId="1" dataDxfId="100"/>
+    <tableColumn id="2" xr3:uid="{C68FAFFA-BEA0-4F94-BA99-6450F477971E}" uniqueName="2" name="date" queryTableFieldId="2" dataDxfId="99"/>
+    <tableColumn id="3" xr3:uid="{CDF65428-BE02-471D-A8F7-90F1D8454251}" uniqueName="3" name="agent_id" queryTableFieldId="3" dataDxfId="98"/>
+    <tableColumn id="4" xr3:uid="{22F84FAA-57F1-425F-B37C-F8428C49E033}" uniqueName="4" name="client_id" queryTableFieldId="4" dataDxfId="97"/>
+    <tableColumn id="5" xr3:uid="{93A8CFD1-D585-478D-9AFB-02301838500E}" uniqueName="5" name="commune" queryTableFieldId="5" dataDxfId="96"/>
+    <tableColumn id="6" xr3:uid="{956E7CEA-E833-4F96-9E51-2D67194B8C61}" uniqueName="6" name="produit" queryTableFieldId="6" dataDxfId="95"/>
     <tableColumn id="7" xr3:uid="{E636C8A0-3C3C-48BE-AFE5-1B3DB129CA7E}" uniqueName="7" name="montant_fc" queryTableFieldId="7"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
@@ -6007,11 +6396,11 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{AB24B926-8F3E-4EE6-9138-D47BB2378B02}" name="Dataset_day4" displayName="Dataset_day4" ref="B2:G17" totalsRowShown="0">
   <autoFilter ref="B2:G17" xr:uid="{AB24B926-8F3E-4EE6-9138-D47BB2378B02}"/>
   <tableColumns count="6">
-    <tableColumn id="1" xr3:uid="{2FA77349-5B7D-430C-A299-CA8EF8B94F8F}" name="transaction_id" dataDxfId="109"/>
-    <tableColumn id="2" xr3:uid="{EA88A0A8-EDC4-468E-80F4-EF0578FE9A03}" name="date" dataDxfId="108"/>
-    <tableColumn id="3" xr3:uid="{811F8411-B146-492E-A697-2D905854F94D}" name="client_id" dataDxfId="107"/>
-    <tableColumn id="4" xr3:uid="{7B37CE19-01A8-4470-8A2B-849B751FB37D}" name="commune" dataDxfId="106"/>
-    <tableColumn id="5" xr3:uid="{863A1A63-AC11-4715-82E2-F6EC444E5B51}" name="produit" dataDxfId="105"/>
+    <tableColumn id="1" xr3:uid="{2FA77349-5B7D-430C-A299-CA8EF8B94F8F}" name="transaction_id" dataDxfId="85"/>
+    <tableColumn id="2" xr3:uid="{EA88A0A8-EDC4-468E-80F4-EF0578FE9A03}" name="date" dataDxfId="84"/>
+    <tableColumn id="3" xr3:uid="{811F8411-B146-492E-A697-2D905854F94D}" name="client_id" dataDxfId="83"/>
+    <tableColumn id="4" xr3:uid="{7B37CE19-01A8-4470-8A2B-849B751FB37D}" name="commune" dataDxfId="82"/>
+    <tableColumn id="5" xr3:uid="{863A1A63-AC11-4715-82E2-F6EC444E5B51}" name="produit" dataDxfId="81"/>
     <tableColumn id="6" xr3:uid="{DDFB738A-4C05-4F97-882D-16FE65EF8A7E}" name="montant_fc"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
@@ -6019,7 +6408,7 @@
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="9" xr:uid="{B1C5B688-9C67-4CAD-9DAE-7207D5E5E850}" name="Tableau9" displayName="Tableau9" ref="AA3:AA11" totalsRowShown="0" headerRowDxfId="104">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="9" xr:uid="{B1C5B688-9C67-4CAD-9DAE-7207D5E5E850}" name="Tableau9" displayName="Tableau9" ref="AA3:AA11" totalsRowShown="0" headerRowDxfId="80">
   <autoFilter ref="AA3:AA11" xr:uid="{B1C5B688-9C67-4CAD-9DAE-7207D5E5E850}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="AA4:AA11">
     <sortCondition ref="AA3:AA11"/>
@@ -6034,16 +6423,16 @@
 </file>
 
 <file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="10" xr:uid="{C4A92EC0-501A-4751-9A16-2163E0BD39EA}" name="Dataset_day5" displayName="Dataset_day5" ref="B2:H17" tableType="queryTable" totalsRowShown="0" headerRowDxfId="63">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="10" xr:uid="{C4A92EC0-501A-4751-9A16-2163E0BD39EA}" name="Dataset_day5" displayName="Dataset_day5" ref="B2:H17" tableType="queryTable" totalsRowShown="0" headerRowDxfId="39">
   <autoFilter ref="B2:H17" xr:uid="{C4A92EC0-501A-4751-9A16-2163E0BD39EA}"/>
   <tableColumns count="7">
-    <tableColumn id="1" xr3:uid="{FBC21564-1B48-423F-AFDB-04B5AE20CF75}" uniqueName="1" name="transaction_id" queryTableFieldId="1" dataDxfId="62"/>
-    <tableColumn id="2" xr3:uid="{CA4A50D7-5720-4F71-ACD1-3781681C0231}" uniqueName="2" name="date" queryTableFieldId="2" dataDxfId="61"/>
-    <tableColumn id="3" xr3:uid="{A265E5F8-50A6-4DD3-8C5E-10BB05E3F126}" uniqueName="3" name="client_id" queryTableFieldId="3" dataDxfId="60"/>
-    <tableColumn id="4" xr3:uid="{0E595B89-2727-474B-B4A6-66BC0AC0864A}" uniqueName="4" name="commune" queryTableFieldId="4" dataDxfId="59"/>
-    <tableColumn id="5" xr3:uid="{4D992877-9744-466D-982E-E1F06CDEF762}" uniqueName="5" name="produit" queryTableFieldId="5" dataDxfId="58"/>
+    <tableColumn id="1" xr3:uid="{FBC21564-1B48-423F-AFDB-04B5AE20CF75}" uniqueName="1" name="transaction_id" queryTableFieldId="1" dataDxfId="38"/>
+    <tableColumn id="2" xr3:uid="{CA4A50D7-5720-4F71-ACD1-3781681C0231}" uniqueName="2" name="date" queryTableFieldId="2" dataDxfId="37"/>
+    <tableColumn id="3" xr3:uid="{A265E5F8-50A6-4DD3-8C5E-10BB05E3F126}" uniqueName="3" name="client_id" queryTableFieldId="3" dataDxfId="36"/>
+    <tableColumn id="4" xr3:uid="{0E595B89-2727-474B-B4A6-66BC0AC0864A}" uniqueName="4" name="commune" queryTableFieldId="4" dataDxfId="35"/>
+    <tableColumn id="5" xr3:uid="{4D992877-9744-466D-982E-E1F06CDEF762}" uniqueName="5" name="produit" queryTableFieldId="5" dataDxfId="34"/>
     <tableColumn id="6" xr3:uid="{D10FAE6E-7969-4551-94AB-82C2D27DFD50}" uniqueName="6" name="montant_fc" queryTableFieldId="6"/>
-    <tableColumn id="7" xr3:uid="{7306D68B-3C9A-40F7-A0D9-E00CC8C73541}" uniqueName="7" name="periode" queryTableFieldId="7" dataDxfId="57"/>
+    <tableColumn id="7" xr3:uid="{7306D68B-3C9A-40F7-A0D9-E00CC8C73541}" uniqueName="7" name="periode" queryTableFieldId="7" dataDxfId="33"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -6054,7 +6443,7 @@
   <autoFilter ref="A1:G6" xr:uid="{68E59C74-D329-4B48-A967-CC868365949C}"/>
   <tableColumns count="7">
     <tableColumn id="1" xr3:uid="{C102BD58-3DF8-48B7-9114-2067608D3DB4}" name="transaction_id"/>
-    <tableColumn id="2" xr3:uid="{998F6E83-476D-414D-8353-8E6146354739}" name="date" dataDxfId="56"/>
+    <tableColumn id="2" xr3:uid="{998F6E83-476D-414D-8353-8E6146354739}" name="date" dataDxfId="32"/>
     <tableColumn id="3" xr3:uid="{1ACC5CD9-2A0F-4DB2-B7B7-A25781DA1795}" name="agent_id"/>
     <tableColumn id="4" xr3:uid="{D4B111D2-01DE-4AFC-91B0-641E23172B8C}" name="client_id"/>
     <tableColumn id="5" xr3:uid="{C0E2906A-2633-4FB3-89D8-883ADDF86D4F}" name="commune"/>
@@ -6382,30 +6771,30 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{04B3012F-C756-4CF6-A456-1922518EC017}">
-  <dimension ref="A2:I70"/>
+  <dimension ref="A2:I79"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="3" width="21.42578125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="24.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="21.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="24.42578125" bestFit="1" customWidth="1"/>
     <col min="5" max="9" width="21.42578125" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="21.85546875" bestFit="1" customWidth="1"/>
     <col min="11" max="12" width="21.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="B2" s="46" t="s">
+      <c r="B2" s="48" t="s">
         <v>43</v>
       </c>
-      <c r="C2" s="46"/>
-      <c r="D2" s="46"/>
-      <c r="E2" s="46"/>
-      <c r="F2" s="46"/>
-      <c r="G2" s="46"/>
-      <c r="H2" s="46"/>
+      <c r="C2" s="48"/>
+      <c r="D2" s="48"/>
+      <c r="E2" s="48"/>
+      <c r="F2" s="48"/>
+      <c r="G2" s="48"/>
+      <c r="H2" s="48"/>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" s="12" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>0</v>
@@ -6700,18 +7089,18 @@
       <c r="H14" s="5"/>
     </row>
     <row r="15" spans="1:9" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B15" s="43" t="s">
-        <v>171</v>
-      </c>
-      <c r="C15" s="48"/>
-      <c r="D15" s="48"/>
-      <c r="E15" s="48"/>
-      <c r="F15" s="48"/>
-      <c r="G15" s="48"/>
-      <c r="H15" s="48"/>
+      <c r="B15" s="50" t="s">
+        <v>169</v>
+      </c>
+      <c r="C15" s="51"/>
+      <c r="D15" s="51"/>
+      <c r="E15" s="51"/>
+      <c r="F15" s="51"/>
+      <c r="G15" s="51"/>
+      <c r="H15" s="51"/>
     </row>
     <row r="16" spans="1:9" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B16" s="36"/>
+      <c r="B16" s="35"/>
       <c r="C16" s="1"/>
       <c r="D16" s="1"/>
       <c r="E16" s="1"/>
@@ -6720,18 +7109,18 @@
       <c r="H16" s="1"/>
     </row>
     <row r="17" spans="2:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B17" s="43" t="s">
-        <v>172</v>
-      </c>
-      <c r="C17" s="43"/>
-      <c r="D17" s="43"/>
-      <c r="E17" s="37"/>
+      <c r="B17" s="50" t="s">
+        <v>170</v>
+      </c>
+      <c r="C17" s="50"/>
+      <c r="D17" s="50"/>
+      <c r="E17" s="36"/>
     </row>
     <row r="19" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B19" s="46" t="s">
+      <c r="B19" s="48" t="s">
         <v>44</v>
       </c>
-      <c r="C19" s="46"/>
+      <c r="C19" s="48"/>
     </row>
     <row r="20" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B20" s="8" t="s">
@@ -6773,266 +7162,317 @@
         <v>77000</v>
       </c>
     </row>
-    <row r="26" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B26" s="9"/>
-      <c r="C26" s="10"/>
-    </row>
-    <row r="27" spans="2:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B27" s="43" t="s">
-        <v>173</v>
-      </c>
-      <c r="C27" s="43"/>
-      <c r="D27" s="43"/>
-      <c r="E27" s="37"/>
-      <c r="F27" s="1"/>
-      <c r="G27" s="1"/>
-    </row>
-    <row r="30" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B30" s="46" t="s">
+    <row r="26" spans="2:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B26" s="59" t="s">
+        <v>205</v>
+      </c>
+      <c r="C26" s="59"/>
+      <c r="D26" s="59"/>
+    </row>
+    <row r="27" spans="2:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B27" s="59"/>
+      <c r="C27" s="59"/>
+      <c r="D27" s="59"/>
+    </row>
+    <row r="28" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B28" s="60"/>
+      <c r="C28" s="60"/>
+      <c r="D28" s="60"/>
+    </row>
+    <row r="29" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B29" s="58"/>
+      <c r="C29" s="10"/>
+    </row>
+    <row r="30" spans="2:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B30" s="50" t="s">
+        <v>171</v>
+      </c>
+      <c r="C30" s="50"/>
+      <c r="D30" s="50"/>
+      <c r="E30" s="36"/>
+      <c r="F30" s="1"/>
+      <c r="G30" s="1"/>
+    </row>
+    <row r="32" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B32" s="48" t="s">
         <v>45</v>
       </c>
-      <c r="C30" s="46"/>
-    </row>
-    <row r="31" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B31" s="8" t="s">
+      <c r="C32" s="48"/>
+    </row>
+    <row r="33" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B33" s="8" t="s">
         <v>38</v>
       </c>
-      <c r="C31" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="32" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B32" s="38" t="s">
+      <c r="C33" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="34" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B34" s="37" t="s">
         <v>9</v>
       </c>
-      <c r="C32" s="21">
+      <c r="C34" s="21">
         <v>29000</v>
-      </c>
-    </row>
-    <row r="33" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B33" s="9" t="s">
-        <v>14</v>
-      </c>
-      <c r="C33" s="10">
-        <v>9000</v>
-      </c>
-    </row>
-    <row r="34" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B34" s="9" t="s">
-        <v>31</v>
-      </c>
-      <c r="C34" s="10">
-        <v>10000</v>
       </c>
     </row>
     <row r="35" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B35" s="9" t="s">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="C35" s="10">
-        <v>11000</v>
+        <v>18000</v>
       </c>
     </row>
     <row r="36" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B36" s="9" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="C36" s="10">
-        <v>18000</v>
+        <v>11000</v>
       </c>
     </row>
     <row r="37" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B37" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="C37" s="10">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="38" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B38" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="C38" s="10">
+        <v>9000</v>
+      </c>
+    </row>
+    <row r="39" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B39" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="C37" s="10">
+      <c r="C39" s="10">
         <v>77000</v>
       </c>
     </row>
-    <row r="40" spans="2:4" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B40" s="43" t="s">
-        <v>174</v>
-      </c>
-      <c r="C40" s="43"/>
-      <c r="D40" s="43"/>
+    <row r="41" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B41" s="58" t="s">
+        <v>206</v>
+      </c>
     </row>
     <row r="42" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B42" s="46" t="s">
+      <c r="B42" s="58"/>
+    </row>
+    <row r="44" spans="2:4" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B44" s="50" t="s">
+        <v>172</v>
+      </c>
+      <c r="C44" s="50"/>
+      <c r="D44" s="50"/>
+    </row>
+    <row r="46" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B46" s="48" t="s">
         <v>46</v>
       </c>
-      <c r="C42" s="46"/>
-    </row>
-    <row r="43" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B43" s="8" t="s">
+      <c r="C46" s="48"/>
+    </row>
+    <row r="47" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B47" s="8" t="s">
         <v>38</v>
       </c>
-      <c r="C43" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="44" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B44" s="15" t="s">
+      <c r="C47" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="48" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B48" s="15" t="s">
         <v>26</v>
       </c>
-      <c r="C44" s="16">
+      <c r="C48" s="16">
         <v>36000</v>
       </c>
     </row>
-    <row r="45" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B45" s="9" t="s">
+    <row r="49" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B49" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="C45" s="10">
+      <c r="C49" s="10">
         <v>30000</v>
       </c>
     </row>
-    <row r="46" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B46" s="9" t="s">
+    <row r="50" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B50" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="C46" s="10">
+      <c r="C50" s="10">
         <v>9000</v>
       </c>
     </row>
-    <row r="47" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B47" s="9" t="s">
+    <row r="51" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B51" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="C47" s="10">
+      <c r="C51" s="10">
         <v>2000</v>
       </c>
     </row>
-    <row r="48" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B48" s="9" t="s">
+    <row r="52" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B52" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="C48" s="10">
+      <c r="C52" s="10">
         <v>77000</v>
       </c>
     </row>
-    <row r="50" spans="2:5" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B50" s="43" t="s">
+    <row r="53" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B53" s="9"/>
+      <c r="C53" s="10"/>
+    </row>
+    <row r="54" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B54" s="58" t="s">
+        <v>208</v>
+      </c>
+      <c r="C54" s="10"/>
+    </row>
+    <row r="55" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B55" s="58"/>
+      <c r="C55" s="10"/>
+    </row>
+    <row r="57" spans="2:4" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B57" s="50" t="s">
+        <v>173</v>
+      </c>
+      <c r="C57" s="50"/>
+      <c r="D57" s="50"/>
+    </row>
+    <row r="59" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B59" s="48" t="s">
+        <v>47</v>
+      </c>
+      <c r="C59" s="49"/>
+    </row>
+    <row r="60" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B60" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="C60" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="61" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B61" s="15" t="s">
+        <v>20</v>
+      </c>
+      <c r="C61" s="16">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="62" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B62" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="C62" s="10">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B63" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="C63" s="10">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="64" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B64" s="9" t="s">
+        <v>40</v>
+      </c>
+      <c r="C64" s="10">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="66" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B66" s="9" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="67" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B67" s="9"/>
+    </row>
+    <row r="68" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B68" s="9"/>
+    </row>
+    <row r="69" spans="2:5" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="B69" s="52" t="s">
+        <v>180</v>
+      </c>
+      <c r="C69" s="52"/>
+    </row>
+    <row r="71" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B71" s="53" t="s">
+        <v>181</v>
+      </c>
+      <c r="C71" s="53"/>
+      <c r="D71" s="53"/>
+      <c r="E71" s="53"/>
+    </row>
+    <row r="72" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B72" s="53"/>
+      <c r="C72" s="53"/>
+      <c r="D72" s="53"/>
+      <c r="E72" s="53"/>
+    </row>
+    <row r="73" spans="2:5" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B73" s="39"/>
+      <c r="C73" s="39"/>
+      <c r="D73" s="39"/>
+      <c r="E73" s="39"/>
+    </row>
+    <row r="74" spans="2:5" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="B74" s="40" t="s">
         <v>175</v>
       </c>
-      <c r="C50" s="43"/>
-      <c r="D50" s="43"/>
-    </row>
-    <row r="52" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B52" s="46" t="s">
-        <v>47</v>
-      </c>
-      <c r="C52" s="47"/>
-    </row>
-    <row r="53" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B53" s="8" t="s">
-        <v>38</v>
-      </c>
-      <c r="C53" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="54" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B54" s="15" t="s">
-        <v>20</v>
-      </c>
-      <c r="C54" s="16">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="55" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B55" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="C55" s="10">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="56" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B56" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="C56" s="10">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="57" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B57" s="9" t="s">
-        <v>40</v>
-      </c>
-      <c r="C57" s="10">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="60" spans="2:5" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="B60" s="44" t="s">
-        <v>182</v>
-      </c>
-      <c r="C60" s="44"/>
-    </row>
-    <row r="62" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B62" s="45" t="s">
-        <v>183</v>
-      </c>
-      <c r="C62" s="45"/>
-      <c r="D62" s="45"/>
-      <c r="E62" s="45"/>
-    </row>
-    <row r="63" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B63" s="45"/>
-      <c r="C63" s="45"/>
-      <c r="D63" s="45"/>
-      <c r="E63" s="45"/>
-    </row>
-    <row r="64" spans="2:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B64" s="40"/>
-      <c r="C64" s="40"/>
-      <c r="D64" s="40"/>
-      <c r="E64" s="40"/>
-    </row>
-    <row r="65" spans="2:2" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="B65" s="41" t="s">
+    </row>
+    <row r="75" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B75" s="38"/>
+    </row>
+    <row r="76" spans="2:5" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B76" s="41" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="77" spans="2:5" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B77" s="41" t="s">
         <v>177</v>
       </c>
     </row>
-    <row r="66" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B66" s="39"/>
-    </row>
-    <row r="67" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B67" s="42" t="s">
+    <row r="78" spans="2:5" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B78" s="41" t="s">
         <v>178</v>
       </c>
     </row>
-    <row r="68" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B68" s="42" t="s">
+    <row r="79" spans="2:5" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B79" s="41" t="s">
         <v>179</v>
       </c>
     </row>
-    <row r="69" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B69" s="42" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="70" spans="2:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B70" s="42" t="s">
-        <v>181</v>
-      </c>
-    </row>
   </sheetData>
-  <mergeCells count="12">
+  <mergeCells count="13">
+    <mergeCell ref="B69:C69"/>
+    <mergeCell ref="B71:E72"/>
+    <mergeCell ref="B26:D27"/>
     <mergeCell ref="B2:H2"/>
     <mergeCell ref="B19:C19"/>
-    <mergeCell ref="B30:C30"/>
-    <mergeCell ref="B42:C42"/>
-    <mergeCell ref="B52:C52"/>
+    <mergeCell ref="B32:C32"/>
+    <mergeCell ref="B46:C46"/>
+    <mergeCell ref="B59:C59"/>
     <mergeCell ref="B15:H15"/>
     <mergeCell ref="B17:D17"/>
-    <mergeCell ref="B27:D27"/>
-    <mergeCell ref="B40:D40"/>
-    <mergeCell ref="B50:D50"/>
-    <mergeCell ref="B60:C60"/>
-    <mergeCell ref="B62:E63"/>
+    <mergeCell ref="B30:D30"/>
+    <mergeCell ref="B44:D44"/>
+    <mergeCell ref="B57:D57"/>
   </mergeCells>
-  <conditionalFormatting pivot="1" sqref="C32:C36">
+  <conditionalFormatting pivot="1" sqref="C34:C38">
     <cfRule type="colorScale" priority="3">
       <colorScale>
         <cfvo type="min"/>
@@ -7044,7 +7484,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B32">
+  <conditionalFormatting sqref="B34">
     <cfRule type="colorScale" priority="2">
       <colorScale>
         <cfvo type="min"/>
@@ -7056,7 +7496,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting pivot="1" sqref="C44:C47">
+  <conditionalFormatting pivot="1" sqref="C48:C51">
     <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="min"/>
@@ -7078,14 +7518,14 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{752D5758-93E2-487B-85C5-0ABD94158F0A}">
-  <dimension ref="B2:T79"/>
+  <dimension ref="B2:T92"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="7.140625" customWidth="1"/>
     <col min="2" max="2" width="15.42578125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="24.42578125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="11.140625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="5.5703125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="12.28515625" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="11.140625" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="13.7109375" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="11.140625" bestFit="1" customWidth="1"/>
@@ -7472,47 +7912,47 @@
       </c>
     </row>
     <row r="19" spans="2:8" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B19" s="43" t="s">
-        <v>171</v>
-      </c>
-      <c r="C19" s="48"/>
-      <c r="D19" s="48"/>
-      <c r="E19" s="48"/>
-      <c r="F19" s="48"/>
-      <c r="G19" s="48"/>
-      <c r="H19" s="48"/>
+      <c r="B19" s="50" t="s">
+        <v>169</v>
+      </c>
+      <c r="C19" s="51"/>
+      <c r="D19" s="51"/>
+      <c r="E19" s="51"/>
+      <c r="F19" s="51"/>
+      <c r="G19" s="51"/>
+      <c r="H19" s="51"/>
     </row>
     <row r="20" spans="2:8" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B20" s="36"/>
-      <c r="C20" s="35"/>
-      <c r="D20" s="35"/>
-      <c r="E20" s="35"/>
-      <c r="F20" s="35"/>
-      <c r="G20" s="35"/>
-      <c r="H20" s="35"/>
+      <c r="B20" s="35"/>
+      <c r="C20" s="34"/>
+      <c r="D20" s="34"/>
+      <c r="E20" s="34"/>
+      <c r="F20" s="34"/>
+      <c r="G20" s="34"/>
+      <c r="H20" s="34"/>
     </row>
     <row r="21" spans="2:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B21" s="43" t="s">
-        <v>184</v>
-      </c>
-      <c r="C21" s="43"/>
-      <c r="D21" s="43"/>
-      <c r="E21" s="43"/>
+      <c r="B21" s="50" t="s">
+        <v>182</v>
+      </c>
+      <c r="C21" s="50"/>
+      <c r="D21" s="50"/>
+      <c r="E21" s="50"/>
     </row>
     <row r="22" spans="2:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B22" s="36"/>
-      <c r="C22" s="36"/>
-      <c r="D22" s="36"/>
-      <c r="E22" s="36"/>
+      <c r="B22" s="35"/>
+      <c r="C22" s="35"/>
+      <c r="D22" s="35"/>
+      <c r="E22" s="35"/>
     </row>
     <row r="23" spans="2:8" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B23" s="43" t="s">
-        <v>185</v>
-      </c>
-      <c r="C23" s="43"/>
-      <c r="D23" s="37"/>
-      <c r="E23" s="37"/>
-      <c r="F23" s="37"/>
+      <c r="B23" s="50" t="s">
+        <v>183</v>
+      </c>
+      <c r="C23" s="50"/>
+      <c r="D23" s="36"/>
+      <c r="E23" s="36"/>
+      <c r="F23" s="36"/>
     </row>
     <row r="24" spans="2:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B24" s="8" t="s">
@@ -7599,286 +8039,239 @@
       <c r="C34" s="10"/>
     </row>
     <row r="35" spans="2:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B35" s="9"/>
+      <c r="B35" s="58" t="s">
+        <v>201</v>
+      </c>
       <c r="C35" s="10"/>
     </row>
     <row r="36" spans="2:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B36" s="43" t="s">
-        <v>186</v>
-      </c>
-      <c r="C36" s="43"/>
-      <c r="D36" s="43"/>
-      <c r="E36" s="43"/>
+      <c r="B36" s="58"/>
+      <c r="C36" s="10"/>
     </row>
     <row r="37" spans="2:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B37" s="36"/>
-      <c r="C37" s="36"/>
-      <c r="D37" s="36"/>
-      <c r="E37" s="36"/>
+      <c r="B37" s="9"/>
+      <c r="C37" s="10"/>
     </row>
     <row r="38" spans="2:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B38" s="43" t="s">
-        <v>189</v>
-      </c>
-      <c r="C38" s="43"/>
-      <c r="D38" s="36"/>
-      <c r="E38" s="36"/>
+      <c r="B38" s="50" t="s">
+        <v>184</v>
+      </c>
+      <c r="C38" s="50"/>
+      <c r="D38" s="50"/>
+      <c r="E38" s="50"/>
     </row>
     <row r="39" spans="2:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B39" s="18" t="s">
+      <c r="B39" s="35"/>
+      <c r="C39" s="35"/>
+      <c r="D39" s="35"/>
+      <c r="E39" s="35"/>
+    </row>
+    <row r="40" spans="2:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B40" s="50" t="s">
+        <v>187</v>
+      </c>
+      <c r="C40" s="50"/>
+      <c r="D40" s="35"/>
+      <c r="E40" s="35"/>
+    </row>
+    <row r="41" spans="2:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B41" s="18" t="s">
         <v>74</v>
       </c>
-      <c r="C39" s="11" t="s">
+      <c r="C41" s="11" t="s">
         <v>41</v>
-      </c>
-    </row>
-    <row r="40" spans="2:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B40" s="9" t="s">
-        <v>8</v>
-      </c>
-      <c r="C40" s="10">
-        <v>110000</v>
-      </c>
-    </row>
-    <row r="41" spans="2:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B41" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="C41" s="10">
-        <v>6000</v>
       </c>
     </row>
     <row r="42" spans="2:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B42" s="9" t="s">
-        <v>52</v>
+        <v>8</v>
       </c>
       <c r="C42" s="10">
-        <v>1000</v>
+        <v>110000</v>
       </c>
     </row>
     <row r="43" spans="2:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B43" s="9" t="s">
-        <v>54</v>
+        <v>13</v>
       </c>
       <c r="C43" s="10">
-        <v>18000</v>
+        <v>6000</v>
       </c>
     </row>
     <row r="44" spans="2:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B44" s="9" t="s">
-        <v>58</v>
+        <v>52</v>
       </c>
       <c r="C44" s="10">
-        <v>10000</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="45" spans="2:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B45" s="9" t="s">
-        <v>61</v>
+        <v>54</v>
       </c>
       <c r="C45" s="10">
-        <v>1000</v>
+        <v>18000</v>
       </c>
     </row>
     <row r="46" spans="2:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B46" s="9" t="s">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="C46" s="10">
-        <v>3000</v>
+        <v>10000</v>
       </c>
     </row>
     <row r="47" spans="2:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B47" s="9" t="s">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="C47" s="10">
-        <v>18000</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="48" spans="2:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B48" s="9" t="s">
+        <v>64</v>
+      </c>
+      <c r="C48" s="10">
+        <v>3000</v>
+      </c>
+    </row>
+    <row r="49" spans="2:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B49" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="C49" s="10">
+        <v>18000</v>
+      </c>
+    </row>
+    <row r="50" spans="2:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B50" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="C48" s="10">
+      <c r="C50" s="10">
         <v>167000</v>
       </c>
     </row>
-    <row r="49" spans="2:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="50" spans="2:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="51" spans="2:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B51" s="43" t="s">
-        <v>188</v>
-      </c>
-      <c r="C51" s="43"/>
-      <c r="D51" s="43"/>
-      <c r="E51" s="43"/>
+      <c r="B51" s="9"/>
+      <c r="C51" s="10"/>
     </row>
     <row r="52" spans="2:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B52" s="36"/>
-      <c r="C52" s="36"/>
-      <c r="D52" s="36"/>
-      <c r="E52" s="36"/>
+      <c r="B52" s="9" t="s">
+        <v>202</v>
+      </c>
     </row>
     <row r="53" spans="2:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B53" s="36" t="s">
-        <v>187</v>
-      </c>
-      <c r="C53" s="36"/>
-      <c r="D53" s="36"/>
-      <c r="E53" s="36"/>
-    </row>
-    <row r="54" spans="2:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B54" s="8" t="s">
+      <c r="B53" s="9"/>
+    </row>
+    <row r="54" spans="2:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="55" spans="2:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B55" s="50" t="s">
+        <v>186</v>
+      </c>
+      <c r="C55" s="50"/>
+      <c r="D55" s="50"/>
+      <c r="E55" s="50"/>
+    </row>
+    <row r="56" spans="2:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B56" s="35"/>
+      <c r="C56" s="35"/>
+      <c r="D56" s="35"/>
+      <c r="E56" s="35"/>
+    </row>
+    <row r="57" spans="2:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B57" s="35" t="s">
+        <v>185</v>
+      </c>
+      <c r="C57" s="35"/>
+      <c r="D57" s="35"/>
+      <c r="E57" s="35"/>
+    </row>
+    <row r="58" spans="2:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B58" s="8" t="s">
         <v>72</v>
       </c>
-      <c r="C54" s="8" t="s">
+      <c r="C58" s="8" t="s">
         <v>42</v>
       </c>
-      <c r="G54" s="49"/>
-    </row>
-    <row r="55" spans="2:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B55" s="18" t="s">
+      <c r="G58" s="43"/>
+    </row>
+    <row r="59" spans="2:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B59" s="18" t="s">
         <v>74</v>
       </c>
-      <c r="C55" s="11" t="s">
+      <c r="C59" s="11" t="s">
         <v>20</v>
       </c>
-      <c r="D55" s="11" t="s">
+      <c r="D59" s="11" t="s">
         <v>11</v>
       </c>
-      <c r="E55" s="11" t="s">
+      <c r="E59" s="11" t="s">
         <v>16</v>
       </c>
-      <c r="F55" s="11" t="s">
+      <c r="F59" s="11" t="s">
         <v>40</v>
       </c>
-      <c r="G55" s="52" t="s">
-        <v>193</v>
-      </c>
-    </row>
-    <row r="56" spans="2:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B56" s="9" t="s">
-        <v>8</v>
-      </c>
-      <c r="C56" s="10"/>
-      <c r="D56" s="10">
-        <v>7</v>
-      </c>
-      <c r="E56" s="10"/>
-      <c r="F56" s="10">
-        <v>7</v>
-      </c>
-      <c r="G56" s="10" t="str" cm="1">
-        <f t="array" ref="G56">_xlfn.IFS(MAX(C56:E56)=C56,"Agent",MAX(C56:E56)=D56,"Mobile Money",MAX(C56:E56)=E56,"USSD")</f>
-        <v>Mobile Money</v>
-      </c>
-    </row>
-    <row r="57" spans="2:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B57" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="C57" s="10"/>
-      <c r="D57" s="10"/>
-      <c r="E57" s="10">
-        <v>2</v>
-      </c>
-      <c r="F57" s="10">
-        <v>2</v>
-      </c>
-      <c r="G57" s="10" t="str" cm="1">
-        <f t="array" ref="G57">_xlfn.IFS(MAX(C57:E57)=C57,"Agent",MAX(C57:E57)=D57,"Mobile Money",MAX(C57:E57)=E57,"USSD")</f>
-        <v>USSD</v>
-      </c>
-    </row>
-    <row r="58" spans="2:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B58" s="9" t="s">
-        <v>52</v>
-      </c>
-      <c r="C58" s="10">
-        <v>1</v>
-      </c>
-      <c r="D58" s="10"/>
-      <c r="E58" s="10"/>
-      <c r="F58" s="10">
-        <v>1</v>
-      </c>
-      <c r="G58" s="10" t="str" cm="1">
-        <f t="array" ref="G58">_xlfn.IFS(MAX(C58:E58)=C58,"Agent",MAX(C58:E58)=D58,"Mobile Money",MAX(C58:E58)=E58,"USSD")</f>
-        <v>Agent</v>
-      </c>
-    </row>
-    <row r="59" spans="2:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B59" s="9" t="s">
-        <v>54</v>
-      </c>
-      <c r="C59" s="10">
-        <v>1</v>
-      </c>
-      <c r="D59" s="10"/>
-      <c r="E59" s="10"/>
-      <c r="F59" s="10">
-        <v>1</v>
-      </c>
-      <c r="G59" s="10" t="str" cm="1">
-        <f t="array" ref="G59">_xlfn.IFS(MAX(C59:E59)=C59,"Agent",MAX(C59:E59)=D59,"Mobile Money",MAX(C59:E59)=E59,"USSD")</f>
-        <v>Agent</v>
+      <c r="G59" s="44" t="s">
+        <v>191</v>
       </c>
     </row>
     <row r="60" spans="2:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B60" s="9" t="s">
-        <v>58</v>
-      </c>
-      <c r="C60" s="10">
-        <v>1</v>
-      </c>
-      <c r="D60" s="10"/>
+        <v>8</v>
+      </c>
+      <c r="C60" s="10"/>
+      <c r="D60" s="10">
+        <v>7</v>
+      </c>
       <c r="E60" s="10"/>
       <c r="F60" s="10">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="G60" s="10" t="str" cm="1">
         <f t="array" ref="G60">_xlfn.IFS(MAX(C60:E60)=C60,"Agent",MAX(C60:E60)=D60,"Mobile Money",MAX(C60:E60)=E60,"USSD")</f>
-        <v>Agent</v>
+        <v>Mobile Money</v>
       </c>
     </row>
     <row r="61" spans="2:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B61" s="9" t="s">
-        <v>61</v>
+        <v>13</v>
       </c>
       <c r="C61" s="10"/>
-      <c r="D61" s="10">
-        <v>1</v>
-      </c>
-      <c r="E61" s="10"/>
+      <c r="D61" s="10"/>
+      <c r="E61" s="10">
+        <v>2</v>
+      </c>
       <c r="F61" s="10">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G61" s="10" t="str" cm="1">
         <f t="array" ref="G61">_xlfn.IFS(MAX(C61:E61)=C61,"Agent",MAX(C61:E61)=D61,"Mobile Money",MAX(C61:E61)=E61,"USSD")</f>
-        <v>Mobile Money</v>
+        <v>USSD</v>
       </c>
     </row>
     <row r="62" spans="2:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B62" s="9" t="s">
-        <v>64</v>
-      </c>
-      <c r="C62" s="10"/>
+        <v>52</v>
+      </c>
+      <c r="C62" s="10">
+        <v>1</v>
+      </c>
       <c r="D62" s="10"/>
-      <c r="E62" s="10">
-        <v>1</v>
-      </c>
+      <c r="E62" s="10"/>
       <c r="F62" s="10">
         <v>1</v>
       </c>
       <c r="G62" s="10" t="str" cm="1">
         <f t="array" ref="G62">_xlfn.IFS(MAX(C62:E62)=C62,"Agent",MAX(C62:E62)=D62,"Mobile Money",MAX(C62:E62)=E62,"USSD")</f>
-        <v>USSD</v>
+        <v>Agent</v>
       </c>
     </row>
     <row r="63" spans="2:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B63" s="9" t="s">
-        <v>67</v>
+        <v>54</v>
       </c>
       <c r="C63" s="10">
         <v>1</v>
@@ -7895,210 +8288,320 @@
     </row>
     <row r="64" spans="2:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B64" s="9" t="s">
+        <v>58</v>
+      </c>
+      <c r="C64" s="10">
+        <v>1</v>
+      </c>
+      <c r="D64" s="10"/>
+      <c r="E64" s="10"/>
+      <c r="F64" s="10">
+        <v>1</v>
+      </c>
+      <c r="G64" s="10" t="str" cm="1">
+        <f t="array" ref="G64">_xlfn.IFS(MAX(C64:E64)=C64,"Agent",MAX(C64:E64)=D64,"Mobile Money",MAX(C64:E64)=E64,"USSD")</f>
+        <v>Agent</v>
+      </c>
+    </row>
+    <row r="65" spans="2:20" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B65" s="9" t="s">
+        <v>61</v>
+      </c>
+      <c r="C65" s="10"/>
+      <c r="D65" s="10">
+        <v>1</v>
+      </c>
+      <c r="E65" s="10"/>
+      <c r="F65" s="10">
+        <v>1</v>
+      </c>
+      <c r="G65" s="10" t="str" cm="1">
+        <f t="array" ref="G65">_xlfn.IFS(MAX(C65:E65)=C65,"Agent",MAX(C65:E65)=D65,"Mobile Money",MAX(C65:E65)=E65,"USSD")</f>
+        <v>Mobile Money</v>
+      </c>
+    </row>
+    <row r="66" spans="2:20" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B66" s="9" t="s">
+        <v>64</v>
+      </c>
+      <c r="C66" s="10"/>
+      <c r="D66" s="10"/>
+      <c r="E66" s="10">
+        <v>1</v>
+      </c>
+      <c r="F66" s="10">
+        <v>1</v>
+      </c>
+      <c r="G66" s="10" t="str" cm="1">
+        <f t="array" ref="G66">_xlfn.IFS(MAX(C66:E66)=C66,"Agent",MAX(C66:E66)=D66,"Mobile Money",MAX(C66:E66)=E66,"USSD")</f>
+        <v>USSD</v>
+      </c>
+    </row>
+    <row r="67" spans="2:20" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B67" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="C67" s="10">
+        <v>1</v>
+      </c>
+      <c r="D67" s="10"/>
+      <c r="E67" s="10"/>
+      <c r="F67" s="10">
+        <v>1</v>
+      </c>
+      <c r="G67" s="10" t="str" cm="1">
+        <f t="array" ref="G67">_xlfn.IFS(MAX(C67:E67)=C67,"Agent",MAX(C67:E67)=D67,"Mobile Money",MAX(C67:E67)=E67,"USSD")</f>
+        <v>Agent</v>
+      </c>
+    </row>
+    <row r="68" spans="2:20" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B68" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="C64" s="10">
+      <c r="C68" s="10">
         <v>4</v>
       </c>
-      <c r="E64" s="36"/>
-      <c r="F64" s="36"/>
-      <c r="G64" s="53"/>
-    </row>
-    <row r="65" spans="2:20" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B65" s="36"/>
-      <c r="C65" s="36"/>
-      <c r="D65" s="36"/>
-      <c r="E65" s="36"/>
-    </row>
-    <row r="66" spans="2:20" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B66" s="36"/>
-      <c r="C66" s="36"/>
-      <c r="D66" s="36"/>
-      <c r="E66" s="36"/>
-    </row>
-    <row r="67" spans="2:20" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B67" s="43" t="s">
+      <c r="E68" s="35"/>
+      <c r="F68" s="35"/>
+      <c r="G68" s="45"/>
+    </row>
+    <row r="69" spans="2:20" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B69" s="9"/>
+      <c r="C69" s="10"/>
+      <c r="E69" s="42"/>
+      <c r="F69" s="42"/>
+      <c r="G69" s="42"/>
+    </row>
+    <row r="70" spans="2:20" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B70" s="9" t="s">
+        <v>203</v>
+      </c>
+      <c r="C70" s="10"/>
+      <c r="E70" s="42"/>
+      <c r="F70" s="42"/>
+      <c r="G70" s="42"/>
+    </row>
+    <row r="71" spans="2:20" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B71" s="9"/>
+      <c r="C71" s="10"/>
+      <c r="E71" s="42"/>
+      <c r="F71" s="42"/>
+      <c r="G71" s="42"/>
+    </row>
+    <row r="72" spans="2:20" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B72" s="9"/>
+      <c r="C72" s="42"/>
+      <c r="D72" s="42"/>
+      <c r="E72" s="42"/>
+    </row>
+    <row r="73" spans="2:20" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B73" s="50" t="s">
+        <v>188</v>
+      </c>
+      <c r="C73" s="50"/>
+      <c r="D73" s="50"/>
+      <c r="E73" s="50"/>
+    </row>
+    <row r="74" spans="2:20" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B74" s="35"/>
+      <c r="C74" s="35"/>
+      <c r="D74" s="35"/>
+      <c r="E74" s="35"/>
+    </row>
+    <row r="75" spans="2:20" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B75" s="50" t="s">
+        <v>189</v>
+      </c>
+      <c r="C75" s="50"/>
+      <c r="D75" s="50"/>
+      <c r="E75" s="50"/>
+      <c r="F75" s="50"/>
+      <c r="G75" s="50"/>
+    </row>
+    <row r="76" spans="2:20" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B76" s="50"/>
+      <c r="C76" s="50"/>
+      <c r="F76" s="9"/>
+      <c r="G76" s="10"/>
+      <c r="H76" s="10"/>
+      <c r="I76" s="10"/>
+      <c r="J76" s="10"/>
+    </row>
+    <row r="77" spans="2:20" x14ac:dyDescent="0.25">
+      <c r="C77" s="20" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="78" spans="2:20" ht="60.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C78" s="22" t="s">
+        <v>8</v>
+      </c>
+      <c r="D78" s="22"/>
+      <c r="E78" s="19" t="s">
+        <v>69</v>
+      </c>
+      <c r="F78" s="19" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="79" spans="2:20" s="19" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+      <c r="B79" s="20" t="s">
+        <v>38</v>
+      </c>
+      <c r="C79" s="19" t="s">
+        <v>39</v>
+      </c>
+      <c r="D79" s="19" t="s">
+        <v>41</v>
+      </c>
+      <c r="G79"/>
+      <c r="H79"/>
+      <c r="I79"/>
+      <c r="J79"/>
+      <c r="K79"/>
+      <c r="L79"/>
+      <c r="M79"/>
+      <c r="N79"/>
+      <c r="O79"/>
+      <c r="P79"/>
+      <c r="Q79"/>
+      <c r="R79"/>
+      <c r="S79"/>
+      <c r="T79"/>
+    </row>
+    <row r="80" spans="2:20" x14ac:dyDescent="0.25">
+      <c r="B80" s="17">
+        <v>46146</v>
+      </c>
+      <c r="C80" s="21">
+        <v>2</v>
+      </c>
+      <c r="D80" s="21">
+        <v>28000</v>
+      </c>
+      <c r="E80" s="10">
+        <v>2</v>
+      </c>
+      <c r="F80" s="10">
+        <v>28000</v>
+      </c>
+    </row>
+    <row r="81" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B81" s="17">
+        <v>46147</v>
+      </c>
+      <c r="C81" s="47">
+        <v>4</v>
+      </c>
+      <c r="D81" s="47">
+        <v>64000</v>
+      </c>
+      <c r="E81" s="10">
+        <v>4</v>
+      </c>
+      <c r="F81" s="10">
+        <v>64000</v>
+      </c>
+    </row>
+    <row r="82" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B82" s="17">
+        <v>46148</v>
+      </c>
+      <c r="C82" s="10">
+        <v>1</v>
+      </c>
+      <c r="D82" s="10">
+        <v>18000</v>
+      </c>
+      <c r="E82" s="10">
+        <v>1</v>
+      </c>
+      <c r="F82" s="10">
+        <v>18000</v>
+      </c>
+    </row>
+    <row r="83" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B83" s="17" t="s">
+        <v>40</v>
+      </c>
+      <c r="C83" s="46">
+        <v>7</v>
+      </c>
+      <c r="D83" s="46">
+        <v>110000</v>
+      </c>
+      <c r="E83" s="10">
+        <v>7</v>
+      </c>
+      <c r="F83" s="10">
+        <v>110000</v>
+      </c>
+    </row>
+    <row r="84" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B84" s="17"/>
+      <c r="C84" s="10"/>
+      <c r="D84" s="10"/>
+      <c r="E84" s="10"/>
+      <c r="F84" s="10"/>
+      <c r="G84" s="10"/>
+      <c r="H84" s="10"/>
+      <c r="I84" s="10"/>
+      <c r="J84" s="10"/>
+      <c r="K84" s="10"/>
+      <c r="L84" s="10"/>
+    </row>
+    <row r="85" spans="2:12" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="B85" s="54" t="s">
         <v>190</v>
       </c>
-      <c r="C67" s="43"/>
-      <c r="D67" s="43"/>
-      <c r="E67" s="43"/>
-    </row>
-    <row r="68" spans="2:20" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B68" s="36"/>
-      <c r="C68" s="36"/>
-      <c r="D68" s="36"/>
-      <c r="E68" s="36"/>
-    </row>
-    <row r="69" spans="2:20" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B69" s="43" t="s">
-        <v>191</v>
-      </c>
-      <c r="C69" s="43"/>
-      <c r="D69" s="43"/>
-      <c r="E69" s="43"/>
-      <c r="F69" s="43"/>
-      <c r="G69" s="43"/>
-    </row>
-    <row r="70" spans="2:20" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B70" s="43"/>
-      <c r="C70" s="43"/>
-      <c r="F70" s="9"/>
-      <c r="G70" s="10"/>
-      <c r="H70" s="10"/>
-      <c r="I70" s="10"/>
-      <c r="J70" s="10"/>
-    </row>
-    <row r="71" spans="2:20" x14ac:dyDescent="0.25">
-      <c r="C71" s="20" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="72" spans="2:20" ht="60.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C72" s="22" t="s">
-        <v>8</v>
-      </c>
-      <c r="D72" s="22"/>
-      <c r="E72" s="19" t="s">
-        <v>69</v>
-      </c>
-      <c r="F72" s="19" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="73" spans="2:20" s="19" customFormat="1" ht="30" x14ac:dyDescent="0.25">
-      <c r="B73" s="20" t="s">
-        <v>38</v>
-      </c>
-      <c r="C73" s="19" t="s">
-        <v>39</v>
-      </c>
-      <c r="D73" s="19" t="s">
-        <v>41</v>
-      </c>
-      <c r="G73"/>
-      <c r="H73"/>
-      <c r="I73"/>
-      <c r="J73"/>
-      <c r="K73"/>
-      <c r="L73"/>
-      <c r="M73"/>
-      <c r="N73"/>
-      <c r="O73"/>
-      <c r="P73"/>
-      <c r="Q73"/>
-      <c r="R73"/>
-      <c r="S73"/>
-      <c r="T73"/>
-    </row>
-    <row r="74" spans="2:20" x14ac:dyDescent="0.25">
-      <c r="B74" s="17">
-        <v>46146</v>
-      </c>
-      <c r="C74" s="21">
-        <v>2</v>
-      </c>
-      <c r="D74" s="21">
-        <v>28000</v>
-      </c>
-      <c r="E74" s="10">
-        <v>2</v>
-      </c>
-      <c r="F74" s="10">
-        <v>28000</v>
-      </c>
-    </row>
-    <row r="75" spans="2:20" x14ac:dyDescent="0.25">
-      <c r="B75" s="17">
-        <v>46147</v>
-      </c>
-      <c r="C75" s="55">
-        <v>4</v>
-      </c>
-      <c r="D75" s="55">
-        <v>64000</v>
-      </c>
-      <c r="E75" s="10">
-        <v>4</v>
-      </c>
-      <c r="F75" s="10">
-        <v>64000</v>
-      </c>
-    </row>
-    <row r="76" spans="2:20" x14ac:dyDescent="0.25">
-      <c r="B76" s="17">
-        <v>46148</v>
-      </c>
-      <c r="C76" s="10">
-        <v>1</v>
-      </c>
-      <c r="D76" s="10">
-        <v>18000</v>
-      </c>
-      <c r="E76" s="10">
-        <v>1</v>
-      </c>
-      <c r="F76" s="10">
-        <v>18000</v>
-      </c>
-    </row>
-    <row r="77" spans="2:20" x14ac:dyDescent="0.25">
-      <c r="B77" s="17" t="s">
-        <v>40</v>
-      </c>
-      <c r="C77" s="54">
-        <v>7</v>
-      </c>
-      <c r="D77" s="54">
-        <v>110000</v>
-      </c>
-      <c r="E77" s="10">
-        <v>7</v>
-      </c>
-      <c r="F77" s="10">
-        <v>110000</v>
-      </c>
-    </row>
-    <row r="78" spans="2:20" x14ac:dyDescent="0.25">
-      <c r="B78" s="17"/>
-      <c r="C78" s="10"/>
-      <c r="D78" s="10"/>
-      <c r="E78" s="10"/>
-      <c r="F78" s="10"/>
-      <c r="G78" s="10"/>
-      <c r="H78" s="10"/>
-      <c r="I78" s="10"/>
-      <c r="J78" s="10"/>
-      <c r="K78" s="10"/>
-      <c r="L78" s="10"/>
-    </row>
-    <row r="79" spans="2:20" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="B79" s="50" t="s">
-        <v>192</v>
-      </c>
-      <c r="C79" s="51"/>
+      <c r="C85" s="55"/>
+    </row>
+    <row r="92" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B92" s="9" t="s">
+        <v>204</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="10">
-    <mergeCell ref="B79:C79"/>
-    <mergeCell ref="B67:E67"/>
-    <mergeCell ref="B70:C70"/>
-    <mergeCell ref="B69:G69"/>
-    <mergeCell ref="B51:E51"/>
-    <mergeCell ref="B36:E36"/>
-    <mergeCell ref="B38:C38"/>
+    <mergeCell ref="B38:E38"/>
+    <mergeCell ref="B40:C40"/>
     <mergeCell ref="B19:H19"/>
     <mergeCell ref="B21:E21"/>
     <mergeCell ref="B23:C23"/>
+    <mergeCell ref="B85:C85"/>
+    <mergeCell ref="B73:E73"/>
+    <mergeCell ref="B76:C76"/>
+    <mergeCell ref="B75:G75"/>
+    <mergeCell ref="B55:E55"/>
   </mergeCells>
-  <conditionalFormatting pivot="1" sqref="C40:C47">
-    <cfRule type="colorScale" priority="1">
+  <conditionalFormatting pivot="1" sqref="C42:C49">
+    <cfRule type="colorScale" priority="4">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
         <cfvo type="max"/>
         <color rgb="FFF8696B"/>
         <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting pivot="1" sqref="C80:C81">
+    <cfRule type="cellIs" dxfId="12" priority="3" operator="greaterThan">
+      <formula>5</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting pivot="1" sqref="C80:C81">
+    <cfRule type="cellIs" dxfId="11" priority="2" operator="greaterThan">
+      <formula>5</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting pivot="1" sqref="C25:C32">
+    <cfRule type="colorScale" priority="1">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="FFFCFCFF"/>
         <color rgb="FF63BE7B"/>
       </colorScale>
     </cfRule>
@@ -8121,14 +8624,15 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{97224B5B-E13D-448C-A67F-DA6B2EEDCE5C}">
-  <dimension ref="B2:P20"/>
+  <dimension ref="B1:P59"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="4.85546875" customWidth="1"/>
     <col min="2" max="2" width="21.42578125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="24.42578125" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="7.28515625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.7109375" customWidth="1"/>
+    <col min="3" max="3" width="17.85546875" customWidth="1"/>
+    <col min="4" max="4" width="11.28515625" customWidth="1"/>
+    <col min="5" max="5" width="9.85546875" customWidth="1"/>
+    <col min="6" max="6" width="11.42578125" customWidth="1"/>
     <col min="7" max="7" width="10.85546875" customWidth="1"/>
     <col min="8" max="8" width="12.5703125" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="12.7109375" bestFit="1" customWidth="1"/>
@@ -8137,6 +8641,17 @@
     <col min="15" max="16" width="11.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
+    <row r="1" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="B1" s="48" t="s">
+        <v>192</v>
+      </c>
+      <c r="C1" s="48"/>
+      <c r="D1" s="48"/>
+      <c r="E1" s="48"/>
+      <c r="F1" s="48"/>
+      <c r="G1" s="48"/>
+      <c r="H1" s="48"/>
+    </row>
     <row r="2" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B2" t="s">
         <v>0</v>
@@ -8159,18 +8674,11 @@
       <c r="H2" t="s">
         <v>5</v>
       </c>
-      <c r="J2" s="46" t="s">
-        <v>111</v>
-      </c>
-      <c r="K2" s="46"/>
-      <c r="L2" s="46"/>
-      <c r="N2" s="46" t="s">
-        <v>112</v>
-      </c>
-      <c r="O2" s="46"/>
-      <c r="P2" s="46"/>
-    </row>
-    <row r="3" spans="2:16" ht="45" x14ac:dyDescent="0.25">
+      <c r="N2" s="48"/>
+      <c r="O2" s="48"/>
+      <c r="P2" s="48"/>
+    </row>
+    <row r="3" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B3" s="10" t="s">
         <v>76</v>
       </c>
@@ -8192,25 +8700,7 @@
       <c r="H3">
         <v>18000</v>
       </c>
-      <c r="J3" s="20" t="s">
-        <v>38</v>
-      </c>
-      <c r="K3" s="19" t="s">
-        <v>39</v>
-      </c>
-      <c r="L3" s="19" t="s">
-        <v>41</v>
-      </c>
       <c r="M3" s="19"/>
-      <c r="N3" s="20" t="s">
-        <v>38</v>
-      </c>
-      <c r="O3" s="19" t="s">
-        <v>39</v>
-      </c>
-      <c r="P3" s="19" t="s">
-        <v>41</v>
-      </c>
     </row>
     <row r="4" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B4" s="10" t="s">
@@ -8234,24 +8724,6 @@
       <c r="H4">
         <v>3000</v>
       </c>
-      <c r="J4" s="9" t="s">
-        <v>77</v>
-      </c>
-      <c r="K4" s="10">
-        <v>5</v>
-      </c>
-      <c r="L4" s="10">
-        <v>82000</v>
-      </c>
-      <c r="N4" s="9" t="s">
-        <v>9</v>
-      </c>
-      <c r="O4" s="10">
-        <v>5</v>
-      </c>
-      <c r="P4" s="10">
-        <v>82000</v>
-      </c>
     </row>
     <row r="5" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B5" s="10" t="s">
@@ -8275,24 +8747,6 @@
       <c r="H5">
         <v>10000</v>
       </c>
-      <c r="J5" s="9" t="s">
-        <v>88</v>
-      </c>
-      <c r="K5" s="10">
-        <v>2</v>
-      </c>
-      <c r="L5" s="10">
-        <v>36000</v>
-      </c>
-      <c r="N5" s="9" t="s">
-        <v>25</v>
-      </c>
-      <c r="O5" s="10">
-        <v>2</v>
-      </c>
-      <c r="P5" s="10">
-        <v>36000</v>
-      </c>
     </row>
     <row r="6" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B6" s="10" t="s">
@@ -8316,24 +8770,6 @@
       <c r="H6">
         <v>1000</v>
       </c>
-      <c r="J6" s="9" t="s">
-        <v>99</v>
-      </c>
-      <c r="K6" s="10">
-        <v>2</v>
-      </c>
-      <c r="L6" s="10">
-        <v>20000</v>
-      </c>
-      <c r="N6" s="9" t="s">
-        <v>19</v>
-      </c>
-      <c r="O6" s="10">
-        <v>2</v>
-      </c>
-      <c r="P6" s="10">
-        <v>20000</v>
-      </c>
     </row>
     <row r="7" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B7" s="10" t="s">
@@ -8357,24 +8793,6 @@
       <c r="H7">
         <v>18000</v>
       </c>
-      <c r="J7" s="23" t="s">
-        <v>80</v>
-      </c>
-      <c r="K7" s="10">
-        <v>3</v>
-      </c>
-      <c r="L7" s="10">
-        <v>9000</v>
-      </c>
-      <c r="N7" s="9" t="s">
-        <v>14</v>
-      </c>
-      <c r="O7" s="10">
-        <v>3</v>
-      </c>
-      <c r="P7" s="10">
-        <v>9000</v>
-      </c>
     </row>
     <row r="8" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B8" s="10" t="s">
@@ -8398,24 +8816,6 @@
       <c r="H8">
         <v>18000</v>
       </c>
-      <c r="J8" s="23" t="s">
-        <v>85</v>
-      </c>
-      <c r="K8" s="10">
-        <v>3</v>
-      </c>
-      <c r="L8" s="10">
-        <v>3000</v>
-      </c>
-      <c r="N8" s="9" t="s">
-        <v>31</v>
-      </c>
-      <c r="O8" s="10">
-        <v>3</v>
-      </c>
-      <c r="P8" s="10">
-        <v>3000</v>
-      </c>
     </row>
     <row r="9" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B9" s="10" t="s">
@@ -8439,24 +8839,6 @@
       <c r="H9">
         <v>3000</v>
       </c>
-      <c r="J9" s="9" t="s">
-        <v>40</v>
-      </c>
-      <c r="K9" s="10">
-        <v>15</v>
-      </c>
-      <c r="L9" s="10">
-        <v>150000</v>
-      </c>
-      <c r="N9" s="9" t="s">
-        <v>40</v>
-      </c>
-      <c r="O9" s="10">
-        <v>15</v>
-      </c>
-      <c r="P9" s="10">
-        <v>150000</v>
-      </c>
     </row>
     <row r="10" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B10" s="10" t="s">
@@ -8503,12 +8885,6 @@
       <c r="H11">
         <v>18000</v>
       </c>
-      <c r="J11" s="8" t="s">
-        <v>41</v>
-      </c>
-      <c r="K11" s="8" t="s">
-        <v>42</v>
-      </c>
     </row>
     <row r="12" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B12" s="10" t="s">
@@ -8532,27 +8908,6 @@
       <c r="H12">
         <v>10000</v>
       </c>
-      <c r="J12" s="8" t="s">
-        <v>38</v>
-      </c>
-      <c r="K12" t="s">
-        <v>9</v>
-      </c>
-      <c r="L12" t="s">
-        <v>14</v>
-      </c>
-      <c r="M12" t="s">
-        <v>31</v>
-      </c>
-      <c r="N12" t="s">
-        <v>19</v>
-      </c>
-      <c r="O12" t="s">
-        <v>25</v>
-      </c>
-      <c r="P12" t="s">
-        <v>40</v>
-      </c>
     </row>
     <row r="13" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B13" s="10" t="s">
@@ -8576,21 +8931,6 @@
       <c r="H13">
         <v>18000</v>
       </c>
-      <c r="J13" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="K13" s="10">
-        <v>72000</v>
-      </c>
-      <c r="L13" s="10"/>
-      <c r="M13" s="10"/>
-      <c r="N13" s="10"/>
-      <c r="O13" s="10">
-        <v>36000</v>
-      </c>
-      <c r="P13" s="10">
-        <v>108000</v>
-      </c>
     </row>
     <row r="14" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B14" s="10" t="s">
@@ -8614,21 +8954,6 @@
       <c r="H14">
         <v>3000</v>
       </c>
-      <c r="J14" s="9" t="s">
-        <v>10</v>
-      </c>
-      <c r="K14" s="10">
-        <v>10000</v>
-      </c>
-      <c r="L14" s="10"/>
-      <c r="M14" s="10"/>
-      <c r="N14" s="10">
-        <v>20000</v>
-      </c>
-      <c r="O14" s="10"/>
-      <c r="P14" s="10">
-        <v>30000</v>
-      </c>
     </row>
     <row r="15" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B15" s="10" t="s">
@@ -8652,19 +8977,6 @@
       <c r="H15">
         <v>1000</v>
       </c>
-      <c r="J15" s="9" t="s">
-        <v>22</v>
-      </c>
-      <c r="K15" s="10"/>
-      <c r="L15" s="10"/>
-      <c r="M15" s="10">
-        <v>3000</v>
-      </c>
-      <c r="N15" s="10"/>
-      <c r="O15" s="10"/>
-      <c r="P15" s="10">
-        <v>3000</v>
-      </c>
     </row>
     <row r="16" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B16" s="10" t="s">
@@ -8688,21 +9000,8 @@
       <c r="H16">
         <v>18000</v>
       </c>
-      <c r="J16" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="K16" s="10"/>
-      <c r="L16" s="10">
-        <v>9000</v>
-      </c>
-      <c r="M16" s="10"/>
-      <c r="N16" s="10"/>
-      <c r="O16" s="10"/>
-      <c r="P16" s="10">
-        <v>9000</v>
-      </c>
-    </row>
-    <row r="17" spans="2:16" x14ac:dyDescent="0.25">
+    </row>
+    <row r="17" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B17" s="10" t="s">
         <v>109</v>
       </c>
@@ -8724,56 +9023,449 @@
       <c r="H17">
         <v>10000</v>
       </c>
-      <c r="J17" s="9" t="s">
+    </row>
+    <row r="20" spans="2:8" s="19" customFormat="1" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B20" s="56" t="s">
+        <v>193</v>
+      </c>
+      <c r="C20" s="56"/>
+      <c r="D20" s="56"/>
+      <c r="E20" s="56"/>
+    </row>
+    <row r="22" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B22" s="48" t="s">
+        <v>209</v>
+      </c>
+      <c r="C22" s="48"/>
+      <c r="D22" s="48"/>
+    </row>
+    <row r="23" spans="2:8" ht="30" x14ac:dyDescent="0.25">
+      <c r="B23" s="20" t="s">
+        <v>38</v>
+      </c>
+      <c r="C23" s="19" t="s">
+        <v>39</v>
+      </c>
+      <c r="D23" s="19" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="24" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B24" s="10" t="s">
+        <v>77</v>
+      </c>
+      <c r="C24" s="10">
+        <v>5</v>
+      </c>
+      <c r="D24" s="10">
+        <v>82000</v>
+      </c>
+    </row>
+    <row r="25" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B25" s="10" t="s">
+        <v>88</v>
+      </c>
+      <c r="C25" s="10">
+        <v>2</v>
+      </c>
+      <c r="D25" s="10">
+        <v>36000</v>
+      </c>
+    </row>
+    <row r="26" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B26" s="10" t="s">
+        <v>99</v>
+      </c>
+      <c r="C26" s="10">
+        <v>2</v>
+      </c>
+      <c r="D26" s="10">
+        <v>20000</v>
+      </c>
+    </row>
+    <row r="27" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B27" s="10" t="s">
+        <v>80</v>
+      </c>
+      <c r="C27" s="10">
+        <v>3</v>
+      </c>
+      <c r="D27" s="10">
+        <v>9000</v>
+      </c>
+    </row>
+    <row r="28" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B28" s="10" t="s">
+        <v>85</v>
+      </c>
+      <c r="C28" s="10">
+        <v>3</v>
+      </c>
+      <c r="D28" s="10">
+        <v>3000</v>
+      </c>
+    </row>
+    <row r="29" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B29" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="K17" s="10">
+      <c r="C29" s="10">
+        <v>15</v>
+      </c>
+      <c r="D29" s="10">
+        <v>150000</v>
+      </c>
+    </row>
+    <row r="30" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B30" s="9"/>
+      <c r="C30" s="10"/>
+      <c r="D30" s="10"/>
+    </row>
+    <row r="31" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B31" s="10" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="33" spans="2:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B33" s="56" t="s">
+        <v>194</v>
+      </c>
+      <c r="C33" s="56"/>
+      <c r="D33" s="56"/>
+      <c r="E33" s="56"/>
+    </row>
+    <row r="35" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B35" s="48" t="s">
+        <v>195</v>
+      </c>
+      <c r="C35" s="48"/>
+      <c r="D35" s="48"/>
+    </row>
+    <row r="36" spans="2:8" ht="30" x14ac:dyDescent="0.25">
+      <c r="B36" s="20" t="s">
+        <v>38</v>
+      </c>
+      <c r="C36" s="20" t="s">
+        <v>39</v>
+      </c>
+      <c r="D36" s="19" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="37" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B37" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="C37" s="10">
+        <v>5</v>
+      </c>
+      <c r="D37" s="10">
         <v>82000</v>
       </c>
-      <c r="L17" s="10">
+    </row>
+    <row r="38" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B38" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="C38" s="10">
+        <v>2</v>
+      </c>
+      <c r="D38" s="10">
+        <v>36000</v>
+      </c>
+    </row>
+    <row r="39" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B39" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="C39" s="10">
+        <v>2</v>
+      </c>
+      <c r="D39" s="10">
+        <v>20000</v>
+      </c>
+    </row>
+    <row r="40" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B40" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="C40" s="10">
+        <v>3</v>
+      </c>
+      <c r="D40" s="10">
         <v>9000</v>
       </c>
-      <c r="M17" s="10">
+    </row>
+    <row r="41" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B41" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="C41" s="10">
+        <v>3</v>
+      </c>
+      <c r="D41" s="10">
         <v>3000</v>
       </c>
-      <c r="N17" s="10">
+    </row>
+    <row r="42" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B42" s="9" t="s">
+        <v>40</v>
+      </c>
+      <c r="C42" s="10">
+        <v>15</v>
+      </c>
+      <c r="D42" s="10">
+        <v>150000</v>
+      </c>
+    </row>
+    <row r="43" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B43" s="9"/>
+      <c r="C43" s="10"/>
+      <c r="D43" s="10"/>
+    </row>
+    <row r="44" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B44" s="10" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="46" spans="2:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B46" s="56" t="s">
+        <v>196</v>
+      </c>
+      <c r="C46" s="56"/>
+      <c r="D46" s="56"/>
+      <c r="E46" s="56"/>
+    </row>
+    <row r="47" spans="2:8" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B47" s="42"/>
+      <c r="C47" s="42"/>
+      <c r="D47" s="42"/>
+      <c r="E47" s="42"/>
+    </row>
+    <row r="48" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B48" s="48" t="s">
+        <v>197</v>
+      </c>
+      <c r="C48" s="49"/>
+      <c r="D48" s="49"/>
+      <c r="E48" s="49"/>
+      <c r="F48" s="49"/>
+      <c r="G48" s="49"/>
+      <c r="H48" s="49"/>
+    </row>
+    <row r="49" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B49" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="C49" s="8" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="50" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B50" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="C50" t="s">
+        <v>9</v>
+      </c>
+      <c r="D50" t="s">
+        <v>14</v>
+      </c>
+      <c r="E50" t="s">
+        <v>31</v>
+      </c>
+      <c r="F50" t="s">
+        <v>19</v>
+      </c>
+      <c r="G50" t="s">
+        <v>25</v>
+      </c>
+      <c r="H50" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="51" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B51" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="C51" s="10">
+        <v>72000</v>
+      </c>
+      <c r="D51" s="10"/>
+      <c r="E51" s="10"/>
+      <c r="F51" s="10"/>
+      <c r="G51" s="10">
+        <v>36000</v>
+      </c>
+      <c r="H51" s="10">
+        <v>108000</v>
+      </c>
+    </row>
+    <row r="52" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B52" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="C52" s="10">
+        <v>10000</v>
+      </c>
+      <c r="D52" s="10"/>
+      <c r="E52" s="10"/>
+      <c r="F52" s="10">
         <v>20000</v>
       </c>
-      <c r="O17" s="10">
+      <c r="G52" s="10"/>
+      <c r="H52" s="10">
+        <v>30000</v>
+      </c>
+    </row>
+    <row r="53" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B53" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="C53" s="10"/>
+      <c r="D53" s="10"/>
+      <c r="E53" s="10">
+        <v>3000</v>
+      </c>
+      <c r="F53" s="10"/>
+      <c r="G53" s="10"/>
+      <c r="H53" s="10">
+        <v>3000</v>
+      </c>
+    </row>
+    <row r="54" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B54" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="C54" s="10"/>
+      <c r="D54" s="10">
+        <v>9000</v>
+      </c>
+      <c r="E54" s="10"/>
+      <c r="F54" s="10"/>
+      <c r="G54" s="10"/>
+      <c r="H54" s="10">
+        <v>9000</v>
+      </c>
+    </row>
+    <row r="55" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B55" s="9" t="s">
+        <v>40</v>
+      </c>
+      <c r="C55" s="10">
+        <v>82000</v>
+      </c>
+      <c r="D55" s="10">
+        <v>9000</v>
+      </c>
+      <c r="E55" s="10">
+        <v>3000</v>
+      </c>
+      <c r="F55" s="10">
+        <v>20000</v>
+      </c>
+      <c r="G55" s="10">
         <v>36000</v>
       </c>
-      <c r="P17" s="10">
+      <c r="H55" s="10">
         <v>150000</v>
       </c>
     </row>
-    <row r="20" spans="2:16" s="19" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B20"/>
-      <c r="C20"/>
-      <c r="D20"/>
+    <row r="57" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B57" s="57" t="s">
+        <v>200</v>
+      </c>
+      <c r="C57" s="57"/>
+      <c r="D57" s="57"/>
+      <c r="E57" s="57"/>
+      <c r="F57" s="57"/>
+      <c r="G57" s="57"/>
+      <c r="H57" s="57"/>
+    </row>
+    <row r="58" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B58" s="57"/>
+      <c r="C58" s="57"/>
+      <c r="D58" s="57"/>
+      <c r="E58" s="57"/>
+      <c r="F58" s="57"/>
+      <c r="G58" s="57"/>
+      <c r="H58" s="57"/>
+    </row>
+    <row r="59" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B59" s="57"/>
+      <c r="C59" s="57"/>
+      <c r="D59" s="57"/>
+      <c r="E59" s="57"/>
+      <c r="F59" s="57"/>
+      <c r="G59" s="57"/>
+      <c r="H59" s="57"/>
     </row>
   </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="J2:L2"/>
+  <mergeCells count="9">
+    <mergeCell ref="B35:D35"/>
+    <mergeCell ref="B46:E46"/>
+    <mergeCell ref="B48:H48"/>
+    <mergeCell ref="B57:H59"/>
+    <mergeCell ref="B22:D22"/>
     <mergeCell ref="N2:P2"/>
+    <mergeCell ref="B1:H1"/>
+    <mergeCell ref="B20:E20"/>
+    <mergeCell ref="B33:E33"/>
   </mergeCells>
-  <conditionalFormatting pivot="1" sqref="L4:L8">
-    <cfRule type="cellIs" dxfId="42" priority="5" operator="lessThan">
+  <conditionalFormatting pivot="1" sqref="D24:D28">
+    <cfRule type="cellIs" dxfId="10" priority="11" operator="lessThan">
       <formula>10000</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting pivot="1" sqref="P4:P8">
-    <cfRule type="cellIs" dxfId="41" priority="4" operator="lessThan">
+  <conditionalFormatting pivot="1" sqref="D24:D28">
+    <cfRule type="colorScale" priority="6">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B24:B28">
+    <cfRule type="cellIs" dxfId="7" priority="5" operator="lessThan">
+      <formula>10000</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B24:B28">
+    <cfRule type="colorScale" priority="4">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting pivot="1" sqref="D37:D41">
+    <cfRule type="cellIs" dxfId="6" priority="3" operator="lessThan">
       <formula>$Q$4</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting pivot="1" sqref="P4:P9">
-    <cfRule type="cellIs" dxfId="40" priority="3" operator="lessThan">
+  <conditionalFormatting pivot="1" sqref="D37:D42">
+    <cfRule type="cellIs" dxfId="5" priority="2" operator="lessThan">
       <formula>30000</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J7:J8">
-    <cfRule type="cellIs" dxfId="39" priority="1" operator="lessThan">
-      <formula>10000</formula>
+  <conditionalFormatting pivot="1" sqref="D37:D41">
+    <cfRule type="colorScale" priority="1">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -8842,13 +9534,13 @@
     </row>
     <row r="3" spans="2:27" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B3" s="10" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="C3" s="6">
         <v>46152</v>
       </c>
       <c r="D3" s="10" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="E3" s="10" t="s">
         <v>9</v>
@@ -8863,66 +9555,66 @@
         <v>38</v>
       </c>
       <c r="J3" t="s">
+        <v>111</v>
+      </c>
+      <c r="K3" t="s">
         <v>113</v>
       </c>
-      <c r="K3" t="s">
+      <c r="L3" t="s">
         <v>115</v>
       </c>
-      <c r="L3" t="s">
+      <c r="M3" t="s">
         <v>117</v>
       </c>
-      <c r="M3" t="s">
-        <v>119</v>
-      </c>
       <c r="N3" t="s">
+        <v>118</v>
+      </c>
+      <c r="O3" t="s">
         <v>120</v>
       </c>
-      <c r="O3" t="s">
+      <c r="P3" t="s">
         <v>122</v>
       </c>
-      <c r="P3" t="s">
+      <c r="Q3" t="s">
+        <v>123</v>
+      </c>
+      <c r="R3" t="s">
         <v>124</v>
       </c>
-      <c r="Q3" t="s">
-        <v>125</v>
-      </c>
-      <c r="R3" t="s">
+      <c r="S3" t="s">
         <v>126</v>
       </c>
-      <c r="S3" t="s">
+      <c r="T3" t="s">
+        <v>127</v>
+      </c>
+      <c r="U3" t="s">
         <v>128</v>
       </c>
-      <c r="T3" t="s">
-        <v>129</v>
-      </c>
-      <c r="U3" t="s">
+      <c r="V3" t="s">
         <v>130</v>
       </c>
-      <c r="V3" t="s">
-        <v>132</v>
-      </c>
       <c r="W3" t="s">
+        <v>131</v>
+      </c>
+      <c r="X3" t="s">
         <v>133</v>
-      </c>
-      <c r="X3" t="s">
-        <v>135</v>
       </c>
       <c r="Y3" s="19" t="s">
         <v>40</v>
       </c>
-      <c r="AA3" s="26" t="s">
-        <v>136</v>
+      <c r="AA3" s="25" t="s">
+        <v>134</v>
       </c>
     </row>
     <row r="4" spans="2:27" x14ac:dyDescent="0.25">
       <c r="B4" s="10" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="C4" s="6">
         <v>46152</v>
       </c>
       <c r="D4" s="10" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="E4" s="10" t="s">
         <v>14</v>
@@ -8934,7 +9626,7 @@
         <v>3000</v>
       </c>
       <c r="I4" s="9" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="J4" s="10">
         <v>18000</v>
@@ -8971,13 +9663,13 @@
     </row>
     <row r="5" spans="2:27" x14ac:dyDescent="0.25">
       <c r="B5" s="10" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="C5" s="6">
         <v>46152</v>
       </c>
       <c r="D5" s="10" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="E5" s="10" t="s">
         <v>19</v>
@@ -8989,7 +9681,7 @@
         <v>10000</v>
       </c>
       <c r="I5" s="9" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="J5" s="10"/>
       <c r="K5" s="10">
@@ -9022,13 +9714,13 @@
     </row>
     <row r="6" spans="2:27" x14ac:dyDescent="0.25">
       <c r="B6" s="10" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="C6" s="6">
         <v>46153</v>
       </c>
       <c r="D6" s="10" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="E6" s="10" t="s">
         <v>9</v>
@@ -9040,7 +9732,7 @@
         <v>18000</v>
       </c>
       <c r="I6" s="9" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="J6" s="10"/>
       <c r="K6" s="10"/>
@@ -9071,13 +9763,13 @@
     </row>
     <row r="7" spans="2:27" x14ac:dyDescent="0.25">
       <c r="B7" s="10" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="C7" s="6">
         <v>46153</v>
       </c>
       <c r="D7" s="10" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="E7" s="10" t="s">
         <v>31</v>
@@ -9089,7 +9781,7 @@
         <v>1000</v>
       </c>
       <c r="I7" s="9" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="J7" s="10"/>
       <c r="K7" s="10"/>
@@ -9118,13 +9810,13 @@
     </row>
     <row r="8" spans="2:27" x14ac:dyDescent="0.25">
       <c r="B8" s="10" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="C8" s="6">
         <v>46153</v>
       </c>
       <c r="D8" s="10" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="E8" s="10" t="s">
         <v>25</v>
@@ -9136,7 +9828,7 @@
         <v>18000</v>
       </c>
       <c r="I8" s="9" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="J8" s="10"/>
       <c r="K8" s="10"/>
@@ -9165,13 +9857,13 @@
     </row>
     <row r="9" spans="2:27" x14ac:dyDescent="0.25">
       <c r="B9" s="10" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="C9" s="6">
         <v>46154</v>
       </c>
       <c r="D9" s="10" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="E9" s="10" t="s">
         <v>9</v>
@@ -9183,7 +9875,7 @@
         <v>10000</v>
       </c>
       <c r="I9" s="9" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="J9" s="10"/>
       <c r="K9" s="10"/>
@@ -9212,13 +9904,13 @@
     </row>
     <row r="10" spans="2:27" x14ac:dyDescent="0.25">
       <c r="B10" s="10" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="C10" s="6">
         <v>46154</v>
       </c>
       <c r="D10" s="10" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="E10" s="10" t="s">
         <v>14</v>
@@ -9230,7 +9922,7 @@
         <v>3000</v>
       </c>
       <c r="I10" s="9" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="J10" s="10"/>
       <c r="K10" s="10"/>
@@ -9259,13 +9951,13 @@
     </row>
     <row r="11" spans="2:27" x14ac:dyDescent="0.25">
       <c r="B11" s="10" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="C11" s="6">
         <v>46154</v>
       </c>
       <c r="D11" s="10" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="E11" s="10" t="s">
         <v>9</v>
@@ -9277,7 +9969,7 @@
         <v>1000</v>
       </c>
       <c r="I11" s="9" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="J11" s="10"/>
       <c r="K11" s="10"/>
@@ -9306,13 +9998,13 @@
     </row>
     <row r="12" spans="2:27" x14ac:dyDescent="0.25">
       <c r="B12" s="10" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="C12" s="6">
         <v>46155</v>
       </c>
       <c r="D12" s="10" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="E12" s="10" t="s">
         <v>9</v>
@@ -9377,13 +10069,13 @@
     </row>
     <row r="13" spans="2:27" x14ac:dyDescent="0.25">
       <c r="B13" s="10" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="C13" s="6">
         <v>46155</v>
       </c>
       <c r="D13" s="10" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="E13" s="10" t="s">
         <v>19</v>
@@ -9397,13 +10089,13 @@
     </row>
     <row r="14" spans="2:27" x14ac:dyDescent="0.25">
       <c r="B14" s="10" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="C14" s="6">
         <v>46155</v>
       </c>
       <c r="D14" s="10" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="E14" s="10" t="s">
         <v>31</v>
@@ -9417,13 +10109,13 @@
     </row>
     <row r="15" spans="2:27" x14ac:dyDescent="0.25">
       <c r="B15" s="10" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="C15" s="6">
         <v>46156</v>
       </c>
       <c r="D15" s="10" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="E15" s="10" t="s">
         <v>9</v>
@@ -9437,13 +10129,13 @@
     </row>
     <row r="16" spans="2:27" x14ac:dyDescent="0.25">
       <c r="B16" s="10" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="C16" s="6">
         <v>46156</v>
       </c>
       <c r="D16" s="10" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="E16" s="10" t="s">
         <v>25</v>
@@ -9457,13 +10149,13 @@
     </row>
     <row r="17" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B17" s="10" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="C17" s="6">
         <v>46156</v>
       </c>
       <c r="D17" s="10" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="E17" s="10" t="s">
         <v>14</v>
@@ -9498,7 +10190,7 @@
     </row>
     <row r="21" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B21" s="9" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="C21" s="10">
         <v>5</v>
@@ -9512,13 +10204,13 @@
       <c r="H21" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="I21" s="24">
+      <c r="I21" s="23">
         <v>6</v>
       </c>
     </row>
     <row r="22" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B22" s="9" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="C22" s="10">
         <v>3</v>
@@ -9538,7 +10230,7 @@
     </row>
     <row r="23" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B23" s="9" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="C23" s="10">
         <v>2</v>
@@ -9558,7 +10250,7 @@
     </row>
     <row r="24" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B24" s="9" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="C24" s="10">
         <v>1</v>
@@ -9578,7 +10270,7 @@
     </row>
     <row r="25" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B25" s="9" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="C25" s="10">
         <v>1</v>
@@ -9598,7 +10290,7 @@
     </row>
     <row r="26" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B26" s="9" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="C26" s="10">
         <v>1</v>
@@ -9612,7 +10304,7 @@
     </row>
     <row r="27" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B27" s="9" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="C27" s="10">
         <v>1</v>
@@ -9620,7 +10312,7 @@
     </row>
     <row r="28" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B28" s="9" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="C28" s="10">
         <v>1</v>
@@ -9636,23 +10328,23 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B20:C29">
-    <cfRule type="cellIs" dxfId="38" priority="5" operator="lessThan">
+    <cfRule type="cellIs" dxfId="4" priority="5" operator="lessThan">
       <formula>2</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting pivot="1" sqref="F21:F25">
-    <cfRule type="cellIs" dxfId="37" priority="4" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="3" priority="4" operator="greaterThan">
       <formula>5</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting pivot="1" sqref="F21:F25">
-    <cfRule type="cellIs" dxfId="36" priority="3" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="2" priority="3" operator="greaterThan">
       <formula>5</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AA4:AA11">
-    <cfRule type="top10" dxfId="35" priority="1" rank="2"/>
-    <cfRule type="top10" dxfId="34" priority="2" rank="2"/>
+    <cfRule type="top10" dxfId="1" priority="1" rank="2"/>
+    <cfRule type="top10" dxfId="0" priority="2" rank="2"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="2">
@@ -9727,7 +10419,7 @@
         <v>5</v>
       </c>
       <c r="H2" s="19" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="J2" s="20" t="s">
         <v>39</v>
@@ -9738,13 +10430,13 @@
     </row>
     <row r="3" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B3" s="10" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="C3" s="6">
         <v>46157</v>
       </c>
       <c r="D3" s="10" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="E3" s="10" t="s">
         <v>9</v>
@@ -9756,37 +10448,37 @@
         <v>18000</v>
       </c>
       <c r="H3" s="10" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="J3" s="8" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="K3" t="s">
+        <v>112</v>
+      </c>
+      <c r="L3" t="s">
         <v>114</v>
       </c>
-      <c r="L3" t="s">
+      <c r="M3" t="s">
         <v>116</v>
       </c>
-      <c r="M3" t="s">
-        <v>118</v>
-      </c>
       <c r="N3" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="O3" t="s">
+        <v>145</v>
+      </c>
+      <c r="P3" t="s">
         <v>147</v>
       </c>
-      <c r="P3" t="s">
-        <v>149</v>
-      </c>
       <c r="Q3" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="R3" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="S3" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="T3" t="s">
         <v>40</v>
@@ -9794,13 +10486,13 @@
     </row>
     <row r="4" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B4" s="10" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="C4" s="6">
         <v>46157</v>
       </c>
       <c r="D4" s="10" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="E4" s="10" t="s">
         <v>14</v>
@@ -9812,10 +10504,10 @@
         <v>3000</v>
       </c>
       <c r="H4" s="10" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="J4" s="9" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="K4" s="10">
         <v>1</v>
@@ -9840,13 +10532,13 @@
     </row>
     <row r="5" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B5" s="10" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="C5" s="6">
         <v>46157</v>
       </c>
       <c r="D5" s="10" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="E5" s="10" t="s">
         <v>19</v>
@@ -9858,12 +10550,12 @@
         <v>10000</v>
       </c>
       <c r="H5" s="10" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="J5" s="9" t="s">
-        <v>144</v>
-      </c>
-      <c r="K5" s="29">
+        <v>142</v>
+      </c>
+      <c r="K5" s="28">
         <v>2</v>
       </c>
       <c r="L5" s="10">
@@ -9873,16 +10565,16 @@
         <v>1</v>
       </c>
       <c r="N5" s="10"/>
-      <c r="O5" s="24">
+      <c r="O5" s="23">
         <v>1</v>
       </c>
-      <c r="P5" s="24">
+      <c r="P5" s="23">
         <v>1</v>
       </c>
-      <c r="Q5" s="24">
+      <c r="Q5" s="23">
         <v>1</v>
       </c>
-      <c r="R5" s="24">
+      <c r="R5" s="23">
         <v>1</v>
       </c>
       <c r="S5" s="10"/>
@@ -9892,13 +10584,13 @@
     </row>
     <row r="6" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B6" s="10" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="C6" s="6">
         <v>46157</v>
       </c>
       <c r="D6" s="10" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="E6" s="10" t="s">
         <v>25</v>
@@ -9910,10 +10602,10 @@
         <v>18000</v>
       </c>
       <c r="H6" s="10" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="J6" s="9" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="K6" s="10">
         <v>1</v>
@@ -9927,7 +10619,7 @@
       <c r="P6" s="10"/>
       <c r="Q6" s="10"/>
       <c r="R6" s="10"/>
-      <c r="S6" s="24">
+      <c r="S6" s="23">
         <v>1</v>
       </c>
       <c r="T6" s="10">
@@ -9936,13 +10628,13 @@
     </row>
     <row r="7" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B7" s="10" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="C7" s="6">
         <v>46158</v>
       </c>
       <c r="D7" s="10" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="E7" s="10" t="s">
         <v>9</v>
@@ -9954,7 +10646,7 @@
         <v>12600</v>
       </c>
       <c r="H7" s="10" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="J7" s="9" t="s">
         <v>40</v>
@@ -9992,13 +10684,13 @@
     </row>
     <row r="8" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B8" s="10" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="C8" s="6">
         <v>46158</v>
       </c>
       <c r="D8" s="10" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="E8" s="10" t="s">
         <v>14</v>
@@ -10010,36 +10702,36 @@
         <v>3000</v>
       </c>
       <c r="H8" s="10" t="s">
-        <v>144</v>
-      </c>
-      <c r="J8" s="28" t="s">
-        <v>165</v>
-      </c>
-      <c r="K8" s="34" t="s">
+        <v>142</v>
+      </c>
+      <c r="J8" s="27" t="s">
+        <v>163</v>
+      </c>
+      <c r="K8" s="33" t="s">
+        <v>145</v>
+      </c>
+      <c r="L8" s="33" t="s">
         <v>147</v>
       </c>
-      <c r="L8" s="34" t="s">
-        <v>149</v>
-      </c>
-      <c r="M8" s="34" t="s">
-        <v>153</v>
-      </c>
-      <c r="N8" s="34" t="s">
-        <v>157</v>
-      </c>
-      <c r="O8" s="34" t="s">
-        <v>163</v>
+      <c r="M8" s="33" t="s">
+        <v>151</v>
+      </c>
+      <c r="N8" s="33" t="s">
+        <v>155</v>
+      </c>
+      <c r="O8" s="33" t="s">
+        <v>161</v>
       </c>
     </row>
     <row r="9" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B9" s="10" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="C9" s="6">
         <v>46158</v>
       </c>
       <c r="D9" s="10" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="E9" s="10" t="s">
         <v>31</v>
@@ -10051,27 +10743,27 @@
         <v>12600</v>
       </c>
       <c r="H9" s="10" t="s">
-        <v>144</v>
-      </c>
-      <c r="J9" s="30" t="s">
-        <v>166</v>
-      </c>
-      <c r="K9" s="30" t="s">
-        <v>114</v>
+        <v>142</v>
+      </c>
+      <c r="J9" s="29" t="s">
+        <v>164</v>
+      </c>
+      <c r="K9" s="29" t="s">
+        <v>112</v>
       </c>
     </row>
     <row r="10" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B10" s="10" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="C10" s="6">
         <v>46158</v>
       </c>
       <c r="D10" s="10" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="E10" s="10" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="F10" s="10" t="s">
         <v>26</v>
@@ -10080,18 +10772,18 @@
         <v>12600</v>
       </c>
       <c r="H10" s="10" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
     </row>
     <row r="11" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B11" s="10" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="C11" s="6">
         <v>46159</v>
       </c>
       <c r="D11" s="10" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="E11" s="10" t="s">
         <v>9</v>
@@ -10103,21 +10795,21 @@
         <v>12600</v>
       </c>
       <c r="H11" s="10" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
     </row>
     <row r="12" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B12" s="10" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="C12" s="6">
         <v>46159</v>
       </c>
       <c r="D12" s="10" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="E12" s="10" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="F12" s="10" t="s">
         <v>26</v>
@@ -10126,7 +10818,7 @@
         <v>12600</v>
       </c>
       <c r="H12" s="10" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="J12" s="8" t="s">
         <v>39</v>
@@ -10136,38 +10828,38 @@
       </c>
     </row>
     <row r="13" spans="2:20" s="19" customFormat="1" ht="27" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B13" s="31" t="s">
-        <v>155</v>
-      </c>
-      <c r="C13" s="32">
+      <c r="B13" s="30" t="s">
+        <v>153</v>
+      </c>
+      <c r="C13" s="31">
         <v>46159</v>
       </c>
-      <c r="D13" s="31" t="s">
-        <v>118</v>
-      </c>
-      <c r="E13" s="31" t="s">
+      <c r="D13" s="30" t="s">
+        <v>116</v>
+      </c>
+      <c r="E13" s="30" t="s">
         <v>19</v>
       </c>
-      <c r="F13" s="31" t="s">
+      <c r="F13" s="30" t="s">
         <v>10</v>
       </c>
       <c r="G13" s="19">
         <v>10000</v>
       </c>
-      <c r="H13" s="31" t="s">
-        <v>144</v>
+      <c r="H13" s="30" t="s">
+        <v>142</v>
       </c>
       <c r="J13" s="20" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="K13" s="19" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="L13" s="19" t="s">
         <v>9</v>
       </c>
       <c r="M13" s="19" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="N13" s="19" t="s">
         <v>14</v>
@@ -10182,10 +10874,10 @@
         <v>25</v>
       </c>
       <c r="R13" s="19" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="S13" s="19" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="T13" s="19" t="s">
         <v>40</v>
@@ -10193,16 +10885,16 @@
     </row>
     <row r="14" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B14" s="10" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="C14" s="6">
         <v>46159</v>
       </c>
       <c r="D14" s="10" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="E14" s="10" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="F14" s="10" t="s">
         <v>26</v>
@@ -10211,10 +10903,10 @@
         <v>12600</v>
       </c>
       <c r="H14" s="10" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="J14" s="9" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="K14" s="10"/>
       <c r="L14" s="10">
@@ -10239,13 +10931,13 @@
     </row>
     <row r="15" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B15" s="10" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="C15" s="6">
         <v>46160</v>
       </c>
       <c r="D15" s="10" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="E15" s="10" t="s">
         <v>9</v>
@@ -10257,31 +10949,31 @@
         <v>18000</v>
       </c>
       <c r="H15" s="10" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="J15" s="9" t="s">
-        <v>144</v>
-      </c>
-      <c r="K15" s="24">
+        <v>142</v>
+      </c>
+      <c r="K15" s="23">
         <v>1</v>
       </c>
       <c r="L15" s="10">
         <v>2</v>
       </c>
-      <c r="M15" s="24">
+      <c r="M15" s="23">
         <v>1</v>
       </c>
       <c r="N15" s="10">
         <v>1</v>
       </c>
-      <c r="O15" s="24">
+      <c r="O15" s="23">
         <v>1</v>
       </c>
       <c r="P15" s="10">
         <v>1</v>
       </c>
       <c r="Q15" s="10"/>
-      <c r="R15" s="24">
+      <c r="R15" s="23">
         <v>1</v>
       </c>
       <c r="S15" s="10"/>
@@ -10291,13 +10983,13 @@
     </row>
     <row r="16" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B16" s="10" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="C16" s="6">
         <v>46160</v>
       </c>
       <c r="D16" s="10" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="E16" s="10" t="s">
         <v>14</v>
@@ -10309,10 +11001,10 @@
         <v>3000</v>
       </c>
       <c r="H16" s="10" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="J16" s="9" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="K16" s="10"/>
       <c r="L16" s="10">
@@ -10326,7 +11018,7 @@
       <c r="P16" s="10"/>
       <c r="Q16" s="10"/>
       <c r="R16" s="10"/>
-      <c r="S16" s="24">
+      <c r="S16" s="23">
         <v>1</v>
       </c>
       <c r="T16" s="10">
@@ -10335,16 +11027,16 @@
     </row>
     <row r="17" spans="2:38" x14ac:dyDescent="0.25">
       <c r="B17" s="10" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="C17" s="6">
         <v>46160</v>
       </c>
       <c r="D17" s="10" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="E17" s="10" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="F17" s="10" t="s">
         <v>26</v>
@@ -10353,7 +11045,7 @@
         <v>18000</v>
       </c>
       <c r="H17" s="10" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="J17" s="9" t="s">
         <v>40</v>
@@ -10390,8 +11082,8 @@
       </c>
     </row>
     <row r="18" spans="2:38" x14ac:dyDescent="0.25">
-      <c r="J18" s="28" t="s">
-        <v>167</v>
+      <c r="J18" s="27" t="s">
+        <v>165</v>
       </c>
     </row>
     <row r="19" spans="2:38" ht="45" x14ac:dyDescent="0.25">
@@ -10419,42 +11111,42 @@
       <c r="AG19" s="19"/>
     </row>
     <row r="20" spans="2:38" s="19" customFormat="1" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="N20" s="33" t="s">
+      <c r="N20" s="32" t="s">
+        <v>112</v>
+      </c>
+      <c r="O20" s="32"/>
+      <c r="P20" s="26" t="s">
         <v>114</v>
       </c>
-      <c r="O20" s="33"/>
-      <c r="P20" s="27" t="s">
+      <c r="Q20" s="26"/>
+      <c r="R20" s="32" t="s">
         <v>116</v>
       </c>
-      <c r="Q20" s="27"/>
-      <c r="R20" s="33" t="s">
-        <v>118</v>
-      </c>
-      <c r="S20" s="33"/>
-      <c r="T20" s="27" t="s">
-        <v>123</v>
-      </c>
-      <c r="U20" s="27"/>
-      <c r="V20" s="33" t="s">
+      <c r="S20" s="32"/>
+      <c r="T20" s="26" t="s">
+        <v>121</v>
+      </c>
+      <c r="U20" s="26"/>
+      <c r="V20" s="32" t="s">
+        <v>145</v>
+      </c>
+      <c r="W20" s="32"/>
+      <c r="X20" s="26" t="s">
         <v>147</v>
       </c>
-      <c r="W20" s="33"/>
-      <c r="X20" s="27" t="s">
-        <v>149</v>
-      </c>
-      <c r="Y20" s="27"/>
-      <c r="Z20" s="33" t="s">
-        <v>153</v>
-      </c>
-      <c r="AA20" s="33"/>
-      <c r="AB20" s="27" t="s">
-        <v>157</v>
-      </c>
-      <c r="AC20" s="27"/>
-      <c r="AD20" s="33" t="s">
-        <v>163</v>
-      </c>
-      <c r="AE20" s="33"/>
+      <c r="Y20" s="26"/>
+      <c r="Z20" s="32" t="s">
+        <v>151</v>
+      </c>
+      <c r="AA20" s="32"/>
+      <c r="AB20" s="26" t="s">
+        <v>155</v>
+      </c>
+      <c r="AC20" s="26"/>
+      <c r="AD20" s="32" t="s">
+        <v>161</v>
+      </c>
+      <c r="AE20" s="32"/>
       <c r="AF20" s="19" t="s">
         <v>70</v>
       </c>
@@ -10469,13 +11161,13 @@
     </row>
     <row r="21" spans="2:38" s="19" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="J21" s="20" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="K21" s="19" t="s">
         <v>37</v>
       </c>
       <c r="M21" s="20" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="N21" s="19" t="s">
         <v>41</v>
@@ -10534,21 +11226,21 @@
     </row>
     <row r="22" spans="2:38" x14ac:dyDescent="0.25">
       <c r="J22" s="9" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="K22" s="10">
         <v>49000</v>
       </c>
       <c r="M22" s="9" t="s">
-        <v>139</v>
-      </c>
-      <c r="N22" s="24">
+        <v>137</v>
+      </c>
+      <c r="N22" s="23">
         <v>18000</v>
       </c>
-      <c r="O22" s="24">
+      <c r="O22" s="23">
         <v>1</v>
       </c>
-      <c r="P22" s="24">
+      <c r="P22" s="23">
         <v>3000</v>
       </c>
       <c r="Q22" s="21">
@@ -10585,21 +11277,21 @@
     </row>
     <row r="23" spans="2:38" x14ac:dyDescent="0.25">
       <c r="J23" s="9" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="K23" s="10">
         <v>88600</v>
       </c>
       <c r="M23" s="9" t="s">
-        <v>144</v>
-      </c>
-      <c r="N23" s="24">
+        <v>142</v>
+      </c>
+      <c r="N23" s="23">
         <v>25200</v>
       </c>
-      <c r="O23" s="24">
+      <c r="O23" s="23">
         <v>2</v>
       </c>
-      <c r="P23" s="24">
+      <c r="P23" s="23">
         <v>3000</v>
       </c>
       <c r="Q23" s="21">
@@ -10648,21 +11340,21 @@
     </row>
     <row r="24" spans="2:38" x14ac:dyDescent="0.25">
       <c r="J24" s="9" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="K24" s="10">
         <v>39000</v>
       </c>
       <c r="M24" s="9" t="s">
-        <v>160</v>
-      </c>
-      <c r="N24" s="24">
+        <v>158</v>
+      </c>
+      <c r="N24" s="23">
         <v>18000</v>
       </c>
-      <c r="O24" s="24">
+      <c r="O24" s="23">
         <v>1</v>
       </c>
-      <c r="P24" s="24">
+      <c r="P24" s="23">
         <v>3000</v>
       </c>
       <c r="Q24" s="21">
@@ -10765,11 +11457,11 @@
       </c>
     </row>
     <row r="26" spans="2:38" x14ac:dyDescent="0.25">
-      <c r="J26" s="25" t="s">
-        <v>168</v>
-      </c>
-      <c r="M26" s="28" t="s">
-        <v>169</v>
+      <c r="J26" s="24" t="s">
+        <v>166</v>
+      </c>
+      <c r="M26" s="27" t="s">
+        <v>167</v>
       </c>
     </row>
     <row r="28" spans="2:38" x14ac:dyDescent="0.25">

--- a/Analyses Excel/Préparation_Stage_Academique_2026_(exercices_pratique).xlsx
+++ b/Analyses Excel/Préparation_Stage_Academique_2026_(exercices_pratique).xlsx
@@ -2,13 +2,13 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27932"/>
-  <workbookPr hidePivotFieldList="1" defaultThemeVersion="202300"/>
+  <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\JevainBkg\Projets\Datascience-roadmap\Analyses Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F8C1A734-BDA7-4378-8725-97A2C2A990CE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E5BD14AF-B1A9-45BF-9624-ADE1DA15E3FC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13740" activeTab="3" xr2:uid="{7D3A7277-DCDC-4547-AB5A-331124B03413}"/>
   </bookViews>
@@ -105,7 +105,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="691" uniqueCount="210">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="703" uniqueCount="221">
   <si>
     <t>transaction_id</t>
   </si>
@@ -980,6 +980,95 @@
   </si>
   <si>
     <t>Classement agents</t>
+  </si>
+  <si>
+    <t>Question 1 : Quels clients semblent les plus fidèles ?</t>
+  </si>
+  <si>
+    <t>Fidelité  clients</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Note : </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Nos clients les plus fidèles sont c201, C202, C203; le reste de clients présente malheureusement un profil "one shot"</t>
+    </r>
+  </si>
+  <si>
+    <t>Question 2 : Quelle commune fidélise le mieux ?</t>
+  </si>
+  <si>
+    <t>Fidelisation commune</t>
+  </si>
+  <si>
+    <t>Pourcentage de fidélisation</t>
+  </si>
+  <si>
+    <t>Question 3 : Quel produit favorise le plus la récurrence ?</t>
+  </si>
+  <si>
+    <t>Fréquence produit</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">Note : </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>la majorité de nos clients opte pour le forfait mensuel Airbox de Data 10GB</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Remarque  : </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Alors, dans le souci d'améliorer notre taux de rétention ainsi que nos chiffres par la même occasion, je proposerai une campagne publicitaire bien ciblé, présentant nos autres offres tel que sms, Voice, leurs avantages ou utilités dans la vie courante, du cross-selling, ainsi qu'un petit sondage dans les zones masina, matete et ndjili histoire d'avoir un feedback du pourquoi le marché nous est capricieux dans ces dites zones Merci</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Note : </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Nous noterons également le taux de fidélisation élevé de la zone Gombe</t>
+    </r>
   </si>
 </sst>
 </file>
@@ -1177,10 +1266,11 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="9" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="61">
+  <cellXfs count="69">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1312,6 +1402,9 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
@@ -1324,11 +1417,49 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="9" fontId="2" fillId="3" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Pourcentage" xfId="1" builtinId="5"/>
   </cellStyles>
-  <dxfs count="164">
+  <dxfs count="191">
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -1341,11 +1472,13 @@
     </dxf>
     <dxf>
       <font>
-        <color rgb="FF006100"/>
+        <color theme="1"/>
       </font>
+    </dxf>
+    <dxf>
       <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
         </patternFill>
       </fill>
     </dxf>
@@ -1371,11 +1504,23 @@
     </dxf>
     <dxf>
       <font>
-        <color rgb="FF9C0006"/>
+        <color theme="1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
       </font>
       <fill>
         <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
+          <bgColor rgb="FFC6EFCE"/>
         </patternFill>
       </fill>
     </dxf>
@@ -1391,11 +1536,13 @@
     </dxf>
     <dxf>
       <font>
-        <color rgb="FF9C0006"/>
+        <color theme="1"/>
       </font>
+    </dxf>
+    <dxf>
       <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
         </patternFill>
       </fill>
     </dxf>
@@ -1411,11 +1558,21 @@
     </dxf>
     <dxf>
       <font>
-        <color rgb="FF9C0006"/>
+        <color rgb="FF006100"/>
       </font>
       <fill>
         <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
         </patternFill>
       </fill>
     </dxf>
@@ -1460,108 +1617,6 @@
       </fill>
     </dxf>
     <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="9" tint="0.39997558519241921"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="9" tint="0.39997558519241921"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="9" tint="0.39997558519241921"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="9" tint="0.39997558519241921"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <fgColor theme="9" tint="0.39997558519241921"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF4DD36D"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="9" tint="0.39997558519241921"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="9" tint="0.39997558519241921"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <fgColor theme="9" tint="0.39997558519241921"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF4DD36D"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
       <font>
         <color rgb="FF9C0006"/>
       </font>
@@ -1580,6 +1635,271 @@
           <bgColor rgb="FFFFC7CE"/>
         </patternFill>
       </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1"/>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1"/>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1"/>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="9" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1"/>
     </dxf>
     <dxf>
       <alignment wrapText="1"/>
@@ -1828,19 +2148,6 @@
     </dxf>
     <dxf>
       <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <alignment wrapText="1"/>
-    </dxf>
-    <dxf>
-      <alignment wrapText="1"/>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="9" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
     </dxf>
     <dxf>
       <alignment wrapText="1"/>
@@ -3348,7 +3655,7 @@
     <dataField name="Nombre de transaction_id" fld="0" subtotal="count" baseField="0" baseItem="0"/>
   </dataFields>
   <formats count="2">
-    <format dxfId="155">
+    <format dxfId="182">
       <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
         <references count="1">
           <reference field="6" count="1">
@@ -3357,7 +3664,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="154">
+    <format dxfId="181">
       <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
         <references count="1">
           <reference field="6" count="1">
@@ -3535,10 +3842,10 @@
     <dataField name="Somme de montant_fc" fld="6" baseField="0" baseItem="0"/>
   </dataFields>
   <formats count="6">
-    <format dxfId="105">
+    <format dxfId="132">
       <pivotArea field="2" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
     </format>
-    <format dxfId="104">
+    <format dxfId="131">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="1">
           <reference field="4294967294" count="2">
@@ -3548,7 +3855,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="103">
+    <format dxfId="130">
       <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
         <references count="1">
           <reference field="2" count="2">
@@ -3558,7 +3865,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="102">
+    <format dxfId="129">
       <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
         <references count="1">
           <reference field="2" count="2">
@@ -3568,7 +3875,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="101">
+    <format dxfId="128">
       <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
         <references count="1">
           <reference field="2" count="2">
@@ -3578,7 +3885,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="31">
+    <format dxfId="61">
       <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
         <references count="1">
           <reference field="2" count="0"/>
@@ -3775,10 +4082,10 @@
     <dataField name="Somme de montant_fc" fld="5" baseField="0" baseItem="0"/>
   </dataFields>
   <formats count="2">
-    <format dxfId="87">
+    <format dxfId="117">
       <pivotArea field="2" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
     </format>
-    <format dxfId="86">
+    <format dxfId="116">
       <pivotArea dataOnly="0" labelOnly="1" grandCol="1" outline="0" fieldPosition="0"/>
     </format>
   </formats>
@@ -3796,7 +4103,7 @@
 
 <file path=xl/pivotTables/pivotTable13.xml><?xml version="1.0" encoding="utf-8"?>
 <pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{6CF2CD07-335D-47F6-B7D4-64AD9F8422C1}" name="Tableau croisé dynamique34" cacheId="3" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valeurs" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
-  <location ref="H20:I25" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+  <location ref="B56:C61" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="6">
     <pivotField dataField="1" showAll="0">
       <items count="16">
@@ -3859,13 +4166,13 @@
     <dataField name="Nombre de transaction_id" fld="0" subtotal="count" baseField="0" baseItem="0"/>
   </dataFields>
   <formats count="3">
-    <format dxfId="90">
+    <format dxfId="119">
       <pivotArea field="4" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
     </format>
-    <format dxfId="89">
+    <format dxfId="118">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
     </format>
-    <format dxfId="88">
+    <format dxfId="37">
       <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
         <references count="1">
           <reference field="4" count="1">
@@ -3875,6 +4182,64 @@
       </pivotArea>
     </format>
   </formats>
+  <conditionalFormats count="4">
+    <conditionalFormat priority="12">
+      <pivotAreas count="1">
+        <pivotArea type="data" collapsedLevelsAreSubtotals="1" fieldPosition="0">
+          <references count="2">
+            <reference field="4294967294" count="1" selected="0">
+              <x v="0"/>
+            </reference>
+            <reference field="4" count="1">
+              <x v="0"/>
+            </reference>
+          </references>
+        </pivotArea>
+      </pivotAreas>
+    </conditionalFormat>
+    <conditionalFormat priority="11">
+      <pivotAreas count="1">
+        <pivotArea type="data" collapsedLevelsAreSubtotals="1" fieldPosition="0">
+          <references count="2">
+            <reference field="4294967294" count="1" selected="0">
+              <x v="0"/>
+            </reference>
+            <reference field="4" count="1">
+              <x v="0"/>
+            </reference>
+          </references>
+        </pivotArea>
+      </pivotAreas>
+    </conditionalFormat>
+    <conditionalFormat priority="10">
+      <pivotAreas count="1">
+        <pivotArea type="data" collapsedLevelsAreSubtotals="1" fieldPosition="0">
+          <references count="2">
+            <reference field="4294967294" count="1" selected="0">
+              <x v="0"/>
+            </reference>
+            <reference field="4" count="1">
+              <x v="0"/>
+            </reference>
+          </references>
+        </pivotArea>
+      </pivotAreas>
+    </conditionalFormat>
+    <conditionalFormat priority="9">
+      <pivotAreas count="1">
+        <pivotArea type="data" collapsedLevelsAreSubtotals="1" fieldPosition="0">
+          <references count="2">
+            <reference field="4294967294" count="1" selected="0">
+              <x v="0"/>
+            </reference>
+            <reference field="4" count="1">
+              <x v="0"/>
+            </reference>
+          </references>
+        </pivotArea>
+      </pivotAreas>
+    </conditionalFormat>
+  </conditionalFormats>
   <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
@@ -3889,7 +4254,7 @@
 
 <file path=xl/pivotTables/pivotTable14.xml><?xml version="1.0" encoding="utf-8"?>
 <pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{12A32755-1450-4078-8441-200639987E8B}" name="Tableau croisé dynamique33" cacheId="3" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valeurs" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
-  <location ref="E20:F26" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+  <location ref="B41:C47" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="6">
     <pivotField dataField="1" showAll="0">
       <items count="16">
@@ -3955,16 +4320,25 @@
   <dataFields count="1">
     <dataField name="Nombre de transaction_id" fld="0" subtotal="count" baseField="0" baseItem="0"/>
   </dataFields>
-  <formats count="2">
-    <format dxfId="92">
+  <formats count="3">
+    <format dxfId="121">
       <pivotArea field="3" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
     </format>
-    <format dxfId="91">
+    <format dxfId="120">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
     </format>
+    <format dxfId="53">
+      <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
+        <references count="1">
+          <reference field="3" count="1">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
   </formats>
-  <conditionalFormats count="2">
-    <conditionalFormat priority="4">
+  <conditionalFormats count="4">
+    <conditionalFormat priority="20">
       <pivotAreas count="1">
         <pivotArea type="data" collapsedLevelsAreSubtotals="1" fieldPosition="0">
           <references count="2">
@@ -3982,7 +4356,7 @@
         </pivotArea>
       </pivotAreas>
     </conditionalFormat>
-    <conditionalFormat priority="3">
+    <conditionalFormat priority="19">
       <pivotAreas count="1">
         <pivotArea type="data" collapsedLevelsAreSubtotals="1" fieldPosition="0">
           <references count="2">
@@ -3995,6 +4369,34 @@
               <x v="2"/>
               <x v="3"/>
               <x v="4"/>
+            </reference>
+          </references>
+        </pivotArea>
+      </pivotAreas>
+    </conditionalFormat>
+    <conditionalFormat priority="14">
+      <pivotAreas count="1">
+        <pivotArea type="data" collapsedLevelsAreSubtotals="1" fieldPosition="0">
+          <references count="2">
+            <reference field="4294967294" count="1" selected="0">
+              <x v="0"/>
+            </reference>
+            <reference field="3" count="1">
+              <x v="0"/>
+            </reference>
+          </references>
+        </pivotArea>
+      </pivotAreas>
+    </conditionalFormat>
+    <conditionalFormat priority="13">
+      <pivotAreas count="1">
+        <pivotArea type="data" collapsedLevelsAreSubtotals="1" fieldPosition="0">
+          <references count="2">
+            <reference field="4294967294" count="1" selected="0">
+              <x v="0"/>
+            </reference>
+            <reference field="3" count="1">
+              <x v="0"/>
             </reference>
           </references>
         </pivotArea>
@@ -4015,7 +4417,7 @@
 
 <file path=xl/pivotTables/pivotTable15.xml><?xml version="1.0" encoding="utf-8"?>
 <pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{FFBC07AA-ACC0-49E5-BC9B-2B10D6352CD6}" name="Tableau croisé dynamique32" cacheId="3" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valeurs" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
-  <location ref="B20:C29" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+  <location ref="B23:C32" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="6">
     <pivotField dataField="1" showAll="0">
       <items count="16">
@@ -4101,12 +4503,25 @@
   <dataFields count="1">
     <dataField name="Nombre de transaction_id" fld="0" subtotal="count" baseField="0" baseItem="0"/>
   </dataFields>
-  <formats count="2">
-    <format dxfId="94">
+  <formats count="3">
+    <format dxfId="54">
       <pivotArea field="2" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
     </format>
-    <format dxfId="93">
+    <format dxfId="55">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
+    </format>
+    <format dxfId="56">
+      <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
+        <references count="1">
+          <reference field="2" count="5">
+            <x v="3"/>
+            <x v="4"/>
+            <x v="5"/>
+            <x v="6"/>
+            <x v="7"/>
+          </reference>
+        </references>
+      </pivotArea>
     </format>
   </formats>
   <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
@@ -4222,7 +4637,7 @@
     <dataField name="Nombre de transaction_id" fld="0" subtotal="count" baseField="0" baseItem="0"/>
   </dataFields>
   <formats count="8">
-    <format dxfId="47">
+    <format dxfId="77">
       <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
         <references count="2">
           <reference field="3" count="1" selected="0">
@@ -4234,7 +4649,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="46">
+    <format dxfId="76">
       <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
         <references count="2">
           <reference field="3" count="1" selected="0">
@@ -4246,7 +4661,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="45">
+    <format dxfId="75">
       <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
         <references count="2">
           <reference field="3" count="1" selected="0">
@@ -4258,7 +4673,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="44">
+    <format dxfId="74">
       <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
         <references count="2">
           <reference field="3" count="1" selected="0">
@@ -4270,20 +4685,20 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="43">
+    <format dxfId="73">
       <pivotArea field="6" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
     </format>
-    <format dxfId="42">
+    <format dxfId="72">
       <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
         <references count="1">
           <reference field="3" count="0"/>
         </references>
       </pivotArea>
     </format>
-    <format dxfId="41">
+    <format dxfId="71">
       <pivotArea dataOnly="0" labelOnly="1" grandCol="1" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="40">
+    <format dxfId="70">
       <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
         <references count="2">
           <reference field="3" count="1" selected="0">
@@ -4396,7 +4811,7 @@
     <dataField name="Nombre de transaction_id" fld="0" subtotal="count" baseField="0" baseItem="0"/>
   </dataFields>
   <formats count="6">
-    <format dxfId="53">
+    <format dxfId="83">
       <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
         <references count="2">
           <reference field="2" count="4" selected="0">
@@ -4411,7 +4826,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="52">
+    <format dxfId="82">
       <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
         <references count="2">
           <reference field="2" count="1" selected="0">
@@ -4423,7 +4838,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="51">
+    <format dxfId="81">
       <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
         <references count="2">
           <reference field="2" count="1" selected="0">
@@ -4435,13 +4850,13 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="50">
+    <format dxfId="80">
       <pivotArea type="origin" dataOnly="0" labelOnly="1" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="49">
+    <format dxfId="79">
       <pivotArea field="2" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisCol" fieldPosition="0"/>
     </format>
-    <format dxfId="48">
+    <format dxfId="78">
       <pivotArea type="topRight" dataOnly="0" labelOnly="1" outline="0" fieldPosition="0"/>
     </format>
   </formats>
@@ -4618,29 +5033,29 @@
     <dataField name="Nombre de transaction_id" fld="0" subtotal="count" baseField="0" baseItem="0"/>
   </dataFields>
   <formats count="24">
-    <format dxfId="77">
+    <format dxfId="107">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
     </format>
-    <format dxfId="76">
+    <format dxfId="106">
       <pivotArea type="origin" dataOnly="0" labelOnly="1" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="75">
+    <format dxfId="105">
       <pivotArea field="2" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisCol" fieldPosition="0"/>
     </format>
-    <format dxfId="74">
+    <format dxfId="104">
       <pivotArea type="topRight" dataOnly="0" labelOnly="1" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="73">
+    <format dxfId="103">
       <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
         <references count="1">
           <reference field="6" count="0"/>
         </references>
       </pivotArea>
     </format>
-    <format dxfId="72">
+    <format dxfId="102">
       <pivotArea field="6" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
     </format>
-    <format dxfId="71">
+    <format dxfId="101">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="2">
           <reference field="4294967294" count="2">
@@ -4653,7 +5068,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="70">
+    <format dxfId="100">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="2">
           <reference field="4294967294" count="2">
@@ -4666,7 +5081,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="69">
+    <format dxfId="99">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="2">
           <reference field="4294967294" count="2">
@@ -4679,7 +5094,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="68">
+    <format dxfId="98">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="2">
           <reference field="4294967294" count="2">
@@ -4692,7 +5107,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="67">
+    <format dxfId="97">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="2">
           <reference field="4294967294" count="2">
@@ -4705,7 +5120,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="66">
+    <format dxfId="96">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="2">
           <reference field="4294967294" count="2">
@@ -4718,7 +5133,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="65">
+    <format dxfId="95">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="2">
           <reference field="4294967294" count="2">
@@ -4731,7 +5146,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="64">
+    <format dxfId="94">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="2">
           <reference field="4294967294" count="2">
@@ -4744,7 +5159,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="63">
+    <format dxfId="93">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="2">
           <reference field="4294967294" count="2">
@@ -4757,7 +5172,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="62">
+    <format dxfId="92">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="2">
           <reference field="4294967294" count="1">
@@ -4769,7 +5184,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="61">
+    <format dxfId="91">
       <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
         <references count="1">
           <reference field="2" count="1">
@@ -4778,7 +5193,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="60">
+    <format dxfId="90">
       <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
         <references count="1">
           <reference field="2" count="1">
@@ -4787,7 +5202,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="59">
+    <format dxfId="89">
       <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
         <references count="1">
           <reference field="2" count="7">
@@ -4802,7 +5217,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="58">
+    <format dxfId="88">
       <pivotArea field="2" dataOnly="0" labelOnly="1" grandCol="1" outline="0" axis="axisCol" fieldPosition="0">
         <references count="1">
           <reference field="4294967294" count="1" selected="0">
@@ -4811,7 +5226,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="57">
+    <format dxfId="87">
       <pivotArea field="2" dataOnly="0" labelOnly="1" grandCol="1" outline="0" axis="axisCol" fieldPosition="0">
         <references count="1">
           <reference field="4294967294" count="1" selected="0">
@@ -4820,7 +5235,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="56">
+    <format dxfId="86">
       <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
         <references count="3">
           <reference field="4294967294" count="1" selected="0">
@@ -4833,7 +5248,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="55">
+    <format dxfId="85">
       <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
         <references count="3">
           <reference field="4294967294" count="1" selected="0">
@@ -4846,7 +5261,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="54">
+    <format dxfId="84">
       <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
         <references count="3">
           <reference field="4294967294" count="1" selected="0">
@@ -4941,10 +5356,10 @@
     <dataField name="CA" fld="5" baseField="6" baseItem="0"/>
   </dataFields>
   <formats count="2">
-    <format dxfId="79">
+    <format dxfId="109">
       <pivotArea field="6" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
     </format>
-    <format dxfId="78">
+    <format dxfId="108">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
     </format>
   </formats>
@@ -5034,7 +5449,7 @@
     <dataField name="Chiffre d'affaire" fld="5" baseField="0" baseItem="0"/>
   </dataFields>
   <formats count="2">
-    <format dxfId="157">
+    <format dxfId="184">
       <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
         <references count="1">
           <reference field="4" count="1">
@@ -5043,7 +5458,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="156">
+    <format dxfId="183">
       <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
         <references count="1">
           <reference field="4" count="1">
@@ -5166,7 +5581,7 @@
     <dataField name="Chiffre d'affaire" fld="5" baseField="0" baseItem="0"/>
   </dataFields>
   <formats count="6">
-    <format dxfId="163">
+    <format dxfId="190">
       <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
         <references count="1">
           <reference field="3" count="1">
@@ -5175,7 +5590,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="162">
+    <format dxfId="189">
       <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
         <references count="1">
           <reference field="3" count="1">
@@ -5184,7 +5599,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="161">
+    <format dxfId="188">
       <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
         <references count="1">
           <reference field="3" count="1">
@@ -5193,7 +5608,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="160">
+    <format dxfId="187">
       <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
         <references count="1">
           <reference field="3" count="1">
@@ -5202,7 +5617,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="159">
+    <format dxfId="186">
       <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
         <references count="1">
           <reference field="3" count="1">
@@ -5211,7 +5626,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="158">
+    <format dxfId="185">
       <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
         <references count="1">
           <reference field="3" count="1">
@@ -5419,10 +5834,10 @@
     <dataField name="Somme de montant_fc" fld="5" baseField="0" baseItem="0"/>
   </dataFields>
   <formats count="2">
-    <format dxfId="113">
+    <format dxfId="140">
       <pivotArea field="2" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
     </format>
-    <format dxfId="112">
+    <format dxfId="139">
       <pivotArea dataOnly="0" labelOnly="1" grandCol="1" outline="0" fieldPosition="0"/>
     </format>
   </formats>
@@ -5645,7 +6060,7 @@
     <dataField name="Somme de montant_fc" fld="5" baseField="0" baseItem="0"/>
   </dataFields>
   <formats count="28">
-    <format dxfId="141">
+    <format dxfId="168">
       <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
         <references count="2">
           <reference field="1" count="2">
@@ -5658,10 +6073,10 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="140">
+    <format dxfId="167">
       <pivotArea field="1" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
     </format>
-    <format dxfId="139">
+    <format dxfId="166">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="2">
           <reference field="4294967294" count="2">
@@ -5674,7 +6089,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="138">
+    <format dxfId="165">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="2">
           <reference field="4294967294" count="2">
@@ -5687,7 +6102,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="137">
+    <format dxfId="164">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="2">
           <reference field="4294967294" count="2">
@@ -5700,7 +6115,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="136">
+    <format dxfId="163">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="2">
           <reference field="4294967294" count="2">
@@ -5713,7 +6128,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="135">
+    <format dxfId="162">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="2">
           <reference field="4294967294" count="2">
@@ -5726,7 +6141,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="134">
+    <format dxfId="161">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="2">
           <reference field="4294967294" count="2">
@@ -5739,7 +6154,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="133">
+    <format dxfId="160">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="2">
           <reference field="4294967294" count="2">
@@ -5752,7 +6167,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="132">
+    <format dxfId="159">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="2">
           <reference field="4294967294" count="2">
@@ -5765,7 +6180,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="131">
+    <format dxfId="158">
       <pivotArea field="2" dataOnly="0" labelOnly="1" grandCol="1" outline="0" axis="axisCol" fieldPosition="0">
         <references count="1">
           <reference field="4294967294" count="1" selected="0">
@@ -5774,7 +6189,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="130">
+    <format dxfId="157">
       <pivotArea field="2" dataOnly="0" labelOnly="1" grandCol="1" outline="0" axis="axisCol" fieldPosition="0">
         <references count="1">
           <reference field="4294967294" count="1" selected="0">
@@ -5783,10 +6198,10 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="129">
+    <format dxfId="156">
       <pivotArea field="2" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisCol" fieldPosition="0"/>
     </format>
-    <format dxfId="128">
+    <format dxfId="155">
       <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
         <references count="3">
           <reference field="4294967294" count="2" selected="0">
@@ -5803,7 +6218,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="127">
+    <format dxfId="154">
       <pivotArea dataOnly="0" labelOnly="1" offset="A256" fieldPosition="0">
         <references count="1">
           <reference field="2" count="1">
@@ -5812,7 +6227,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="126">
+    <format dxfId="153">
       <pivotArea dataOnly="0" labelOnly="1" offset="IV256" fieldPosition="0">
         <references count="1">
           <reference field="2" count="1">
@@ -5821,7 +6236,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="125">
+    <format dxfId="152">
       <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
         <references count="1">
           <reference field="2" count="1">
@@ -5830,7 +6245,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="124">
+    <format dxfId="151">
       <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
         <references count="1">
           <reference field="2" count="1">
@@ -5839,7 +6254,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="123">
+    <format dxfId="150">
       <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
         <references count="1">
           <reference field="2" count="1">
@@ -5848,7 +6263,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="122">
+    <format dxfId="149">
       <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
         <references count="1">
           <reference field="2" count="1">
@@ -5857,7 +6272,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="121">
+    <format dxfId="148">
       <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
         <references count="1">
           <reference field="2" count="1">
@@ -5866,7 +6281,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="120">
+    <format dxfId="147">
       <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
         <references count="1">
           <reference field="2" count="1">
@@ -5875,7 +6290,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="119">
+    <format dxfId="146">
       <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
         <references count="1">
           <reference field="2" count="1">
@@ -5884,7 +6299,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="118">
+    <format dxfId="145">
       <pivotArea field="2" grandRow="1" outline="0" collapsedLevelsAreSubtotals="1" axis="axisCol" fieldPosition="0">
         <references count="2">
           <reference field="4294967294" count="1" selected="0">
@@ -5894,7 +6309,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="117">
+    <format dxfId="144">
       <pivotArea field="2" grandRow="1" outline="0" collapsedLevelsAreSubtotals="1" axis="axisCol" fieldPosition="0">
         <references count="2">
           <reference field="4294967294" count="1" selected="0">
@@ -5904,7 +6319,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="116">
+    <format dxfId="143">
       <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
         <references count="3">
           <reference field="4294967294" count="2" selected="0">
@@ -5918,7 +6333,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="115">
+    <format dxfId="142">
       <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
         <references count="3">
           <reference field="4294967294" count="1" selected="0">
@@ -5931,7 +6346,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="114">
+    <format dxfId="141">
       <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
         <references count="3">
           <reference field="4294967294" count="1" selected="0">
@@ -6098,17 +6513,17 @@
     <dataField name="Canal preferé par client" fld="0" subtotal="count" baseField="0" baseItem="0"/>
   </dataFields>
   <formats count="3">
-    <format dxfId="144">
+    <format dxfId="171">
       <pivotArea field="2" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
     </format>
-    <format dxfId="143">
+    <format dxfId="170">
       <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
         <references count="1">
           <reference field="6" count="0"/>
         </references>
       </pivotArea>
     </format>
-    <format dxfId="142">
+    <format dxfId="169">
       <pivotArea dataOnly="0" labelOnly="1" grandCol="1" outline="0" fieldPosition="0"/>
     </format>
   </formats>
@@ -6193,10 +6608,10 @@
     <dataField name="Somme de montant_fc" fld="6" baseField="0" baseItem="0"/>
   </dataFields>
   <formats count="2">
-    <format dxfId="29">
+    <format dxfId="59">
       <pivotArea field="4" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
     </format>
-    <format dxfId="30">
+    <format dxfId="60">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="1">
           <reference field="4294967294" count="2">
@@ -6345,16 +6760,16 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{6EC83A65-D9A6-475F-8D16-1CE811FFF2E9}" name="Tableau1" displayName="Tableau1" ref="B3:H13" totalsRowShown="0" headerRowDxfId="153" dataDxfId="152">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{6EC83A65-D9A6-475F-8D16-1CE811FFF2E9}" name="Tableau1" displayName="Tableau1" ref="B3:H13" totalsRowShown="0" headerRowDxfId="180" dataDxfId="179">
   <autoFilter ref="B3:H13" xr:uid="{6EC83A65-D9A6-475F-8D16-1CE811FFF2E9}"/>
   <tableColumns count="7">
-    <tableColumn id="1" xr3:uid="{54537CD7-847D-4C04-9BD6-B993FB8C0924}" name="transaction_id" dataDxfId="151"/>
-    <tableColumn id="2" xr3:uid="{7DFAA592-DC98-463C-A6AF-A94A0F915646}" name="date" dataDxfId="150"/>
-    <tableColumn id="3" xr3:uid="{122DF7BD-714F-4B55-830F-7573F364E80A}" name="client_id" dataDxfId="149"/>
-    <tableColumn id="4" xr3:uid="{1B94713D-DD23-416E-B23B-98EF629AFCBE}" name="commune" dataDxfId="148"/>
-    <tableColumn id="5" xr3:uid="{084E48D7-3EDD-4FC4-B38B-BD3872EDFF23}" name="produit" dataDxfId="147"/>
-    <tableColumn id="6" xr3:uid="{D1BF92F6-B520-4D49-B97E-C1395DDE5A98}" name="montant_fc" dataDxfId="146"/>
-    <tableColumn id="7" xr3:uid="{21C18558-D71D-47B7-B0D0-001594508953}" name="canal" dataDxfId="145"/>
+    <tableColumn id="1" xr3:uid="{54537CD7-847D-4C04-9BD6-B993FB8C0924}" name="transaction_id" dataDxfId="178"/>
+    <tableColumn id="2" xr3:uid="{7DFAA592-DC98-463C-A6AF-A94A0F915646}" name="date" dataDxfId="177"/>
+    <tableColumn id="3" xr3:uid="{122DF7BD-714F-4B55-830F-7573F364E80A}" name="client_id" dataDxfId="176"/>
+    <tableColumn id="4" xr3:uid="{1B94713D-DD23-416E-B23B-98EF629AFCBE}" name="commune" dataDxfId="175"/>
+    <tableColumn id="5" xr3:uid="{084E48D7-3EDD-4FC4-B38B-BD3872EDFF23}" name="produit" dataDxfId="174"/>
+    <tableColumn id="6" xr3:uid="{D1BF92F6-B520-4D49-B97E-C1395DDE5A98}" name="montant_fc" dataDxfId="173"/>
+    <tableColumn id="7" xr3:uid="{21C18558-D71D-47B7-B0D0-001594508953}" name="canal" dataDxfId="172"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -6364,13 +6779,13 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{5B43BC6D-66A6-432F-982F-C406FA282078}" name="Dataset_day2__2" displayName="Dataset_day2__2" ref="B2:H17" tableType="queryTable" totalsRowShown="0">
   <autoFilter ref="B2:H17" xr:uid="{5B43BC6D-66A6-432F-982F-C406FA282078}"/>
   <tableColumns count="7">
-    <tableColumn id="1" xr3:uid="{F0363F15-00D8-44D9-B9E8-73E1201A36E6}" uniqueName="1" name="transaction_id" queryTableFieldId="1" dataDxfId="111"/>
-    <tableColumn id="2" xr3:uid="{85F76B94-3323-41EB-B99E-F9DE7DD9EF5D}" uniqueName="2" name="date" queryTableFieldId="2" dataDxfId="110"/>
-    <tableColumn id="3" xr3:uid="{90258075-E8BA-4181-AEBF-14DCE9CF1AC4}" uniqueName="3" name="client_id" queryTableFieldId="3" dataDxfId="109"/>
-    <tableColumn id="4" xr3:uid="{3B088930-C813-470C-9790-11DA318C42A1}" uniqueName="4" name="commune" queryTableFieldId="4" dataDxfId="108"/>
-    <tableColumn id="5" xr3:uid="{E074DF00-E0E7-41D6-B91A-ABE22CB1881A}" uniqueName="5" name="produit" queryTableFieldId="5" dataDxfId="107"/>
+    <tableColumn id="1" xr3:uid="{F0363F15-00D8-44D9-B9E8-73E1201A36E6}" uniqueName="1" name="transaction_id" queryTableFieldId="1" dataDxfId="138"/>
+    <tableColumn id="2" xr3:uid="{85F76B94-3323-41EB-B99E-F9DE7DD9EF5D}" uniqueName="2" name="date" queryTableFieldId="2" dataDxfId="137"/>
+    <tableColumn id="3" xr3:uid="{90258075-E8BA-4181-AEBF-14DCE9CF1AC4}" uniqueName="3" name="client_id" queryTableFieldId="3" dataDxfId="136"/>
+    <tableColumn id="4" xr3:uid="{3B088930-C813-470C-9790-11DA318C42A1}" uniqueName="4" name="commune" queryTableFieldId="4" dataDxfId="135"/>
+    <tableColumn id="5" xr3:uid="{E074DF00-E0E7-41D6-B91A-ABE22CB1881A}" uniqueName="5" name="produit" queryTableFieldId="5" dataDxfId="134"/>
     <tableColumn id="6" xr3:uid="{7C01ABE9-F9C0-40F6-9F95-D610FB820086}" uniqueName="6" name="montant_fc" queryTableFieldId="6"/>
-    <tableColumn id="7" xr3:uid="{30F6D1BA-4065-4D54-BF94-1BE05C99AC63}" uniqueName="7" name="canal" queryTableFieldId="7" dataDxfId="106"/>
+    <tableColumn id="7" xr3:uid="{30F6D1BA-4065-4D54-BF94-1BE05C99AC63}" uniqueName="7" name="canal" queryTableFieldId="7" dataDxfId="133"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -6380,12 +6795,12 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{A4A0DCA2-C1C4-44D4-AD45-BDA248A44995}" name="Dataset_day3" displayName="Dataset_day3" ref="B2:H17" tableType="queryTable" totalsRowShown="0">
   <autoFilter ref="B2:H17" xr:uid="{A4A0DCA2-C1C4-44D4-AD45-BDA248A44995}"/>
   <tableColumns count="7">
-    <tableColumn id="1" xr3:uid="{A0067E32-0369-4D8A-BDF1-C8B907B86BD0}" uniqueName="1" name="transaction_id" queryTableFieldId="1" dataDxfId="100"/>
-    <tableColumn id="2" xr3:uid="{C68FAFFA-BEA0-4F94-BA99-6450F477971E}" uniqueName="2" name="date" queryTableFieldId="2" dataDxfId="99"/>
-    <tableColumn id="3" xr3:uid="{CDF65428-BE02-471D-A8F7-90F1D8454251}" uniqueName="3" name="agent_id" queryTableFieldId="3" dataDxfId="98"/>
-    <tableColumn id="4" xr3:uid="{22F84FAA-57F1-425F-B37C-F8428C49E033}" uniqueName="4" name="client_id" queryTableFieldId="4" dataDxfId="97"/>
-    <tableColumn id="5" xr3:uid="{93A8CFD1-D585-478D-9AFB-02301838500E}" uniqueName="5" name="commune" queryTableFieldId="5" dataDxfId="96"/>
-    <tableColumn id="6" xr3:uid="{956E7CEA-E833-4F96-9E51-2D67194B8C61}" uniqueName="6" name="produit" queryTableFieldId="6" dataDxfId="95"/>
+    <tableColumn id="1" xr3:uid="{A0067E32-0369-4D8A-BDF1-C8B907B86BD0}" uniqueName="1" name="transaction_id" queryTableFieldId="1" dataDxfId="127"/>
+    <tableColumn id="2" xr3:uid="{C68FAFFA-BEA0-4F94-BA99-6450F477971E}" uniqueName="2" name="date" queryTableFieldId="2" dataDxfId="126"/>
+    <tableColumn id="3" xr3:uid="{CDF65428-BE02-471D-A8F7-90F1D8454251}" uniqueName="3" name="agent_id" queryTableFieldId="3" dataDxfId="125"/>
+    <tableColumn id="4" xr3:uid="{22F84FAA-57F1-425F-B37C-F8428C49E033}" uniqueName="4" name="client_id" queryTableFieldId="4" dataDxfId="124"/>
+    <tableColumn id="5" xr3:uid="{93A8CFD1-D585-478D-9AFB-02301838500E}" uniqueName="5" name="commune" queryTableFieldId="5" dataDxfId="123"/>
+    <tableColumn id="6" xr3:uid="{956E7CEA-E833-4F96-9E51-2D67194B8C61}" uniqueName="6" name="produit" queryTableFieldId="6" dataDxfId="122"/>
     <tableColumn id="7" xr3:uid="{E636C8A0-3C3C-48BE-AFE5-1B3DB129CA7E}" uniqueName="7" name="montant_fc" queryTableFieldId="7"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
@@ -6396,11 +6811,11 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{AB24B926-8F3E-4EE6-9138-D47BB2378B02}" name="Dataset_day4" displayName="Dataset_day4" ref="B2:G17" totalsRowShown="0">
   <autoFilter ref="B2:G17" xr:uid="{AB24B926-8F3E-4EE6-9138-D47BB2378B02}"/>
   <tableColumns count="6">
-    <tableColumn id="1" xr3:uid="{2FA77349-5B7D-430C-A299-CA8EF8B94F8F}" name="transaction_id" dataDxfId="85"/>
-    <tableColumn id="2" xr3:uid="{EA88A0A8-EDC4-468E-80F4-EF0578FE9A03}" name="date" dataDxfId="84"/>
-    <tableColumn id="3" xr3:uid="{811F8411-B146-492E-A697-2D905854F94D}" name="client_id" dataDxfId="83"/>
-    <tableColumn id="4" xr3:uid="{7B37CE19-01A8-4470-8A2B-849B751FB37D}" name="commune" dataDxfId="82"/>
-    <tableColumn id="5" xr3:uid="{863A1A63-AC11-4715-82E2-F6EC444E5B51}" name="produit" dataDxfId="81"/>
+    <tableColumn id="1" xr3:uid="{2FA77349-5B7D-430C-A299-CA8EF8B94F8F}" name="transaction_id" dataDxfId="115"/>
+    <tableColumn id="2" xr3:uid="{EA88A0A8-EDC4-468E-80F4-EF0578FE9A03}" name="date" dataDxfId="114"/>
+    <tableColumn id="3" xr3:uid="{811F8411-B146-492E-A697-2D905854F94D}" name="client_id" dataDxfId="113"/>
+    <tableColumn id="4" xr3:uid="{7B37CE19-01A8-4470-8A2B-849B751FB37D}" name="commune" dataDxfId="112"/>
+    <tableColumn id="5" xr3:uid="{863A1A63-AC11-4715-82E2-F6EC444E5B51}" name="produit" dataDxfId="111"/>
     <tableColumn id="6" xr3:uid="{DDFB738A-4C05-4F97-882D-16FE65EF8A7E}" name="montant_fc"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
@@ -6408,7 +6823,7 @@
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="9" xr:uid="{B1C5B688-9C67-4CAD-9DAE-7207D5E5E850}" name="Tableau9" displayName="Tableau9" ref="AA3:AA11" totalsRowShown="0" headerRowDxfId="80">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="9" xr:uid="{B1C5B688-9C67-4CAD-9DAE-7207D5E5E850}" name="Tableau9" displayName="Tableau9" ref="AA3:AA11" totalsRowShown="0" headerRowDxfId="110">
   <autoFilter ref="AA3:AA11" xr:uid="{B1C5B688-9C67-4CAD-9DAE-7207D5E5E850}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="AA4:AA11">
     <sortCondition ref="AA3:AA11"/>
@@ -6423,16 +6838,16 @@
 </file>
 
 <file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="10" xr:uid="{C4A92EC0-501A-4751-9A16-2163E0BD39EA}" name="Dataset_day5" displayName="Dataset_day5" ref="B2:H17" tableType="queryTable" totalsRowShown="0" headerRowDxfId="39">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="10" xr:uid="{C4A92EC0-501A-4751-9A16-2163E0BD39EA}" name="Dataset_day5" displayName="Dataset_day5" ref="B2:H17" tableType="queryTable" totalsRowShown="0" headerRowDxfId="69">
   <autoFilter ref="B2:H17" xr:uid="{C4A92EC0-501A-4751-9A16-2163E0BD39EA}"/>
   <tableColumns count="7">
-    <tableColumn id="1" xr3:uid="{FBC21564-1B48-423F-AFDB-04B5AE20CF75}" uniqueName="1" name="transaction_id" queryTableFieldId="1" dataDxfId="38"/>
-    <tableColumn id="2" xr3:uid="{CA4A50D7-5720-4F71-ACD1-3781681C0231}" uniqueName="2" name="date" queryTableFieldId="2" dataDxfId="37"/>
-    <tableColumn id="3" xr3:uid="{A265E5F8-50A6-4DD3-8C5E-10BB05E3F126}" uniqueName="3" name="client_id" queryTableFieldId="3" dataDxfId="36"/>
-    <tableColumn id="4" xr3:uid="{0E595B89-2727-474B-B4A6-66BC0AC0864A}" uniqueName="4" name="commune" queryTableFieldId="4" dataDxfId="35"/>
-    <tableColumn id="5" xr3:uid="{4D992877-9744-466D-982E-E1F06CDEF762}" uniqueName="5" name="produit" queryTableFieldId="5" dataDxfId="34"/>
+    <tableColumn id="1" xr3:uid="{FBC21564-1B48-423F-AFDB-04B5AE20CF75}" uniqueName="1" name="transaction_id" queryTableFieldId="1" dataDxfId="68"/>
+    <tableColumn id="2" xr3:uid="{CA4A50D7-5720-4F71-ACD1-3781681C0231}" uniqueName="2" name="date" queryTableFieldId="2" dataDxfId="67"/>
+    <tableColumn id="3" xr3:uid="{A265E5F8-50A6-4DD3-8C5E-10BB05E3F126}" uniqueName="3" name="client_id" queryTableFieldId="3" dataDxfId="66"/>
+    <tableColumn id="4" xr3:uid="{0E595B89-2727-474B-B4A6-66BC0AC0864A}" uniqueName="4" name="commune" queryTableFieldId="4" dataDxfId="65"/>
+    <tableColumn id="5" xr3:uid="{4D992877-9744-466D-982E-E1F06CDEF762}" uniqueName="5" name="produit" queryTableFieldId="5" dataDxfId="64"/>
     <tableColumn id="6" xr3:uid="{D10FAE6E-7969-4551-94AB-82C2D27DFD50}" uniqueName="6" name="montant_fc" queryTableFieldId="6"/>
-    <tableColumn id="7" xr3:uid="{7306D68B-3C9A-40F7-A0D9-E00CC8C73541}" uniqueName="7" name="periode" queryTableFieldId="7" dataDxfId="33"/>
+    <tableColumn id="7" xr3:uid="{7306D68B-3C9A-40F7-A0D9-E00CC8C73541}" uniqueName="7" name="periode" queryTableFieldId="7" dataDxfId="63"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -6443,7 +6858,7 @@
   <autoFilter ref="A1:G6" xr:uid="{68E59C74-D329-4B48-A967-CC868365949C}"/>
   <tableColumns count="7">
     <tableColumn id="1" xr3:uid="{C102BD58-3DF8-48B7-9114-2067608D3DB4}" name="transaction_id"/>
-    <tableColumn id="2" xr3:uid="{998F6E83-476D-414D-8353-8E6146354739}" name="date" dataDxfId="32"/>
+    <tableColumn id="2" xr3:uid="{998F6E83-476D-414D-8353-8E6146354739}" name="date" dataDxfId="62"/>
     <tableColumn id="3" xr3:uid="{1ACC5CD9-2A0F-4DB2-B7B7-A25781DA1795}" name="agent_id"/>
     <tableColumn id="4" xr3:uid="{D4B111D2-01DE-4AFC-91B0-641E23172B8C}" name="client_id"/>
     <tableColumn id="5" xr3:uid="{C0E2906A-2633-4FB3-89D8-883ADDF86D4F}" name="commune"/>
@@ -7163,24 +7578,24 @@
       </c>
     </row>
     <row r="26" spans="2:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B26" s="59" t="s">
+      <c r="B26" s="60" t="s">
         <v>205</v>
       </c>
-      <c r="C26" s="59"/>
-      <c r="D26" s="59"/>
+      <c r="C26" s="60"/>
+      <c r="D26" s="60"/>
     </row>
     <row r="27" spans="2:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B27" s="59"/>
-      <c r="C27" s="59"/>
-      <c r="D27" s="59"/>
+      <c r="B27" s="60"/>
+      <c r="C27" s="60"/>
+      <c r="D27" s="60"/>
     </row>
     <row r="28" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B28" s="60"/>
-      <c r="C28" s="60"/>
-      <c r="D28" s="60"/>
+      <c r="B28" s="61"/>
+      <c r="C28" s="61"/>
+      <c r="D28" s="61"/>
     </row>
     <row r="29" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B29" s="58"/>
+      <c r="B29" s="59"/>
       <c r="C29" s="10"/>
     </row>
     <row r="30" spans="2:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -7256,12 +7671,12 @@
       </c>
     </row>
     <row r="41" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B41" s="58" t="s">
+      <c r="B41" s="59" t="s">
         <v>206</v>
       </c>
     </row>
     <row r="42" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B42" s="58"/>
+      <c r="B42" s="59"/>
     </row>
     <row r="44" spans="2:4" ht="18.75" x14ac:dyDescent="0.25">
       <c r="B44" s="50" t="s">
@@ -7329,13 +7744,13 @@
       <c r="C53" s="10"/>
     </row>
     <row r="54" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B54" s="58" t="s">
+      <c r="B54" s="59" t="s">
         <v>208</v>
       </c>
       <c r="C54" s="10"/>
     </row>
     <row r="55" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B55" s="58"/>
+      <c r="B55" s="59"/>
       <c r="C55" s="10"/>
     </row>
     <row r="57" spans="2:4" ht="18.75" x14ac:dyDescent="0.25">
@@ -8039,13 +8454,13 @@
       <c r="C34" s="10"/>
     </row>
     <row r="35" spans="2:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B35" s="58" t="s">
+      <c r="B35" s="59" t="s">
         <v>201</v>
       </c>
       <c r="C35" s="10"/>
     </row>
     <row r="36" spans="2:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B36" s="58"/>
+      <c r="B36" s="59"/>
       <c r="C36" s="10"/>
     </row>
     <row r="37" spans="2:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -8587,12 +9002,12 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting pivot="1" sqref="C80:C81">
-    <cfRule type="cellIs" dxfId="12" priority="3" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="26" priority="3" operator="greaterThan">
       <formula>5</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting pivot="1" sqref="C80:C81">
-    <cfRule type="cellIs" dxfId="11" priority="2" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="25" priority="2" operator="greaterThan">
       <formula>5</formula>
     </cfRule>
   </conditionalFormatting>
@@ -9025,12 +9440,12 @@
       </c>
     </row>
     <row r="20" spans="2:8" s="19" customFormat="1" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B20" s="56" t="s">
+      <c r="B20" s="57" t="s">
         <v>193</v>
       </c>
-      <c r="C20" s="56"/>
-      <c r="D20" s="56"/>
-      <c r="E20" s="56"/>
+      <c r="C20" s="57"/>
+      <c r="D20" s="57"/>
+      <c r="E20" s="57"/>
     </row>
     <row r="22" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B22" s="48" t="s">
@@ -9127,12 +9542,12 @@
       </c>
     </row>
     <row r="33" spans="2:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B33" s="56" t="s">
+      <c r="B33" s="57" t="s">
         <v>194</v>
       </c>
-      <c r="C33" s="56"/>
-      <c r="D33" s="56"/>
-      <c r="E33" s="56"/>
+      <c r="C33" s="57"/>
+      <c r="D33" s="57"/>
+      <c r="E33" s="57"/>
     </row>
     <row r="35" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B35" s="48" t="s">
@@ -9229,12 +9644,12 @@
       </c>
     </row>
     <row r="46" spans="2:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B46" s="56" t="s">
+      <c r="B46" s="57" t="s">
         <v>196</v>
       </c>
-      <c r="C46" s="56"/>
-      <c r="D46" s="56"/>
-      <c r="E46" s="56"/>
+      <c r="C46" s="57"/>
+      <c r="D46" s="57"/>
+      <c r="E46" s="57"/>
     </row>
     <row r="47" spans="2:8" ht="18.75" x14ac:dyDescent="0.25">
       <c r="B47" s="42"/>
@@ -9372,33 +9787,33 @@
       </c>
     </row>
     <row r="57" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B57" s="57" t="s">
+      <c r="B57" s="58" t="s">
         <v>200</v>
       </c>
-      <c r="C57" s="57"/>
-      <c r="D57" s="57"/>
-      <c r="E57" s="57"/>
-      <c r="F57" s="57"/>
-      <c r="G57" s="57"/>
-      <c r="H57" s="57"/>
+      <c r="C57" s="58"/>
+      <c r="D57" s="58"/>
+      <c r="E57" s="58"/>
+      <c r="F57" s="58"/>
+      <c r="G57" s="58"/>
+      <c r="H57" s="58"/>
     </row>
     <row r="58" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B58" s="57"/>
-      <c r="C58" s="57"/>
-      <c r="D58" s="57"/>
-      <c r="E58" s="57"/>
-      <c r="F58" s="57"/>
-      <c r="G58" s="57"/>
-      <c r="H58" s="57"/>
+      <c r="B58" s="58"/>
+      <c r="C58" s="58"/>
+      <c r="D58" s="58"/>
+      <c r="E58" s="58"/>
+      <c r="F58" s="58"/>
+      <c r="G58" s="58"/>
+      <c r="H58" s="58"/>
     </row>
     <row r="59" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B59" s="57"/>
-      <c r="C59" s="57"/>
-      <c r="D59" s="57"/>
-      <c r="E59" s="57"/>
-      <c r="F59" s="57"/>
-      <c r="G59" s="57"/>
-      <c r="H59" s="57"/>
+      <c r="B59" s="58"/>
+      <c r="C59" s="58"/>
+      <c r="D59" s="58"/>
+      <c r="E59" s="58"/>
+      <c r="F59" s="58"/>
+      <c r="G59" s="58"/>
+      <c r="H59" s="58"/>
     </row>
   </sheetData>
   <mergeCells count="9">
@@ -9413,7 +9828,7 @@
     <mergeCell ref="B33:E33"/>
   </mergeCells>
   <conditionalFormatting pivot="1" sqref="D24:D28">
-    <cfRule type="cellIs" dxfId="10" priority="11" operator="lessThan">
+    <cfRule type="cellIs" dxfId="24" priority="11" operator="lessThan">
       <formula>10000</formula>
     </cfRule>
   </conditionalFormatting>
@@ -9430,7 +9845,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B24:B28">
-    <cfRule type="cellIs" dxfId="7" priority="5" operator="lessThan">
+    <cfRule type="cellIs" dxfId="21" priority="5" operator="lessThan">
       <formula>10000</formula>
     </cfRule>
   </conditionalFormatting>
@@ -9447,12 +9862,12 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting pivot="1" sqref="D37:D41">
-    <cfRule type="cellIs" dxfId="6" priority="3" operator="lessThan">
+    <cfRule type="cellIs" dxfId="20" priority="3" operator="lessThan">
       <formula>$Q$4</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting pivot="1" sqref="D37:D42">
-    <cfRule type="cellIs" dxfId="5" priority="2" operator="lessThan">
+    <cfRule type="cellIs" dxfId="19" priority="2" operator="lessThan">
       <formula>30000</formula>
     </cfRule>
   </conditionalFormatting>
@@ -9477,13 +9892,13 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{84601EC8-C861-4E54-B5F8-83B9BDC7AB04}">
-  <dimension ref="B2:AA29"/>
+  <dimension ref="B1:AA72"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="3.7109375" customWidth="1"/>
     <col min="2" max="2" width="15.5703125" customWidth="1"/>
     <col min="3" max="3" width="14.140625" customWidth="1"/>
-    <col min="4" max="4" width="21.42578125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.85546875" customWidth="1"/>
     <col min="5" max="5" width="18.5703125" customWidth="1"/>
     <col min="6" max="6" width="14.42578125" customWidth="1"/>
     <col min="7" max="7" width="13.42578125" bestFit="1" customWidth="1"/>
@@ -9506,6 +9921,16 @@
     <col min="29" max="29" width="7.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
+    <row r="1" spans="2:27" x14ac:dyDescent="0.25">
+      <c r="B1" s="48" t="s">
+        <v>192</v>
+      </c>
+      <c r="C1" s="48"/>
+      <c r="D1" s="48"/>
+      <c r="E1" s="48"/>
+      <c r="F1" s="48"/>
+      <c r="G1" s="48"/>
+    </row>
     <row r="2" spans="2:27" x14ac:dyDescent="0.25">
       <c r="B2" t="s">
         <v>0</v>
@@ -10147,7 +10572,7 @@
         <v>18000</v>
       </c>
     </row>
-    <row r="17" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B17" s="10" t="s">
         <v>133</v>
       </c>
@@ -10167,189 +10592,472 @@
         <v>3000</v>
       </c>
     </row>
-    <row r="20" spans="2:10" s="19" customFormat="1" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B20" s="20" t="s">
+    <row r="18" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="F18" s="10"/>
+    </row>
+    <row r="19" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="F19" s="10"/>
+    </row>
+    <row r="20" spans="2:7" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B20" s="57" t="s">
+        <v>210</v>
+      </c>
+      <c r="C20" s="57"/>
+      <c r="D20" s="57"/>
+      <c r="E20" s="57"/>
+      <c r="F20" s="10"/>
+    </row>
+    <row r="21" spans="2:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F21" s="10"/>
+    </row>
+    <row r="22" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B22" s="48" t="s">
+        <v>211</v>
+      </c>
+      <c r="C22" s="48"/>
+      <c r="D22" s="65"/>
+      <c r="F22" s="10"/>
+    </row>
+    <row r="23" spans="2:7" ht="30" x14ac:dyDescent="0.25">
+      <c r="B23" s="20" t="s">
         <v>38</v>
       </c>
-      <c r="C20" s="19" t="s">
+      <c r="C23" s="19" t="s">
         <v>39</v>
       </c>
-      <c r="E20" s="20" t="s">
+      <c r="D23" s="10"/>
+      <c r="G23" s="19"/>
+    </row>
+    <row r="24" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B24" s="9" t="s">
+        <v>112</v>
+      </c>
+      <c r="C24" s="10">
+        <v>5</v>
+      </c>
+      <c r="D24" s="10"/>
+    </row>
+    <row r="25" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B25" s="9" t="s">
+        <v>114</v>
+      </c>
+      <c r="C25" s="10">
+        <v>3</v>
+      </c>
+      <c r="D25" s="10"/>
+    </row>
+    <row r="26" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B26" s="9" t="s">
+        <v>116</v>
+      </c>
+      <c r="C26" s="10">
+        <v>2</v>
+      </c>
+      <c r="D26" s="10"/>
+    </row>
+    <row r="27" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B27" s="9" t="s">
+        <v>119</v>
+      </c>
+      <c r="C27" s="63">
+        <v>1</v>
+      </c>
+      <c r="D27" s="10"/>
+    </row>
+    <row r="28" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B28" s="9" t="s">
+        <v>121</v>
+      </c>
+      <c r="C28" s="63">
+        <v>1</v>
+      </c>
+      <c r="D28" s="10"/>
+    </row>
+    <row r="29" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B29" s="9" t="s">
+        <v>125</v>
+      </c>
+      <c r="C29" s="63">
+        <v>1</v>
+      </c>
+      <c r="D29" s="10"/>
+    </row>
+    <row r="30" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B30" s="9" t="s">
+        <v>129</v>
+      </c>
+      <c r="C30" s="63">
+        <v>1</v>
+      </c>
+      <c r="D30" s="10"/>
+      <c r="E30" s="10"/>
+      <c r="F30" s="10"/>
+    </row>
+    <row r="31" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B31" s="9" t="s">
+        <v>132</v>
+      </c>
+      <c r="C31" s="63">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="32" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B32" s="9" t="s">
+        <v>40</v>
+      </c>
+      <c r="C32" s="10">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="33" spans="2:10" s="19" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="J33"/>
+    </row>
+    <row r="34" spans="2:10" s="19" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B34" s="62" t="s">
+        <v>212</v>
+      </c>
+      <c r="C34" s="62"/>
+      <c r="D34" s="62"/>
+      <c r="E34" s="62"/>
+      <c r="J34"/>
+    </row>
+    <row r="35" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B35" s="62"/>
+      <c r="C35" s="62"/>
+      <c r="D35" s="62"/>
+      <c r="E35" s="62"/>
+    </row>
+    <row r="36" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B36" s="64"/>
+      <c r="C36" s="64"/>
+      <c r="D36" s="64"/>
+      <c r="E36" s="64"/>
+    </row>
+    <row r="37" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B37" s="64"/>
+      <c r="C37" s="64"/>
+      <c r="D37" s="64"/>
+      <c r="E37" s="64"/>
+    </row>
+    <row r="38" spans="2:10" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B38" s="57" t="s">
+        <v>213</v>
+      </c>
+      <c r="C38" s="57"/>
+      <c r="D38" s="57"/>
+      <c r="E38" s="57"/>
+    </row>
+    <row r="40" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B40" s="48" t="s">
+        <v>214</v>
+      </c>
+      <c r="C40" s="48"/>
+      <c r="D40" s="65"/>
+    </row>
+    <row r="41" spans="2:10" ht="45" x14ac:dyDescent="0.25">
+      <c r="B41" s="20" t="s">
         <v>38</v>
       </c>
-      <c r="F20" s="19" t="s">
+      <c r="C41" s="19" t="s">
         <v>39</v>
       </c>
-      <c r="H20" s="20" t="s">
+      <c r="D41" s="66" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="42" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B42" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="C42" s="10">
+        <v>6</v>
+      </c>
+      <c r="D42" s="67">
+        <f>C42/GETPIVOTDATA("transaction_id",$B$41)</f>
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="43" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B43" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="C43" s="10">
+        <v>3</v>
+      </c>
+      <c r="D43" s="67">
+        <f t="shared" ref="D43:D47" si="1">C43/GETPIVOTDATA("transaction_id",$B$41)</f>
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="44" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B44" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="C44" s="10">
+        <v>2</v>
+      </c>
+      <c r="D44" s="67">
+        <f t="shared" si="1"/>
+        <v>0.13333333333333333</v>
+      </c>
+    </row>
+    <row r="45" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B45" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="C45" s="10">
+        <v>2</v>
+      </c>
+      <c r="D45" s="67">
+        <f t="shared" si="1"/>
+        <v>0.13333333333333333</v>
+      </c>
+    </row>
+    <row r="46" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B46" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="C46" s="10">
+        <v>2</v>
+      </c>
+      <c r="D46" s="67">
+        <f t="shared" si="1"/>
+        <v>0.13333333333333333</v>
+      </c>
+    </row>
+    <row r="47" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B47" s="9" t="s">
+        <v>40</v>
+      </c>
+      <c r="C47" s="10">
+        <v>15</v>
+      </c>
+      <c r="D47" s="68">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="49" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B49" s="62" t="s">
+        <v>220</v>
+      </c>
+      <c r="C49" s="62"/>
+      <c r="D49" s="62"/>
+      <c r="E49" s="62"/>
+    </row>
+    <row r="50" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B50" s="62"/>
+      <c r="C50" s="62"/>
+      <c r="D50" s="62"/>
+      <c r="E50" s="62"/>
+    </row>
+    <row r="52" spans="2:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B52" s="56" t="s">
+        <v>216</v>
+      </c>
+      <c r="C52" s="56"/>
+      <c r="D52" s="56"/>
+      <c r="E52" s="56"/>
+    </row>
+    <row r="53" spans="2:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B53" s="56"/>
+      <c r="C53" s="56"/>
+      <c r="D53" s="56"/>
+      <c r="E53" s="56"/>
+    </row>
+    <row r="55" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B55" s="48" t="s">
+        <v>217</v>
+      </c>
+      <c r="C55" s="48"/>
+      <c r="D55" s="65"/>
+    </row>
+    <row r="56" spans="2:5" ht="30" x14ac:dyDescent="0.25">
+      <c r="B56" s="20" t="s">
         <v>38</v>
       </c>
-      <c r="I20" s="19" t="s">
+      <c r="C56" s="19" t="s">
         <v>39</v>
       </c>
-      <c r="J20"/>
-    </row>
-    <row r="21" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B21" s="9" t="s">
-        <v>112</v>
-      </c>
-      <c r="C21" s="10">
-        <v>5</v>
-      </c>
-      <c r="E21" s="9" t="s">
-        <v>9</v>
-      </c>
-      <c r="F21" s="10">
+    </row>
+    <row r="57" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B57" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="C57" s="10">
         <v>6</v>
       </c>
-      <c r="H21" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="I21" s="23">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="22" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B22" s="9" t="s">
-        <v>114</v>
-      </c>
-      <c r="C22" s="10">
+    </row>
+    <row r="58" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B58" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="C58" s="10">
         <v>3</v>
       </c>
-      <c r="E22" s="9" t="s">
-        <v>14</v>
-      </c>
-      <c r="F22" s="10">
-        <v>3</v>
-      </c>
-      <c r="H22" s="9" t="s">
-        <v>10</v>
-      </c>
-      <c r="I22" s="10">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="23" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B23" s="9" t="s">
-        <v>116</v>
-      </c>
-      <c r="C23" s="10">
+    </row>
+    <row r="59" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B59" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="C59" s="10">
         <v>2</v>
       </c>
-      <c r="E23" s="9" t="s">
-        <v>31</v>
-      </c>
-      <c r="F23" s="10">
-        <v>2</v>
-      </c>
-      <c r="H23" s="9" t="s">
-        <v>22</v>
-      </c>
-      <c r="I23" s="10">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="24" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B24" s="9" t="s">
-        <v>119</v>
-      </c>
-      <c r="C24" s="10">
-        <v>1</v>
-      </c>
-      <c r="E24" s="9" t="s">
-        <v>19</v>
-      </c>
-      <c r="F24" s="10">
-        <v>2</v>
-      </c>
-      <c r="H24" s="9" t="s">
+    </row>
+    <row r="60" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B60" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="I24" s="10">
+      <c r="C60" s="10">
         <v>4</v>
       </c>
     </row>
-    <row r="25" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B25" s="9" t="s">
-        <v>121</v>
-      </c>
-      <c r="C25" s="10">
-        <v>1</v>
-      </c>
-      <c r="E25" s="9" t="s">
-        <v>25</v>
-      </c>
-      <c r="F25" s="10">
-        <v>2</v>
-      </c>
-      <c r="H25" s="9" t="s">
+    <row r="61" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B61" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="I25" s="10">
+      <c r="C61" s="10">
         <v>15</v>
       </c>
     </row>
-    <row r="26" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B26" s="9" t="s">
-        <v>125</v>
-      </c>
-      <c r="C26" s="10">
-        <v>1</v>
-      </c>
-      <c r="E26" s="9" t="s">
-        <v>40</v>
-      </c>
-      <c r="F26" s="10">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="27" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B27" s="9" t="s">
-        <v>129</v>
-      </c>
-      <c r="C27" s="10">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="28" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B28" s="9" t="s">
-        <v>132</v>
-      </c>
-      <c r="C28" s="10">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="29" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B29" s="9" t="s">
-        <v>40</v>
-      </c>
-      <c r="C29" s="10">
-        <v>15</v>
-      </c>
+    <row r="63" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B63" s="62" t="s">
+        <v>218</v>
+      </c>
+      <c r="C63" s="62"/>
+      <c r="D63" s="62"/>
+      <c r="E63" s="62"/>
+    </row>
+    <row r="64" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B64" s="62"/>
+      <c r="C64" s="62"/>
+      <c r="D64" s="62"/>
+      <c r="E64" s="62"/>
+    </row>
+    <row r="65" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B65" s="64"/>
+      <c r="C65" s="64"/>
+      <c r="D65" s="64"/>
+      <c r="E65" s="64"/>
+    </row>
+    <row r="66" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B66" s="64"/>
+      <c r="C66" s="64"/>
+      <c r="D66" s="64"/>
+      <c r="E66" s="64"/>
+    </row>
+    <row r="67" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B67" s="62" t="s">
+        <v>219</v>
+      </c>
+      <c r="C67" s="62"/>
+      <c r="D67" s="62"/>
+      <c r="E67" s="62"/>
+      <c r="F67" s="62"/>
+    </row>
+    <row r="68" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B68" s="62"/>
+      <c r="C68" s="62"/>
+      <c r="D68" s="62"/>
+      <c r="E68" s="62"/>
+      <c r="F68" s="62"/>
+    </row>
+    <row r="69" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B69" s="62"/>
+      <c r="C69" s="62"/>
+      <c r="D69" s="62"/>
+      <c r="E69" s="62"/>
+      <c r="F69" s="62"/>
+    </row>
+    <row r="70" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B70" s="62"/>
+      <c r="C70" s="62"/>
+      <c r="D70" s="62"/>
+      <c r="E70" s="62"/>
+      <c r="F70" s="62"/>
+    </row>
+    <row r="71" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B71" s="62"/>
+      <c r="C71" s="62"/>
+      <c r="D71" s="62"/>
+      <c r="E71" s="62"/>
+      <c r="F71" s="62"/>
+    </row>
+    <row r="72" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B72" s="62"/>
+      <c r="C72" s="62"/>
+      <c r="D72" s="62"/>
+      <c r="E72" s="62"/>
+      <c r="F72" s="62"/>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="B20:C29">
-    <cfRule type="cellIs" dxfId="4" priority="5" operator="lessThan">
+  <mergeCells count="11">
+    <mergeCell ref="B49:E50"/>
+    <mergeCell ref="B63:E64"/>
+    <mergeCell ref="B67:F72"/>
+    <mergeCell ref="B34:E35"/>
+    <mergeCell ref="B40:C40"/>
+    <mergeCell ref="B22:C22"/>
+    <mergeCell ref="B55:C55"/>
+    <mergeCell ref="B52:E53"/>
+    <mergeCell ref="B1:G1"/>
+    <mergeCell ref="B20:E20"/>
+    <mergeCell ref="B38:E38"/>
+  </mergeCells>
+  <conditionalFormatting sqref="B23:C32">
+    <cfRule type="cellIs" dxfId="18" priority="21" operator="lessThan">
       <formula>2</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting pivot="1" sqref="F21:F25">
-    <cfRule type="cellIs" dxfId="3" priority="4" operator="greaterThan">
+  <conditionalFormatting pivot="1" sqref="C42:C46">
+    <cfRule type="cellIs" dxfId="17" priority="20" operator="greaterThan">
       <formula>5</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting pivot="1" sqref="F21:F25">
-    <cfRule type="cellIs" dxfId="2" priority="3" operator="greaterThan">
+  <conditionalFormatting pivot="1" sqref="C42:C46">
+    <cfRule type="cellIs" dxfId="16" priority="19" operator="greaterThan">
       <formula>5</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AA4:AA11">
-    <cfRule type="top10" dxfId="1" priority="1" rank="2"/>
-    <cfRule type="top10" dxfId="0" priority="2" rank="2"/>
+    <cfRule type="top10" dxfId="15" priority="17" rank="2"/>
+    <cfRule type="top10" dxfId="14" priority="18" rank="2"/>
+  </conditionalFormatting>
+  <conditionalFormatting pivot="1" sqref="C42">
+    <cfRule type="cellIs" dxfId="13" priority="14" operator="greaterThan">
+      <formula>4</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting pivot="1" sqref="C42">
+    <cfRule type="cellIs" dxfId="12" priority="13" operator="greaterThan">
+      <formula>3</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting pivot="1" sqref="C57">
+    <cfRule type="cellIs" dxfId="11" priority="12" operator="greaterThan">
+      <formula>5</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting pivot="1" sqref="C57">
+    <cfRule type="cellIs" dxfId="10" priority="11" operator="greaterThan">
+      <formula>5</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting pivot="1" sqref="C57">
+    <cfRule type="cellIs" dxfId="9" priority="10" operator="greaterThan">
+      <formula>4</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting pivot="1" sqref="C57">
+    <cfRule type="cellIs" dxfId="8" priority="9" operator="greaterThan">
+      <formula>3</formula>
+    </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId5"/>
   <tableParts count="2">
-    <tablePart r:id="rId5"/>
     <tablePart r:id="rId6"/>
+    <tablePart r:id="rId7"/>
   </tableParts>
 </worksheet>
 </file>
